--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52F02EB-234B-4E51-BD35-629DC674728B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9FCFEA-15D8-45F8-97D7-64B80D6D27CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -19,21 +19,35 @@
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId7"/>
-    <sheet name="投资主题" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$M$73</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$9</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$91</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$101</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$E$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$E$16</definedName>
+    <definedName name="FV_adjustments" localSheetId="7">[1]DCF!$F$7</definedName>
     <definedName name="FV_adjustments">DCF!$F$7</definedName>
+    <definedName name="Holding_Period" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="Holding_Period">Thesis!$E$21</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$7</definedName>
     <definedName name="Market_currency">Thesis!$C$7</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$8</definedName>
     <definedName name="Market_Price">Thesis!$C$8</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$E$17</definedName>
     <definedName name="Reporting_currency">Thesis!$E$17</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$17</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="557">
   <si>
     <t>Sales</t>
   </si>
@@ -1257,10 +1271,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1418,10 +1428,6 @@
   </si>
   <si>
     <t>1x for stable businesses, 2x for for volatile ones, 6x for cash hoarders</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3264,6 +3270,15 @@
   <si>
     <t>更新日期:</t>
   </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
+  </si>
 </sst>
 </file>
 
@@ -3290,7 +3305,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3811,6 +3826,12 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -4002,11 +4023,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="473">
+  <cellXfs count="476">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4881,60 +4903,6 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5020,9 +4988,69 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{AFD61BCC-344D-4D7C-9A1E-59EC5319B854}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5100,6 +5128,93 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+      <sheetName val="投资主题"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>6.46</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>580004033</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="C101">
+            <v>7.4999999999999997E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="91">
+          <cell r="C91">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="7">
+          <cell r="F7">
+            <v>-1686446.6667440513</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5327,39 +5442,39 @@
       <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="E3" s="456" t="s">
-        <v>551</v>
-      </c>
-      <c r="F3" s="457">
+      <c r="E3" s="438" t="s">
+        <v>549</v>
+      </c>
+      <c r="F3" s="439">
         <v>45930</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.4">
-      <c r="B4" s="449" t="s">
-        <v>546</v>
-      </c>
-      <c r="C4" s="448" t="s">
-        <v>508</v>
-      </c>
-      <c r="E4" s="458" t="s">
-        <v>550</v>
-      </c>
-      <c r="F4" s="459" t="s">
-        <v>327</v>
+      <c r="B4" s="431" t="s">
+        <v>544</v>
+      </c>
+      <c r="C4" s="430" t="s">
+        <v>506</v>
+      </c>
+      <c r="E4" s="440" t="s">
+        <v>548</v>
+      </c>
+      <c r="F4" s="441" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>509</v>
-      </c>
-      <c r="E5" s="461" t="s">
-        <v>552</v>
-      </c>
-      <c r="F5" s="460" t="s">
-        <v>510</v>
+        <v>507</v>
+      </c>
+      <c r="E5" s="443" t="s">
+        <v>550</v>
+      </c>
+      <c r="F5" s="442" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5367,24 +5482,24 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C8" s="47">
         <v>6.46</v>
@@ -5393,22 +5508,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C9" s="48">
         <v>580004033</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.12879429732248779</v>
+        <v>0.12123938704206341</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
@@ -5420,13 +5535,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.6" customHeight="1">
-      <c r="B12" s="424" t="s">
-        <v>360</v>
-      </c>
-      <c r="C12" s="424"/>
-      <c r="D12" s="424"/>
-      <c r="E12" s="424"/>
-      <c r="F12" s="424"/>
+      <c r="B12" s="460" t="s">
+        <v>358</v>
+      </c>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5437,13 +5552,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C15" s="445" t="s">
-        <v>260</v>
+        <v>320</v>
+      </c>
+      <c r="C15" s="427" t="s">
+        <v>554</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E15" s="260" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5452,30 +5567,30 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16" s="445" t="s">
-        <v>260</v>
+        <v>321</v>
+      </c>
+      <c r="C16" s="427" t="s">
+        <v>554</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="E16" s="444">
+        <v>357</v>
+      </c>
+      <c r="E16" s="426">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C17" s="443">
+        <v>543</v>
+      </c>
+      <c r="C17" s="425">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E17" s="228" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5485,27 +5600,27 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>7.3796628952847572</v>
+        <v>7.7546312099082444</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E18" s="446">
+        <v>350</v>
+      </c>
+      <c r="E18" s="428">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E19" s="447">
+        <v>351</v>
+      </c>
+      <c r="E19" s="429">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
         <v>45991</v>
       </c>
@@ -5516,29 +5631,29 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C21" s="261" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="E21" s="470">
-        <v>2</v>
+        <v>317</v>
+      </c>
+      <c r="E21" s="452">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>4.5649727820492494</v>
+        <v>3.830160528337446</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5546,47 +5661,47 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>5.298984252982244</v>
+        <v>4.7511711794730207</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>416</v>
-      </c>
-      <c r="E23" s="471">
+        <v>414</v>
+      </c>
+      <c r="E23" s="453">
         <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>6.5887686093669577</v>
+        <v>6.5232537640741466</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="471">
+        <v>415</v>
+      </c>
+      <c r="E24" s="453">
         <v>0.1174</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>7.1040890386455446</v>
+        <v>7.3308758318019924</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>418</v>
-      </c>
-      <c r="E25" s="472">
-        <v>7.4999999999999997E-2</v>
+        <v>416</v>
+      </c>
+      <c r="E25" s="454">
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -5595,7 +5710,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="203" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5604,22 +5719,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="424" t="s">
-        <v>361</v>
-      </c>
-      <c r="C29" s="424"/>
-      <c r="D29" s="424"/>
-      <c r="E29" s="424"/>
-      <c r="F29" s="424"/>
+      <c r="B29" s="460" t="s">
+        <v>359</v>
+      </c>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="426" t="s">
-        <v>268</v>
-      </c>
-      <c r="C30" s="426"/>
-      <c r="D30" s="426"/>
-      <c r="E30" s="426"/>
-      <c r="F30" s="426"/>
+      <c r="B30" s="464" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5631,13 +5746,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B33" s="425" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="425"/>
-      <c r="D33" s="425"/>
-      <c r="E33" s="425"/>
-      <c r="F33" s="425"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5657,13 +5772,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B36" s="425" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="425"/>
-      <c r="D36" s="425"/>
-      <c r="E36" s="425"/>
-      <c r="F36" s="425"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5692,13 +5807,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="425" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="425"/>
-      <c r="D40" s="425"/>
-      <c r="E40" s="425"/>
-      <c r="F40" s="425"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5714,17 +5829,17 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="425" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="425"/>
-      <c r="D43" s="425"/>
-      <c r="E43" s="425"/>
-      <c r="F43" s="425"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C44" s="294">
         <f>Normalized_FCF!C46</f>
@@ -5739,7 +5854,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C45" s="294">
         <f>Normalized_FCF!C45</f>
@@ -5784,13 +5899,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="425" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="425"/>
-      <c r="D51" s="425"/>
-      <c r="E51" s="425"/>
-      <c r="F51" s="425"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5806,13 +5921,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="425" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="428"/>
-      <c r="D54" s="428"/>
-      <c r="E54" s="428"/>
-      <c r="F54" s="428"/>
+      <c r="B54" s="461" t="s">
+        <v>266</v>
+      </c>
+      <c r="C54" s="462"/>
+      <c r="D54" s="462"/>
+      <c r="E54" s="462"/>
+      <c r="F54" s="462"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5828,22 +5943,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B57" s="424" t="s">
-        <v>272</v>
-      </c>
-      <c r="C57" s="424"/>
-      <c r="D57" s="424"/>
-      <c r="E57" s="424"/>
-      <c r="F57" s="424"/>
+      <c r="B57" s="460" t="s">
+        <v>271</v>
+      </c>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B58" s="424" t="s">
-        <v>285</v>
-      </c>
-      <c r="C58" s="424"/>
-      <c r="D58" s="424"/>
-      <c r="E58" s="424"/>
-      <c r="F58" s="424"/>
+      <c r="B58" s="460" t="s">
+        <v>283</v>
+      </c>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5873,7 +5988,7 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="207" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
@@ -5883,14 +5998,14 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="207" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
         <v>6.1919504643962855E-2</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F63" s="265">
         <f>Normalized_FCF!C90</f>
@@ -5899,18 +6014,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="193" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" s="271" t="s">
         <v>328</v>
       </c>
-      <c r="C65" s="271" t="s">
-        <v>330</v>
-      </c>
       <c r="D65" s="271" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
@@ -5965,7 +6080,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="203" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5978,18 +6093,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="424" t="s">
-        <v>489</v>
-      </c>
-      <c r="C73" s="424"/>
-      <c r="D73" s="424"/>
-      <c r="E73" s="424"/>
-      <c r="F73" s="424"/>
+      <c r="B73" s="460" t="s">
+        <v>487</v>
+      </c>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
       <c r="B74" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6003,13 +6118,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="424" t="s">
-        <v>273</v>
-      </c>
-      <c r="C77" s="424"/>
-      <c r="D77" s="424"/>
-      <c r="E77" s="424"/>
-      <c r="F77" s="424"/>
+      <c r="B77" s="460" t="s">
+        <v>272</v>
+      </c>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6042,7 +6157,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="192"/>
       <c r="B80" s="233" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C80" s="346">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6052,7 +6167,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="192"/>
       <c r="B81" s="233" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C81" s="347">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6065,7 +6180,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="192"/>
       <c r="B83" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6153,7 +6268,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="192"/>
       <c r="B92" s="44" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
@@ -6166,7 +6281,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="203" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6178,31 +6293,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.65" customHeight="1">
-      <c r="B96" s="424" t="s">
-        <v>496</v>
-      </c>
-      <c r="C96" s="424"/>
-      <c r="D96" s="424"/>
-      <c r="E96" s="424"/>
-      <c r="F96" s="424"/>
+      <c r="B96" s="460" t="s">
+        <v>494</v>
+      </c>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="426" t="s">
-        <v>495</v>
-      </c>
-      <c r="C97" s="426"/>
-      <c r="D97" s="426"/>
-      <c r="E97" s="426"/>
-      <c r="F97" s="426"/>
+      <c r="B97" s="464" t="s">
+        <v>493</v>
+      </c>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="426" t="s">
-        <v>494</v>
-      </c>
-      <c r="C98" s="426"/>
-      <c r="D98" s="426"/>
-      <c r="E98" s="426"/>
-      <c r="F98" s="426"/>
+      <c r="B98" s="464" t="s">
+        <v>492</v>
+      </c>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6211,25 +6326,25 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C101" s="215">
         <f>E25+C103</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="233" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C102" s="270">
         <f>E25</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="233" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C103" s="270">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6247,36 +6362,36 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="257" t="s">
+        <v>282</v>
+      </c>
+      <c r="C106" s="117"/>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C106" s="117"/>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="424" t="s">
-        <v>286</v>
-      </c>
-      <c r="C107" s="424"/>
-      <c r="D107" s="424"/>
-      <c r="E107" s="424"/>
-      <c r="F107" s="424"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="424" t="s">
-        <v>287</v>
-      </c>
-      <c r="C108" s="424"/>
-      <c r="D108" s="424"/>
-      <c r="E108" s="424"/>
-      <c r="F108" s="424"/>
+      <c r="B108" s="460" t="s">
+        <v>285</v>
+      </c>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
@@ -6289,11 +6404,11 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6301,17 +6416,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B114" s="424" t="s">
-        <v>502</v>
-      </c>
-      <c r="C114" s="424"/>
-      <c r="D114" s="424"/>
-      <c r="E114" s="424"/>
-      <c r="F114" s="424"/>
+      <c r="B114" s="460" t="s">
+        <v>500</v>
+      </c>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6346,7 +6461,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.84 HKD</v>
+        <v>8.23 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6368,7 +6483,7 @@
       </c>
       <c r="E119" s="211" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>7.61 HKD</v>
+        <v>7.99 HKD</v>
       </c>
       <c r="F119" s="202">
         <f>DCF!F75</f>
@@ -6390,7 +6505,7 @@
       </c>
       <c r="E120" s="211" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>7.38 HKD</v>
+        <v>7.75 HKD</v>
       </c>
       <c r="F120" s="202">
         <f>DCF!F76</f>
@@ -6412,7 +6527,7 @@
       </c>
       <c r="E121" s="211" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.15 HKD</v>
+        <v>7.52 HKD</v>
       </c>
       <c r="F121" s="202">
         <f>DCF!F77</f>
@@ -6434,7 +6549,7 @@
       </c>
       <c r="E122" s="211" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>6.93 HKD</v>
+        <v>7.29 HKD</v>
       </c>
       <c r="F122" s="202">
         <f>DCF!F78</f>
@@ -6442,13 +6557,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="425" t="s">
-        <v>362</v>
-      </c>
-      <c r="C124" s="425"/>
-      <c r="D124" s="425"/>
-      <c r="E124" s="425"/>
-      <c r="F124" s="425"/>
+      <c r="B124" s="461" t="s">
+        <v>360</v>
+      </c>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6456,7 +6571,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>7.3796628952847572</v>
+        <v>7.7546312099082444</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6464,17 +6579,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B127" s="429" t="s">
-        <v>363</v>
-      </c>
-      <c r="C127" s="429"/>
-      <c r="D127" s="429"/>
-      <c r="E127" s="429"/>
-      <c r="F127" s="429"/>
+      <c r="B127" s="463" t="s">
+        <v>361</v>
+      </c>
+      <c r="C127" s="463"/>
+      <c r="D127" s="463"/>
+      <c r="E127" s="463"/>
+      <c r="F127" s="463"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="203" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6483,22 +6598,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="427" t="s">
-        <v>288</v>
-      </c>
-      <c r="C131" s="427"/>
-      <c r="D131" s="427"/>
-      <c r="E131" s="427"/>
-      <c r="F131" s="427"/>
+      <c r="B131" s="465" t="s">
+        <v>286</v>
+      </c>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="424" t="s">
-        <v>364</v>
-      </c>
-      <c r="C132" s="424"/>
-      <c r="D132" s="424"/>
-      <c r="E132" s="424"/>
-      <c r="F132" s="424"/>
+      <c r="B132" s="460" t="s">
+        <v>362</v>
+      </c>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6511,7 +6626,7 @@
       </c>
       <c r="C135" s="205">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6529,45 +6644,45 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="193" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C138" s="218"/>
       <c r="D138" s="219"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="349" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="345" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C140" s="342">
         <f>Scenarios!C62</f>
-        <v>0.51577503429355298</v>
+        <v>0.67835187725448365</v>
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>4.049197747755696</v>
+        <v>3.1518086510829622</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>4.5649727820492494</v>
+        <v>3.830160528337446</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6576,19 +6691,19 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="345" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C141" s="342">
         <f>Scenarios!C63</f>
-        <v>0.57600000000000007</v>
+        <v>0.78080000000000005</v>
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>4.7229842529822443</v>
+        <v>3.970371179473021</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>5.298984252982244</v>
+        <v>4.7511711794730207</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6604,38 +6719,38 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="349" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="345" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C144" s="342">
         <f>Scenarios!C66</f>
-        <v>0.67833709316953872</v>
+        <v>0.96504125037545974</v>
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>5.910431516197419</v>
+        <v>5.5582125136986873</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>6.5887686093669577</v>
+        <v>6.5232537640741466</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6644,28 +6759,28 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="345" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C145" s="342">
         <f>Scenarios!C67</f>
-        <v>0.71822606814494294</v>
+        <v>1.0449500908692064</v>
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>6.385862970500602</v>
+        <v>6.285925740932786</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>7.1040890386455446</v>
+        <v>7.3308758318019924</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="203" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6674,114 +6789,102 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="431" t="s">
-        <v>365</v>
-      </c>
-      <c r="C149" s="424"/>
-      <c r="D149" s="424"/>
-      <c r="E149" s="424"/>
-      <c r="F149" s="424"/>
+      <c r="B149" s="459" t="s">
+        <v>363</v>
+      </c>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="428" t="s">
-        <v>296</v>
-      </c>
-      <c r="C152" s="428"/>
-      <c r="D152" s="428"/>
-      <c r="E152" s="428"/>
-      <c r="F152" s="428"/>
+      <c r="B152" s="462" t="s">
+        <v>294</v>
+      </c>
+      <c r="C152" s="462"/>
+      <c r="D152" s="462"/>
+      <c r="E152" s="462"/>
+      <c r="F152" s="462"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="197" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="197" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="197" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B158" s="425" t="s">
-        <v>449</v>
-      </c>
-      <c r="C158" s="425"/>
-      <c r="D158" s="425"/>
-      <c r="E158" s="425"/>
-      <c r="F158" s="425"/>
+      <c r="B158" s="461" t="s">
+        <v>447</v>
+      </c>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B161" s="430" t="s">
-        <v>297</v>
-      </c>
-      <c r="C161" s="430"/>
-      <c r="D161" s="430"/>
-      <c r="E161" s="430"/>
-      <c r="F161" s="430"/>
+      <c r="B161" s="458" t="s">
+        <v>295</v>
+      </c>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B162" s="430" t="s">
-        <v>298</v>
-      </c>
-      <c r="C162" s="430"/>
-      <c r="D162" s="430"/>
-      <c r="E162" s="430"/>
-      <c r="F162" s="430"/>
+      <c r="B162" s="458" t="s">
+        <v>296</v>
+      </c>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="197" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="197" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="197" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6798,6 +6901,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7320,7 +7435,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C22" s="295">
         <v>1510999</v>
@@ -7356,7 +7471,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C23" s="295">
         <v>-254050</v>
@@ -7392,7 +7507,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C24" s="295">
         <v>-1460236</v>
@@ -7459,7 +7574,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>188</v>
+        <v>555</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8764,7 +8879,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C64" s="278">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -9578,7 +9693,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9650,7 +9765,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C15" s="18">
         <v>307271</v>
@@ -10148,7 +10263,7 @@
         <v>113</v>
       </c>
       <c r="D45" s="165" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F45" s="230" t="s">
         <v>56</v>
@@ -10444,12 +10559,12 @@
         <v>-669251.86674405111</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="231" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C74" s="232">
         <f>-$C$66/C73</f>
@@ -10473,12 +10588,12 @@
         <v>669251.86674405111</v>
       </c>
       <c r="F75" s="227" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="233" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C76" s="234"/>
       <c r="D76" s="255">
@@ -10486,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="227" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10761,7 +10876,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10771,7 +10886,7 @@
       <c r="E3" s="242"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11115,7 +11230,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C10" s="274">
         <f>-C4*C76</f>
@@ -11170,7 +11285,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="26" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C11" s="308">
         <f>C61</f>
@@ -11514,7 +11629,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="241" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="280"/>
@@ -11539,7 +11654,7 @@
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="241" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="281"/>
@@ -12153,7 +12268,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="306" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C35" s="284">
         <f>G35</f>
@@ -12221,7 +12336,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="306" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12294,7 +12409,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="239" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -12433,7 +12548,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C46" s="274">
         <f>BS!D75*C51</f>
@@ -12488,7 +12603,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="252" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C47" s="286">
         <f>BS!$C$66*C51</f>
@@ -12957,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="240" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G60" s="274">
         <f>Data!C58</f>
@@ -13518,7 +13633,7 @@
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="240" t="s">
-        <v>282</v>
+        <v>556</v>
       </c>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
@@ -14197,7 +14312,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C91" s="300">
         <v>0</v>
@@ -14218,7 +14333,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
@@ -14912,7 +15027,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C112" s="152"/>
       <c r="E112" s="242"/>
@@ -14964,7 +15079,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C113" s="152"/>
       <c r="E113" s="242"/>
@@ -15473,7 +15588,7 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C125" s="152"/>
       <c r="G125" s="22">
@@ -16257,15 +16372,15 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C4" s="283">
         <f>Normalized_FCF!C19</f>
@@ -16276,7 +16391,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="136" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F4" s="283">
         <f>-BS!G31</f>
@@ -16287,7 +16402,7 @@
         <v>HKD</v>
       </c>
       <c r="H4" s="316" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I4" s="313">
         <f>Normalized_FCF!C4</f>
@@ -16301,10 +16416,10 @@
       </c>
       <c r="C5" s="189">
         <f>Equity_Cost</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="136" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F5" s="283">
         <f>BS!D66</f>
@@ -16315,7 +16430,7 @@
         <v>HKD</v>
       </c>
       <c r="H5" s="316" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I5" s="313">
         <f>Normalized_FCF!C7</f>
@@ -16329,14 +16444,14 @@
       </c>
       <c r="C6" s="291">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3532842.3480044305</v>
+        <v>3654664.4979356183</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E6" s="188" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F6" s="292">
         <f>BS!H42</f>
@@ -16347,7 +16462,7 @@
         <v>HKD</v>
       </c>
       <c r="H6" s="316" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I6" s="313">
         <f>I7+I8</f>
@@ -16358,14 +16473,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="326" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C7" s="283">
         <f>F7</f>
         <v>-1686446.6667440513</v>
       </c>
       <c r="E7" s="141" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F7" s="291">
         <f>SUM(F4:F6)</f>
@@ -16376,7 +16491,7 @@
         <v>HKD</v>
       </c>
       <c r="H7" s="320" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I7" s="321">
         <f>Normalized_FCF!C11</f>
@@ -16388,18 +16503,18 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="137" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C8" s="291">
         <f>C6+C7</f>
-        <v>1846395.6812603793</v>
+        <v>1968217.831191567</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E8" s="141" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16436,7 +16551,7 @@
       </c>
       <c r="F9" s="331"/>
       <c r="H9" s="316" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="I9" s="314">
         <f>Normalized_FCF!C41</f>
@@ -16448,11 +16563,11 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>1846395.6812603793</v>
+        <v>1968217.831191567</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16463,25 +16578,25 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="137" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E11" s="315" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I11" s="315"/>
       <c r="J11" s="315"/>
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16496,25 +16611,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C14" s="317" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F14" s="317" t="str">
         <f>IF(F17=C17,"I","II")</f>
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="140" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C15" s="149">
         <f>Scenarios!C45</f>
@@ -16529,7 +16644,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I15" s="127">
         <f>Terminal_Growth</f>
@@ -16539,14 +16654,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.35" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C16" s="148">
         <f>Scenarios!C46</f>
-        <v>2.0194760895005222E-2</v>
+        <v>2.0194760895005201E-2</v>
       </c>
       <c r="E16" s="316" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F16" s="319">
         <f>Scenarios!C41</f>
@@ -16555,33 +16670,33 @@
     </row>
     <row r="17" spans="1:21" ht="13.35" customHeight="1">
       <c r="B17" s="316" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C17" s="314">
         <f>Normalized_FCF!C32</f>
         <v>0.89099809462634716</v>
       </c>
       <c r="E17" s="316" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F17" s="319">
         <f>Scenarios!C40</f>
         <v>0.86799999999999999</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.35" customHeight="1">
       <c r="B18" s="316" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C18" s="314">
         <f>Normalized_FCF!C75-Normalized_FCF!C76</f>
         <v>0</v>
       </c>
       <c r="E18" s="316" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F18" s="145">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16592,7 +16707,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.3832422893238983</v>
+        <v>7.7583423472162005</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16604,41 +16719,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="122" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B20" s="122" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="122" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D20" s="122" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="122" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F20" s="122" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G20" s="122" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H20" s="122" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="122" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J20" s="122" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K20" s="122" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L20" s="123" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -16655,7 +16770,7 @@
       </c>
       <c r="D21" s="307">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>2.0194760895005222E-2</v>
+        <v>2.0194760895005201E-2</v>
       </c>
       <c r="E21" s="307">
         <f>$C$17</f>
@@ -16683,11 +16798,11 @@
       </c>
       <c r="K21" s="120">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.93023255813953487</v>
+        <v>0.93240093240093236</v>
       </c>
       <c r="L21" s="285">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>255160.63067566868</v>
+        <v>255755.41070055368</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16704,7 +16819,7 @@
       </c>
       <c r="D22" s="307">
         <f t="shared" si="1"/>
-        <v>2.0194760895005222E-2</v>
+        <v>2.0194760895005201E-2</v>
       </c>
       <c r="E22" s="307">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16732,11 +16847,11 @@
       </c>
       <c r="K22" s="120">
         <f t="shared" si="3"/>
-        <v>0.86533261222282321</v>
+        <v>0.86937149874212816</v>
       </c>
       <c r="L22" s="285">
         <f t="shared" si="4"/>
-        <v>243300.20842264095</v>
+        <v>244435.79711774178</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16781,11 +16896,11 @@
       </c>
       <c r="K23" s="120">
         <f t="shared" si="3"/>
-        <v>0.80496056950960304</v>
+        <v>0.81060279602995633</v>
       </c>
       <c r="L23" s="285">
         <f t="shared" si="4"/>
-        <v>366444.77867838094</v>
+        <v>369013.30753161875</v>
       </c>
       <c r="N23" s="283"/>
       <c r="O23" s="283"/>
@@ -16838,11 +16953,11 @@
       </c>
       <c r="K24" s="120">
         <f t="shared" si="3"/>
-        <v>0.7488005297763749</v>
+        <v>0.75580680282513402</v>
       </c>
       <c r="L24" s="285">
         <f t="shared" si="4"/>
-        <v>348680.33062957349</v>
+        <v>351942.81443664554</v>
       </c>
       <c r="N24" s="283"/>
       <c r="O24" s="283"/>
@@ -16895,11 +17010,11 @@
       </c>
       <c r="K25" s="120">
         <f t="shared" si="3"/>
-        <v>0.69655863235011617</v>
+        <v>0.70471496766912267</v>
       </c>
       <c r="L25" s="285">
         <f t="shared" si="4"/>
-        <v>331756.1178671025</v>
+        <v>335640.80756267981</v>
       </c>
       <c r="N25" s="283"/>
       <c r="O25" s="283"/>
@@ -18193,7 +18308,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="323" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B51" s="324">
         <f>C15+1</f>
@@ -18225,32 +18340,32 @@
       </c>
       <c r="I51" s="285">
         <f>(G51+C51*H51)*(1-$I$9)/Equity_Cost</f>
-        <v>6350384.1592926057</v>
-      </c>
-      <c r="J51" s="442">
+        <v>6569362.9234061446</v>
+      </c>
+      <c r="J51" s="424">
         <f>(G51+C51*H51)*(1-$I$9)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
         <v>0</v>
       </c>
       <c r="K51" s="120">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.69655863235011617</v>
+        <v>0.70471496766912267</v>
       </c>
       <c r="L51" s="285">
         <f>I51*K51</f>
-        <v>4423414.9048946993</v>
+        <v>4629528.3801748948</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="441" t="s">
-        <v>431</v>
-      </c>
-      <c r="K52" s="441"/>
+      <c r="J52" s="466" t="s">
+        <v>429</v>
+      </c>
+      <c r="K52" s="466"/>
       <c r="L52" s="325">
         <f>SUM(L21:L51)</f>
-        <v>5968756.9711680654</v>
+        <v>6186316.5175241344</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18274,7 +18389,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="126">
         <f>L52</f>
-        <v>5968756.9711680654</v>
+        <v>6186316.5175241344</v>
       </c>
       <c r="B55" s="124">
         <f>C78</f>
@@ -18309,19 +18424,19 @@
       </c>
       <c r="B56" s="119">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>5706592.9650296271</v>
+        <v>5914454.8667167993</v>
       </c>
       <c r="C56" s="119">
-        <v>5835771.3249580022</v>
+        <v>6048411.0895425407</v>
       </c>
       <c r="D56" s="119">
-        <v>5966204.1945264461</v>
+        <v>6183669.2910278663</v>
       </c>
       <c r="E56" s="119">
-        <v>6097891.5737349428</v>
+        <v>6320229.4711727584</v>
       </c>
       <c r="F56" s="119">
-        <v>6230833.4625835046</v>
+        <v>6458091.6299772309</v>
       </c>
       <c r="G56" s="303"/>
       <c r="H56" s="303"/>
@@ -18335,19 +18450,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="119">
-        <v>5657007.0154802334</v>
+        <v>5875266.559272632</v>
       </c>
       <c r="C57" s="119">
-        <v>5904107.384358367</v>
+        <v>6132386.5311118178</v>
       </c>
       <c r="D57" s="119">
-        <v>6158364.3578833435</v>
+        <v>6396963.8385578413</v>
       </c>
       <c r="E57" s="119">
-        <v>6419917.5770003796</v>
+        <v>6669144.0902566426</v>
       </c>
       <c r="F57" s="119">
-        <v>6688908.04256952</v>
+        <v>6949074.3134529162</v>
       </c>
       <c r="G57" s="303"/>
       <c r="H57" s="303"/>
@@ -18361,19 +18476,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="119">
-        <v>5361646.5326971374</v>
+        <v>5581226.0720410738</v>
       </c>
       <c r="C58" s="285">
-        <v>5751042.4838047065</v>
+        <v>5988283.4789860584</v>
       </c>
       <c r="D58" s="119">
-        <v>6162749.2708606413</v>
+        <v>6418720.7118496615</v>
       </c>
       <c r="E58" s="119">
-        <v>6597857.80189123</v>
+        <v>6873682.2939743027</v>
       </c>
       <c r="F58" s="119">
-        <v>7057501.8004495548</v>
+        <v>7354357.6989958473</v>
       </c>
       <c r="G58" s="303"/>
       <c r="H58" s="303"/>
@@ -18396,19 +18511,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="119">
-        <v>5247789.8461047579</v>
+        <v>5472052.1874691751</v>
       </c>
       <c r="C59" s="285">
-        <v>5720876.4436985534</v>
+        <v>5968253.1708341325</v>
       </c>
       <c r="D59" s="119">
-        <v>6229853.4324367419</v>
+        <v>6502218.7788243024</v>
       </c>
       <c r="E59" s="119">
-        <v>6777182.2380387522</v>
+        <v>7076542.9555222429</v>
       </c>
       <c r="F59" s="119">
-        <v>7365469.9562814292</v>
+        <v>7693973.2927271929</v>
       </c>
       <c r="G59" s="303"/>
       <c r="H59" s="303"/>
@@ -18431,19 +18546,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="119">
-        <v>4980164.8811299782</v>
+        <v>5200297.9058892755</v>
       </c>
       <c r="C60" s="285">
-        <v>5546530.9904946871</v>
+        <v>5796812.8110374203</v>
       </c>
       <c r="D60" s="119">
-        <v>6171179.7295454256</v>
+        <v>6454989.2328412253</v>
       </c>
       <c r="E60" s="119">
-        <v>6859829.0864592055</v>
+        <v>7180889.6848746464</v>
       </c>
       <c r="F60" s="119">
-        <v>7618708.2840237636</v>
+        <v>7981119.3812992098</v>
       </c>
       <c r="G60" s="303"/>
       <c r="H60" s="303"/>
@@ -18466,19 +18581,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="119">
-        <v>4858367.3489946714</v>
+        <v>5078642.5800520014</v>
       </c>
       <c r="C61" s="285">
-        <v>5479295.8718834938</v>
+        <v>5734590.765649654</v>
       </c>
       <c r="D61" s="119">
-        <v>6175069.7818890531</v>
+        <v>6470037.2051600013</v>
       </c>
       <c r="E61" s="119">
-        <v>6954510.4006559821</v>
+        <v>7294376.0633280417</v>
       </c>
       <c r="F61" s="119">
-        <v>7827407.8182470696</v>
+        <v>8218034.7033554614</v>
       </c>
       <c r="G61" s="303"/>
       <c r="H61" s="303"/>
@@ -18575,23 +18690,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18607,23 +18722,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>6.9312385251734545</v>
+        <v>7.2896186223118002</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>7.1539582867244489</v>
+        <v>7.5205760212334409</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>7.3788409808908941</v>
+        <v>7.7537781953385396</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>7.6058866076727627</v>
+        <v>7.9892251446270661</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>7.8350951670700768</v>
+        <v>8.2269168690990444</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18639,23 +18754,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>6.8457461031761166</v>
+        <v>7.2220530448080185</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>7.2717782595389568</v>
+        <v>7.6653602585686951</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>7.7101493036330186</v>
+        <v>8.1215248581104085</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>8.1610999940345739</v>
+        <v>8.5907978910770613</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>8.6248734339843267</v>
+        <v>9.0734328509554771</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18671,23 +18786,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>6.336507432445881</v>
+        <v>6.7150902126520604</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>7.0078750936213838</v>
+        <v>7.4169084480176481</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>7.717709445852404</v>
+        <v>8.1590364477786483</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>8.4678913519678556</v>
+        <v>8.9434475143214236</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>9.2603754941571292</v>
+        <v>9.7721924499993875</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18703,23 +18818,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>6.1402041653746675</v>
+        <v>6.526860686027546</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>6.9558650412944667</v>
+        <v>7.3823736740983676</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>7.8334054716696944</v>
+        <v>8.3029976311910421</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>8.7770692644385484</v>
+        <v>9.2932048435914769</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>9.7913513810642385</v>
+        <v>10.357732505599907</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18735,23 +18850,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>5.6787850204240335</v>
+        <v>6.0583220791935837</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>6.6552715224837682</v>
+        <v>7.0867889021960799</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>7.7322446183772904</v>
+        <v>8.2215679457131881</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>8.919562839859001</v>
+        <v>9.473111746674002</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>10.227966151538315</v>
+        <v>10.852808526169609</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18767,23 +18882,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>5.4687907355475573</v>
+        <v>5.8485729758847214</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>6.5393497102449327</v>
+        <v>6.979510259552975</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>7.7389515585402862</v>
+        <v>8.2475125451687159</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>9.0828053499275079</v>
+        <v>9.6687765558761036</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>10.58779043266242</v>
+        <v>11.261280379082139</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18806,7 +18921,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="155" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G73" s="332"/>
       <c r="H73" s="332"/>
@@ -18830,7 +18945,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.8350951670700768</v>
+        <v>8.2269168690990444</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18858,7 +18973,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>7.6058866076727627</v>
+        <v>7.9892251446270661</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -18886,7 +19001,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>7.3788409808908941</v>
+        <v>7.7537781953385396</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -18914,7 +19029,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.1539582867244489</v>
+        <v>7.5205760212334409</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -18942,7 +19057,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>6.9312385251734545</v>
+        <v>7.2896186223118002</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19098,17 +19213,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="116"/>
-      <c r="E4" s="432" t="str">
+      <c r="E4" s="467" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C18&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C4&amp;"("&amp;Thesis!C5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 5-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 大家乐集团(0341.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F4" s="432"/>
-      <c r="G4" s="432"/>
+      <c r="F4" s="467"/>
+      <c r="G4" s="467"/>
     </row>
     <row r="5" spans="2:7">
-      <c r="E5" s="432"/>
-      <c r="F5" s="432"/>
-      <c r="G5" s="432"/>
+      <c r="E5" s="467"/>
+      <c r="F5" s="467"/>
+      <c r="G5" s="467"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="146" t="s">
@@ -19118,9 +19233,9 @@
         <f>DCF!C3</f>
         <v>1000</v>
       </c>
-      <c r="E6" s="432"/>
-      <c r="F6" s="432"/>
-      <c r="G6" s="432"/>
+      <c r="E6" s="467"/>
+      <c r="F6" s="467"/>
+      <c r="G6" s="467"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19134,9 +19249,9 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="432"/>
-      <c r="F7" s="432"/>
-      <c r="G7" s="432"/>
+      <c r="E7" s="467"/>
+      <c r="F7" s="467"/>
+      <c r="G7" s="467"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19150,9 +19265,9 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="432"/>
-      <c r="F8" s="432"/>
-      <c r="G8" s="432"/>
+      <c r="E8" s="467"/>
+      <c r="F8" s="467"/>
+      <c r="G8" s="467"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19166,22 +19281,22 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="432"/>
-      <c r="F9" s="432"/>
-      <c r="G9" s="432"/>
+      <c r="E9" s="467"/>
+      <c r="F9" s="467"/>
+      <c r="G9" s="467"/>
     </row>
     <row r="10" spans="2:7">
-      <c r="E10" s="432"/>
-      <c r="F10" s="432"/>
-      <c r="G10" s="432"/>
+      <c r="E10" s="467"/>
+      <c r="F10" s="467"/>
+      <c r="G10" s="467"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="146" t="s">
-        <v>324</v>
-      </c>
-      <c r="E11" s="432"/>
-      <c r="F11" s="432"/>
-      <c r="G11" s="432"/>
+        <v>322</v>
+      </c>
+      <c r="E11" s="467"/>
+      <c r="F11" s="467"/>
+      <c r="G11" s="467"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19192,9 +19307,9 @@
         <v>3.3358728201447585E-2</v>
       </c>
       <c r="D12" s="145"/>
-      <c r="E12" s="432"/>
-      <c r="F12" s="432"/>
-      <c r="G12" s="432"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
+      <c r="G12" s="467"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="136" t="s">
@@ -19204,9 +19319,9 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.35590966478967423</v>
       </c>
-      <c r="E13" s="432"/>
-      <c r="F13" s="432"/>
-      <c r="G13" s="432"/>
+      <c r="E13" s="467"/>
+      <c r="F13" s="467"/>
+      <c r="G13" s="467"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19216,13 +19331,13 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.82412654882629588</v>
       </c>
-      <c r="E14" s="432"/>
-      <c r="F14" s="432"/>
-      <c r="G14" s="432"/>
+      <c r="E14" s="467"/>
+      <c r="F14" s="467"/>
+      <c r="G14" s="467"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19252,35 +19367,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E20" s="328"/>
       <c r="F20" s="328"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="154" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C21" s="154" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E21" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="155" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G21" s="155" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="310" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C22" s="333">
         <v>0.03</v>
@@ -19291,7 +19406,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>7.6058866076727627</v>
+        <v>7.9892251446270661</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19304,7 +19419,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="310" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C23" s="333">
         <v>0.02</v>
@@ -19315,7 +19430,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>7.3788409808908941</v>
+        <v>7.7537781953385396</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19327,7 +19442,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="310" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C24" s="333">
         <v>0.01</v>
@@ -19338,7 +19453,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>7.1539582867244489</v>
+        <v>7.5205760212334409</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19350,11 +19465,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="142" t="s">
-        <v>462</v>
-      </c>
-      <c r="C25" s="469">
+        <v>460</v>
+      </c>
+      <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>7.3792735674139784</v>
+        <v>7.7542271503752254</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19364,33 +19479,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="154" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C28" s="154" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D28" s="154" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E28" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="155" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G28" s="155" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="310" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C29" s="333">
         <v>0.04</v>
@@ -19401,7 +19516,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>7.8350951670700768</v>
+        <v>8.2269168690990444</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19413,7 +19528,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="323" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C30" s="333">
         <v>0</v>
@@ -19424,7 +19539,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>6.9312385251734545</v>
+        <v>7.2896186223118002</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19440,12 +19555,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="146" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C33" s="156">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19456,11 +19571,11 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F33" s="223">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -19476,55 +19591,55 @@
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12879429732248779</v>
+        <v>0.12123938704206341</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.62735571881907415</v>
+        <v>0.41006763945510488</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>7.3796628952847572</v>
+        <v>7.7546312099082444</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F36" s="340" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19543,18 +19658,18 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C40" s="139">
         <v>0.86799999999999999</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C41" s="139">
         <v>0.02</v>
@@ -19563,7 +19678,7 @@
     </row>
     <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -19589,7 +19704,7 @@
       </c>
       <c r="D45" s="138"/>
       <c r="E45" s="225" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="2:7">
@@ -19597,7 +19712,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="139">
-        <v>2.0194760895005222E-2</v>
+        <v>2.0194760895005201E-2</v>
       </c>
       <c r="D46" s="139"/>
       <c r="E46" s="225" t="s">
@@ -19610,7 +19725,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>7.3832422893238983</v>
+        <v>7.7583423472162005</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19622,7 +19737,7 @@
     </row>
     <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E49" s="226" t="s">
         <v>255</v>
@@ -19669,11 +19784,11 @@
         <v>Y</v>
       </c>
       <c r="E53" s="127" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.60327850944527739</v>
+        <v>0.57410751216480937</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19697,13 +19812,13 @@
       </c>
       <c r="C57" s="223">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" s="127"/>
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C58" s="156">
         <f>C33</f>
@@ -19716,13 +19831,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E60" s="422"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="154" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C61" s="154" t="s">
         <v>103</v>
@@ -19735,65 +19850,65 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="155" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G61" s="155" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="310" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C62" s="120">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.51577503429355298</v>
+        <v>0.67835187725448365</v>
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>4.049197747755696</v>
+        <v>3.1518086510829622</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>4.5649727820492494</v>
+        <v>3.830160528337446</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
         <v>0.35</v>
       </c>
-      <c r="G62" s="468">
+      <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.38141174646797982</v>
+        <v>0.50608089222301444</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="310" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C63" s="120">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.57600000000000007</v>
+        <v>0.78080000000000005</v>
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.7229842529822443</v>
+        <v>3.970371179473021</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>5.298984252982244</v>
+        <v>4.7511711794730207</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
         <v>0.25</v>
       </c>
-      <c r="G63" s="468">
+      <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.28194765422577295</v>
+        <v>0.3873117817127969</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="154" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C65" s="154" t="s">
         <v>103</v>
@@ -19806,60 +19921,60 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="155" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G65" s="155" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="310" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C66" s="120">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>0.67833709316953872</v>
+        <v>0.96504125037545974</v>
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.910431516197419</v>
+        <v>5.5582125136986873</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>6.5887686093669577</v>
+        <v>6.5232537640741466</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
         <v>0.1174</v>
       </c>
-      <c r="G66" s="468">
+      <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.10760498556382769</v>
+        <v>0.15919490631722644</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="310" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C67" s="120">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>0.71822606814494294</v>
+        <v>1.0449500908692064</v>
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.385862970500602</v>
+        <v>6.285925740932786</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>7.1040890386455446</v>
+        <v>7.3308758318019924</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G67" s="468">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>3.734233670961995E-2</v>
+        <v>5.4645458518363998E-2</v>
       </c>
     </row>
   </sheetData>
@@ -19873,29 +19988,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
-  <dimension ref="B2:E2"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -19912,7 +20004,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="354" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B2" s="354"/>
       <c r="C2" s="354"/>
@@ -19925,50 +20017,50 @@
       <c r="J2" s="355"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="E3" s="463" t="s">
-        <v>555</v>
-      </c>
-      <c r="F3" s="464">
+      <c r="E3" s="445" t="s">
+        <v>553</v>
+      </c>
+      <c r="F3" s="446">
         <f>Thesis!F3</f>
         <v>45930</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="450" t="s">
-        <v>547</v>
-      </c>
-      <c r="C4" s="451" t="str">
+      <c r="B4" s="432" t="s">
+        <v>545</v>
+      </c>
+      <c r="C4" s="433" t="str">
         <f>Thesis!C4</f>
         <v>大家乐集团</v>
       </c>
       <c r="D4" s="358"/>
-      <c r="E4" s="462" t="s">
-        <v>553</v>
-      </c>
-      <c r="F4" s="465" t="str">
+      <c r="E4" s="444" t="s">
+        <v>551</v>
+      </c>
+      <c r="F4" s="447" t="str">
         <f>Thesis!F4</f>
         <v>INT</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="352" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C5" s="364" t="str">
         <f>Thesis!C5</f>
         <v>0341.HK</v>
       </c>
-      <c r="E5" s="466" t="s">
-        <v>554</v>
-      </c>
-      <c r="F5" s="467" t="str">
+      <c r="E5" s="448" t="s">
+        <v>552</v>
+      </c>
+      <c r="F5" s="449" t="str">
         <f>Thesis!F5</f>
         <v>Y</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="359" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C6" s="361" t="str">
         <f>Thesis!C6</f>
@@ -19978,7 +20070,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="352" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C7" s="361" t="str">
         <f>Market_currency</f>
@@ -19989,23 +20081,23 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="360" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
         <v>6.46</v>
       </c>
       <c r="D8" s="352" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.12879429732248779</v>
+        <v>0.12123938704206341</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="360" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C9" s="362">
         <f>Common_Shares</f>
@@ -20014,7 +20106,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="360" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
@@ -20027,31 +20119,31 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.6" customHeight="1">
-      <c r="B12" s="434" t="s">
-        <v>511</v>
-      </c>
-      <c r="C12" s="434"/>
-      <c r="D12" s="434"/>
-      <c r="E12" s="434"/>
-      <c r="F12" s="434"/>
+      <c r="B12" s="472" t="s">
+        <v>509</v>
+      </c>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C14" s="357"/>
       <c r="D14" s="358"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="352" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C15" s="367" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="360" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E15" s="353" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20060,30 +20152,30 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="352" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C16" s="367" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="360" t="s">
-        <v>374</v>
-      </c>
-      <c r="E16" s="453">
+        <v>372</v>
+      </c>
+      <c r="E16" s="435">
         <f>Exchange_Rate</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="352" t="s">
-        <v>548</v>
-      </c>
-      <c r="C17" s="452">
+        <v>546</v>
+      </c>
+      <c r="C17" s="434">
         <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="D17" s="360" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E17" s="353" t="str">
         <f>Reporting_currency</f>
@@ -20097,28 +20189,28 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>7.3796628952847572</v>
+        <v>7.7546312099082444</v>
       </c>
       <c r="D18" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="E18" s="454">
+        <v>365</v>
+      </c>
+      <c r="E18" s="436">
         <f>Thesis!E18</f>
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="359" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C19" s="361" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="352" t="s">
-        <v>368</v>
-      </c>
-      <c r="E19" s="455">
+        <v>366</v>
+      </c>
+      <c r="E19" s="437">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
         <v>45991</v>
       </c>
@@ -20129,30 +20221,30 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="356" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C21" s="370" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="371" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E21" s="372">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="352" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>4.5649727820492494</v>
+        <v>3.830160528337446</v>
       </c>
       <c r="D22" s="374" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E22" s="375">
         <f>Thesis!E22</f>
@@ -20161,14 +20253,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="352" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>5.298984252982244</v>
+        <v>4.7511711794730207</v>
       </c>
       <c r="D23" s="374" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E23" s="377">
         <f>Thesis!E23</f>
@@ -20177,14 +20269,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="352" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>6.5887686093669577</v>
+        <v>6.5232537640741466</v>
       </c>
       <c r="D24" s="374" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E24" s="377">
         <f>Thesis!E24</f>
@@ -20193,23 +20285,23 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="352" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>7.1040890386455446</v>
+        <v>7.3308758318019924</v>
       </c>
       <c r="D25" s="374" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E25" s="377">
         <f>Thesis!E25</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="354" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B27" s="354"/>
       <c r="C27" s="354"/>
@@ -20218,26 +20310,26 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="434" t="s">
-        <v>512</v>
-      </c>
-      <c r="C29" s="434"/>
-      <c r="D29" s="434"/>
-      <c r="E29" s="434"/>
-      <c r="F29" s="434"/>
+      <c r="B29" s="472" t="s">
+        <v>510</v>
+      </c>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="435" t="s">
-        <v>513</v>
-      </c>
-      <c r="C30" s="435"/>
-      <c r="D30" s="435"/>
-      <c r="E30" s="435"/>
-      <c r="F30" s="435"/>
+      <c r="B30" s="475" t="s">
+        <v>511</v>
+      </c>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C32" s="379">
         <f>scaling_factor</f>
@@ -20245,13 +20337,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="433" t="s">
-        <v>514</v>
-      </c>
-      <c r="C33" s="433"/>
-      <c r="D33" s="433"/>
-      <c r="E33" s="433"/>
-      <c r="F33" s="433"/>
+      <c r="B33" s="468" t="s">
+        <v>512</v>
+      </c>
+      <c r="C33" s="468"/>
+      <c r="D33" s="468"/>
+      <c r="E33" s="468"/>
+      <c r="F33" s="468"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="381" t="s">
@@ -20271,13 +20363,13 @@
       <c r="C35" s="383"/>
     </row>
     <row r="36" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B36" s="433" t="s">
-        <v>515</v>
-      </c>
-      <c r="C36" s="433"/>
-      <c r="D36" s="433"/>
-      <c r="E36" s="433"/>
-      <c r="F36" s="433"/>
+      <c r="B36" s="468" t="s">
+        <v>513</v>
+      </c>
+      <c r="C36" s="468"/>
+      <c r="D36" s="468"/>
+      <c r="E36" s="468"/>
+      <c r="F36" s="468"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="381" t="s">
@@ -20306,13 +20398,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="433" t="s">
-        <v>516</v>
-      </c>
-      <c r="C40" s="433"/>
-      <c r="D40" s="433"/>
-      <c r="E40" s="433"/>
-      <c r="F40" s="433"/>
+      <c r="B40" s="468" t="s">
+        <v>514</v>
+      </c>
+      <c r="C40" s="468"/>
+      <c r="D40" s="468"/>
+      <c r="E40" s="468"/>
+      <c r="F40" s="468"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="381" t="s">
@@ -20328,17 +20420,17 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="433" t="s">
-        <v>517</v>
-      </c>
-      <c r="C43" s="433"/>
-      <c r="D43" s="433"/>
-      <c r="E43" s="433"/>
-      <c r="F43" s="433"/>
+      <c r="B43" s="468" t="s">
+        <v>515</v>
+      </c>
+      <c r="C43" s="468"/>
+      <c r="D43" s="468"/>
+      <c r="E43" s="468"/>
+      <c r="F43" s="468"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="381" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C44" s="385">
         <f>Normalized_FCF!C46</f>
@@ -20353,7 +20445,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="381" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C45" s="385">
         <f>Normalized_FCF!C45</f>
@@ -20381,7 +20473,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="352" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20398,17 +20490,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="433" t="s">
-        <v>519</v>
-      </c>
-      <c r="C51" s="433"/>
-      <c r="D51" s="433"/>
-      <c r="E51" s="433"/>
-      <c r="F51" s="433"/>
+      <c r="B51" s="468" t="s">
+        <v>517</v>
+      </c>
+      <c r="C51" s="468"/>
+      <c r="D51" s="468"/>
+      <c r="E51" s="468"/>
+      <c r="F51" s="468"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="381" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C52" s="382">
         <f>Normalized_FCF!C14</f>
@@ -20420,13 +20512,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="433" t="s">
-        <v>520</v>
-      </c>
-      <c r="C54" s="436"/>
-      <c r="D54" s="436"/>
-      <c r="E54" s="436"/>
-      <c r="F54" s="436"/>
+      <c r="B54" s="468" t="s">
+        <v>518</v>
+      </c>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20442,26 +20534,26 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="434" t="s">
-        <v>521</v>
-      </c>
-      <c r="C57" s="434"/>
-      <c r="D57" s="434"/>
-      <c r="E57" s="434"/>
-      <c r="F57" s="434"/>
+      <c r="B57" s="472" t="s">
+        <v>519</v>
+      </c>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="434" t="s">
-        <v>522</v>
-      </c>
-      <c r="C58" s="434"/>
-      <c r="D58" s="434"/>
-      <c r="E58" s="434"/>
-      <c r="F58" s="434"/>
+      <c r="B58" s="472" t="s">
+        <v>520</v>
+      </c>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C60" s="382">
         <f>Normalized_FCF!G19</f>
@@ -20487,7 +20579,7 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="386" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
@@ -20497,14 +20589,14 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="386" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
         <v>6.1919504643962855E-2</v>
       </c>
       <c r="E63" s="381" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F63" s="389">
         <f>Normalized_FCF!C90</f>
@@ -20513,18 +20605,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="378" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C65" s="390" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D65" s="390" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="381" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C66" s="387">
         <f>Normalized_FCF!C119</f>
@@ -20579,7 +20671,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="354" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B71" s="354"/>
       <c r="C71" s="354"/>
@@ -20592,36 +20684,36 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="434" t="s">
-        <v>523</v>
-      </c>
-      <c r="C73" s="434"/>
-      <c r="D73" s="434"/>
-      <c r="E73" s="434"/>
-      <c r="F73" s="434"/>
+      <c r="B73" s="472" t="s">
+        <v>521</v>
+      </c>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="435" t="s">
-        <v>490</v>
-      </c>
-      <c r="C74" s="435"/>
-      <c r="D74" s="435"/>
-      <c r="E74" s="435"/>
-      <c r="F74" s="435"/>
+      <c r="B74" s="475" t="s">
+        <v>488</v>
+      </c>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="434" t="s">
-        <v>524</v>
-      </c>
-      <c r="C77" s="434"/>
-      <c r="D77" s="434"/>
-      <c r="E77" s="434"/>
-      <c r="F77" s="434"/>
+      <c r="B77" s="472" t="s">
+        <v>522</v>
+      </c>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20651,7 +20743,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="B80" s="391" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C80" s="397">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -20660,7 +20752,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="391" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C81" s="398">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -20669,7 +20761,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="352" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20687,7 +20779,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="391" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C85" s="399">
         <f>BS!C66</f>
@@ -20713,7 +20805,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="352" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20744,7 +20836,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="381" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
@@ -20757,7 +20849,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="354" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B94" s="354"/>
       <c r="C94" s="354"/>
@@ -20770,33 +20862,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="434" t="s">
-        <v>527</v>
-      </c>
-      <c r="C96" s="434"/>
-      <c r="D96" s="434"/>
-      <c r="E96" s="434"/>
-      <c r="F96" s="434"/>
+      <c r="B96" s="472" t="s">
+        <v>525</v>
+      </c>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="435" t="s">
-        <v>528</v>
-      </c>
-      <c r="C97" s="435"/>
-      <c r="D97" s="435"/>
-      <c r="E97" s="435"/>
-      <c r="F97" s="435"/>
+      <c r="B97" s="475" t="s">
+        <v>526</v>
+      </c>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="435" t="s">
-        <v>529</v>
-      </c>
-      <c r="C98" s="435"/>
-      <c r="D98" s="435"/>
-      <c r="E98" s="435"/>
-      <c r="F98" s="435"/>
+      <c r="B98" s="475" t="s">
+        <v>527</v>
+      </c>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20804,7 +20896,7 @@
     <row r="100" spans="1:6">
       <c r="A100" s="394"/>
       <c r="B100" s="378" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -20814,23 +20906,23 @@
       </c>
       <c r="C101" s="377">
         <f>E25+C103</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="394"/>
       <c r="B102" s="391" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C102" s="392">
         <f>E25</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="394"/>
       <c r="B103" s="391" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C103" s="392">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -20840,7 +20932,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="394"/>
       <c r="B104" s="381" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C104" s="377">
         <v>0</v>
@@ -20853,29 +20945,29 @@
     <row r="106" spans="1:6">
       <c r="A106" s="394"/>
       <c r="B106" s="402" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C106" s="401"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="434" t="s">
-        <v>530</v>
-      </c>
-      <c r="C107" s="434"/>
-      <c r="D107" s="434"/>
-      <c r="E107" s="434"/>
-      <c r="F107" s="434"/>
+      <c r="B107" s="472" t="s">
+        <v>528</v>
+      </c>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="434" t="s">
-        <v>549</v>
-      </c>
-      <c r="C108" s="434"/>
-      <c r="D108" s="434"/>
-      <c r="E108" s="434"/>
-      <c r="F108" s="434"/>
+      <c r="B108" s="472" t="s">
+        <v>547</v>
+      </c>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -20883,13 +20975,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="394"/>
       <c r="B110" s="378" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="394"/>
       <c r="B111" s="384" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
@@ -20903,11 +20995,11 @@
     <row r="112" spans="1:6">
       <c r="A112" s="394"/>
       <c r="B112" s="381" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>3.1834186940220452</v>
+        <v>3.3934554230790441</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -20919,13 +21011,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="434" t="s">
-        <v>531</v>
-      </c>
-      <c r="C114" s="434"/>
-      <c r="D114" s="434"/>
-      <c r="E114" s="434"/>
-      <c r="F114" s="434"/>
+      <c r="B114" s="472" t="s">
+        <v>529</v>
+      </c>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -20933,25 +21025,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="394"/>
       <c r="B116" s="378" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="394"/>
       <c r="B117" s="351" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C117" s="351" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D117" s="351" t="s">
         <v>99</v>
       </c>
       <c r="E117" s="351" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F117" s="351" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -20970,7 +21062,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.84 HKD</v>
+        <v>8.23 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -20993,7 +21085,7 @@
       </c>
       <c r="E119" s="407" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>7.61 HKD</v>
+        <v>7.99 HKD</v>
       </c>
       <c r="F119" s="412">
         <f>DCF!F75</f>
@@ -21015,7 +21107,7 @@
       </c>
       <c r="E120" s="407" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>7.38 HKD</v>
+        <v>7.75 HKD</v>
       </c>
       <c r="F120" s="412">
         <f>DCF!F76</f>
@@ -21037,7 +21129,7 @@
       </c>
       <c r="E121" s="407" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.15 HKD</v>
+        <v>7.52 HKD</v>
       </c>
       <c r="F121" s="412">
         <f>DCF!F77</f>
@@ -21059,7 +21151,7 @@
       </c>
       <c r="E122" s="407" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>6.93 HKD</v>
+        <v>7.29 HKD</v>
       </c>
       <c r="F122" s="412">
         <f>DCF!F78</f>
@@ -21067,13 +21159,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="433" t="s">
-        <v>532</v>
-      </c>
-      <c r="C124" s="433"/>
-      <c r="D124" s="433"/>
-      <c r="E124" s="433"/>
-      <c r="F124" s="433"/>
+      <c r="B124" s="468" t="s">
+        <v>530</v>
+      </c>
+      <c r="C124" s="468"/>
+      <c r="D124" s="468"/>
+      <c r="E124" s="468"/>
+      <c r="F124" s="468"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="381" t="s">
@@ -21081,7 +21173,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>7.3796628952847572</v>
+        <v>7.7546312099082444</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21089,17 +21181,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="438" t="s">
-        <v>533</v>
-      </c>
-      <c r="C127" s="438"/>
-      <c r="D127" s="438"/>
-      <c r="E127" s="438"/>
-      <c r="F127" s="438"/>
+      <c r="B127" s="470" t="s">
+        <v>531</v>
+      </c>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B129" s="354"/>
       <c r="C129" s="354"/>
@@ -21108,40 +21200,40 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="439" t="s">
-        <v>534</v>
-      </c>
-      <c r="C131" s="439"/>
-      <c r="D131" s="439"/>
-      <c r="E131" s="439"/>
-      <c r="F131" s="439"/>
+      <c r="B131" s="471" t="s">
+        <v>532</v>
+      </c>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B132" s="434" t="s">
-        <v>535</v>
-      </c>
-      <c r="C132" s="434"/>
-      <c r="D132" s="434"/>
-      <c r="E132" s="434"/>
-      <c r="F132" s="434"/>
+      <c r="B132" s="472" t="s">
+        <v>533</v>
+      </c>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="352" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C135" s="414">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="352" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C136" s="415">
         <f>Scenarios!C58</f>
@@ -21154,45 +21246,45 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="378" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C138" s="416"/>
       <c r="D138" s="416"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="349" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="417" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C140" s="418">
         <f>Scenarios!C62</f>
-        <v>0.51577503429355298</v>
+        <v>0.67835187725448365</v>
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>4.049197747755696</v>
+        <v>3.1518086510829622</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>4.5649727820492494</v>
+        <v>3.830160528337446</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21201,19 +21293,19 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="417" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C141" s="418">
         <f>Scenarios!C63</f>
-        <v>0.57600000000000007</v>
+        <v>0.78080000000000005</v>
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>4.7229842529822443</v>
+        <v>3.970371179473021</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>5.298984252982244</v>
+        <v>4.7511711794730207</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21222,38 +21314,38 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="349" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="417" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C144" s="418">
         <f>Scenarios!C66</f>
-        <v>0.67833709316953872</v>
+        <v>0.96504125037545974</v>
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>5.910431516197419</v>
+        <v>5.5582125136986873</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>6.5887686093669577</v>
+        <v>6.5232537640741466</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21262,28 +21354,28 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="417" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C145" s="418">
         <f>Scenarios!C67</f>
-        <v>0.71822606814494294</v>
+        <v>1.0449500908692064</v>
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>6.385862970500602</v>
+        <v>6.285925740932786</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>7.1040890386455446</v>
+        <v>7.3308758318019924</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="354" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B147" s="354"/>
       <c r="C147" s="354"/>
@@ -21292,111 +21384,108 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="440" t="s">
-        <v>536</v>
-      </c>
-      <c r="C149" s="434"/>
-      <c r="D149" s="434"/>
-      <c r="E149" s="434"/>
-      <c r="F149" s="434"/>
+      <c r="B149" s="473" t="s">
+        <v>534</v>
+      </c>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="436" t="s">
-        <v>537</v>
-      </c>
-      <c r="C152" s="436"/>
-      <c r="D152" s="436"/>
-      <c r="E152" s="436"/>
-      <c r="F152" s="436"/>
+      <c r="B152" s="474" t="s">
+        <v>535</v>
+      </c>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="421" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="421" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="352" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B158" s="433" t="s">
-        <v>450</v>
-      </c>
-      <c r="C158" s="433"/>
-      <c r="D158" s="433"/>
-      <c r="E158" s="433"/>
-      <c r="F158" s="433"/>
+      <c r="B158" s="468" t="s">
+        <v>448</v>
+      </c>
+      <c r="C158" s="468"/>
+      <c r="D158" s="468"/>
+      <c r="E158" s="468"/>
+      <c r="F158" s="468"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="352" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="437" t="s">
-        <v>393</v>
-      </c>
-      <c r="C161" s="437"/>
-      <c r="D161" s="437"/>
-      <c r="E161" s="437"/>
-      <c r="F161" s="437"/>
+      <c r="B161" s="469" t="s">
+        <v>391</v>
+      </c>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="437" t="s">
-        <v>394</v>
-      </c>
-      <c r="C162" s="437"/>
-      <c r="D162" s="437"/>
-      <c r="E162" s="437"/>
-      <c r="F162" s="437"/>
+      <c r="B162" s="469" t="s">
+        <v>392</v>
+      </c>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="421" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="421" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="421" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21411,12 +21500,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21435,4 +21527,28 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAFC6CD-A457-45C7-A858-119AB4C1BCD1}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="457" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="457" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="457" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="457"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="455" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2" s="456"/>
+      <c r="D2" s="456"/>
+      <c r="E2" s="456"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9FCFEA-15D8-45F8-97D7-64B80D6D27CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E3EE5F-2E79-4529-9355-22B572C83EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4993,30 +4993,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5026,6 +5026,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5035,22 +5044,13 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{AFD61BCC-344D-4D7C-9A1E-59EC5319B854}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{9CEEE9BB-26AF-4B02-871F-29D7DAE075EF}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5143,8 +5143,8 @@
       <sheetName val="Normalized_FCF"/>
       <sheetName val="DCF"/>
       <sheetName val="Scenarios"/>
+      <sheetName val="投资主题"/>
       <sheetName val="Breakdown"/>
-      <sheetName val="投资主题"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5178,12 +5178,12 @@
         </row>
         <row r="21">
           <cell r="E21">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="101">
           <cell r="C101">
-            <v>7.4999999999999997E-2</v>
+            <v>7.2499999999999995E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.12123938704206341</v>
+        <v>0.15491941305006585</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5535,13 +5535,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.6" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5641,7 +5641,7 @@
         <v>317</v>
       </c>
       <c r="E21" s="452">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>3.830160528337446</v>
+        <v>4.7707167132555526</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>413</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>4.7511711794730207</v>
+        <v>5.5389639743412769</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>414</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>6.5232537640741466</v>
+        <v>6.8890837559764515</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>415</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>7.3308758318019924</v>
+        <v>7.4623643296076372</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>416</v>
@@ -5719,22 +5719,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5746,13 +5746,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5772,13 +5772,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5829,13 +5829,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5899,13 +5899,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5921,7 +5921,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5943,22 +5943,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C67" s="270">
         <f>Normalized_FCF!C116</f>
-        <v>3.9086921133773919E-2</v>
+        <v>3.176685498586024E-4</v>
       </c>
       <c r="D67" s="270">
         <f>Normalized_FCF!G116</f>
@@ -6093,13 +6093,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6118,13 +6118,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6293,31 +6293,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.65" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>493</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>492</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6367,22 +6367,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6416,13 +6416,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>500</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6557,13 +6557,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>360</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6598,22 +6598,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>362</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C135" s="205">
         <f>E21</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
+        <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
         <v>480</v>
@@ -6674,15 +6674,15 @@
       </c>
       <c r="C140" s="342">
         <f>Scenarios!C62</f>
-        <v>0.67835187725448365</v>
+        <v>0.51577503429355298</v>
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>3.1518086510829622</v>
+        <v>4.2549416789619992</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>3.830160528337446</v>
+        <v>4.7707167132555526</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6695,15 +6695,15 @@
       </c>
       <c r="C141" s="342">
         <f>Scenarios!C63</f>
-        <v>0.78080000000000005</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>3.970371179473021</v>
+        <v>4.9629639743412763</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>4.7511711794730207</v>
+        <v>5.5389639743412769</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
+        <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
         <v>480</v>
@@ -6742,15 +6742,15 @@
       </c>
       <c r="C144" s="342">
         <f>Scenarios!C66</f>
-        <v>0.96504125037545974</v>
+        <v>0.67833709316953872</v>
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>5.5582125136986873</v>
+        <v>6.2107466628069128</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>6.5232537640741466</v>
+        <v>6.8890837559764515</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6763,15 +6763,15 @@
       </c>
       <c r="C145" s="342">
         <f>Scenarios!C67</f>
-        <v>1.0449500908692064</v>
+        <v>0.72070897245722421</v>
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>6.285925740932786</v>
+        <v>6.741655357150413</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>7.3308758318019924</v>
+        <v>7.4623643296076372</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6789,13 +6789,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>363</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6832,13 +6832,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>447</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6846,22 +6846,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6885,6 +6885,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6901,18 +6913,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -13801,8 +13801,8 @@
         <v>137</v>
       </c>
       <c r="C79" s="75">
-        <f>C13/C4</f>
-        <v>3.9086921133773919E-2</v>
+        <f>MIN(BS!C62,MAX(G81:K81))</f>
+        <v>3.176685498586024E-4</v>
       </c>
       <c r="D79" s="26"/>
       <c r="E79" s="239"/>
@@ -13973,8 +13973,8 @@
         <v>129</v>
       </c>
       <c r="C82" s="75">
-        <f>ABS(C16/C$4)</f>
-        <v>3.2319910596842617E-2</v>
+        <f>MAX(AVERAGE(G76:J76),C81)</f>
+        <v>1.8000768044788736E-2</v>
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="239"/>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="C116" s="22">
         <f>C79</f>
-        <v>3.9086921133773919E-2</v>
+        <v>3.176685498586024E-4</v>
       </c>
       <c r="E116" s="242"/>
       <c r="G116" s="22">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="F33" s="223">
         <f>Holding_Period</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12123938704206341</v>
+        <v>0.15491941305006585</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.41006763945510488</v>
+        <v>0.61023323266846963</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="C57" s="223">
         <f>Holding_Period</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" s="127"/>
     </row>
@@ -19862,15 +19862,15 @@
       </c>
       <c r="C62" s="120">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.67835187725448365</v>
+        <v>0.51577503429355298</v>
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.1518086510829622</v>
+        <v>4.2549416789619992</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>3.830160528337446</v>
+        <v>4.7707167132555526</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.50608089222301444</v>
+        <v>0.38479128354164482</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19887,15 +19887,15 @@
       </c>
       <c r="C63" s="120">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.78080000000000005</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.970371179473021</v>
+        <v>4.9629639743412763</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>4.7511711794730207</v>
+        <v>5.5389639743412769</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.3873117817127969</v>
+        <v>0.28572180618157139</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19933,15 +19933,15 @@
       </c>
       <c r="C66" s="120">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>0.96504125037545974</v>
+        <v>0.67833709316953872</v>
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.5582125136986873</v>
+        <v>6.2107466628069128</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>6.5232537640741466</v>
+        <v>6.8890837559764515</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.15919490631722644</v>
+        <v>0.11204179350910581</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19958,15 +19958,15 @@
       </c>
       <c r="C67" s="120">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.0449500908692064</v>
+        <v>0.72070897245722421</v>
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.285925740932786</v>
+        <v>6.741655357150413</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>7.3308758318019924</v>
+        <v>7.4623643296076372</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19974,7 +19974,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>5.4645458518363998E-2</v>
+        <v>3.76893333015208E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20092,7 +20092,7 @@
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.12123938704206341</v>
+        <v>0.15491941305006585</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20119,13 +20119,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.6" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>509</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="E21" s="372">
         <f>Holding_Period</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>3.830160528337446</v>
+        <v>4.7707167132555526</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>449</v>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>4.7511711794730207</v>
+        <v>5.5389639743412769</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>450</v>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>6.5232537640741466</v>
+        <v>6.8890837559764515</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>452</v>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>7.3308758318019924</v>
+        <v>7.4623643296076372</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>451</v>
@@ -20310,22 +20310,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>510</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20515,10 +20515,10 @@
       <c r="B54" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20534,22 +20534,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>519</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>520</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C67" s="392">
         <f>Normalized_FCF!C116</f>
-        <v>3.9086921133773919E-2</v>
+        <v>3.176685498586024E-4</v>
       </c>
       <c r="D67" s="392">
         <f>Normalized_FCF!G116</f>
@@ -20684,22 +20684,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>521</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>488</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20707,13 +20707,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>522</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20862,33 +20862,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>525</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>526</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>527</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20951,23 +20951,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>528</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>547</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21011,13 +21011,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>529</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21181,13 +21181,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>531</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21200,22 +21200,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>533</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="C135" s="414">
         <f>E21</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -21257,7 +21257,7 @@
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
+        <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
         <v>480</v>
@@ -21276,15 +21276,15 @@
       </c>
       <c r="C140" s="418">
         <f>Scenarios!C62</f>
-        <v>0.67835187725448365</v>
+        <v>0.51577503429355298</v>
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>3.1518086510829622</v>
+        <v>4.2549416789619992</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>3.830160528337446</v>
+        <v>4.7707167132555526</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21297,15 +21297,15 @@
       </c>
       <c r="C141" s="418">
         <f>Scenarios!C63</f>
-        <v>0.78080000000000005</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>3.970371179473021</v>
+        <v>4.9629639743412763</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>4.7511711794730207</v>
+        <v>5.5389639743412769</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21318,7 +21318,7 @@
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
+        <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
         <v>480</v>
@@ -21337,15 +21337,15 @@
       </c>
       <c r="C144" s="418">
         <f>Scenarios!C66</f>
-        <v>0.96504125037545974</v>
+        <v>0.67833709316953872</v>
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>5.5582125136986873</v>
+        <v>6.2107466628069128</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>6.5232537640741466</v>
+        <v>6.8890837559764515</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21358,15 +21358,15 @@
       </c>
       <c r="C145" s="418">
         <f>Scenarios!C67</f>
-        <v>1.0449500908692064</v>
+        <v>0.72070897245722421</v>
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>6.285925740932786</v>
+        <v>6.741655357150413</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>7.3308758318019924</v>
+        <v>7.4623643296076372</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21384,13 +21384,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>534</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21398,13 +21398,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21441,22 +21441,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21480,12 +21480,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21500,15 +21503,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21530,7 +21530,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAFC6CD-A457-45C7-A858-119AB4C1BCD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7486D8-6F03-4F16-B46F-BAEF0C1D914A}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E3EE5F-2E79-4529-9355-22B572C83EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EC985B-FE8F-41A3-BEDF-B1A90E7002F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="556">
   <si>
     <t>Sales</t>
   </si>
@@ -2126,9 +2126,6 @@
     <t>I</t>
   </si>
   <si>
-    <t>Note on g=0: It's to avoid overestimating the stock’s value, especially if future growth is uncertain or unreliable.</t>
-  </si>
-  <si>
     <t>@Target return</t>
   </si>
   <si>
@@ -2163,9 +2160,6 @@
   </si>
   <si>
     <t>Non-op EBIT</t>
-  </si>
-  <si>
-    <t>EBITDA</t>
   </si>
   <si>
     <t>T</t>
@@ -2539,12 +2533,6 @@
   </si>
   <si>
     <t xml:space="preserve">Taxes = </t>
-  </si>
-  <si>
-    <t>大家乐集团</t>
-  </si>
-  <si>
-    <t>0341.HK</t>
   </si>
   <si>
     <t>Y</t>
@@ -3269,6 +3257,15 @@
   </si>
   <si>
     <t>更新日期:</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>大家乐集团</t>
+  </si>
+  <si>
+    <t>0341.HK</t>
   </si>
   <si>
     <t>N</t>
@@ -4993,30 +4990,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5026,31 +5023,31 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{9CEEE9BB-26AF-4B02-871F-29D7DAE075EF}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{0533B5A3-0297-4086-A30C-64FBADBAC6B3}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5178,7 +5175,7 @@
         </row>
         <row r="21">
           <cell r="E21">
-            <v>3</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="101">
@@ -5421,10 +5418,10 @@
   <dimension ref="A2:I167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5443,7 +5440,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="438" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F3" s="439">
         <v>45930</v>
@@ -5451,13 +5448,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="431" t="s">
+        <v>540</v>
+      </c>
+      <c r="C4" s="430" t="s">
+        <v>551</v>
+      </c>
+      <c r="E4" s="440" t="s">
         <v>544</v>
-      </c>
-      <c r="C4" s="430" t="s">
-        <v>506</v>
-      </c>
-      <c r="E4" s="440" t="s">
-        <v>548</v>
       </c>
       <c r="F4" s="441" t="s">
         <v>325</v>
@@ -5468,13 +5465,13 @@
         <v>352</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>507</v>
+        <v>552</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F5" s="442" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5502,7 +5499,7 @@
         <v>353</v>
       </c>
       <c r="C8" s="47">
-        <v>6.46</v>
+        <v>6.43</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5514,11 +5511,11 @@
         <v>580004033</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.15491941305006585</v>
+        <v>0.13834890491956828</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5527,21 +5524,21 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3746.8260531799997</v>
+        <v>3729.4259321899999</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.6" customHeight="1">
-      <c r="B12" s="458" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5555,7 +5552,7 @@
         <v>320</v>
       </c>
       <c r="C15" s="427" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>356</v>
@@ -5570,7 +5567,7 @@
         <v>321</v>
       </c>
       <c r="C16" s="427" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>357</v>
@@ -5581,7 +5578,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C17" s="425">
         <v>0</v>
@@ -5600,7 +5597,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>7.7546312099082444</v>
+        <v>7.4769002526339001</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>350</v>
@@ -5650,10 +5647,10 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>4.7707167132555526</v>
+        <v>4.6183266132421945</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5665,10 +5662,10 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>5.5389639743412769</v>
+        <v>5.3612161616856966</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E23" s="453">
         <v>0.25</v>
@@ -5680,10 +5677,10 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>6.8890837559764515</v>
+        <v>6.6666467929077449</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E24" s="453">
         <v>0.1174</v>
@@ -5695,10 +5692,10 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>7.4623643296076372</v>
+        <v>7.2209129510349541</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E25" s="454">
         <v>7.2499999999999995E-2</v>
@@ -5719,22 +5716,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5745,14 +5742,14 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B33" s="459" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5771,21 +5768,21 @@
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B36" s="459" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
       <c r="C37" s="293">
-        <f>Normalized_FCF!C9</f>
+        <f>Normalized_FCF!C15</f>
         <v>378473</v>
       </c>
       <c r="D37" s="1" t="str">
@@ -5798,7 +5795,7 @@
         <v>200</v>
       </c>
       <c r="C38" s="293">
-        <f>Normalized_FCF!C10</f>
+        <f>Normalized_FCF!C16</f>
         <v>-378473</v>
       </c>
       <c r="D38" s="1" t="str">
@@ -5807,20 +5804,20 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
       <c r="C41" s="293">
-        <f>Normalized_FCF!C11</f>
+        <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
       <c r="D41" s="1" t="str">
@@ -5829,13 +5826,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5872,7 +5869,7 @@
         <v>203</v>
       </c>
       <c r="C46" s="293">
-        <f>Normalized_FCF!C12</f>
+        <f>Normalized_FCF!C10</f>
         <v>-78679.881332559497</v>
       </c>
       <c r="D46" s="1" t="str">
@@ -5890,8 +5887,8 @@
         <v>223</v>
       </c>
       <c r="C49" s="293">
-        <f>Normalized_FCF!C15</f>
-        <v>-2604.2914835892152</v>
+        <f>Normalized_FCF!C13</f>
+        <v>-37355.845009453624</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5899,20 +5896,20 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
       <c r="C52" s="293">
-        <f>Normalized_FCF!C14</f>
+        <f>Normalized_FCF!C12</f>
         <v>-52872.613354906651</v>
       </c>
       <c r="D52" s="1" t="str">
@@ -5921,7 +5918,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5942,23 +5939,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B57" s="458" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5966,7 +5963,7 @@
       </c>
       <c r="C60" s="293">
         <f>Normalized_FCF!G19</f>
-        <v>362404.65016124537</v>
+        <v>289000.65016124537</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5979,7 +5976,7 @@
       </c>
       <c r="C61" s="293">
         <f>Normalized_FCF!C19</f>
-        <v>264963.17610033229</v>
+        <v>230211.62257446788</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5992,7 +5989,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.0716700572596158E-2</v>
+        <v>6.1728434016460706E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -6002,14 +5999,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1919504643962855E-2</v>
+        <v>6.2208398133748059E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
       </c>
       <c r="F63" s="265">
         <f>Normalized_FCF!C90</f>
-        <v>0.87559945730779254</v>
+        <v>1.0077754137932506</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -6033,7 +6030,7 @@
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.14467098116585544</v>
+        <v>0.11792742550148552</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -6043,11 +6040,11 @@
       </c>
       <c r="C67" s="270">
         <f>Normalized_FCF!C116</f>
-        <v>3.176685498586024E-4</v>
+        <v>3.9086921133773919E-2</v>
       </c>
       <c r="D67" s="270">
         <f>Normalized_FCF!G116</f>
-        <v>4.6343249224001092E-2</v>
+        <v>3.7776339292914275E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6080,7 +6077,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="203" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6093,18 +6090,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
-        <v>487</v>
-      </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="B73" s="460" t="s">
+        <v>485</v>
+      </c>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
       <c r="B74" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6118,13 +6115,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6180,7 +6177,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="192"/>
       <c r="B83" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6268,7 +6265,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="192"/>
       <c r="B92" s="44" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
@@ -6281,7 +6278,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="203" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6292,32 +6289,32 @@
     <row r="95" spans="1:6">
       <c r="A95" s="192"/>
     </row>
-    <row r="96" spans="1:6" ht="11.65" customHeight="1">
-      <c r="B96" s="458" t="s">
-        <v>494</v>
-      </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="460" t="s">
+        <v>492</v>
+      </c>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
-        <v>493</v>
-      </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="B97" s="464" t="s">
+        <v>491</v>
+      </c>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
-        <v>492</v>
-      </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="B98" s="464" t="s">
+        <v>490</v>
+      </c>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6326,7 +6323,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C101" s="215">
         <f>E25+C103</f>
@@ -6367,31 +6364,31 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
@@ -6408,25 +6405,25 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B114" s="458" t="s">
-        <v>500</v>
-      </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="460" t="s">
+        <v>498</v>
+      </c>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6461,7 +6458,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>8.23 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6483,7 +6480,7 @@
       </c>
       <c r="E119" s="211" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>7.99 HKD</v>
+        <v>7.71 HKD</v>
       </c>
       <c r="F119" s="202">
         <f>DCF!F75</f>
@@ -6505,7 +6502,7 @@
       </c>
       <c r="E120" s="211" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>7.75 HKD</v>
+        <v>7.48 HKD</v>
       </c>
       <c r="F120" s="202">
         <f>DCF!F76</f>
@@ -6527,7 +6524,7 @@
       </c>
       <c r="E121" s="211" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.52 HKD</v>
+        <v>7.25 HKD</v>
       </c>
       <c r="F121" s="202">
         <f>DCF!F77</f>
@@ -6549,7 +6546,7 @@
       </c>
       <c r="E122" s="211" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.29 HKD</v>
+        <v>7.02 HKD</v>
       </c>
       <c r="F122" s="202">
         <f>DCF!F78</f>
@@ -6557,13 +6554,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6571,14 +6568,14 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>7.7546312099082444</v>
+        <v>7.4769002526339001</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.6" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="463" t="s">
         <v>361</v>
       </c>
@@ -6589,7 +6586,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="203" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6598,22 +6595,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>362</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6644,28 +6641,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="193" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C138" s="218"/>
       <c r="D138" s="219"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="349" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6678,11 +6675,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>4.2549416789619992</v>
+        <v>4.1025515789486411</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>4.7707167132555526</v>
+        <v>4.6183266132421945</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6699,11 +6696,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>4.9629639743412763</v>
+        <v>4.7852161616856961</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>5.5389639743412769</v>
+        <v>5.3612161616856966</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6719,21 +6716,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="349" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6746,11 +6743,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>6.2107466628069128</v>
+        <v>5.9883096997382061</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>6.8890837559764515</v>
+        <v>6.6666467929077449</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6767,11 +6764,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>6.741655357150413</v>
+        <v>6.5002039785777299</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>7.4623643296076372</v>
+        <v>7.2209129510349541</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6780,7 +6777,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="203" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6789,13 +6786,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>363</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6831,37 +6828,37 @@
         <v>297</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B158" s="459" t="s">
-        <v>447</v>
-      </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="461" t="s">
+        <v>445</v>
+      </c>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B161" s="464" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6885,18 +6882,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6913,6 +6898,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6940,12 +6937,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -7574,7 +7571,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8278,11 +8275,11 @@
         <v>47</v>
       </c>
       <c r="C46" s="278">
-        <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
+        <f>IF(C$4="","",-C14)</f>
         <v>-32312</v>
       </c>
       <c r="D46" s="278">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D46:M46" si="20">IF(D$4="","",-D14)</f>
         <v>-56313</v>
       </c>
       <c r="E46" s="278">
@@ -8479,11 +8476,11 @@
         <v>64</v>
       </c>
       <c r="C52" s="278">
-        <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
+        <f>IF(C$4="","",C13)</f>
         <v>46652</v>
       </c>
       <c r="D52" s="278">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="D52:M52" si="24">IF(D$4="","",D13)</f>
         <v>45304</v>
       </c>
       <c r="E52" s="278">
@@ -9497,15 +9494,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -10373,11 +10370,11 @@
         <v>118</v>
       </c>
       <c r="C55" s="89">
-        <f>Normalized_FCF!C11/G40</f>
+        <f>Normalized_FCF!C9/G40</f>
         <v>0</v>
       </c>
       <c r="D55" s="89">
-        <f>Normalized_FCF!G11/G40</f>
+        <f>Normalized_FCF!G9/G40</f>
         <v>0</v>
       </c>
       <c r="F55" s="227"/>
@@ -10403,7 +10400,7 @@
       </c>
       <c r="C58" s="95"/>
       <c r="D58" s="22">
-        <f>Normalized_FCF!G9/BS!$G$39</f>
+        <f>Normalized_FCF!G15/BS!$G$39</f>
         <v>0.10443400183220936</v>
       </c>
       <c r="F58" s="5"/>
@@ -10781,16 +10778,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10886,7 +10883,7 @@
       <c r="E3" s="242"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11174,447 +11171,447 @@
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
-      <c r="B9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="274">
-        <f>BS!$G$39*BS!D58</f>
-        <v>378473</v>
-      </c>
-      <c r="E9" s="242"/>
-      <c r="G9" s="274">
-        <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>378473</v>
-      </c>
-      <c r="H9" s="274">
-        <f>IF(Data!D61="","",-Data!D61)</f>
-        <v>394190</v>
-      </c>
-      <c r="I9" s="274">
-        <f>IF(Data!E61="","",-Data!E61)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="274">
-        <f>IF(Data!F61="","",-Data!F61)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="274">
-        <f>IF(Data!G61="","",-Data!G61)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="274">
-        <f>IF(Data!H61="","",-Data!H61)</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="274">
-        <f>IF(Data!I61="","",-Data!I61)</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="274">
-        <f>IF(Data!J61="","",-Data!J61)</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="274">
-        <f>IF(Data!K61="","",-Data!K61)</f>
-        <v>0</v>
-      </c>
-      <c r="P9" s="274">
-        <f>IF(Data!L61="","",-Data!L61)</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="274" t="str">
-        <f>IF(Data!M61="","",-Data!M61)</f>
+      <c r="B9" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="C9" s="308">
+        <f>C61</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="278">
+        <f>G59</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="278">
+        <f t="shared" ref="H9:Q9" si="5">H59</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="278" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>402</v>
+        <v>65</v>
       </c>
       <c r="C10" s="274">
-        <f>-C4*C76</f>
-        <v>-378473</v>
+        <f>C48</f>
+        <v>-78679.881332559497</v>
       </c>
       <c r="E10" s="242"/>
       <c r="G10" s="274">
-        <f>Data!C62</f>
-        <v>-305069</v>
+        <f>G48</f>
+        <v>-74482.349838754599</v>
       </c>
       <c r="H10" s="274">
-        <f>Data!D62</f>
-        <v>-316358</v>
+        <f t="shared" ref="H10:Q10" si="6">H48</f>
+        <v>-79815.579205498987</v>
       </c>
       <c r="I10" s="274">
-        <f>Data!E62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-73832.968687003769</v>
       </c>
       <c r="J10" s="274">
-        <f>Data!F62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-83179.118160315134</v>
       </c>
       <c r="K10" s="274">
-        <f>Data!G62</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L10" s="274">
-        <f>Data!H62</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M10" s="274">
-        <f>Data!I62</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N10" s="274">
-        <f>Data!J62</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O10" s="274">
-        <f>Data!K62</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P10" s="274">
-        <f>Data!L62</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q10" s="274" t="str">
-        <f>Data!M62</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
-      <c r="B11" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="C11" s="308">
-        <f>C61</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="55"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="278">
-        <f>G59</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="278">
-        <f t="shared" ref="H11:Q11" si="5">H59</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="278" t="str">
-        <f t="shared" si="5"/>
+      <c r="B11" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="275">
+        <f>SUM(C8:C10)</f>
+        <v>320440.08093882818</v>
+      </c>
+      <c r="E11" s="242"/>
+      <c r="G11" s="275">
+        <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
+        <v>323679.65016124537</v>
+      </c>
+      <c r="H11" s="275">
+        <f t="shared" si="7"/>
+        <v>406257.42079450103</v>
+      </c>
+      <c r="I11" s="275">
+        <f t="shared" si="7"/>
+        <v>142737.03131299623</v>
+      </c>
+      <c r="J11" s="275">
+        <f t="shared" si="7"/>
+        <v>5698.8818396848656</v>
+      </c>
+      <c r="K11" s="275">
+        <f t="shared" si="7"/>
+        <v>-87431</v>
+      </c>
+      <c r="L11" s="275">
+        <f t="shared" si="7"/>
+        <v>249238</v>
+      </c>
+      <c r="M11" s="275">
+        <f t="shared" si="7"/>
+        <v>689430</v>
+      </c>
+      <c r="N11" s="275">
+        <f t="shared" si="7"/>
+        <v>583289</v>
+      </c>
+      <c r="O11" s="275">
+        <f t="shared" si="7"/>
+        <v>626211</v>
+      </c>
+      <c r="P11" s="275">
+        <f t="shared" si="7"/>
+        <v>614633</v>
+      </c>
+      <c r="Q11" s="275" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C12" s="274">
-        <f>C48</f>
-        <v>-78679.881332559497</v>
+        <f>-C11*C41</f>
+        <v>-52872.613354906651</v>
       </c>
       <c r="E12" s="242"/>
       <c r="G12" s="274">
-        <f>G48</f>
-        <v>-74482.349838754599</v>
+        <f>Data!C46</f>
+        <v>-32312</v>
       </c>
       <c r="H12" s="274">
-        <f t="shared" ref="H12:Q12" si="6">H48</f>
-        <v>-79815.579205498987</v>
+        <f>Data!D46</f>
+        <v>-56313</v>
       </c>
       <c r="I12" s="274">
-        <f t="shared" si="6"/>
-        <v>-73832.968687003769</v>
+        <f>Data!E46</f>
+        <v>-32989</v>
       </c>
       <c r="J12" s="274">
-        <f t="shared" si="6"/>
-        <v>-83179.118160315134</v>
+        <f>Data!F46</f>
+        <v>-27939</v>
       </c>
       <c r="K12" s="274">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>Data!G46</f>
+        <v>-29996</v>
       </c>
       <c r="L12" s="274">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>Data!H46</f>
+        <v>-39872</v>
       </c>
       <c r="M12" s="274">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>Data!I46</f>
+        <v>-129810</v>
       </c>
       <c r="N12" s="274">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>Data!J46</f>
+        <v>-121949</v>
       </c>
       <c r="O12" s="274">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>Data!K46</f>
+        <v>-108832</v>
       </c>
       <c r="P12" s="274">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>Data!L46</f>
+        <v>-110223</v>
       </c>
       <c r="Q12" s="274" t="str">
-        <f t="shared" si="6"/>
+        <f>Data!M46</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
-      <c r="B13" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="275">
-        <f>SUM(C8:C12)</f>
-        <v>320440.08093882818</v>
-      </c>
-      <c r="E13" s="242"/>
-      <c r="G13" s="275">
-        <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>397083.65016124537</v>
-      </c>
-      <c r="H13" s="275">
-        <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>484089.42079450103</v>
-      </c>
-      <c r="I13" s="275">
-        <f t="shared" si="7"/>
-        <v>142737.03131299623</v>
-      </c>
-      <c r="J13" s="275">
-        <f t="shared" si="7"/>
-        <v>5698.8818396848656</v>
-      </c>
-      <c r="K13" s="275">
-        <f t="shared" si="7"/>
-        <v>-87431</v>
-      </c>
-      <c r="L13" s="275">
-        <f t="shared" si="7"/>
-        <v>249238</v>
-      </c>
-      <c r="M13" s="275">
-        <f t="shared" si="7"/>
-        <v>689430</v>
-      </c>
-      <c r="N13" s="275">
-        <f t="shared" si="7"/>
-        <v>583289</v>
-      </c>
-      <c r="O13" s="275">
-        <f t="shared" si="7"/>
-        <v>626211</v>
-      </c>
-      <c r="P13" s="275">
-        <f t="shared" si="7"/>
-        <v>614633</v>
-      </c>
-      <c r="Q13" s="275" t="str">
-        <f t="shared" si="7"/>
+      <c r="B13" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="274">
+        <f>-C4*C79</f>
+        <v>-37355.845009453624</v>
+      </c>
+      <c r="D13" s="57"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="278">
+        <f>Data!C48</f>
+        <v>-2367</v>
+      </c>
+      <c r="H13" s="278">
+        <f>Data!D48</f>
+        <v>-2761</v>
+      </c>
+      <c r="I13" s="278">
+        <f>Data!E48</f>
+        <v>-834</v>
+      </c>
+      <c r="J13" s="278">
+        <f>Data!F48</f>
+        <v>-1636</v>
+      </c>
+      <c r="K13" s="278">
+        <f>Data!G48</f>
+        <v>-1420</v>
+      </c>
+      <c r="L13" s="278">
+        <f>Data!H48</f>
+        <v>-752</v>
+      </c>
+      <c r="M13" s="278">
+        <f>Data!I48</f>
+        <v>-1825</v>
+      </c>
+      <c r="N13" s="278">
+        <f>Data!J48</f>
+        <v>-1240</v>
+      </c>
+      <c r="O13" s="278">
+        <f>Data!K48</f>
+        <v>-23</v>
+      </c>
+      <c r="P13" s="278">
+        <f>Data!L48</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="278" t="str">
+        <f>Data!M48</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
-      <c r="B14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="274">
-        <f>-SUM(C8+C11,C12)*C41</f>
-        <v>-52872.613354906651</v>
-      </c>
-      <c r="E14" s="242"/>
-      <c r="G14" s="274">
-        <f>Data!C46</f>
-        <v>-32312</v>
-      </c>
-      <c r="H14" s="274">
-        <f>Data!D46</f>
-        <v>-56313</v>
-      </c>
-      <c r="I14" s="274">
-        <f>Data!E46</f>
-        <v>-32989</v>
-      </c>
-      <c r="J14" s="274">
-        <f>Data!F46</f>
-        <v>-27939</v>
-      </c>
-      <c r="K14" s="274">
-        <f>Data!G46</f>
-        <v>-29996</v>
-      </c>
-      <c r="L14" s="274">
-        <f>Data!H46</f>
-        <v>-39872</v>
-      </c>
-      <c r="M14" s="274">
-        <f>Data!I46</f>
-        <v>-129810</v>
-      </c>
-      <c r="N14" s="274">
-        <f>Data!J46</f>
-        <v>-121949</v>
-      </c>
-      <c r="O14" s="274">
-        <f>Data!K46</f>
-        <v>-108832</v>
-      </c>
-      <c r="P14" s="274">
-        <f>Data!L46</f>
-        <v>-110223</v>
-      </c>
-      <c r="Q14" s="274" t="str">
-        <f>Data!M46</f>
+      <c r="B14" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="277">
+        <f>SUM(C11:C13)</f>
+        <v>230211.62257446788</v>
+      </c>
+      <c r="D14" s="58"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="275">
+        <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
+        <v>289000.65016124537</v>
+      </c>
+      <c r="H14" s="275">
+        <f t="shared" si="8"/>
+        <v>347183.42079450103</v>
+      </c>
+      <c r="I14" s="275">
+        <f t="shared" si="8"/>
+        <v>108914.03131299623</v>
+      </c>
+      <c r="J14" s="275">
+        <f t="shared" si="8"/>
+        <v>-23876.118160315134</v>
+      </c>
+      <c r="K14" s="275">
+        <f t="shared" si="8"/>
+        <v>-118847</v>
+      </c>
+      <c r="L14" s="275">
+        <f t="shared" si="8"/>
+        <v>208614</v>
+      </c>
+      <c r="M14" s="275">
+        <f t="shared" si="8"/>
+        <v>557795</v>
+      </c>
+      <c r="N14" s="275">
+        <f t="shared" si="8"/>
+        <v>460100</v>
+      </c>
+      <c r="O14" s="275">
+        <f t="shared" si="8"/>
+        <v>517356</v>
+      </c>
+      <c r="P14" s="275">
+        <f t="shared" si="8"/>
+        <v>504410</v>
+      </c>
+      <c r="Q14" s="275" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
-      <c r="B15" s="38" t="s">
-        <v>208</v>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C15" s="274">
-        <f>-C4*C81</f>
-        <v>-2604.2914835892152</v>
-      </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="249"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="278">
-        <f>Data!C48</f>
-        <v>-2367</v>
-      </c>
-      <c r="H15" s="278">
-        <f>Data!D48</f>
-        <v>-2761</v>
-      </c>
-      <c r="I15" s="278">
-        <f>Data!E48</f>
-        <v>-834</v>
-      </c>
-      <c r="J15" s="278">
-        <f>Data!F48</f>
-        <v>-1636</v>
-      </c>
-      <c r="K15" s="278">
-        <f>Data!G48</f>
-        <v>-1420</v>
-      </c>
-      <c r="L15" s="278">
-        <f>Data!H48</f>
-        <v>-752</v>
-      </c>
-      <c r="M15" s="278">
-        <f>Data!I48</f>
-        <v>-1825</v>
-      </c>
-      <c r="N15" s="278">
-        <f>Data!J48</f>
-        <v>-1240</v>
-      </c>
-      <c r="O15" s="278">
-        <f>Data!K48</f>
-        <v>-23</v>
-      </c>
-      <c r="P15" s="278">
-        <f>Data!L48</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="278" t="str">
-        <f>Data!M48</f>
+        <f>BS!$G$39*BS!D58</f>
+        <v>378473</v>
+      </c>
+      <c r="E15" s="242"/>
+      <c r="G15" s="274">
+        <f>IF(Data!C61="","",-Data!C61)</f>
+        <v>378473</v>
+      </c>
+      <c r="H15" s="274">
+        <f>IF(Data!D61="","",-Data!D61)</f>
+        <v>394190</v>
+      </c>
+      <c r="I15" s="274">
+        <f>IF(Data!E61="","",-Data!E61)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="274">
+        <f>IF(Data!F61="","",-Data!F61)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="274">
+        <f>IF(Data!G61="","",-Data!G61)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="274">
+        <f>IF(Data!H61="","",-Data!H61)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="274">
+        <f>IF(Data!I61="","",-Data!I61)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="274">
+        <f>IF(Data!J61="","",-Data!J61)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="274">
+        <f>IF(Data!K61="","",-Data!K61)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="274">
+        <f>IF(Data!L61="","",-Data!L61)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="274" t="str">
+        <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
-      <c r="B16" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="277">
-        <f>SUM(C13:C15)</f>
-        <v>264963.17610033229</v>
-      </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="250"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="275">
-        <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>362404.65016124537</v>
-      </c>
-      <c r="H16" s="275">
-        <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>425015.42079450103</v>
-      </c>
-      <c r="I16" s="275">
-        <f t="shared" si="8"/>
-        <v>108914.03131299623</v>
-      </c>
-      <c r="J16" s="275">
-        <f t="shared" si="8"/>
-        <v>-23876.118160315134</v>
-      </c>
-      <c r="K16" s="275">
-        <f t="shared" si="8"/>
-        <v>-118847</v>
-      </c>
-      <c r="L16" s="275">
-        <f t="shared" si="8"/>
-        <v>208614</v>
-      </c>
-      <c r="M16" s="275">
-        <f t="shared" si="8"/>
-        <v>557795</v>
-      </c>
-      <c r="N16" s="275">
-        <f t="shared" si="8"/>
-        <v>460100</v>
-      </c>
-      <c r="O16" s="275">
-        <f t="shared" si="8"/>
-        <v>517356</v>
-      </c>
-      <c r="P16" s="275">
-        <f t="shared" si="8"/>
-        <v>504410</v>
-      </c>
-      <c r="Q16" s="275" t="str">
-        <f t="shared" si="8"/>
+      <c r="B16" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C16" s="274">
+        <f>-C4*C82</f>
+        <v>-378473</v>
+      </c>
+      <c r="E16" s="242"/>
+      <c r="G16" s="274">
+        <f>Data!C62</f>
+        <v>-305069</v>
+      </c>
+      <c r="H16" s="274">
+        <f>Data!D62</f>
+        <v>-316358</v>
+      </c>
+      <c r="I16" s="274">
+        <f>Data!E62</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="274">
+        <f>Data!F62</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="274">
+        <f>Data!G62</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="274">
+        <f>Data!H62</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="274">
+        <f>Data!I62</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="274">
+        <f>Data!J62</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="274">
+        <f>Data!K62</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="274">
+        <f>Data!L62</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="274" t="str">
+        <f>Data!M62</f>
         <v/>
       </c>
     </row>
@@ -11675,19 +11672,19 @@
         <v>63</v>
       </c>
       <c r="C19" s="275">
-        <f>C16+C17</f>
-        <v>264963.17610033229</v>
+        <f>C14+C17</f>
+        <v>230211.62257446788</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="239"/>
       <c r="F19" s="26"/>
       <c r="G19" s="279">
-        <f>IF(G$4="","",G16+G17)</f>
-        <v>362404.65016124537</v>
+        <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
+        <v>289000.65016124537</v>
       </c>
       <c r="H19" s="279">
-        <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>425015.42079450103</v>
+        <f t="shared" si="9"/>
+        <v>347183.42079450103</v>
       </c>
       <c r="I19" s="279">
         <f t="shared" si="9"/>
@@ -12413,7 +12410,7 @@
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
-        <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
+        <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
         <v>9.9827097514172861E-2</v>
       </c>
       <c r="H41" s="6">
@@ -13343,54 +13340,54 @@
         <v>43</v>
       </c>
       <c r="C71" s="74">
-        <f>ABS(C5/C$4)</f>
+        <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
         <v>0.89099809462634716</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="239"/>
       <c r="F71" s="26"/>
       <c r="G71" s="6">
-        <f t="shared" ref="G71:Q71" si="22">IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G71:Q71" si="23">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.89581909726262465</v>
       </c>
       <c r="H71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.88617709199006978</v>
       </c>
       <c r="I71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.9124320604423406</v>
       </c>
       <c r="J71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.92705566423612551</v>
       </c>
       <c r="K71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.94412068055204934</v>
       </c>
       <c r="L71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.90824524679279939</v>
       </c>
       <c r="M71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.86611329588599228</v>
       </c>
       <c r="N71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.87634286687980478</v>
       </c>
       <c r="O71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.86614503736544779</v>
       </c>
       <c r="P71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.86194691388174405</v>
       </c>
       <c r="Q71" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -13400,54 +13397,54 @@
         <v>45</v>
       </c>
       <c r="C72" s="75">
-        <f>ABS(C6/C$4)</f>
+        <f t="shared" si="22"/>
         <v>0.10900190537365288</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="239"/>
       <c r="F72" s="26"/>
       <c r="G72" s="62">
-        <f t="shared" ref="G72:Q72" si="23">IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G72:Q72" si="24">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.10418090273737537</v>
       </c>
       <c r="H72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.11382290800993022</v>
       </c>
       <c r="I72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.7567939557659458E-2</v>
       </c>
       <c r="J72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.2944335763874504E-2</v>
       </c>
       <c r="K72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.5879319447950666E-2</v>
       </c>
       <c r="L72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.1754753207200668E-2</v>
       </c>
       <c r="M72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.13388670411400769</v>
       </c>
       <c r="N72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.12365713312019522</v>
       </c>
       <c r="O72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.13385496263455221</v>
       </c>
       <c r="P72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.13805308611825601</v>
       </c>
       <c r="Q72" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -13457,54 +13454,54 @@
         <v>42</v>
       </c>
       <c r="C73" s="74">
-        <f>ABS(C7/C$4)</f>
+        <f t="shared" si="22"/>
         <v>6.0317700693294389E-2</v>
       </c>
       <c r="D73" s="26"/>
       <c r="E73" s="239"/>
       <c r="F73" s="26"/>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="25">IF(G$4="","",ABS(G7/G$4))</f>
         <v>5.7711800345388718E-2</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5.7897480615717818E-2</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.0577808396863227E-2</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.1107749848743197E-2</v>
       </c>
       <c r="K73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.8901017313164309E-2</v>
       </c>
       <c r="L73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.0455624237655277E-2</v>
       </c>
       <c r="M73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5.2718880163524738E-2</v>
       </c>
       <c r="N73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5.444372575690317E-2</v>
       </c>
       <c r="O73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5.4540178653982606E-2</v>
       </c>
       <c r="P73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5.6829522664729883E-2</v>
       </c>
       <c r="Q73" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -13514,513 +13511,513 @@
         <v>127</v>
       </c>
       <c r="C74" s="75">
-        <f>ABS(C8/C$4)</f>
+        <f t="shared" si="22"/>
         <v>4.8684204680358494E-2</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="239"/>
       <c r="F74" s="26"/>
       <c r="G74" s="62">
-        <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="26">IF(G$4="","",ABS(G8/G$4))</f>
         <v>4.6469102391986664E-2</v>
       </c>
       <c r="H74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.5925427394212406E-2</v>
       </c>
       <c r="I74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.6990131160796228E-2</v>
       </c>
       <c r="J74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.1836585915131315E-2</v>
       </c>
       <c r="K74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.3021697865213639E-2</v>
       </c>
       <c r="L74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3.1299128969545391E-2</v>
       </c>
       <c r="M74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.1167823950482956E-2</v>
       </c>
       <c r="N74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6.921340736329204E-2</v>
       </c>
       <c r="O74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.9314783980569611E-2</v>
       </c>
       <c r="P74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.1223563453526118E-2</v>
       </c>
       <c r="Q74" s="62" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
-      <c r="B75" s="2" t="s">
-        <v>62</v>
+      <c r="B75" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="C75" s="74">
-        <f>ABS(C9/C$4)</f>
-        <v>4.6165711414505782E-2</v>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="D75" s="26"/>
       <c r="E75" s="239"/>
       <c r="F75" s="26"/>
       <c r="G75" s="6">
-        <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",G9/G$4)</f>
-        <v>4.4171218221734795E-2</v>
+        <f t="shared" ref="G75:Q75" si="27">IF(G$4="","",G9/G$4)</f>
+        <v>0</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="26"/>
-        <v>4.5353772426208791E-2</v>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="K75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="L75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="O75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="Q75" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="85">
-        <f>MAX(AVERAGE(G76:J76),C75)</f>
-        <v>4.6165711414505782E-2</v>
+        <v>65</v>
+      </c>
+      <c r="C76" s="74">
+        <f t="shared" si="22"/>
+        <v>9.5972835465845709E-3</v>
       </c>
       <c r="D76" s="26"/>
-      <c r="E76" s="240" t="s">
-        <v>556</v>
+      <c r="E76" s="239" t="s">
+        <v>555</v>
       </c>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
-        <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",-G10/G$4)</f>
-        <v>3.5604308290647979E-2</v>
+        <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
+        <v>8.6927630990723849E-3</v>
       </c>
       <c r="H76" s="6">
-        <f t="shared" si="27"/>
-        <v>3.639876388850697E-2</v>
+        <f t="shared" si="28"/>
+        <v>9.1832304608240791E-3</v>
       </c>
       <c r="I76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>9.2014660795733134E-3</v>
       </c>
       <c r="J76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>1.1077620766099928E-2</v>
       </c>
       <c r="K76" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L76" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M76" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N76" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="O76" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="P76" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Q76" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
-      <c r="B77" s="30" t="s">
-        <v>128</v>
+      <c r="B77" s="67" t="s">
+        <v>137</v>
       </c>
       <c r="C77" s="75">
-        <f>ABS(C11/C$4)</f>
-        <v>0</v>
+        <f>C11/C4</f>
+        <v>3.9086921133773919E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="239"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
-        <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G11/G$4)</f>
-        <v>0</v>
+        <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
+        <v>3.7776339292914275E-2</v>
       </c>
       <c r="H77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>4.6742196933388325E-2</v>
       </c>
       <c r="I77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>1.7788665081222912E-2</v>
       </c>
       <c r="J77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>7.5896514903138587E-4</v>
       </c>
       <c r="K77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>-1.3021697865213639E-2</v>
       </c>
       <c r="L77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>3.1299128969545391E-2</v>
       </c>
       <c r="M77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>8.1167823950482956E-2</v>
       </c>
       <c r="N77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>6.921340736329204E-2</v>
       </c>
       <c r="O77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>7.9314783980569611E-2</v>
       </c>
       <c r="P77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>8.1223563453526118E-2</v>
       </c>
       <c r="Q77" s="62" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>9.5972835465845709E-3</v>
+        <v>6.4493419870726969E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="239"/>
       <c r="F78" s="26"/>
       <c r="G78" s="6">
-        <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>8.6927630990723849E-3</v>
+        <f t="shared" ref="G78:Q78" si="30">IF(G$4="","",ABS(G12/G$4))</f>
+        <v>3.7711023063222333E-3</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="29"/>
-        <v>9.1832304608240791E-3</v>
+        <f t="shared" si="30"/>
+        <v>6.4791267831175213E-3</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="29"/>
-        <v>9.2014660795733134E-3</v>
+        <f t="shared" si="30"/>
+        <v>4.1112685822759691E-3</v>
       </c>
       <c r="J78" s="6">
-        <f t="shared" si="29"/>
-        <v>1.1077620766099928E-2</v>
+        <f t="shared" si="30"/>
+        <v>3.7208575112272304E-3</v>
       </c>
       <c r="K78" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>4.4675097981831191E-3</v>
       </c>
       <c r="L78" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>5.0070971130955705E-3</v>
       </c>
       <c r="M78" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1.5282762901254939E-2</v>
       </c>
       <c r="N78" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1.4470538300132698E-2</v>
       </c>
       <c r="O78" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1.3784469723740643E-2</v>
       </c>
       <c r="P78" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1.4565935825993739E-2</v>
       </c>
       <c r="Q78" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
-      <c r="B79" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C79" s="75">
+      <c r="B79" s="38" t="str">
+        <f>B13</f>
+        <v>NCI’s Share of Profits</v>
+      </c>
+      <c r="C79" s="238">
         <f>MIN(BS!C62,MAX(G81:K81))</f>
-        <v>3.176685498586024E-4</v>
+        <v>4.556624013737947E-3</v>
       </c>
       <c r="D79" s="26"/>
       <c r="E79" s="239"/>
       <c r="F79" s="26"/>
-      <c r="G79" s="62">
-        <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G13/G$4)</f>
-        <v>4.6343249224001092E-2</v>
-      </c>
-      <c r="H79" s="62">
-        <f t="shared" si="30"/>
-        <v>5.5697205471090153E-2</v>
-      </c>
-      <c r="I79" s="62">
-        <f t="shared" si="30"/>
-        <v>1.7788665081222912E-2</v>
-      </c>
-      <c r="J79" s="62">
-        <f t="shared" si="30"/>
-        <v>7.5896514903138587E-4</v>
-      </c>
-      <c r="K79" s="62">
-        <f t="shared" si="30"/>
-        <v>-1.3021697865213639E-2</v>
-      </c>
-      <c r="L79" s="62">
-        <f t="shared" si="30"/>
-        <v>3.1299128969545391E-2</v>
-      </c>
-      <c r="M79" s="62">
-        <f t="shared" si="30"/>
-        <v>8.1167823950482956E-2</v>
-      </c>
-      <c r="N79" s="62">
-        <f t="shared" si="30"/>
-        <v>6.921340736329204E-2</v>
-      </c>
-      <c r="O79" s="62">
-        <f t="shared" si="30"/>
-        <v>7.9314783980569611E-2</v>
-      </c>
-      <c r="P79" s="62">
-        <f t="shared" si="30"/>
-        <v>8.1223563453526118E-2</v>
-      </c>
-      <c r="Q79" s="62" t="str">
-        <f t="shared" si="30"/>
+      <c r="G79" s="6">
+        <f t="shared" ref="G79:Q79" si="31">IF(G$4="","",-G13/G$4)</f>
+        <v>2.7625028345706632E-4</v>
+      </c>
+      <c r="H79" s="6">
+        <f t="shared" si="31"/>
+        <v>3.176685498586024E-4</v>
+      </c>
+      <c r="I79" s="6">
+        <f t="shared" si="31"/>
+        <v>1.0393761549662489E-4</v>
+      </c>
+      <c r="J79" s="6">
+        <f t="shared" si="31"/>
+        <v>2.1787905395210096E-4</v>
+      </c>
+      <c r="K79" s="6">
+        <f t="shared" si="31"/>
+        <v>2.1149032915788871E-4</v>
+      </c>
+      <c r="L79" s="6">
+        <f t="shared" si="31"/>
+        <v>9.4435619709266379E-5</v>
+      </c>
+      <c r="M79" s="6">
+        <f t="shared" si="31"/>
+        <v>2.1486050608420201E-4</v>
+      </c>
+      <c r="N79" s="6">
+        <f t="shared" si="31"/>
+        <v>1.4713911136757617E-4</v>
+      </c>
+      <c r="O79" s="6">
+        <f t="shared" si="31"/>
+        <v>2.9131395512903816E-6</v>
+      </c>
+      <c r="P79" s="6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Q79" s="6" t="str">
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
-      <c r="B80" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C80" s="74">
+      <c r="B80" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>6.4493419870726969E-3</v>
+        <v>2.8080955132963274E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="239"/>
       <c r="F80" s="26"/>
-      <c r="G80" s="6">
-        <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>3.7711023063222333E-3</v>
-      </c>
-      <c r="H80" s="6">
-        <f t="shared" si="31"/>
-        <v>6.4791267831175213E-3</v>
-      </c>
-      <c r="I80" s="6">
-        <f t="shared" si="31"/>
-        <v>4.1112685822759691E-3</v>
-      </c>
-      <c r="J80" s="6">
-        <f t="shared" si="31"/>
-        <v>3.7208575112272304E-3</v>
-      </c>
-      <c r="K80" s="6">
-        <f t="shared" si="31"/>
-        <v>4.4675097981831191E-3</v>
-      </c>
-      <c r="L80" s="6">
-        <f t="shared" si="31"/>
-        <v>5.0070971130955705E-3</v>
-      </c>
-      <c r="M80" s="6">
-        <f t="shared" si="31"/>
-        <v>1.5282762901254939E-2</v>
-      </c>
-      <c r="N80" s="6">
-        <f t="shared" si="31"/>
-        <v>1.4470538300132698E-2</v>
-      </c>
-      <c r="O80" s="6">
-        <f t="shared" si="31"/>
-        <v>1.3784469723740643E-2</v>
-      </c>
-      <c r="P80" s="6">
-        <f t="shared" si="31"/>
-        <v>1.4565935825993739E-2</v>
-      </c>
-      <c r="Q80" s="6" t="str">
-        <f t="shared" si="31"/>
+      <c r="G80" s="62">
+        <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
+        <v>3.3728986703134976E-2</v>
+      </c>
+      <c r="H80" s="62">
+        <f t="shared" si="32"/>
+        <v>3.9945401600412205E-2</v>
+      </c>
+      <c r="I80" s="62">
+        <f t="shared" si="32"/>
+        <v>1.3573458883450318E-2</v>
+      </c>
+      <c r="J80" s="62">
+        <f t="shared" si="32"/>
+        <v>3.1797714161479456E-3</v>
+      </c>
+      <c r="K80" s="62">
+        <f t="shared" si="32"/>
+        <v>1.7700697992554647E-2</v>
+      </c>
+      <c r="L80" s="62">
+        <f t="shared" si="32"/>
+        <v>2.6197596236740554E-2</v>
+      </c>
+      <c r="M80" s="62">
+        <f t="shared" si="32"/>
+        <v>6.567020054314382E-2</v>
+      </c>
+      <c r="N80" s="62">
+        <f t="shared" si="32"/>
+        <v>5.4595729951791766E-2</v>
+      </c>
+      <c r="O80" s="62">
+        <f t="shared" si="32"/>
+        <v>6.5527401117277673E-2</v>
+      </c>
+      <c r="P80" s="62">
+        <f t="shared" si="32"/>
+        <v>6.6657627627532384E-2</v>
+      </c>
+      <c r="Q80" s="62" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
-      <c r="B81" s="38" t="str">
-        <f>B15</f>
-        <v>NCI’s Share of Profits</v>
-      </c>
-      <c r="C81" s="238">
-        <f>MIN(BS!C62,MAX(G81:K81))</f>
-        <v>3.176685498586024E-4</v>
+      <c r="B81" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C81" s="74">
+        <f>ABS(C15/C$4)</f>
+        <v>4.6165711414505782E-2</v>
       </c>
       <c r="D81" s="26"/>
       <c r="E81" s="239"/>
       <c r="F81" s="26"/>
       <c r="G81" s="6">
-        <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",-G15/G$4)</f>
-        <v>2.7625028345706632E-4</v>
+        <f t="shared" ref="G81:Q81" si="33">IF(G$4="","",G15/G$4)</f>
+        <v>4.4171218221734795E-2</v>
       </c>
       <c r="H81" s="6">
-        <f t="shared" si="32"/>
-        <v>3.176685498586024E-4</v>
+        <f t="shared" si="33"/>
+        <v>4.5353772426208791E-2</v>
       </c>
       <c r="I81" s="6">
-        <f t="shared" si="32"/>
-        <v>1.0393761549662489E-4</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="J81" s="6">
-        <f t="shared" si="32"/>
-        <v>2.1787905395210096E-4</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="K81" s="6">
-        <f t="shared" si="32"/>
-        <v>2.1149032915788871E-4</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="L81" s="6">
-        <f t="shared" si="32"/>
-        <v>9.4435619709266379E-5</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="M81" s="6">
-        <f t="shared" si="32"/>
-        <v>2.1486050608420201E-4</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="N81" s="6">
-        <f t="shared" si="32"/>
-        <v>1.4713911136757617E-4</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="O81" s="6">
-        <f t="shared" si="32"/>
-        <v>2.9131395512903816E-6</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="P81" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Q81" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
-      <c r="B82" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="C82" s="75">
+      <c r="B82" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" s="85">
         <f>MAX(AVERAGE(G76:J76),C81)</f>
-        <v>1.8000768044788736E-2</v>
+        <v>4.6165711414505782E-2</v>
       </c>
       <c r="D82" s="26"/>
-      <c r="E82" s="239"/>
+      <c r="E82" s="240"/>
       <c r="F82" s="26"/>
-      <c r="G82" s="62">
-        <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>4.2295896634221793E-2</v>
-      </c>
-      <c r="H82" s="62">
-        <f t="shared" si="33"/>
-        <v>4.8900410138114025E-2</v>
-      </c>
-      <c r="I82" s="62">
-        <f t="shared" si="33"/>
-        <v>1.3573458883450318E-2</v>
-      </c>
-      <c r="J82" s="62">
-        <f t="shared" si="33"/>
-        <v>3.1797714161479456E-3</v>
-      </c>
-      <c r="K82" s="62">
-        <f t="shared" si="33"/>
-        <v>1.7700697992554647E-2</v>
-      </c>
-      <c r="L82" s="62">
-        <f t="shared" si="33"/>
-        <v>2.6197596236740554E-2</v>
-      </c>
-      <c r="M82" s="62">
-        <f t="shared" si="33"/>
-        <v>6.567020054314382E-2</v>
-      </c>
-      <c r="N82" s="62">
-        <f t="shared" si="33"/>
-        <v>5.4595729951791766E-2</v>
-      </c>
-      <c r="O82" s="62">
-        <f t="shared" si="33"/>
-        <v>6.5527401117277673E-2</v>
-      </c>
-      <c r="P82" s="62">
-        <f t="shared" si="33"/>
-        <v>6.6657627627532384E-2</v>
-      </c>
-      <c r="Q82" s="62" t="str">
-        <f t="shared" si="33"/>
+      <c r="G82" s="6">
+        <f t="shared" ref="G82:Q82" si="34">IF(G$4="","",-G16/G$4)</f>
+        <v>3.5604308290647979E-2</v>
+      </c>
+      <c r="H82" s="6">
+        <f t="shared" si="34"/>
+        <v>3.639876388850697E-2</v>
+      </c>
+      <c r="I82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="L82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="O82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Q82" s="6" t="str">
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -14081,53 +14078,53 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>3.2319910596842617E-2</v>
+        <v>2.8080955132963274E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="239"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
-        <f t="shared" ref="G85:Q85" si="34">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>4.2295896634221793E-2</v>
+        <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
+        <v>3.3728986703134976E-2</v>
       </c>
       <c r="H85" s="62">
-        <f t="shared" si="34"/>
-        <v>4.8900410138114025E-2</v>
+        <f t="shared" si="35"/>
+        <v>3.9945401600412205E-2</v>
       </c>
       <c r="I85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.3573458883450318E-2</v>
       </c>
       <c r="J85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.1797714161479456E-3</v>
       </c>
       <c r="K85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.7700697992554647E-2</v>
       </c>
       <c r="L85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.6197596236740554E-2</v>
       </c>
       <c r="M85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.567020054314382E-2</v>
       </c>
       <c r="N85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.4595729951791766E-2</v>
       </c>
       <c r="O85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.5527401117277673E-2</v>
       </c>
       <c r="P85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.6657627627532384E-2</v>
       </c>
       <c r="Q85" s="62" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -14210,47 +14207,47 @@
       </c>
       <c r="E89" s="242"/>
       <c r="G89" s="71">
-        <f t="shared" ref="G89:Q89" si="35">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
+        <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
         <v>232001.61320000002</v>
       </c>
       <c r="H89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>330602.29880999995</v>
       </c>
       <c r="I89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>220401.53253999999</v>
       </c>
       <c r="J89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>220401.53253999999</v>
       </c>
       <c r="K89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="P89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Q89" s="71" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -14261,51 +14258,51 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.87559945730779254</v>
+        <v>1.0077754137932506</v>
       </c>
       <c r="E90" s="242"/>
       <c r="G90" s="153">
-        <f t="shared" ref="G90:Q90" si="36">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.64017283745331399</v>
+        <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
+        <v>0.802771942106555</v>
       </c>
       <c r="H90" s="153">
-        <f t="shared" si="36"/>
-        <v>0.77785953787744866</v>
+        <f t="shared" si="37"/>
+        <v>0.95224103171010732</v>
       </c>
       <c r="I90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.0236284515684848</v>
       </c>
       <c r="J90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-9.2310454764934455</v>
       </c>
       <c r="K90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="M90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="P90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Q90" s="153" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -14337,51 +14334,51 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1919504643962855E-2</v>
+        <v>6.2208398133748059E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
-        <f t="shared" ref="G92:Q92" si="37">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1919504643962855E-2</v>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>6.2208398133748059E-2</v>
       </c>
       <c r="H92" s="22">
-        <f t="shared" si="37"/>
-        <v>8.8235294117647051E-2</v>
+        <f t="shared" si="38"/>
+        <v>8.8646967340590979E-2</v>
       </c>
       <c r="I92" s="22">
-        <f t="shared" si="37"/>
-        <v>5.8823529411764705E-2</v>
+        <f t="shared" si="38"/>
+        <v>5.9097978227060657E-2</v>
       </c>
       <c r="J92" s="22">
-        <f t="shared" si="37"/>
-        <v>5.8823529411764705E-2</v>
+        <f t="shared" si="38"/>
+        <v>5.9097978227060657E-2</v>
       </c>
       <c r="K92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="N92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="O92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="P92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="Q92" s="22" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -14423,47 +14420,47 @@
       <c r="E95" s="239"/>
       <c r="F95" s="26"/>
       <c r="G95" s="6">
-        <f t="shared" ref="G95:Q95" si="38">IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
         <v>-1.4167027845414459E-2</v>
       </c>
       <c r="H95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>8.3175640612140223E-2</v>
       </c>
       <c r="I95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.862537627752574E-2</v>
       </c>
       <c r="J95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.11833003065865078</v>
       </c>
       <c r="K95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-0.15682868110233994</v>
       </c>
       <c r="L95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-6.2490382784881726E-2</v>
       </c>
       <c r="M95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>7.8890295807758637E-3</v>
       </c>
       <c r="N95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.7399536582826602E-2</v>
       </c>
       <c r="O95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>4.335646481593658E-2</v>
       </c>
       <c r="P95" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q95" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -14473,54 +14470,54 @@
         <v>137</v>
       </c>
       <c r="C96" s="74">
-        <f>C13/G13-1</f>
-        <v>-0.19301617981826813</v>
+        <f>C11/G11-1</f>
+        <v>-1.0008566250004791E-2</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="239"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="39">IF(H5="","",G13/H13-1)</f>
-        <v>-0.17973078298315082</v>
+        <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
+        <v>-0.20326464553376444</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="39"/>
-        <v>2.3914774347028516</v>
+        <f t="shared" si="40"/>
+        <v>1.8461949716724368</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>24.04649777418253</v>
       </c>
       <c r="J96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-1.0651814784193805</v>
       </c>
       <c r="K96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-1.3507932177276338</v>
       </c>
       <c r="L96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.63848686596173643</v>
       </c>
       <c r="M96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.18196982970705777</v>
       </c>
       <c r="N96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-6.8542392260755536E-2</v>
       </c>
       <c r="O96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.8837257355202253E-2</v>
       </c>
       <c r="P96" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -14573,47 +14570,47 @@
       <c r="E100" s="243"/>
       <c r="F100" s="25"/>
       <c r="G100" s="278">
-        <f t="shared" ref="G100:Q100" si="40">IF(G$4="","",G104+G103)</f>
+        <f t="shared" ref="G100:Q100" si="41">IF(G$4="","",G104+G103)</f>
         <v>5980230</v>
       </c>
       <c r="H100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6513924</v>
       </c>
       <c r="I100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7175340</v>
       </c>
       <c r="J100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6871846</v>
       </c>
       <c r="K100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7154673</v>
       </c>
       <c r="L100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6220758</v>
       </c>
       <c r="M100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4494090</v>
       </c>
       <c r="N100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4616329</v>
       </c>
       <c r="O100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4436810</v>
       </c>
       <c r="P100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4445187</v>
       </c>
       <c r="Q100" s="278" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -14885,47 +14882,47 @@
       <c r="E107" s="243"/>
       <c r="F107" s="25"/>
       <c r="G107" s="91">
-        <f t="shared" ref="G107:Q107" si="41">IF(G$4="","",G101/G$4)</f>
+        <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
         <v>1.0437288909829083E-2</v>
       </c>
       <c r="H107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>8.7290393120870863E-3</v>
       </c>
       <c r="I107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.3567697285807504E-3</v>
       </c>
       <c r="J107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4.9709985133350367E-3</v>
       </c>
       <c r="K107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7.4739490829585711E-3</v>
       </c>
       <c r="L107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="O107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="P107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="Q107" s="91" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
@@ -14942,47 +14939,47 @@
       <c r="E108" s="243"/>
       <c r="F108" s="25"/>
       <c r="G108" s="91">
-        <f t="shared" ref="G108:Q108" si="42">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
         <v>2.6876690019755338E-2</v>
       </c>
       <c r="H108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.0862863027787426E-2</v>
       </c>
       <c r="I108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.7829054775871118E-2</v>
       </c>
       <c r="J108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.1286686351249003E-2</v>
       </c>
       <c r="K108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.8816815864157674E-2</v>
       </c>
       <c r="L108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q108" s="91" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -15085,11 +15082,11 @@
       <c r="E113" s="242"/>
       <c r="G113" s="258">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>4.1693697896197204</v>
+        <v>5.2283584800136307</v>
       </c>
       <c r="H113" s="258">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>3.9131615433882119</v>
+        <v>4.7904188402603074</v>
       </c>
       <c r="I113" s="258">
         <f>IF(I$4="","",Data!E$22/I19)</f>
@@ -15192,52 +15189,52 @@
         <v>190</v>
       </c>
       <c r="C116" s="22">
-        <f>C79</f>
-        <v>3.176685498586024E-4</v>
+        <f>C77</f>
+        <v>3.9086921133773919E-2</v>
       </c>
       <c r="E116" s="242"/>
       <c r="G116" s="22">
-        <f>IF(G4="","",G79)</f>
-        <v>4.6343249224001092E-2</v>
+        <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
+        <v>3.7776339292914275E-2</v>
       </c>
       <c r="H116" s="22">
-        <f t="shared" ref="H116:Q116" si="43">IF(H4="","",H79)</f>
-        <v>5.5697205471090153E-2</v>
+        <f t="shared" si="44"/>
+        <v>4.6742196933388325E-2</v>
       </c>
       <c r="I116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.7788665081222912E-2</v>
       </c>
       <c r="J116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>7.5896514903138587E-4</v>
       </c>
       <c r="K116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-1.3021697865213639E-2</v>
       </c>
       <c r="L116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>3.1299128969545391E-2</v>
       </c>
       <c r="M116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>8.1167823950482956E-2</v>
       </c>
       <c r="N116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>6.921340736329204E-2</v>
       </c>
       <c r="O116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>7.9314783980569611E-2</v>
       </c>
       <c r="P116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>8.1223563453526118E-2</v>
       </c>
       <c r="Q116" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
@@ -15251,47 +15248,47 @@
       </c>
       <c r="E117" s="242"/>
       <c r="G117" s="40">
-        <f>IF(G4="","",G4/G100)</f>
+        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",G4/G100)</f>
         <v>1.4327738230803833</v>
       </c>
       <c r="H117" s="40">
-        <f t="shared" ref="H117:Q117" si="44">IF(H4="","",H4/H100)</f>
+        <f t="shared" si="45"/>
         <v>1.3342877503636825</v>
       </c>
       <c r="I117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.1182806668394807</v>
       </c>
       <c r="J117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.0926835380187507</v>
       </c>
       <c r="K117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.93844330831052658</v>
       </c>
       <c r="L117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.2800846777836399</v>
       </c>
       <c r="M117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.8900117710148217</v>
       </c>
       <c r="N117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.8255629094026877</v>
       </c>
       <c r="O117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.7794906700985618</v>
       </c>
       <c r="P117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1.7023301831846445</v>
       </c>
       <c r="Q117" s="40" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -15307,47 +15304,47 @@
       <c r="E118" s="246"/>
       <c r="F118" s="11"/>
       <c r="G118" s="15">
-        <f t="shared" ref="G118:Q118" si="45">IF(G$4="","",G100/G104)</f>
+        <f t="shared" ref="G118:Q118" si="46">IF(G$4="","",G100/G104)</f>
         <v>2.1787997096988563</v>
       </c>
       <c r="H118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.2380673097835331</v>
       </c>
       <c r="I118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.5699061948100743</v>
       </c>
       <c r="J118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.4313276082163164</v>
       </c>
       <c r="K118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.3575155296694779</v>
       </c>
       <c r="L118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.3287276065094606</v>
       </c>
       <c r="M118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.3133893475560752</v>
       </c>
       <c r="N118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2918228627396111</v>
       </c>
       <c r="O118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2708844153165746</v>
       </c>
       <c r="P118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2549945694476872</v>
       </c>
       <c r="Q118" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -15357,54 +15354,54 @@
         <v>191</v>
       </c>
       <c r="C119" s="99">
-        <f>C13/C104</f>
+        <f>C11/C104</f>
         <v>0.1167471410506614</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="245"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
-        <f t="shared" ref="G119:Q119" si="46">IF(G$4="","",G13/G104)</f>
-        <v>0.14467098116585544</v>
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
+        <v>0.11792742550148552</v>
       </c>
       <c r="H119" s="99">
-        <f t="shared" si="46"/>
-        <v>0.16632443173918174</v>
+        <f t="shared" si="47"/>
+        <v>0.13958275424109118</v>
       </c>
       <c r="I119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.1122425000079234E-2</v>
       </c>
       <c r="J119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2.0163211970682122E-3</v>
       </c>
       <c r="K119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-2.880913499114944E-2</v>
       </c>
       <c r="L119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.3301718406535811E-2</v>
       </c>
       <c r="M119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.20148462044275589</v>
       </c>
       <c r="N119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.1632262487757101</v>
       </c>
       <c r="O119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.17937252228511194</v>
       </c>
       <c r="P119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.1735272503054068</v>
       </c>
       <c r="Q119" s="99" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -15478,54 +15475,54 @@
         <v>FCFE per share (HKD)</v>
       </c>
       <c r="C123" s="160">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.45682988569897115</v>
+        <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.39691383072584235</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
-        <f t="shared" ref="G123:Q123" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.62483125899444447</v>
+        <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.49827351831749306</v>
       </c>
       <c r="H123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.73278011291776834</v>
+        <f t="shared" si="48"/>
+        <v>0.59858794256780801</v>
       </c>
       <c r="I123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.18778150687961892</v>
       </c>
       <c r="J123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>-4.1165434724339464E-2</v>
       </c>
       <c r="K123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>-0.20490719587806727</v>
       </c>
       <c r="L123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.35967680935073776</v>
       </c>
       <c r="M123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.96170883004877317</v>
       </c>
       <c r="N123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.79327034610464509</v>
       </c>
       <c r="O123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.89198690106349654</v>
       </c>
       <c r="P123" s="160">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.869666366613006</v>
       </c>
       <c r="Q123" s="160" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -15536,53 +15533,53 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.0716700572596158E-2</v>
+        <v>6.1728434016460706E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
-        <f t="shared" ref="G124" si="48">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.6723105107499138E-2</v>
+        <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
+        <v>7.7491993517495042E-2</v>
       </c>
       <c r="H124" s="74">
-        <f t="shared" ref="H124" si="49">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.11343345401203844</v>
+        <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
+        <v>9.3092992623298301E-2</v>
       </c>
       <c r="I124" s="74">
-        <f t="shared" ref="I124" si="50">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.9068344718207264E-2</v>
+        <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
+        <v>2.9203966855306209E-2</v>
       </c>
       <c r="J124" s="74">
-        <f t="shared" ref="J124" si="51">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3723583164612173E-3</v>
+        <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
+        <v>-6.402089381701317E-3</v>
       </c>
       <c r="K124" s="74">
-        <f t="shared" ref="K124" si="52">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1719380166883478E-2</v>
+        <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
+        <v>-3.1867371054131767E-2</v>
       </c>
       <c r="L124" s="74">
-        <f t="shared" ref="L124" si="53">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.567752466729687E-2</v>
+        <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
+        <v>5.593729538891723E-2</v>
       </c>
       <c r="M124" s="74">
-        <f t="shared" ref="M124" si="54">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14887133592086271</v>
+        <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
+        <v>0.14956591447103781</v>
       </c>
       <c r="N124" s="74">
-        <f t="shared" ref="N124" si="55">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12279726719886147</v>
+        <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
+        <v>0.12337019379543469</v>
       </c>
       <c r="O124" s="74">
-        <f t="shared" ref="O124" si="56">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.138078467656888</v>
+        <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
+        <v>0.13872269067861534</v>
       </c>
       <c r="P124" s="74">
-        <f t="shared" ref="P124" si="57">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13462327656548082</v>
+        <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
+        <v>0.13525137894447994</v>
       </c>
       <c r="Q124" s="74" t="str">
-        <f t="shared" ref="Q124" si="58">IF(Q$4="","",Q123/Market_Price)</f>
+        <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -15593,43 +15590,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2749376849362146E-2</v>
+        <v>6.3042142215688865E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8932604628708167E-2</v>
+        <v>8.9347531244394207E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9674983151575334E-2</v>
+        <v>2.9813435639063243E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0984950130275693E-3</v>
+        <v>6.1269483334616013E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6228112776677907E-2</v>
+        <v>9.6677077533023209E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9853070023591633E-2</v>
+        <v>1.9945697099906987E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15802975414283388</v>
+        <v>0.15876706248253605</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1225824186874616</v>
+        <v>0.12315434288040465</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1344738167314635</v>
+        <v>0.13510122178619816</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13821298150750361</v>
+        <v>0.13885783212106892</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16320,7 +16317,7 @@
     <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q25">
+  <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
@@ -16339,13 +16336,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U102"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="9" width="20.73046875" customWidth="1"/>
-    <col min="10" max="11" width="11.19921875" customWidth="1"/>
-    <col min="12" max="12" width="20.73046875" customWidth="1"/>
-    <col min="13" max="13" width="5.73046875" customWidth="1"/>
+    <col min="2" max="9" width="20.6640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="13.9">
@@ -16372,10 +16369,10 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="2:15">
@@ -16384,14 +16381,14 @@
       </c>
       <c r="C4" s="283">
         <f>Normalized_FCF!C19</f>
-        <v>264963.17610033229</v>
+        <v>230211.62257446788</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E4" s="136" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F4" s="283">
         <f>-BS!G31</f>
@@ -16419,7 +16416,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="136" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F5" s="283">
         <f>BS!D66</f>
@@ -16438,20 +16435,20 @@
       </c>
       <c r="J5" s="313"/>
     </row>
-    <row r="6" spans="2:15" ht="13.35" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="137" t="s">
         <v>194</v>
       </c>
       <c r="C6" s="291">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3654664.4979356183</v>
+        <v>3175332.7251650742</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E6" s="188" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F6" s="292">
         <f>BS!H42</f>
@@ -16462,7 +16459,7 @@
         <v>HKD</v>
       </c>
       <c r="H6" s="316" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I6" s="313">
         <f>I7+I8</f>
@@ -16473,14 +16470,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="326" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C7" s="283">
         <f>F7</f>
         <v>-1686446.6667440513</v>
       </c>
       <c r="E7" s="141" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F7" s="291">
         <f>SUM(F4:F6)</f>
@@ -16491,10 +16488,10 @@
         <v>HKD</v>
       </c>
       <c r="H7" s="320" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I7" s="321">
-        <f>Normalized_FCF!C11</f>
+        <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
       <c r="J7" s="321"/>
@@ -16503,18 +16500,18 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="137" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C8" s="291">
         <f>C6+C7</f>
-        <v>1968217.831191567</v>
+        <v>1488886.058421023</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E8" s="141" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16525,11 +16522,11 @@
         <v>HKD</v>
       </c>
       <c r="H8" s="322" t="str">
-        <f>Normalized_FCF!B12</f>
+        <f>Normalized_FCF!B10</f>
         <v>Net Interest Income</v>
       </c>
       <c r="I8" s="321">
-        <f>Normalized_FCF!C12</f>
+        <f>Normalized_FCF!C10</f>
         <v>-78679.881332559497</v>
       </c>
       <c r="J8" s="321"/>
@@ -16550,12 +16547,13 @@
         <v>HKD</v>
       </c>
       <c r="F9" s="331"/>
-      <c r="H9" s="316" t="s">
-        <v>401</v>
-      </c>
-      <c r="I9" s="314">
-        <f>Normalized_FCF!C41</f>
-        <v>0.16500000000000001</v>
+      <c r="H9" s="316" t="str">
+        <f>Normalized_FCF!B79</f>
+        <v>NCI’s Share of Profits</v>
+      </c>
+      <c r="I9" s="145">
+        <f>Normalized_FCF!C79</f>
+        <v>4.556624013737947E-3</v>
       </c>
       <c r="J9" s="314"/>
       <c r="N9" s="312"/>
@@ -16563,40 +16561,45 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>1968217.831191567</v>
+        <v>1488886.058421023</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
+      <c r="H10" s="316" t="s">
+        <v>401</v>
+      </c>
+      <c r="I10" s="314">
+        <f>Normalized_FCF!C41</f>
+        <v>0.16500000000000001</v>
+      </c>
       <c r="N10" s="312"/>
       <c r="O10" s="312"/>
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="137" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E11" s="315" t="s">
-        <v>412</v>
-      </c>
+      <c r="E11" s="315"/>
       <c r="I11" s="315"/>
       <c r="J11" s="315"/>
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16624,12 +16627,12 @@
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="140" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C15" s="149">
         <f>Scenarios!C45</f>
@@ -16644,7 +16647,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I15" s="127">
         <f>Terminal_Growth</f>
@@ -16652,9 +16655,9 @@
       </c>
       <c r="J15" s="127"/>
     </row>
-    <row r="16" spans="2:15" ht="13.35" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C16" s="148">
         <f>Scenarios!C46</f>
@@ -16668,7 +16671,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.35" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="316" t="s">
         <v>398</v>
       </c>
@@ -16684,19 +16687,19 @@
         <v>0.86799999999999999</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="13.35" customHeight="1">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="316" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C18" s="314">
-        <f>Normalized_FCF!C75-Normalized_FCF!C76</f>
+        <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="316" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F18" s="145">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16707,7 +16710,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.7583423472162005</v>
+        <v>7.4805328351798659</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16737,23 +16740,23 @@
         <v>399</v>
       </c>
       <c r="G20" s="122" t="s">
-        <v>425</v>
+        <v>550</v>
       </c>
       <c r="H20" s="122" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="122" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J20" s="122" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="K20" s="122" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="L20" s="123" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -16789,12 +16792,12 @@
         <v>0</v>
       </c>
       <c r="I21" s="285">
-        <f>(G21+C21*H21)*(1-$I$9)</f>
-        <v>274297.67797634384</v>
+        <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
+        <v>236187.44060889343</v>
       </c>
       <c r="J21" s="307">
         <f>I21/C4-1</f>
-        <v>3.5229430796364314E-2</v>
+        <v>2.5957933694214397E-2</v>
       </c>
       <c r="K21" s="120">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16802,7 +16805,7 @@
       </c>
       <c r="L21" s="285">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>255755.41070055368</v>
+        <v>220221.38984512206</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16838,12 +16841,12 @@
         <v>0</v>
       </c>
       <c r="I22" s="285">
-        <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,(G22+C22*H22)*(1-$I$9))</f>
-        <v>281163.80335841444</v>
+        <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
+        <v>242283.93885967648</v>
       </c>
       <c r="J22" s="307">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>2.5031656967445359E-2</v>
+        <v>2.5812118692959407E-2</v>
       </c>
       <c r="K22" s="120">
         <f t="shared" si="3"/>
@@ -16851,7 +16854,7 @@
       </c>
       <c r="L22" s="285">
         <f t="shared" si="4"/>
-        <v>244435.79711774178</v>
+        <v>210634.75104758309</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16887,12 +16890,12 @@
         <v>0</v>
       </c>
       <c r="I23" s="285">
-        <f t="shared" si="9"/>
-        <v>455233.20341221918</v>
+        <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
+        <v>415575.74162350647</v>
       </c>
       <c r="J23" s="307">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>0.61910316326141457</v>
+        <v>0.71524263465187987</v>
       </c>
       <c r="K23" s="120">
         <f t="shared" si="3"/>
@@ -16900,7 +16903,7 @@
       </c>
       <c r="L23" s="285">
         <f t="shared" si="4"/>
-        <v>369013.30753161875</v>
+        <v>336866.85812223703</v>
       </c>
       <c r="N23" s="283"/>
       <c r="O23" s="283"/>
@@ -16945,11 +16948,11 @@
       </c>
       <c r="I24" s="285">
         <f t="shared" si="9"/>
-        <v>465651.8214987173</v>
+        <v>425201.21047423029</v>
       </c>
       <c r="J24" s="307">
         <f t="shared" si="10"/>
-        <v>2.2886331683200867E-2</v>
+        <v>2.3161767847951209E-2</v>
       </c>
       <c r="K24" s="120">
         <f t="shared" si="3"/>
@@ -16957,7 +16960,7 @@
       </c>
       <c r="L24" s="285">
         <f t="shared" si="4"/>
-        <v>351942.81443664554</v>
+        <v>321369.96744590485</v>
       </c>
       <c r="N24" s="283"/>
       <c r="O24" s="283"/>
@@ -17002,11 +17005,11 @@
       </c>
       <c r="I25" s="285">
         <f t="shared" si="9"/>
-        <v>476278.81194694544</v>
+        <v>435019.1887019687</v>
       </c>
       <c r="J25" s="307">
         <f t="shared" si="10"/>
-        <v>2.282175212807025E-2</v>
+        <v>2.3090193503420009E-2</v>
       </c>
       <c r="K25" s="120">
         <f t="shared" si="3"/>
@@ -17014,7 +17017,7 @@
       </c>
       <c r="L25" s="285">
         <f t="shared" si="4"/>
-        <v>335640.80756267981</v>
+        <v>306564.53350155585</v>
       </c>
       <c r="N25" s="283"/>
       <c r="O25" s="283"/>
@@ -18308,7 +18311,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="323" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B51" s="324">
         <f>C15+1</f>
@@ -18339,12 +18342,12 @@
         <v>0</v>
       </c>
       <c r="I51" s="285">
-        <f>(G51+C51*H51)*(1-$I$9)/Equity_Cost</f>
+        <f>(G51+C51*H51)*(1-$I$10)/Equity_Cost</f>
         <v>6569362.9234061446</v>
       </c>
       <c r="J51" s="424">
-        <f>(G51+C51*H51)*(1-$I$9)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
-        <v>0</v>
+        <f>(G51+C51*H51)*(1-$I$10)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
+        <v>9.4845524787283919E-2</v>
       </c>
       <c r="K51" s="120">
         <f>1/(1+Equity_Cost)^C15</f>
@@ -18360,12 +18363,12 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="466" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K52" s="466"/>
       <c r="L52" s="325">
         <f>SUM(L21:L51)</f>
-        <v>6186316.5175241344</v>
+        <v>6025185.8801372983</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18389,7 +18392,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="126">
         <f>L52</f>
-        <v>6186316.5175241344</v>
+        <v>6025185.8801372983</v>
       </c>
       <c r="B55" s="124">
         <f>C78</f>
@@ -18424,19 +18427,19 @@
       </c>
       <c r="B56" s="119">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>5914454.8667167993</v>
+        <v>5758950.7828361671</v>
       </c>
       <c r="C56" s="119">
-        <v>6048411.0895425407</v>
+        <v>5890133.1628855541</v>
       </c>
       <c r="D56" s="119">
-        <v>6183669.2910278663</v>
+        <v>6022593.3869026918</v>
       </c>
       <c r="E56" s="119">
-        <v>6320229.4711727584</v>
+        <v>6156331.4548875643</v>
       </c>
       <c r="F56" s="119">
-        <v>6458091.6299772309</v>
+        <v>6291347.3668401847</v>
       </c>
       <c r="G56" s="303"/>
       <c r="H56" s="303"/>
@@ -18450,19 +18453,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="119">
-        <v>5875266.559272632</v>
+        <v>5606810.6932469383</v>
       </c>
       <c r="C57" s="119">
-        <v>6132386.5311118178</v>
+        <v>5855074.1105214562</v>
       </c>
       <c r="D57" s="119">
-        <v>6396963.8385578413</v>
+        <v>6110560.8512243973</v>
       </c>
       <c r="E57" s="119">
-        <v>6669144.0902566426</v>
+        <v>6373412.1799634043</v>
       </c>
       <c r="F57" s="119">
-        <v>6949074.3134529162</v>
+        <v>6643770.7389364615</v>
       </c>
       <c r="G57" s="303"/>
       <c r="H57" s="303"/>
@@ -18476,19 +18479,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="119">
-        <v>5581226.0720410738</v>
+        <v>5234603.2044682316</v>
       </c>
       <c r="C58" s="285">
-        <v>5988283.4789860584</v>
+        <v>5623484.6783686709</v>
       </c>
       <c r="D58" s="119">
-        <v>6418720.7118496615</v>
+        <v>6034805.4499721229</v>
       </c>
       <c r="E58" s="119">
-        <v>6873682.2939743027</v>
+        <v>6469666.5848724525</v>
       </c>
       <c r="F58" s="119">
-        <v>7354357.6989958473</v>
+        <v>6929212.4530887045</v>
       </c>
       <c r="G58" s="303"/>
       <c r="H58" s="303"/>
@@ -18511,19 +18514,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="119">
-        <v>5472052.1874691751</v>
+        <v>5067235.6695197485</v>
       </c>
       <c r="C59" s="285">
-        <v>5968253.1708341325</v>
+        <v>5536871.1129420241</v>
       </c>
       <c r="D59" s="119">
-        <v>6502218.7788243024</v>
+        <v>6042432.8955028597</v>
       </c>
       <c r="E59" s="119">
-        <v>7076542.9555222429</v>
+        <v>6586395.1738765407</v>
       </c>
       <c r="F59" s="119">
-        <v>7693973.2927271929</v>
+        <v>7171378.8874938637</v>
       </c>
       <c r="G59" s="303"/>
       <c r="H59" s="303"/>
@@ -18546,19 +18549,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="119">
-        <v>5200297.9058892755</v>
+        <v>4757334.6914210217</v>
       </c>
       <c r="C60" s="285">
-        <v>5796812.8110374203</v>
+        <v>5317616.0069383709</v>
       </c>
       <c r="D60" s="119">
-        <v>6454989.2328412253</v>
+        <v>5936171.2817601394</v>
       </c>
       <c r="E60" s="119">
-        <v>7180889.6848746464</v>
+        <v>6618748.3092536014</v>
       </c>
       <c r="F60" s="119">
-        <v>7981119.3812992098</v>
+        <v>7371610.3990916647</v>
       </c>
       <c r="G60" s="303"/>
       <c r="H60" s="303"/>
@@ -18581,19 +18584,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="119">
-        <v>5078642.5800520014</v>
+        <v>4606406.1385381455</v>
       </c>
       <c r="C61" s="285">
-        <v>5734590.765649654</v>
+        <v>5218515.0461217295</v>
       </c>
       <c r="D61" s="119">
-        <v>6470037.2051600013</v>
+        <v>5905288.6295807939</v>
       </c>
       <c r="E61" s="119">
-        <v>7294376.0633280417</v>
+        <v>6675579.6776464423</v>
       </c>
       <c r="F61" s="119">
-        <v>8218034.7033554614</v>
+        <v>7539216.6112826653</v>
       </c>
       <c r="G61" s="303"/>
       <c r="H61" s="303"/>
@@ -18690,23 +18693,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18722,23 +18725,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>7.2896186223118002</v>
+        <v>7.0215099971418917</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>7.5205760212334409</v>
+        <v>7.2476849417726426</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>7.7537781953385396</v>
+        <v>7.4760630503385492</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>7.9892251446270661</v>
+        <v>7.7066443228395842</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>8.2269168690990444</v>
+        <v>7.9394287592757706</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18754,23 +18757,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>7.2220530448080185</v>
+        <v>6.7592013217999236</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>7.6653602585686951</v>
+        <v>7.1872387200752534</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>8.1215248581104085</v>
+        <v>7.6277300376639721</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>8.5907978910770613</v>
+        <v>8.0809188325408634</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>9.0734328509554771</v>
+        <v>8.5470510378199549</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18786,23 +18789,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>6.7150902126520604</v>
+        <v>6.1174687344358176</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>7.4169084480176481</v>
+        <v>6.7879493721117266</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>8.1590364477786483</v>
+        <v>7.4971181850869497</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>8.9434475143214236</v>
+        <v>8.2468735491161667</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>9.7721924499993875</v>
+        <v>9.0391885022369376</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18818,23 +18821,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>6.526860686027546</v>
+        <v>5.8289060255132696</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>7.3823736740983676</v>
+        <v>6.6386166769946797</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>8.3029976311910421</v>
+        <v>7.5102688618008422</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>9.2932048435914769</v>
+        <v>8.4481283376394884</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>10.357732505599907</v>
+        <v>9.4567139341767525</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18850,23 +18853,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>6.0583220791935837</v>
+        <v>5.2945977095938064</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>7.0867889021960799</v>
+        <v>6.2605932607270667</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>8.2215679457131881</v>
+        <v>7.3270604568642499</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>9.473111746674002</v>
+        <v>8.5039092176615085</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>10.852808526169609</v>
+        <v>9.8019382778112742</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18882,23 +18885,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>5.8485729758847214</v>
+        <v>5.0343778761174471</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>6.979510259552975</v>
+        <v>6.0897307232649505</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>8.2475125451687159</v>
+        <v>7.2738148750712952</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>9.6687765558761036</v>
+        <v>8.6018936542504889</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>11.261280379082139</v>
+        <v>10.090912496359509</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18921,7 +18924,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G73" s="332"/>
       <c r="H73" s="332"/>
@@ -18945,7 +18948,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>8.2269168690990444</v>
+        <v>7.9394287592757706</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18973,7 +18976,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>7.9892251446270661</v>
+        <v>7.7066443228395842</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -19001,7 +19004,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>7.7537781953385396</v>
+        <v>7.4760630503385492</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19029,7 +19032,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.5205760212334409</v>
+        <v>7.2476849417726426</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19057,7 +19060,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.2896186223118002</v>
+        <v>7.0215099971418917</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19180,11 +19183,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="7" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="13.9">
@@ -19259,7 +19262,7 @@
       </c>
       <c r="C8" s="283">
         <f>Normalized_FCF!G19</f>
-        <v>362404.65016124537</v>
+        <v>289000.65016124537</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19275,7 +19278,7 @@
       </c>
       <c r="C9" s="283">
         <f>Normalized_FCF!C19</f>
-        <v>264963.17610033229</v>
+        <v>230211.62257446788</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19329,7 +19332,7 @@
       </c>
       <c r="C14" s="145">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.82412654882629588</v>
+        <v>0.62894902211793369</v>
       </c>
       <c r="E14" s="467"/>
       <c r="F14" s="467"/>
@@ -19337,7 +19340,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19367,35 +19370,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E20" s="328"/>
       <c r="F20" s="328"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="154" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C21" s="154" t="s">
         <v>382</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E21" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="155" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G21" s="155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="310" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C22" s="333">
         <v>0.03</v>
@@ -19406,7 +19409,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>7.9892251446270661</v>
+        <v>7.7066443228395842</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19419,7 +19422,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="310" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C23" s="333">
         <v>0.02</v>
@@ -19430,7 +19433,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>7.7537781953385396</v>
+        <v>7.4760630503385492</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19442,7 +19445,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="310" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C24" s="333">
         <v>0.01</v>
@@ -19453,7 +19456,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>7.5205760212334409</v>
+        <v>7.2476849417726426</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19465,11 +19468,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="142" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>7.7542271503752254</v>
+        <v>7.476503683125574</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19479,33 +19482,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="154" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C28" s="154" t="s">
         <v>382</v>
       </c>
       <c r="D28" s="154" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E28" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="155" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G28" s="155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="310" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C29" s="333">
         <v>0.04</v>
@@ -19516,7 +19519,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>8.2269168690990444</v>
+        <v>7.9394287592757706</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19528,7 +19531,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="323" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C30" s="333">
         <v>0</v>
@@ -19539,7 +19542,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>7.2896186223118002</v>
+        <v>7.0215099971418917</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19555,12 +19558,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="146" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C33" s="156">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19571,7 +19574,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F33" s="223">
         <f>Holding_Period</f>
@@ -19584,62 +19587,62 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>6.46</v>
+        <v>6.43</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15491941305006585</v>
+        <v>0.13834890491956828</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.61023323266846963</v>
+        <v>0.83135387789665138</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>7.7546312099082444</v>
+        <v>7.4769002526339001</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F36" s="340" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19725,7 +19728,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>7.7583423472162005</v>
+        <v>7.4805328351798659</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19788,7 +19791,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.57410751216480937</v>
+        <v>0.59543285068002583</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19831,13 +19834,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E60" s="422"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="154" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C61" s="154" t="s">
         <v>103</v>
@@ -19850,10 +19853,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="155" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G61" s="155" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -19866,11 +19869,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>4.2549416789619992</v>
+        <v>4.1025515789486411</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>4.7707167132555526</v>
+        <v>4.6183266132421945</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19878,7 +19881,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.38479128354164482</v>
+        <v>0.38232068675581321</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19891,11 +19894,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.9629639743412763</v>
+        <v>4.7852161616856961</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>5.5389639743412769</v>
+        <v>5.3612161616856966</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19903,12 +19906,12 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.28572180618157139</v>
+        <v>0.28296272779657694</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="154" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C65" s="154" t="s">
         <v>103</v>
@@ -19921,10 +19924,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="155" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G65" s="155" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -19937,11 +19940,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>6.2107466628069128</v>
+        <v>5.9883096997382061</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>6.8890837559764515</v>
+        <v>6.6666467929077449</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19949,7 +19952,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.11204179350910581</v>
+        <v>0.10880054405276218</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19962,11 +19965,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.741655357150413</v>
+        <v>6.5002039785777299</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>7.4623643296076372</v>
+        <v>7.2209129510349541</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19974,7 +19977,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>3.76893333015208E-2</v>
+        <v>3.4237089294961387E-2</v>
       </c>
     </row>
   </sheetData>
@@ -19995,10 +19998,10 @@
   <dimension ref="A2:J167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="352" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="352" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="352" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="352" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="352" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="352" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="352" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="352" customWidth="1"/>
     <col min="7" max="16384" width="9" style="352"/>
   </cols>
   <sheetData>
@@ -20018,7 +20021,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="445" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F3" s="446">
         <f>Thesis!F3</f>
@@ -20027,7 +20030,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="432" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C4" s="433" t="str">
         <f>Thesis!C4</f>
@@ -20035,7 +20038,7 @@
       </c>
       <c r="D4" s="358"/>
       <c r="E4" s="444" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F4" s="447" t="str">
         <f>Thesis!F4</f>
@@ -20051,7 +20054,7 @@
         <v>0341.HK</v>
       </c>
       <c r="E5" s="448" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F5" s="449" t="str">
         <f>Thesis!F5</f>
@@ -20085,14 +20088,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>6.46</v>
+        <v>6.43</v>
       </c>
       <c r="D8" s="352" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.15491941305006585</v>
+        <v>0.13834890491956828</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20110,7 +20113,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3746.8260531799997</v>
+        <v>3729.4259321899999</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20118,14 +20121,14 @@
       <c r="D11" s="358"/>
       <c r="E11" s="358"/>
     </row>
-    <row r="12" spans="1:10" ht="24.6" customHeight="1">
-      <c r="B12" s="469" t="s">
-        <v>509</v>
-      </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="472" t="s">
+        <v>505</v>
+      </c>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20168,7 +20171,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="352" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C17" s="434">
         <f>Terminal_Growth</f>
@@ -20189,7 +20192,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>7.7546312099082444</v>
+        <v>7.4769002526339001</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>365</v>
@@ -20241,10 +20244,10 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>4.7707167132555526</v>
+        <v>4.6183266132421945</v>
       </c>
       <c r="D22" s="374" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E22" s="375">
         <f>Thesis!E22</f>
@@ -20257,10 +20260,10 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>5.5389639743412769</v>
+        <v>5.3612161616856966</v>
       </c>
       <c r="D23" s="374" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E23" s="377">
         <f>Thesis!E23</f>
@@ -20273,10 +20276,10 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>6.8890837559764515</v>
+        <v>6.6666467929077449</v>
       </c>
       <c r="D24" s="374" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E24" s="377">
         <f>Thesis!E24</f>
@@ -20289,10 +20292,10 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>7.4623643296076372</v>
+        <v>7.2209129510349541</v>
       </c>
       <c r="D25" s="374" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E25" s="377">
         <f>Thesis!E25</f>
@@ -20310,22 +20313,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
-        <v>510</v>
-      </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="470" t="s">
-        <v>511</v>
-      </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="B29" s="472" t="s">
+        <v>506</v>
+      </c>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="475" t="s">
+        <v>507</v>
+      </c>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20338,7 +20341,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="468" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C33" s="468"/>
       <c r="D33" s="468"/>
@@ -20362,9 +20365,9 @@
       <c r="B35" s="381"/>
       <c r="C35" s="383"/>
     </row>
-    <row r="36" spans="2:6" ht="24.6" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="468" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C36" s="468"/>
       <c r="D36" s="468"/>
@@ -20376,7 +20379,7 @@
         <v>199</v>
       </c>
       <c r="C37" s="382">
-        <f>Normalized_FCF!C9</f>
+        <f>Normalized_FCF!C15</f>
         <v>378473</v>
       </c>
       <c r="D37" s="352" t="str">
@@ -20389,7 +20392,7 @@
         <v>200</v>
       </c>
       <c r="C38" s="382">
-        <f>Normalized_FCF!C10</f>
+        <f>Normalized_FCF!C16</f>
         <v>-378473</v>
       </c>
       <c r="D38" s="352" t="str">
@@ -20399,7 +20402,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="468" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C40" s="468"/>
       <c r="D40" s="468"/>
@@ -20411,7 +20414,7 @@
         <v>202</v>
       </c>
       <c r="C41" s="382">
-        <f>Normalized_FCF!C11</f>
+        <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
       <c r="D41" s="352" t="str">
@@ -20421,7 +20424,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="468" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C43" s="468"/>
       <c r="D43" s="468"/>
@@ -20463,7 +20466,7 @@
         <v>203</v>
       </c>
       <c r="C46" s="382">
-        <f>Normalized_FCF!C12</f>
+        <f>Normalized_FCF!C10</f>
         <v>-78679.881332559497</v>
       </c>
       <c r="D46" s="352" t="str">
@@ -20473,7 +20476,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="352" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20481,8 +20484,8 @@
         <v>223</v>
       </c>
       <c r="C49" s="382">
-        <f>Normalized_FCF!C15</f>
-        <v>-2604.2914835892152</v>
+        <f>Normalized_FCF!C13</f>
+        <v>-37355.845009453624</v>
       </c>
       <c r="D49" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20491,7 +20494,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="468" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C51" s="468"/>
       <c r="D51" s="468"/>
@@ -20500,10 +20503,10 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="381" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C52" s="382">
-        <f>Normalized_FCF!C14</f>
+        <f>Normalized_FCF!C12</f>
         <v>-52872.613354906651</v>
       </c>
       <c r="D52" s="352" t="str">
@@ -20513,12 +20516,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="468" t="s">
-        <v>518</v>
-      </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+        <v>514</v>
+      </c>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20534,22 +20537,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
-        <v>519</v>
-      </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="B57" s="472" t="s">
+        <v>515</v>
+      </c>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
-        <v>520</v>
-      </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="B58" s="472" t="s">
+        <v>516</v>
+      </c>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20557,7 +20560,7 @@
       </c>
       <c r="C60" s="382">
         <f>Normalized_FCF!G19</f>
-        <v>362404.65016124537</v>
+        <v>289000.65016124537</v>
       </c>
       <c r="D60" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20570,7 +20573,7 @@
       </c>
       <c r="C61" s="382">
         <f>Normalized_FCF!C19</f>
-        <v>264963.17610033229</v>
+        <v>230211.62257446788</v>
       </c>
       <c r="D61" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20583,7 +20586,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>7.0716700572596158E-2</v>
+        <v>6.1728434016460706E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20593,14 +20596,14 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>6.1919504643962855E-2</v>
+        <v>6.2208398133748059E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>376</v>
       </c>
       <c r="F63" s="389">
         <f>Normalized_FCF!C90</f>
-        <v>0.87559945730779254</v>
+        <v>1.0077754137932506</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20624,7 +20627,7 @@
       </c>
       <c r="D66" s="387">
         <f>Normalized_FCF!G119</f>
-        <v>0.14467098116585544</v>
+        <v>0.11792742550148552</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20634,11 +20637,11 @@
       </c>
       <c r="C67" s="392">
         <f>Normalized_FCF!C116</f>
-        <v>3.176685498586024E-4</v>
+        <v>3.9086921133773919E-2</v>
       </c>
       <c r="D67" s="392">
         <f>Normalized_FCF!G116</f>
-        <v>4.6343249224001092E-2</v>
+        <v>3.7776339292914275E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -20671,7 +20674,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="354" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B71" s="354"/>
       <c r="C71" s="354"/>
@@ -20684,22 +20687,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
-        <v>521</v>
-      </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="B73" s="472" t="s">
+        <v>517</v>
+      </c>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
-        <v>488</v>
-      </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="B74" s="475" t="s">
+        <v>486</v>
+      </c>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20707,13 +20710,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
-        <v>522</v>
-      </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="B77" s="472" t="s">
+        <v>518</v>
+      </c>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20761,7 +20764,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="352" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20779,7 +20782,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="391" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C85" s="399">
         <f>BS!C66</f>
@@ -20805,7 +20808,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="352" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20836,7 +20839,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="381" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
@@ -20849,7 +20852,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="354" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B94" s="354"/>
       <c r="C94" s="354"/>
@@ -20862,33 +20865,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
-        <v>525</v>
-      </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="B96" s="472" t="s">
+        <v>521</v>
+      </c>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
-        <v>526</v>
-      </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="B97" s="475" t="s">
+        <v>522</v>
+      </c>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
-        <v>527</v>
-      </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="B98" s="475" t="s">
+        <v>523</v>
+      </c>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20932,7 +20935,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="394"/>
       <c r="B104" s="381" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C104" s="377">
         <v>0</v>
@@ -20951,23 +20954,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
-        <v>528</v>
-      </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="B107" s="472" t="s">
+        <v>524</v>
+      </c>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
-        <v>547</v>
-      </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="B108" s="472" t="s">
+        <v>543</v>
+      </c>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -20975,13 +20978,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="394"/>
       <c r="B110" s="378" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="394"/>
       <c r="B111" s="384" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
@@ -20999,7 +21002,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>3.3934554230790441</v>
+        <v>2.5670270786220946</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21011,13 +21014,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
-        <v>529</v>
-      </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="B114" s="472" t="s">
+        <v>525</v>
+      </c>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21025,7 +21028,7 @@
     <row r="116" spans="1:6">
       <c r="A116" s="394"/>
       <c r="B116" s="378" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -21062,7 +21065,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>8.23 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -21085,7 +21088,7 @@
       </c>
       <c r="E119" s="407" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>7.99 HKD</v>
+        <v>7.71 HKD</v>
       </c>
       <c r="F119" s="412">
         <f>DCF!F75</f>
@@ -21107,7 +21110,7 @@
       </c>
       <c r="E120" s="407" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>7.75 HKD</v>
+        <v>7.48 HKD</v>
       </c>
       <c r="F120" s="412">
         <f>DCF!F76</f>
@@ -21129,7 +21132,7 @@
       </c>
       <c r="E121" s="407" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.52 HKD</v>
+        <v>7.25 HKD</v>
       </c>
       <c r="F121" s="412">
         <f>DCF!F77</f>
@@ -21151,7 +21154,7 @@
       </c>
       <c r="E122" s="407" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.29 HKD</v>
+        <v>7.02 HKD</v>
       </c>
       <c r="F122" s="412">
         <f>DCF!F78</f>
@@ -21160,7 +21163,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="468" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C124" s="468"/>
       <c r="D124" s="468"/>
@@ -21173,7 +21176,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>7.7546312099082444</v>
+        <v>7.4769002526339001</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21181,17 +21184,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
-        <v>531</v>
-      </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="B127" s="470" t="s">
+        <v>527</v>
+      </c>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B129" s="354"/>
       <c r="C129" s="354"/>
@@ -21200,22 +21203,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
-        <v>532</v>
-      </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B132" s="469" t="s">
-        <v>533</v>
-      </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="B131" s="471" t="s">
+        <v>528</v>
+      </c>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="472" t="s">
+        <v>529</v>
+      </c>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21246,28 +21249,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="378" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C138" s="416"/>
       <c r="D138" s="416"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="349" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21280,11 +21283,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>4.2549416789619992</v>
+        <v>4.1025515789486411</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>4.7707167132555526</v>
+        <v>4.6183266132421945</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21301,11 +21304,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>4.9629639743412763</v>
+        <v>4.7852161616856961</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>5.5389639743412769</v>
+        <v>5.3612161616856966</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21314,21 +21317,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="349" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21341,11 +21344,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>6.2107466628069128</v>
+        <v>5.9883096997382061</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>6.8890837559764515</v>
+        <v>6.6666467929077449</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21362,11 +21365,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>6.741655357150413</v>
+        <v>6.5002039785777299</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>7.4623643296076372</v>
+        <v>7.2209129510349541</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21375,7 +21378,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="354" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B147" s="354"/>
       <c r="C147" s="354"/>
@@ -21384,13 +21387,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
-        <v>534</v>
-      </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="B149" s="473" t="s">
+        <v>530</v>
+      </c>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21398,13 +21401,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
-        <v>535</v>
-      </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="B152" s="474" t="s">
+        <v>531</v>
+      </c>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21423,12 +21426,12 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="352" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" ht="24.6" customHeight="1">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="468" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C158" s="468"/>
       <c r="D158" s="468"/>
@@ -21437,30 +21440,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="352" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21480,15 +21483,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21503,12 +21503,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21530,7 +21533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7486D8-6F03-4F16-B46F-BAEF0C1D914A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E51FA99-13FB-4FB6-B039-08E5CC95A8B5}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EC985B-FE8F-41A3-BEDF-B1A90E7002F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352CDBD2-FAC4-4640-B68C-1C83C6816A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="555">
   <si>
     <t>Sales</t>
   </si>
@@ -1793,9 +1793,6 @@
   </si>
   <si>
     <t>报告货币:</t>
-  </si>
-  <si>
-    <t>估值输出</t>
   </si>
   <si>
     <t>目标价格</t>
@@ -5047,7 +5044,7 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{0533B5A3-0297-4086-A30C-64FBADBAC6B3}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{B6A6389D-A8C2-4930-9ADC-0E57DFA1BE43}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5152,7 +5149,7 @@
         </row>
         <row r="8">
           <cell r="C8">
-            <v>6.46</v>
+            <v>6.43</v>
           </cell>
         </row>
         <row r="9">
@@ -5440,7 +5437,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="438" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F3" s="439">
         <v>45930</v>
@@ -5448,13 +5445,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="431" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C4" s="430" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E4" s="440" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F4" s="441" t="s">
         <v>325</v>
@@ -5462,16 +5459,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F5" s="442" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5479,14 +5476,14 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C7" s="45" t="s">
         <v>309</v>
@@ -5496,35 +5493,35 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>6.43</v>
+        <v>6.49</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C9" s="48">
         <v>580004033</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.13834890491956828</v>
+        <v>8.3497774291450236E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3729.4259321899999</v>
+        <v>3764.2261741699999</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5533,7 +5530,7 @@
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
       <c r="B12" s="460" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C12" s="460"/>
       <c r="D12" s="460"/>
@@ -5552,10 +5549,10 @@
         <v>320</v>
       </c>
       <c r="C15" s="427" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E15" s="260" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5567,10 +5564,10 @@
         <v>321</v>
       </c>
       <c r="C16" s="427" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E16" s="426">
         <v>1</v>
@@ -5578,7 +5575,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C17" s="425">
         <v>0</v>
@@ -5597,10 +5594,10 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>7.4769002526339001</v>
+        <v>6.7856494908288969</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E18" s="428">
         <v>6</v>
@@ -5615,7 +5612,7 @@
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E19" s="429">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5628,7 +5625,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C21" s="261" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5647,10 +5644,10 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>4.6183266132421945</v>
+        <v>4.2390395011406845</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5662,10 +5659,10 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>5.3612161616856966</v>
+        <v>4.918815674130494</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E23" s="453">
         <v>0.25</v>
@@ -5677,10 +5674,10 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>6.6666467929077449</v>
+        <v>6.1130184841162611</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E24" s="453">
         <v>0.1174</v>
@@ -5692,10 +5689,10 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>7.2209129510349541</v>
+        <v>6.6199592402379013</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E25" s="454">
         <v>7.2499999999999995E-2</v>
@@ -5717,7 +5714,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="460" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C29" s="460"/>
       <c r="D29" s="460"/>
@@ -5989,7 +5986,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1728434016460706E-2</v>
+        <v>6.1157755119544271E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -5999,7 +5996,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.2208398133748059E-2</v>
+        <v>6.1633281972265024E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6077,7 +6074,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6091,7 +6088,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
       <c r="B73" s="460" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C73" s="460"/>
       <c r="D73" s="460"/>
@@ -6101,7 +6098,7 @@
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
       <c r="B74" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6177,7 +6174,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="192"/>
       <c r="B83" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6265,7 +6262,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="192"/>
       <c r="B92" s="44" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
@@ -6278,7 +6275,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="203" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6291,7 +6288,7 @@
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
       <c r="B96" s="460" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C96" s="460"/>
       <c r="D96" s="460"/>
@@ -6300,7 +6297,7 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="464" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C97" s="464"/>
       <c r="D97" s="464"/>
@@ -6309,7 +6306,7 @@
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="464" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C98" s="464"/>
       <c r="D98" s="464"/>
@@ -6323,7 +6320,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C101" s="215">
         <f>E25+C103</f>
@@ -6383,12 +6380,12 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
@@ -6414,7 +6411,7 @@
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
       <c r="B114" s="460" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C114" s="460"/>
       <c r="D114" s="460"/>
@@ -6423,7 +6420,7 @@
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6458,7 +6455,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.22 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6480,7 +6477,7 @@
       </c>
       <c r="E119" s="211" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>7.71 HKD</v>
+        <v>7 HKD</v>
       </c>
       <c r="F119" s="202">
         <f>DCF!F75</f>
@@ -6502,7 +6499,7 @@
       </c>
       <c r="E120" s="211" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>7.48 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="F120" s="202">
         <f>DCF!F76</f>
@@ -6524,7 +6521,7 @@
       </c>
       <c r="E121" s="211" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.25 HKD</v>
+        <v>6.57 HKD</v>
       </c>
       <c r="F121" s="202">
         <f>DCF!F77</f>
@@ -6546,7 +6543,7 @@
       </c>
       <c r="E122" s="211" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.02 HKD</v>
+        <v>6.36 HKD</v>
       </c>
       <c r="F122" s="202">
         <f>DCF!F78</f>
@@ -6555,7 +6552,7 @@
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="461" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C124" s="461"/>
       <c r="D124" s="461"/>
@@ -6568,7 +6565,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>7.4769002526339001</v>
+        <v>6.7856494908288969</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6577,7 +6574,7 @@
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="463" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C127" s="463"/>
       <c r="D127" s="463"/>
@@ -6586,7 +6583,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="203" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6605,7 +6602,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="460" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C132" s="460"/>
       <c r="D132" s="460"/>
@@ -6641,28 +6638,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="193" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C138" s="218"/>
       <c r="D138" s="219"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="349" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6675,11 +6672,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>4.1025515789486411</v>
+        <v>3.7232644668471311</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>4.6183266132421945</v>
+        <v>4.2390395011406845</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6696,11 +6693,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>4.7852161616856961</v>
+        <v>4.3428156741304944</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>5.3612161616856966</v>
+        <v>4.918815674130494</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6716,21 +6713,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="349" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6743,11 +6740,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>5.9883096997382061</v>
+        <v>5.4346813909467224</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>6.6666467929077449</v>
+        <v>6.1130184841162611</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6764,11 +6761,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>6.5002039785777299</v>
+        <v>5.8992502677806771</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>7.2209129510349541</v>
+        <v>6.6199592402379013</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6777,7 +6774,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="203" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6787,7 +6784,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="459" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C149" s="460"/>
       <c r="D149" s="460"/>
@@ -6830,7 +6827,7 @@
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
       <c r="B158" s="461" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C158" s="461"/>
       <c r="D158" s="461"/>
@@ -7571,7 +7568,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9690,7 +9687,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -10873,7 +10870,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10883,7 +10880,7 @@
       <c r="E3" s="242"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11172,7 +11169,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C9" s="308">
         <f>C61</f>
@@ -11563,7 +11560,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C16" s="274">
         <f>-C4*C82</f>
@@ -12265,7 +12262,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="306" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C35" s="284">
         <f>G35</f>
@@ -12333,7 +12330,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="306" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12406,7 +12403,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="239" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -13630,7 +13627,7 @@
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="239" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
@@ -14334,24 +14331,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.2208398133748059E-2</v>
+        <v>6.1633281972265024E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.2208398133748059E-2</v>
+        <v>6.1633281972265024E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.8646967340590979E-2</v>
+        <v>8.7827426810477643E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.9097978227060657E-2</v>
+        <v>5.8551617873651769E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.9097978227060657E-2</v>
+        <v>5.8551617873651769E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15533,50 +15530,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1728434016460706E-2</v>
+        <v>6.1157755119544271E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.7491993517495042E-2</v>
+        <v>7.6775580634436527E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.3092992623298301E-2</v>
+        <v>9.2232348623699223E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.9203966855306209E-2</v>
+        <v>2.8933976406720942E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.402089381701317E-3</v>
+        <v>-6.3429021146902097E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1867371054131767E-2</v>
+        <v>-3.1572757454247653E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.593729538891723E-2</v>
+        <v>5.5420155523996574E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14956591447103781</v>
+        <v>0.14818317874403283</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12337019379543469</v>
+        <v>0.12222963730425963</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13872269067861534</v>
+        <v>0.13744020047203337</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13525137894447994</v>
+        <v>0.13400098098813651</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15590,43 +15587,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3042142215688865E-2</v>
+        <v>6.2459318096591589E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9347531244394207E-2</v>
+        <v>8.8521514006387469E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9813435639063243E-2</v>
+        <v>2.9537810656267587E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1269483334616013E-3</v>
+        <v>6.0703047433217404E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6677077533023209E-2</v>
+        <v>9.5783298696046112E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9945697099906987E-2</v>
+        <v>1.9761299283883194E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15876706248253605</v>
+        <v>0.1572992622130519</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12315434288040465</v>
+        <v>0.1220157819292761</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13510122178619816</v>
+        <v>0.13385221203162623</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13885783212106892</v>
+        <v>0.13757409253289263</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16369,15 +16366,15 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C4" s="283">
         <f>Normalized_FCF!C19</f>
@@ -16388,7 +16385,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="136" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F4" s="283">
         <f>-BS!G31</f>
@@ -16399,7 +16396,7 @@
         <v>HKD</v>
       </c>
       <c r="H4" s="316" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I4" s="313">
         <f>Normalized_FCF!C4</f>
@@ -16416,7 +16413,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="136" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F5" s="283">
         <f>BS!D66</f>
@@ -16427,7 +16424,7 @@
         <v>HKD</v>
       </c>
       <c r="H5" s="316" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I5" s="313">
         <f>Normalized_FCF!C7</f>
@@ -16448,7 +16445,7 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="188" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F6" s="292">
         <f>BS!H42</f>
@@ -16459,7 +16456,7 @@
         <v>HKD</v>
       </c>
       <c r="H6" s="316" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I6" s="313">
         <f>I7+I8</f>
@@ -16470,14 +16467,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="326" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C7" s="283">
         <f>F7</f>
         <v>-1686446.6667440513</v>
       </c>
       <c r="E7" s="141" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F7" s="291">
         <f>SUM(F4:F6)</f>
@@ -16488,7 +16485,7 @@
         <v>HKD</v>
       </c>
       <c r="H7" s="320" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I7" s="321">
         <f>Normalized_FCF!C9</f>
@@ -16500,7 +16497,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="137" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C8" s="291">
         <f>C6+C7</f>
@@ -16511,7 +16508,7 @@
         <v>HKD</v>
       </c>
       <c r="E8" s="141" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16561,7 +16558,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
@@ -16572,7 +16569,7 @@
         <v>HKD</v>
       </c>
       <c r="H10" s="316" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I10" s="314">
         <f>Normalized_FCF!C41</f>
@@ -16583,7 +16580,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="137" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16599,7 +16596,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16614,25 +16611,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C14" s="317" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F14" s="317" t="str">
         <f>IF(F17=C17,"I","II")</f>
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="140" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C15" s="149">
         <f>Scenarios!C45</f>
@@ -16647,7 +16644,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I15" s="127">
         <f>Terminal_Growth</f>
@@ -16657,14 +16654,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C16" s="148">
         <f>Scenarios!C46</f>
         <v>2.0194760895005201E-2</v>
       </c>
       <c r="E16" s="316" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F16" s="319">
         <f>Scenarios!C41</f>
@@ -16673,33 +16670,33 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="316" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C17" s="314">
         <f>Normalized_FCF!C32</f>
         <v>0.89099809462634716</v>
       </c>
       <c r="E17" s="316" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F17" s="319">
         <f>Scenarios!C40</f>
         <v>0.86799999999999999</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="316" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C18" s="314">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="316" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F18" s="145">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16710,7 +16707,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.4805328351798659</v>
+        <v>6.7890685811450933</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16722,41 +16719,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="122" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B20" s="122" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="122" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D20" s="122" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="122" t="s">
+        <v>397</v>
+      </c>
+      <c r="F20" s="122" t="s">
         <v>398</v>
       </c>
-      <c r="F20" s="122" t="s">
-        <v>399</v>
-      </c>
       <c r="G20" s="122" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H20" s="122" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="122" t="s">
+        <v>424</v>
+      </c>
+      <c r="J20" s="122" t="s">
+        <v>536</v>
+      </c>
+      <c r="K20" s="122" t="s">
+        <v>537</v>
+      </c>
+      <c r="L20" s="123" t="s">
         <v>425</v>
-      </c>
-      <c r="J20" s="122" t="s">
-        <v>537</v>
-      </c>
-      <c r="K20" s="122" t="s">
-        <v>538</v>
-      </c>
-      <c r="L20" s="123" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18311,7 +18308,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="323" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B51" s="324">
         <f>C15+1</f>
@@ -18342,12 +18339,12 @@
         <v>0</v>
       </c>
       <c r="I51" s="285">
-        <f>(G51+C51*H51)*(1-$I$10)/Equity_Cost</f>
-        <v>6569362.9234061446</v>
+        <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
+        <v>6000264.6717512924</v>
       </c>
       <c r="J51" s="424">
-        <f>(G51+C51*H51)*(1-$I$10)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
-        <v>9.4845524787283919E-2</v>
+        <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
+        <v>0</v>
       </c>
       <c r="K51" s="120">
         <f>1/(1+Equity_Cost)^C15</f>
@@ -18355,7 +18352,7 @@
       </c>
       <c r="L51" s="285">
         <f>I51*K51</f>
-        <v>4629528.3801748948</v>
+        <v>4228476.3241593912</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18363,12 +18360,12 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="466" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K52" s="466"/>
       <c r="L52" s="325">
         <f>SUM(L21:L51)</f>
-        <v>6025185.8801372983</v>
+        <v>5624133.8241217937</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18392,7 +18389,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="126">
         <f>L52</f>
-        <v>6025185.8801372983</v>
+        <v>5624133.8241217937</v>
       </c>
       <c r="B55" s="124">
         <f>C78</f>
@@ -18427,19 +18424,19 @@
       </c>
       <c r="B56" s="119">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>5758950.7828361671</v>
+        <v>5373619.2329866514</v>
       </c>
       <c r="C56" s="119">
-        <v>5890133.1628855541</v>
+        <v>5497056.4488840643</v>
       </c>
       <c r="D56" s="119">
-        <v>6022593.3869026918</v>
+        <v>5621694.4424392562</v>
       </c>
       <c r="E56" s="119">
-        <v>6156331.4548875643</v>
+        <v>5747533.213652215</v>
       </c>
       <c r="F56" s="119">
-        <v>6291347.3668401847</v>
+        <v>5874572.7625229498</v>
       </c>
       <c r="G56" s="303"/>
       <c r="H56" s="303"/>
@@ -18453,19 +18450,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="119">
-        <v>5606810.6932469383</v>
+        <v>5318640.8168270811</v>
       </c>
       <c r="C57" s="119">
-        <v>5855074.1105214562</v>
+        <v>5555203.3815577477</v>
       </c>
       <c r="D57" s="119">
-        <v>6110560.8512243973</v>
+        <v>5798636.5094443168</v>
       </c>
       <c r="E57" s="119">
-        <v>6373412.1799634043</v>
+        <v>6049074.4452762417</v>
       </c>
       <c r="F57" s="119">
-        <v>6643770.7389364615</v>
+        <v>6306652.7422725484</v>
       </c>
       <c r="G57" s="303"/>
       <c r="H57" s="303"/>
@@ -18479,19 +18476,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="119">
-        <v>5234603.2044682316</v>
+        <v>5023321.2432679618</v>
       </c>
       <c r="C58" s="285">
-        <v>5623484.6783686709</v>
+        <v>5396961.8185033593</v>
       </c>
       <c r="D58" s="119">
-        <v>6034805.4499721229</v>
+        <v>5792108.8893085411</v>
       </c>
       <c r="E58" s="119">
-        <v>6469666.5848724525</v>
+        <v>6209816.4225565288</v>
       </c>
       <c r="F58" s="119">
-        <v>6929212.4530887045</v>
+        <v>6651179.8059659954</v>
       </c>
       <c r="G58" s="303"/>
       <c r="H58" s="303"/>
@@ -18514,19 +18511,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="119">
-        <v>5067235.6695197485</v>
+        <v>4909228.6320150206</v>
       </c>
       <c r="C59" s="285">
-        <v>5536871.1129420241</v>
+        <v>5364061.1430426184</v>
       </c>
       <c r="D59" s="119">
-        <v>6042432.8955028597</v>
+        <v>5853599.8591909334</v>
       </c>
       <c r="E59" s="119">
-        <v>6586395.1738765407</v>
+        <v>6380231.8284840696</v>
       </c>
       <c r="F59" s="119">
-        <v>7171378.8874938637</v>
+        <v>6946485.60456766</v>
       </c>
       <c r="G59" s="303"/>
       <c r="H59" s="303"/>
@@ -18549,19 +18546,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="119">
-        <v>4757334.6914210217</v>
+        <v>4641486.2301515881</v>
       </c>
       <c r="C60" s="285">
-        <v>5317616.0069383709</v>
+        <v>5187075.0610776981</v>
       </c>
       <c r="D60" s="119">
-        <v>5936171.2817601394</v>
+        <v>5789247.4213424828</v>
       </c>
       <c r="E60" s="119">
-        <v>6618748.3092536014</v>
+        <v>6453576.1043743286</v>
       </c>
       <c r="F60" s="119">
-        <v>7371610.3990916647</v>
+        <v>7186133.2801278103</v>
       </c>
       <c r="G60" s="303"/>
       <c r="H60" s="303"/>
@@ -18584,19 +18581,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="119">
-        <v>4606406.1385381455</v>
+        <v>4519768.9639271349</v>
       </c>
       <c r="C61" s="285">
-        <v>5218515.0461217295</v>
+        <v>5118927.8479986088</v>
       </c>
       <c r="D61" s="119">
-        <v>5905288.6295807939</v>
+        <v>5790972.7175897965</v>
       </c>
       <c r="E61" s="119">
-        <v>6675579.6776464423</v>
+        <v>6544533.1775393505</v>
       </c>
       <c r="F61" s="119">
-        <v>7539216.6112826653</v>
+        <v>7389189.0565219279</v>
       </c>
       <c r="G61" s="303"/>
       <c r="H61" s="303"/>
@@ -18725,23 +18722,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>7.0215099971418917</v>
+        <v>6.3571498756157778</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>7.2476849417726426</v>
+        <v>6.5699711818038571</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>7.4760630503385492</v>
+        <v>6.7848627799027819</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>7.7066443228395842</v>
+        <v>7.0018246699125335</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>7.9394287592757706</v>
+        <v>7.2208568518331298</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18757,23 +18754,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>6.7592013217999236</v>
+        <v>6.2623601620422349</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>7.1872387200752534</v>
+        <v>6.6702238168983499</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>7.6277300376639721</v>
+        <v>7.0899331879305496</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>8.0809188325408634</v>
+        <v>7.5217197300629639</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>8.5470510378199549</v>
+        <v>7.9658171541170937</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18789,23 +18786,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>6.1174687344358176</v>
+        <v>5.7531920239663412</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>6.7879493721117266</v>
+        <v>6.3973954328681506</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>7.4971181850869497</v>
+        <v>7.0786787487122345</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>8.2468735491161667</v>
+        <v>7.7988591431268164</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>9.0391885022369376</v>
+        <v>8.5598252024946575</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18821,23 +18818,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>5.8289060255132696</v>
+        <v>5.5564819930673988</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>6.6386166769946797</v>
+        <v>6.3406705247833459</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>7.5102688618008422</v>
+        <v>7.1846969251106598</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>8.4481283376394884</v>
+        <v>8.0926767654734881</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>9.4567139341767525</v>
+        <v>9.0689695908090489</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18853,23 +18850,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>5.2945977095938064</v>
+        <v>5.0948603721304409</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>6.2605932607270667</v>
+        <v>6.03552422942143</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>7.3270604568642499</v>
+        <v>7.0737452175585664</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>8.5039092176615085</v>
+        <v>8.2191315342634468</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>9.8019382778112742</v>
+        <v>9.4821523652815003</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18885,23 +18882,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>5.0343778761174471</v>
+        <v>4.885004475793159</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>6.0897307232649505</v>
+        <v>5.918029851448563</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>7.2738148750712952</v>
+        <v>7.0767198455769105</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>8.6018936542504889</v>
+        <v>8.3759529837533027</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>10.090912496359509</v>
+        <v>9.8322460971195973</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18924,7 +18921,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G73" s="332"/>
       <c r="H73" s="332"/>
@@ -18948,7 +18945,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.9394287592757706</v>
+        <v>7.2208568518331298</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18976,7 +18973,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>7.7066443228395842</v>
+        <v>7.0018246699125335</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -19004,7 +19001,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>7.4760630503385492</v>
+        <v>6.7848627799027819</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19032,7 +19029,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>7.2476849417726426</v>
+        <v>6.5699711818038571</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19060,7 +19057,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.0215099971418917</v>
+        <v>6.3571498756157778</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19340,7 +19337,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19370,35 +19367,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E20" s="328"/>
       <c r="F20" s="328"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="154" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C21" s="154" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E21" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G21" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="310" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C22" s="333">
         <v>0.03</v>
@@ -19409,7 +19406,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>7.7066443228395842</v>
+        <v>7.0018246699125335</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19422,7 +19419,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="310" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C23" s="333">
         <v>0.02</v>
@@ -19433,7 +19430,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>7.4760630503385492</v>
+        <v>6.7848627799027819</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19445,7 +19442,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="310" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C24" s="333">
         <v>0.01</v>
@@ -19456,7 +19453,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>7.2476849417726426</v>
+        <v>6.5699711818038571</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19468,11 +19465,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="142" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>7.476503683125574</v>
+        <v>6.7852768382849469</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19482,33 +19479,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="154" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C28" s="154" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D28" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E28" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G28" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="310" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C29" s="333">
         <v>0.04</v>
@@ -19519,7 +19516,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>7.9394287592757706</v>
+        <v>7.2208568518331298</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19531,7 +19528,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="323" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C30" s="333">
         <v>0</v>
@@ -19542,7 +19539,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>7.0215099971418917</v>
+        <v>6.3571498756157778</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19558,12 +19555,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="146" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C33" s="156">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19574,7 +19571,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F33" s="223">
         <f>Holding_Period</f>
@@ -19587,23 +19584,23 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>6.43</v>
+        <v>6.49</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13834890491956828</v>
+        <v>8.3497774291450236E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
@@ -19614,35 +19611,35 @@
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.83135387789665138</v>
+        <v>0.75280838141092954</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>7.4769002526339001</v>
+        <v>6.7856494908288969</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F36" s="340" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19661,18 +19658,18 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="139">
         <v>0.86799999999999999</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C41" s="139">
         <v>0.02</v>
@@ -19728,7 +19725,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>7.4805328351798659</v>
+        <v>6.7890685811450933</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19791,7 +19788,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.59543285068002583</v>
+        <v>0.65608930105999008</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19834,13 +19831,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E60" s="422"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="154" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C61" s="154" t="s">
         <v>103</v>
@@ -19853,10 +19850,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G61" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -19869,11 +19866,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>4.1025515789486411</v>
+        <v>3.7232644668471311</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>4.6183266132421945</v>
+        <v>4.2390395011406845</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19881,7 +19878,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.38232068675581321</v>
+        <v>0.37529347678951996</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19894,11 +19891,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.7852161616856961</v>
+        <v>4.3428156741304944</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>5.3612161616856966</v>
+        <v>4.918815674130494</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19906,12 +19903,12 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.28296272779657694</v>
+        <v>0.27511497893038994</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="154" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C65" s="154" t="s">
         <v>103</v>
@@ -19924,10 +19921,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G65" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -19940,11 +19937,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.9883096997382061</v>
+        <v>5.4346813909467224</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>6.6666467929077449</v>
+        <v>6.1130184841162611</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19952,7 +19949,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.10880054405276218</v>
+        <v>9.9579211632415787E-2</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19965,11 +19962,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.5002039785777299</v>
+        <v>5.8992502677806771</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>7.2209129510349541</v>
+        <v>6.6199592402379013</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19977,7 +19974,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>3.4237089294961387E-2</v>
+        <v>2.4417743771606992E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20021,7 +20018,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="445" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F3" s="446">
         <f>Thesis!F3</f>
@@ -20030,7 +20027,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="432" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C4" s="433" t="str">
         <f>Thesis!C4</f>
@@ -20038,7 +20035,7 @@
       </c>
       <c r="D4" s="358"/>
       <c r="E4" s="444" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F4" s="447" t="str">
         <f>Thesis!F4</f>
@@ -20047,14 +20044,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="352" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C5" s="364" t="str">
         <f>Thesis!C5</f>
         <v>0341.HK</v>
       </c>
       <c r="E5" s="448" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F5" s="449" t="str">
         <f>Thesis!F5</f>
@@ -20073,7 +20070,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="352" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C7" s="361" t="str">
         <f>Market_currency</f>
@@ -20084,23 +20081,23 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="360" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>6.43</v>
+        <v>6.49</v>
       </c>
       <c r="D8" s="352" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.13834890491956828</v>
+        <v>8.3497774291450236E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="360" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C9" s="362">
         <f>Common_Shares</f>
@@ -20109,11 +20106,11 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="360" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3729.4259321899999</v>
+        <v>3764.2261741699999</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20123,7 +20120,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
       <c r="B12" s="472" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C12" s="472"/>
       <c r="D12" s="472"/>
@@ -20132,7 +20129,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C14" s="357"/>
       <c r="D14" s="358"/>
@@ -20146,7 +20143,7 @@
         <v>N</v>
       </c>
       <c r="D15" s="360" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E15" s="353" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20162,7 +20159,7 @@
         <v>N</v>
       </c>
       <c r="D16" s="360" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
@@ -20171,7 +20168,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="352" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C17" s="434">
         <f>Terminal_Growth</f>
@@ -20192,10 +20189,10 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>7.4769002526339001</v>
+        <v>6.7856494908288969</v>
       </c>
       <c r="D18" s="359" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E18" s="436">
         <f>Thesis!E18</f>
@@ -20211,7 +20208,7 @@
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="352" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E19" s="437">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20224,14 +20221,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="356" t="s">
-        <v>342</v>
+        <v>499</v>
       </c>
       <c r="C21" s="370" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="371" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E21" s="372">
         <f>Holding_Period</f>
@@ -20240,14 +20237,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="352" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>4.6183266132421945</v>
+        <v>4.2390395011406845</v>
       </c>
       <c r="D22" s="374" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E22" s="375">
         <f>Thesis!E22</f>
@@ -20256,14 +20253,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="352" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>5.3612161616856966</v>
+        <v>4.918815674130494</v>
       </c>
       <c r="D23" s="374" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E23" s="377">
         <f>Thesis!E23</f>
@@ -20272,14 +20269,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="352" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>6.6666467929077449</v>
+        <v>6.1130184841162611</v>
       </c>
       <c r="D24" s="374" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E24" s="377">
         <f>Thesis!E24</f>
@@ -20288,14 +20285,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="352" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>7.2209129510349541</v>
+        <v>6.6199592402379013</v>
       </c>
       <c r="D25" s="374" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E25" s="377">
         <f>Thesis!E25</f>
@@ -20304,7 +20301,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="354" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B27" s="354"/>
       <c r="C27" s="354"/>
@@ -20314,7 +20311,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="472" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C29" s="472"/>
       <c r="D29" s="472"/>
@@ -20323,7 +20320,7 @@
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
       <c r="B30" s="475" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C30" s="475"/>
       <c r="D30" s="475"/>
@@ -20332,7 +20329,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C32" s="379">
         <f>scaling_factor</f>
@@ -20341,7 +20338,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="468" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C33" s="468"/>
       <c r="D33" s="468"/>
@@ -20367,7 +20364,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="468" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C36" s="468"/>
       <c r="D36" s="468"/>
@@ -20402,7 +20399,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="468" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C40" s="468"/>
       <c r="D40" s="468"/>
@@ -20424,7 +20421,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="468" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C43" s="468"/>
       <c r="D43" s="468"/>
@@ -20476,7 +20473,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="352" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20494,7 +20491,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="468" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C51" s="468"/>
       <c r="D51" s="468"/>
@@ -20503,7 +20500,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="381" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C52" s="382">
         <f>Normalized_FCF!C12</f>
@@ -20516,7 +20513,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="468" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C54" s="474"/>
       <c r="D54" s="474"/>
@@ -20538,7 +20535,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="472" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C57" s="472"/>
       <c r="D57" s="472"/>
@@ -20547,7 +20544,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="472" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C58" s="472"/>
       <c r="D58" s="472"/>
@@ -20556,7 +20553,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C60" s="382">
         <f>Normalized_FCF!G19</f>
@@ -20586,7 +20583,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>6.1728434016460706E-2</v>
+        <v>6.1157755119544271E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20596,10 +20593,10 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>6.2208398133748059E-2</v>
+        <v>6.1633281972265024E-2</v>
       </c>
       <c r="E63" s="381" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F63" s="389">
         <f>Normalized_FCF!C90</f>
@@ -20608,13 +20605,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="378" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C65" s="390" t="s">
         <v>328</v>
       </c>
       <c r="D65" s="390" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -20674,7 +20671,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="354" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B71" s="354"/>
       <c r="C71" s="354"/>
@@ -20688,7 +20685,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
       <c r="B73" s="472" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C73" s="472"/>
       <c r="D73" s="472"/>
@@ -20697,7 +20694,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="475" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C74" s="475"/>
       <c r="D74" s="475"/>
@@ -20706,12 +20703,12 @@
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="472" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C77" s="472"/>
       <c r="D77" s="472"/>
@@ -20764,7 +20761,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="352" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20782,7 +20779,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="391" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C85" s="399">
         <f>BS!C66</f>
@@ -20808,7 +20805,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="352" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20839,7 +20836,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="381" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
@@ -20852,7 +20849,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="354" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B94" s="354"/>
       <c r="C94" s="354"/>
@@ -20866,7 +20863,7 @@
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
       <c r="B96" s="472" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C96" s="472"/>
       <c r="D96" s="472"/>
@@ -20876,7 +20873,7 @@
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
       <c r="B97" s="475" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C97" s="475"/>
       <c r="D97" s="475"/>
@@ -20886,7 +20883,7 @@
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
       <c r="B98" s="475" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C98" s="475"/>
       <c r="D98" s="475"/>
@@ -20899,7 +20896,7 @@
     <row r="100" spans="1:6">
       <c r="A100" s="394"/>
       <c r="B100" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -20935,7 +20932,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="394"/>
       <c r="B104" s="381" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C104" s="377">
         <v>0</v>
@@ -20948,14 +20945,14 @@
     <row r="106" spans="1:6">
       <c r="A106" s="394"/>
       <c r="B106" s="402" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C106" s="401"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
       <c r="B107" s="472" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C107" s="472"/>
       <c r="D107" s="472"/>
@@ -20965,7 +20962,7 @@
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
       <c r="B108" s="472" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C108" s="472"/>
       <c r="D108" s="472"/>
@@ -20978,13 +20975,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="394"/>
       <c r="B110" s="378" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="394"/>
       <c r="B111" s="384" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
@@ -20998,7 +20995,7 @@
     <row r="112" spans="1:6">
       <c r="A112" s="394"/>
       <c r="B112" s="381" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
@@ -21015,7 +21012,7 @@
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
       <c r="B114" s="472" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C114" s="472"/>
       <c r="D114" s="472"/>
@@ -21028,25 +21025,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="394"/>
       <c r="B116" s="378" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="394"/>
       <c r="B117" s="351" t="s">
+        <v>380</v>
+      </c>
+      <c r="C117" s="351" t="s">
         <v>381</v>
-      </c>
-      <c r="C117" s="351" t="s">
-        <v>382</v>
       </c>
       <c r="D117" s="351" t="s">
         <v>99</v>
       </c>
       <c r="E117" s="351" t="s">
+        <v>382</v>
+      </c>
+      <c r="F117" s="351" t="s">
         <v>383</v>
-      </c>
-      <c r="F117" s="351" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21065,7 +21062,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.22 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -21088,7 +21085,7 @@
       </c>
       <c r="E119" s="407" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>7.71 HKD</v>
+        <v>7 HKD</v>
       </c>
       <c r="F119" s="412">
         <f>DCF!F75</f>
@@ -21110,7 +21107,7 @@
       </c>
       <c r="E120" s="407" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>7.48 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="F120" s="412">
         <f>DCF!F76</f>
@@ -21132,7 +21129,7 @@
       </c>
       <c r="E121" s="407" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>7.25 HKD</v>
+        <v>6.57 HKD</v>
       </c>
       <c r="F121" s="412">
         <f>DCF!F77</f>
@@ -21154,7 +21151,7 @@
       </c>
       <c r="E122" s="407" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.02 HKD</v>
+        <v>6.36 HKD</v>
       </c>
       <c r="F122" s="412">
         <f>DCF!F78</f>
@@ -21163,7 +21160,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="468" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C124" s="468"/>
       <c r="D124" s="468"/>
@@ -21176,7 +21173,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>7.4769002526339001</v>
+        <v>6.7856494908288969</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21185,7 +21182,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="B127" s="470" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C127" s="470"/>
       <c r="D127" s="470"/>
@@ -21194,7 +21191,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B129" s="354"/>
       <c r="C129" s="354"/>
@@ -21204,7 +21201,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="471" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C131" s="471"/>
       <c r="D131" s="471"/>
@@ -21213,7 +21210,7 @@
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
       <c r="B132" s="472" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C132" s="472"/>
       <c r="D132" s="472"/>
@@ -21222,12 +21219,12 @@
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="352" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C135" s="414">
         <f>E21</f>
@@ -21236,7 +21233,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="352" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C136" s="415">
         <f>Scenarios!C58</f>
@@ -21249,28 +21246,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="378" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C138" s="416"/>
       <c r="D138" s="416"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="349" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21283,11 +21280,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>4.1025515789486411</v>
+        <v>3.7232644668471311</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>4.6183266132421945</v>
+        <v>4.2390395011406845</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21304,11 +21301,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>4.7852161616856961</v>
+        <v>4.3428156741304944</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>5.3612161616856966</v>
+        <v>4.918815674130494</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21317,21 +21314,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="349" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21344,11 +21341,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>5.9883096997382061</v>
+        <v>5.4346813909467224</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>6.6666467929077449</v>
+        <v>6.1130184841162611</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21365,11 +21362,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>6.5002039785777299</v>
+        <v>5.8992502677806771</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>7.2209129510349541</v>
+        <v>6.6199592402379013</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21378,7 +21375,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="354" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B147" s="354"/>
       <c r="C147" s="354"/>
@@ -21388,7 +21385,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="473" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C149" s="472"/>
       <c r="D149" s="472"/>
@@ -21397,12 +21394,12 @@
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="474" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C152" s="474"/>
       <c r="D152" s="474"/>
@@ -21411,27 +21408,27 @@
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="421" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="421" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="352" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="468" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C158" s="468"/>
       <c r="D158" s="468"/>
@@ -21440,12 +21437,12 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="352" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C161" s="469"/>
       <c r="D161" s="469"/>
@@ -21454,7 +21451,7 @@
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="469" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C162" s="469"/>
       <c r="D162" s="469"/>
@@ -21463,22 +21460,22 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="421" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="421" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="421" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -21533,7 +21530,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E51FA99-13FB-4FB6-B039-08E5CC95A8B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F415E07E-1A44-4C99-8F2C-ED00B47794AD}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352CDBD2-FAC4-4640-B68C-1C83C6816A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549B86BE-9645-43CC-8771-54747B7D28D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3824,6 +3824,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4987,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5020,6 +5021,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5029,16 +5039,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5507,13 +5508,6 @@
       <c r="C9" s="48">
         <v>580004033</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E9" s="311">
-        <f>Scenarios!F34</f>
-        <v>8.3497774291450236E-2</v>
-      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
@@ -5523,19 +5517,26 @@
         <f>Thesis!C8*Common_Shares/1000000</f>
         <v>3764.2261741699999</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E10" s="311">
+        <f>Scenarios!F34</f>
+        <v>8.3497774291450236E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5713,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5740,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5766,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5801,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5823,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5893,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5915,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5937,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6087,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6112,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6287,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6361,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6410,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6551,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6592,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6783,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6826,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6840,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6879,6 +6880,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6895,18 +6908,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20119,13 +20120,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>504</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20310,22 +20311,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20515,10 +20516,10 @@
       <c r="B54" s="468" t="s">
         <v>513</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20534,22 +20535,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20684,22 +20685,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>516</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20707,13 +20708,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>517</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20862,33 +20863,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>520</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>522</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20951,23 +20952,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>542</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21011,13 +21012,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21181,13 +21182,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21200,22 +21201,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>528</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21384,13 +21385,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>529</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21398,13 +21399,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21441,22 +21442,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21480,12 +21481,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21500,15 +21504,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549B86BE-9645-43CC-8771-54747B7D28D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F2C652-CB2C-4858-8D11-B40B43FFED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4988,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5021,25 +5021,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5497,7 +5497,7 @@
         <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5515,14 +5515,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3764.2261741699999</v>
+        <v>3770.0262145000002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>534</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>8.3497774291450236E-2</v>
+        <v>8.2639604252926629E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5530,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5714,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5767,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5802,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5894,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5938,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1157755119544271E-2</v>
+        <v>6.1063666265514203E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1633281972265024E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6088,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6288,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
+      <c r="B97" s="464" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
+      <c r="B98" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6362,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6411,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="460" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6552,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6593,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6784,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6827,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="461" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6841,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="464" t="s">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6880,18 +6880,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6908,6 +6896,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14332,24 +14332,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1633281972265024E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1633281972265024E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7827426810477643E-2</v>
+        <v>8.7692307692307681E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8551617873651769E-2</v>
+        <v>5.8461538461538461E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8551617873651769E-2</v>
+        <v>5.8461538461538461E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15531,50 +15531,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1157755119544271E-2</v>
+        <v>6.1063666265514203E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6775580634436527E-2</v>
+        <v>7.6657464356537391E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.2232348623699223E-2</v>
+        <v>9.2090452702739689E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8933976406720942E-2</v>
+        <v>2.8889462596864448E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3429021146902097E-3</v>
+        <v>-6.333143803744533E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1572757454247653E-2</v>
+        <v>-3.152418398124112E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5420155523996574E-2</v>
+        <v>5.533489374626735E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14818317874403283</v>
+        <v>0.14795520462288819</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12222963730425963</v>
+        <v>0.12204159170840694</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13744020047203337</v>
+        <v>0.13722875400976869</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13400098098813651</v>
+        <v>0.13379482563277015</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15588,43 +15588,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2459318096591589E-2</v>
+        <v>6.2363226837981449E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8521514006387469E-2</v>
+        <v>8.8385327061762262E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9537810656267587E-2</v>
+        <v>2.949236787064256E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0703047433217404E-3</v>
+        <v>6.0609658129473993E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5783298696046112E-2</v>
+        <v>9.5635939774975268E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9761299283883194E-2</v>
+        <v>1.9730897284984915E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1572992622130519</v>
+        <v>0.15705726334810874</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1220157819292761</v>
+        <v>0.1218280653416926</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13385221203162623</v>
+        <v>0.13364628555157756</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13757409253289263</v>
+        <v>0.13736244008284204</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>8.3497774291450236E-2</v>
+        <v>8.2639604252926629E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20086,14 +20086,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="D8" s="352" t="s">
         <v>535</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>8.3497774291450236E-2</v>
+        <v>8.2639604252926629E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3764.2261741699999</v>
+        <v>3770.0262145000002</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20120,13 +20120,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="469" t="s">
+      <c r="B12" s="472" t="s">
         <v>504</v>
       </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20311,22 +20311,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="472" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="470" t="s">
+      <c r="B30" s="475" t="s">
         <v>506</v>
       </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20516,10 +20516,10 @@
       <c r="B54" s="468" t="s">
         <v>513</v>
       </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20535,22 +20535,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
+      <c r="B58" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>6.1157755119544271E-2</v>
+        <v>6.1063666265514203E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>6.1633281972265024E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>375</v>
@@ -20685,22 +20685,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
+      <c r="B73" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
+      <c r="B74" s="475" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20708,13 +20708,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
+      <c r="B77" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20863,33 +20863,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
+      <c r="B96" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
+      <c r="B97" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
+      <c r="B98" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20952,23 +20952,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
+      <c r="B107" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
+      <c r="B108" s="472" t="s">
         <v>542</v>
       </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21012,13 +21012,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
+      <c r="B114" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21182,13 +21182,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="470" t="s">
         <v>526</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21201,22 +21201,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="471" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="469" t="s">
+      <c r="B132" s="472" t="s">
         <v>528</v>
       </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21385,13 +21385,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="473" t="s">
         <v>529</v>
       </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21399,13 +21399,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
+      <c r="B152" s="474" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21442,22 +21442,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21481,15 +21481,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21504,12 +21501,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F2C652-CB2C-4858-8D11-B40B43FFED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0843792D-43F0-4A29-A35B-3D57B08E0D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4988,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5021,6 +5021,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5030,16 +5039,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5530,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5714,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5767,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5802,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5894,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5938,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6088,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6288,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6362,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6411,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6552,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6593,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6784,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6827,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6841,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6880,6 +6880,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6896,18 +6908,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20120,13 +20120,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>504</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20311,22 +20311,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20516,10 +20516,10 @@
       <c r="B54" s="468" t="s">
         <v>513</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20535,22 +20535,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20685,22 +20685,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>516</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20708,13 +20708,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>517</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20863,33 +20863,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>520</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>522</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20952,23 +20952,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>542</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21012,13 +21012,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21182,13 +21182,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21201,22 +21201,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>528</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21385,13 +21385,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>529</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21399,13 +21399,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21442,22 +21442,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21481,12 +21481,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21501,15 +21504,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0843792D-43F0-4A29-A35B-3D57B08E0D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA2690A-EFB8-4AAC-B7C5-473CFDCB91B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4988,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5021,25 +5021,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5530,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5714,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5767,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5802,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5894,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5938,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6088,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6288,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
+      <c r="B97" s="464" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
+      <c r="B98" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6362,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6411,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="460" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6552,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6593,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6784,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6827,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="461" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6841,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="464" t="s">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6880,18 +6880,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6908,6 +6896,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20120,13 +20120,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="469" t="s">
+      <c r="B12" s="472" t="s">
         <v>504</v>
       </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20311,22 +20311,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="472" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="470" t="s">
+      <c r="B30" s="475" t="s">
         <v>506</v>
       </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20516,10 +20516,10 @@
       <c r="B54" s="468" t="s">
         <v>513</v>
       </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20535,22 +20535,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
+      <c r="B58" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20685,22 +20685,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
+      <c r="B73" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
+      <c r="B74" s="475" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20708,13 +20708,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
+      <c r="B77" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20863,33 +20863,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
+      <c r="B96" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
+      <c r="B97" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
+      <c r="B98" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20952,23 +20952,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
+      <c r="B107" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
+      <c r="B108" s="472" t="s">
         <v>542</v>
       </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21012,13 +21012,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
+      <c r="B114" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21182,13 +21182,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="470" t="s">
         <v>526</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21201,22 +21201,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="471" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="469" t="s">
+      <c r="B132" s="472" t="s">
         <v>528</v>
       </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21385,13 +21385,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="473" t="s">
         <v>529</v>
       </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21399,13 +21399,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
+      <c r="B152" s="474" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21442,22 +21442,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21481,15 +21481,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21504,12 +21501,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FD4439-4950-4EED-9C86-EEE7B1E9C0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7B8430-5A98-47EF-BE34-2C89C2EC3507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,65 +4992,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>8.2639604252926629E-2</v>
+        <v>0.15535566535489756</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5539,13 +5539,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>6.7856494908288969</v>
+        <v>7.8143613713918958</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>348</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>4.2390395011406845</v>
+        <v>4.8034904644125618</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>410</v>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>4.918815674130494</v>
+        <v>5.5771912776908135</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>411</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>6.1130184841162611</v>
+        <v>6.9369221239222432</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>412</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>6.6199592402379013</v>
+        <v>7.5142920296167883</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>413</v>
@@ -5723,22 +5723,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="464" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5750,13 +5750,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5776,13 +5776,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5903,13 +5903,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5925,13 +5925,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="463"/>
-      <c r="D54" s="463"/>
-      <c r="E54" s="463"/>
-      <c r="F54" s="463"/>
+      <c r="C54" s="466"/>
+      <c r="D54" s="466"/>
+      <c r="E54" s="466"/>
+      <c r="F54" s="466"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5947,22 +5947,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6097,13 +6097,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6122,13 +6122,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6297,31 +6297,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="464" t="s">
         <v>488</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6371,22 +6371,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6420,13 +6420,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="462" t="s">
         <v>496</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6457,15 +6457,15 @@
       </c>
       <c r="C118" s="208">
         <f>DCF!C82</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D118" s="209">
         <f>DCF!D82</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.22 HKD</v>
+        <v>9.36 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6479,15 +6479,15 @@
       </c>
       <c r="C119" s="199">
         <f>DCF!C83</f>
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D119" s="200">
         <f>DCF!D83</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>7 HKD</v>
+        <v>8.56 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6501,15 +6501,15 @@
       </c>
       <c r="C120" s="199">
         <f>DCF!C84</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D120" s="200">
         <f>DCF!D84</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E120" s="210" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>7.8 HKD</v>
       </c>
       <c r="F120" s="201">
         <f>DCF!F84</f>
@@ -6523,15 +6523,15 @@
       </c>
       <c r="C121" s="199">
         <f>DCF!C85</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D121" s="200">
         <f>DCF!D85</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E121" s="210" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>6.57 HKD</v>
+        <v>7.08 HKD</v>
       </c>
       <c r="F121" s="201">
         <f>DCF!F85</f>
@@ -6545,15 +6545,15 @@
       </c>
       <c r="C122" s="199">
         <f>DCF!C86</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D122" s="200">
         <f>DCF!D86</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E122" s="210" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>6.36 HKD</v>
+        <v>6.4 HKD</v>
       </c>
       <c r="F122" s="201">
         <f>DCF!F86</f>
@@ -6561,13 +6561,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="463" t="s">
         <v>358</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.7856494908288969</v>
+        <v>7.8143613713918958</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6583,13 +6583,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="464" t="s">
+      <c r="B127" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C127" s="464"/>
-      <c r="D127" s="464"/>
-      <c r="E127" s="464"/>
-      <c r="F127" s="464"/>
+      <c r="C127" s="467"/>
+      <c r="D127" s="467"/>
+      <c r="E127" s="467"/>
+      <c r="F127" s="467"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="202" t="s">
@@ -6602,22 +6602,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="465" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>3.7232644668471311</v>
+        <v>4.2877154301190092</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>4.2390395011406845</v>
+        <v>4.8034904644125618</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
@@ -6703,11 +6703,11 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>4.3428156741304944</v>
+        <v>5.001191277690813</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>4.918815674130494</v>
+        <v>5.5771912776908135</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>5.4346813909467224</v>
+        <v>6.2585850307527044</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>6.1130184841162611</v>
+        <v>6.9369221239222432</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6771,11 +6771,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>5.8992502677806771</v>
+        <v>6.7935830571595641</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>6.6199592402379013</v>
+        <v>7.5142920296167883</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6793,13 +6793,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="469" t="s">
         <v>361</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6807,13 +6807,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="463" t="s">
+      <c r="B152" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="463"/>
-      <c r="D152" s="463"/>
-      <c r="E152" s="463"/>
-      <c r="F152" s="463"/>
+      <c r="C152" s="466"/>
+      <c r="D152" s="466"/>
+      <c r="E152" s="466"/>
+      <c r="F152" s="466"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6836,13 +6836,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="463" t="s">
         <v>443</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6850,22 +6850,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="468" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="468"/>
+      <c r="D161" s="468"/>
+      <c r="E161" s="468"/>
+      <c r="F161" s="468"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="468" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="468"/>
+      <c r="D162" s="468"/>
+      <c r="E162" s="468"/>
+      <c r="F162" s="468"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6889,6 +6889,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6905,18 +6917,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E15" s="315" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="F15" s="317">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>434</v>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>2.0194760895005201E-2</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E16" s="315" t="s">
         <v>402</v>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.7890685811450933</v>
+        <v>7.8099395838685268</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16776,11 +16776,11 @@
       </c>
       <c r="C21" s="284">
         <f>I4*(1+D21)</f>
-        <v>8363700.2422298491</v>
+        <v>8445311.6025161762</v>
       </c>
       <c r="D21" s="306">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>2.0194760895005201E-2</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E21" s="306">
         <f>$C$17</f>
@@ -16788,11 +16788,11 @@
       </c>
       <c r="F21" s="284">
         <f>I5*(1+D21)</f>
-        <v>-504479.16789925384</v>
+        <v>-509401.77750217711</v>
       </c>
       <c r="G21" s="284">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>328500.21314532199</v>
+        <v>332473.397313744</v>
       </c>
       <c r="H21" s="306">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16800,11 +16800,11 @@
       </c>
       <c r="I21" s="284">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>236187.44060889343</v>
+        <v>239133.17710545129</v>
       </c>
       <c r="J21" s="306">
         <f>I21/C4-1</f>
-        <v>2.5957933694214397E-2</v>
+        <v>3.8753710308859324E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="L21" s="284">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>220221.38984512206</v>
+        <v>222967.99730112008</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16825,11 +16825,11 @@
       </c>
       <c r="C22" s="284">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>8532603.1688191779</v>
+        <v>8699934.5630403273</v>
       </c>
       <c r="D22" s="306">
         <f t="shared" si="1"/>
-        <v>2.0194760895005201E-2</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E22" s="306">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16837,11 +16837,11 @@
       </c>
       <c r="F22" s="284">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
-        <v>-514667.00407149049</v>
+        <v>-524760.04902471334</v>
       </c>
       <c r="G22" s="284">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>336723.11779450835</v>
+        <v>344869.51364022063</v>
       </c>
       <c r="H22" s="306">
         <f t="shared" si="2"/>
@@ -16849,11 +16849,11 @@
       </c>
       <c r="I22" s="284">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>242283.93885967648</v>
+        <v>248323.71314168588</v>
       </c>
       <c r="J22" s="306">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>2.5812118692959407E-2</v>
+        <v>3.8432709954678623E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16861,36 +16861,36 @@
       </c>
       <c r="L22" s="284">
         <f t="shared" si="4"/>
-        <v>210634.75104758309</v>
+        <v>215885.55866719777</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="309" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B23" s="117">
         <v>3</v>
       </c>
       <c r="C23" s="284">
         <f t="shared" si="5"/>
-        <v>8703255.2321955618</v>
+        <v>8962234.3098190855</v>
       </c>
       <c r="D23" s="306">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E23" s="306">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.89099809462634716</v>
       </c>
       <c r="F23" s="284">
         <f t="shared" si="7"/>
-        <v>-524960.3441529203</v>
+        <v>-540581.36664284149</v>
       </c>
       <c r="G23" s="284">
         <f t="shared" si="8"/>
-        <v>545189.4651643344</v>
+        <v>357639.36820000387</v>
       </c>
       <c r="H23" s="306">
         <f t="shared" si="2"/>
@@ -16898,11 +16898,11 @@
       </c>
       <c r="I23" s="284">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>415575.74162350647</v>
+        <v>257791.34037413541</v>
       </c>
       <c r="J23" s="306">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>0.71524263465187987</v>
+        <v>3.8126150389220292E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16910,7 +16910,7 @@
       </c>
       <c r="L23" s="284">
         <f t="shared" si="4"/>
-        <v>336866.85812223703</v>
+        <v>208966.38129958435</v>
       </c>
       <c r="N23" s="282"/>
       <c r="O23" s="282"/>
@@ -16924,30 +16924,30 @@
     <row r="24" spans="1:21">
       <c r="A24" s="309" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B24" s="117">
         <v>4</v>
       </c>
       <c r="C24" s="284">
         <f t="shared" si="5"/>
-        <v>8877320.3368394729</v>
+        <v>9232442.2950635087</v>
       </c>
       <c r="D24" s="306">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E24" s="306">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.89099809462634716</v>
       </c>
       <c r="F24" s="284">
         <f t="shared" si="7"/>
-        <v>-535459.55103597871</v>
+        <v>-556879.69102175278</v>
       </c>
       <c r="G24" s="284">
         <f t="shared" si="8"/>
-        <v>557666.85209427227</v>
+        <v>370794.22905991052</v>
       </c>
       <c r="H24" s="306">
         <f t="shared" si="2"/>
@@ -16955,11 +16955,11 @@
       </c>
       <c r="I24" s="284">
         <f t="shared" si="9"/>
-        <v>425201.21047423029</v>
+        <v>267544.41299788898</v>
       </c>
       <c r="J24" s="306">
         <f t="shared" si="10"/>
-        <v>2.3161767847951209E-2</v>
+        <v>3.7833204985081359E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16967,7 +16967,7 @@
       </c>
       <c r="L24" s="284">
         <f t="shared" si="4"/>
-        <v>321369.96744590485</v>
+        <v>202211.88740166169</v>
       </c>
       <c r="N24" s="282"/>
       <c r="O24" s="282"/>
@@ -16981,30 +16981,30 @@
     <row r="25" spans="1:21">
       <c r="A25" s="309" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B25" s="117">
         <v>5</v>
       </c>
       <c r="C25" s="284">
         <f t="shared" si="5"/>
-        <v>9054866.7435762621</v>
+        <v>9510796.9491815474</v>
       </c>
       <c r="D25" s="306">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E25" s="306">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.89099809462634716</v>
       </c>
       <c r="F25" s="284">
         <f t="shared" si="7"/>
-        <v>-546168.74205669831</v>
+        <v>-573669.4037354301</v>
       </c>
       <c r="G25" s="284">
         <f t="shared" si="8"/>
-        <v>570393.78676280892</v>
+        <v>384345.70401472354</v>
       </c>
       <c r="H25" s="306">
         <f t="shared" si="2"/>
@@ -17012,11 +17012,11 @@
       </c>
       <c r="I25" s="284">
         <f t="shared" si="9"/>
-        <v>435019.1887019687</v>
+        <v>277591.53708386794</v>
       </c>
       <c r="J25" s="306">
         <f t="shared" si="10"/>
-        <v>2.3090193503420009E-2</v>
+        <v>3.7553107438869304E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="L25" s="284">
         <f t="shared" si="4"/>
-        <v>306564.53350155585</v>
+        <v>195622.91108128006</v>
       </c>
       <c r="N25" s="282"/>
       <c r="O25" s="282"/>
@@ -17038,30 +17038,30 @@
     <row r="26" spans="1:21">
       <c r="A26" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B26" s="117">
         <v>6</v>
       </c>
       <c r="C26" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9797543.8911680523</v>
       </c>
       <c r="D26" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E26" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.89099809462634716</v>
       </c>
       <c r="F26" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-590965.31995688961</v>
       </c>
       <c r="G26" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>398305.75082986127</v>
       </c>
       <c r="H26" s="306">
         <f t="shared" si="2"/>
@@ -17069,48 +17069,48 @@
       </c>
       <c r="I26" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>287941.57817278628</v>
       </c>
       <c r="J26" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3.7285146361617283E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.65707689293158289</v>
       </c>
       <c r="L26" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>189199.75753159091</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B27" s="117">
         <v>7</v>
       </c>
       <c r="C27" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10092936.145337958</v>
       </c>
       <c r="D27" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="E27" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.89099809462634716</v>
       </c>
       <c r="F27" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-608782.70153102756</v>
       </c>
       <c r="G27" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>412686.68779286148</v>
       </c>
       <c r="H27" s="306">
         <f t="shared" si="2"/>
@@ -17118,48 +17118,48 @@
       </c>
       <c r="I27" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>298603.66909806867</v>
       </c>
       <c r="J27" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3.7028660441960737E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.61265910762851561</v>
       </c>
       <c r="L27" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>182942.2574442233</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B28" s="117">
         <v>8</v>
       </c>
       <c r="C28" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10294794.868244717</v>
       </c>
       <c r="D28" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E28" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F28" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-620958.35556164815</v>
       </c>
       <c r="G28" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>659274.68571409502</v>
       </c>
       <c r="H28" s="306">
         <f t="shared" si="2"/>
@@ -17167,48 +17167,48 @@
       </c>
       <c r="I28" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>503584.85305811919</v>
       </c>
       <c r="J28" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.68646572421295238</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5712439231967511</v>
       </c>
       <c r="L28" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>287669.78712337941</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B29" s="117">
         <v>9</v>
       </c>
       <c r="C29" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10500690.765609611</v>
       </c>
       <c r="D29" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E29" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F29" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-633377.52267288114</v>
       </c>
       <c r="G29" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>674033.77705502813</v>
       </c>
       <c r="H29" s="306">
         <f t="shared" si="2"/>
@@ -17216,48 +17216,48 @@
       </c>
       <c r="I29" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>514970.50413753535</v>
       </c>
       <c r="J29" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2609200833334286E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.53262836661701729</v>
       </c>
       <c r="L29" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>274287.8984747174</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B30" s="117">
         <v>10</v>
       </c>
       <c r="C30" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10710704.580921803</v>
       </c>
       <c r="D30" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E30" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F30" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-646045.07312633877</v>
       </c>
       <c r="G30" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>689088.05022277974</v>
       </c>
       <c r="H30" s="306">
         <f t="shared" si="2"/>
@@ -17265,48 +17265,48 @@
       </c>
       <c r="I30" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>526583.86823853967</v>
       </c>
       <c r="J30" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2551513159873471E-2</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.49662318565689262</v>
       </c>
       <c r="L30" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>261513.75816015297</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B31" s="117">
         <v>11</v>
       </c>
       <c r="C31" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10924918.672540238</v>
       </c>
       <c r="D31" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E31" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F31" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-658965.97458886553</v>
       </c>
       <c r="G31" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>704443.40885388653</v>
       </c>
       <c r="H31" s="306">
         <f t="shared" si="2"/>
@@ -17314,48 +17314,48 @@
       </c>
       <c r="I31" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>538429.49962156429</v>
       </c>
       <c r="J31" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2495241684195699E-2</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.46305192135840806</v>
       </c>
       <c r="L31" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>249320.81431581159</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B32" s="117">
         <v>12</v>
       </c>
       <c r="C32" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11143417.045991043</v>
       </c>
       <c r="D32" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E32" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F32" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-672145.29408064287</v>
       </c>
       <c r="G32" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>720105.8746576152</v>
       </c>
       <c r="H32" s="306">
         <f t="shared" si="2"/>
@@ -17363,48 +17363,48 @@
       </c>
       <c r="I32" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>550512.04363224912</v>
       </c>
       <c r="J32" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2440345521887339E-2</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.43175004322462285</v>
       </c>
       <c r="L32" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>237683.598633899</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B33" s="117">
         <v>13</v>
       </c>
       <c r="C33" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11366285.386910863</v>
       </c>
       <c r="D33" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E33" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F33" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-685588.19996225578</v>
       </c>
       <c r="G33" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>736081.58977741865</v>
       </c>
       <c r="H33" s="306">
         <f t="shared" si="2"/>
@@ -17412,19 +17412,19 @@
       </c>
       <c r="I33" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>562836.23852314777</v>
       </c>
       <c r="J33" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2386785236494067E-2</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.40256414286678116</v>
       </c>
       <c r="L33" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>226577.68793543417</v>
       </c>
       <c r="N33" s="282"/>
       <c r="O33" s="282"/>
@@ -17438,30 +17438,30 @@
     <row r="34" spans="1:21">
       <c r="A34" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B34" s="117">
         <v>14</v>
       </c>
       <c r="C34" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11593611.09464908</v>
       </c>
       <c r="D34" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E34" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F34" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-699299.96396150091</v>
       </c>
       <c r="G34" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>752376.81919961818</v>
       </c>
       <c r="H34" s="306">
         <f t="shared" si="2"/>
@@ -17469,19 +17469,19 @@
       </c>
       <c r="I34" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>575406.91731186444</v>
       </c>
       <c r="J34" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2334522776467747E-2</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.37535118216016894</v>
       </c>
       <c r="L34" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>215979.6666361469</v>
       </c>
       <c r="N34" s="282"/>
       <c r="O34" s="282"/>
@@ -17495,30 +17495,30 @@
     <row r="35" spans="1:21">
       <c r="A35" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11825483.316542063</v>
       </c>
       <c r="D35" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E35" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F35" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-713285.96324073093</v>
       </c>
       <c r="G35" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>768997.953210262</v>
       </c>
       <c r="H35" s="306">
         <f t="shared" si="2"/>
@@ -17526,19 +17526,19 @@
       </c>
       <c r="I35" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>588229.00967635564</v>
       </c>
       <c r="J35" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2283521415405128E-2</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.34997779222393377</v>
       </c>
       <c r="L35" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>205867.09012860191</v>
       </c>
       <c r="N35" s="282"/>
       <c r="O35" s="282"/>
@@ -18322,11 +18322,11 @@
       </c>
       <c r="B51" s="323">
         <f>C15+1</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C51" s="284">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>9054866.7435762621</v>
+        <v>11825483.316542063</v>
       </c>
       <c r="D51" s="308">
         <f>Terminal_Growth</f>
@@ -18338,11 +18338,11 @@
       </c>
       <c r="F51" s="284">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-546168.74205669831</v>
+        <v>-713285.96324073093</v>
       </c>
       <c r="G51" s="284">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>570393.78676280892</v>
+        <v>768997.953210262</v>
       </c>
       <c r="H51" s="306">
         <f>F18</f>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="I51" s="284">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>6000264.6717512924</v>
+        <v>8113503.5817428371</v>
       </c>
       <c r="J51" s="422">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18358,24 +18358,24 @@
       </c>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.70471496766912267</v>
+        <v>0.34997779222393377</v>
       </c>
       <c r="L51" s="284">
         <f>I51*K51</f>
-        <v>4228476.3241593912</v>
+        <v>2839546.0707393372</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="467" t="s">
+      <c r="J52" s="470" t="s">
         <v>425</v>
       </c>
-      <c r="K52" s="467"/>
+      <c r="K52" s="470"/>
       <c r="L52" s="324">
         <f>SUM(L21:L51)</f>
-        <v>5624133.8241217937</v>
+        <v>6216243.1228741389</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18399,27 +18399,27 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>5624133.8241217937</v>
+        <v>6216243.1228741389</v>
       </c>
       <c r="B55" s="123">
         <f>C86</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C55" s="123">
         <f>C85</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D55" s="123">
         <f>C84</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E55" s="123">
         <f>C83</f>
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F55" s="123">
         <f>C82</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G55" s="123"/>
       <c r="H55" s="123"/>
@@ -18434,19 +18434,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F65" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>5373619.2329866514</v>
+        <v>5497056.4488840643</v>
       </c>
       <c r="C56" s="118">
-        <v>5497056.4488840643</v>
+        <v>5621694.4424392562</v>
       </c>
       <c r="D56" s="118">
-        <v>5621694.4424392562</v>
+        <v>5747533.213652215</v>
       </c>
       <c r="E56" s="118">
-        <v>5747533.213652215</v>
+        <v>5874572.7625229498</v>
       </c>
       <c r="F56" s="118">
-        <v>5874572.7625229498</v>
+        <v>6002813.0890514571</v>
       </c>
       <c r="G56" s="302"/>
       <c r="H56" s="302"/>
@@ -18460,19 +18460,19 @@
         <v>6</v>
       </c>
       <c r="B57" s="118">
-        <v>5467145.0579635147</v>
+        <v>5592462.1429429594</v>
       </c>
       <c r="C57" s="118">
-        <v>5592462.1429429594</v>
+        <v>5718998.710745181</v>
       </c>
       <c r="D57" s="118">
-        <v>5718998.710745181</v>
+        <v>5846754.7613701653</v>
       </c>
       <c r="E57" s="118">
-        <v>5846754.7613701653</v>
+        <v>5975730.2948179226</v>
       </c>
       <c r="F57" s="118">
-        <v>5975730.2948179226</v>
+        <v>6105925.3110884447</v>
       </c>
       <c r="G57" s="302"/>
       <c r="H57" s="302"/>
@@ -18486,19 +18486,19 @@
         <v>7</v>
       </c>
       <c r="B58" s="118">
-        <v>5312220.6811542958</v>
+        <v>5492418.8643652732</v>
       </c>
       <c r="C58" s="118">
-        <v>5492418.8643652732</v>
+        <v>5676113.7507732855</v>
       </c>
       <c r="D58" s="118">
-        <v>5676113.7507732855</v>
+        <v>5863339.45178595</v>
       </c>
       <c r="E58" s="118">
-        <v>5863339.45178595</v>
+        <v>6054130.0788109051</v>
       </c>
       <c r="F58" s="118">
-        <v>6054130.0788109051</v>
+        <v>6248519.7432557773</v>
       </c>
       <c r="G58" s="302"/>
       <c r="H58" s="302"/>
@@ -18512,19 +18512,19 @@
         <v>8</v>
       </c>
       <c r="B59" s="118">
-        <v>5395155.5415181462</v>
+        <v>5577866.7339330092</v>
       </c>
       <c r="C59" s="118">
-        <v>5577866.7339330092</v>
+        <v>5764124.8880702872</v>
       </c>
       <c r="D59" s="118">
-        <v>5764124.8880702872</v>
+        <v>5953964.6129467599</v>
       </c>
       <c r="E59" s="118">
-        <v>5953964.6129467599</v>
+        <v>6147420.5175792277</v>
       </c>
       <c r="F59" s="118">
-        <v>6147420.5175792277</v>
+        <v>6344527.2109844796</v>
       </c>
       <c r="G59" s="302"/>
       <c r="H59" s="302"/>
@@ -18538,19 +18538,19 @@
         <v>9</v>
       </c>
       <c r="B60" s="118">
-        <v>5245097.5888975412</v>
+        <v>5478674.0036659241</v>
       </c>
       <c r="C60" s="118">
-        <v>5478674.0036659241</v>
+        <v>5719030.9543831721</v>
       </c>
       <c r="D60" s="118">
-        <v>5719030.9543831721</v>
+        <v>5966300.8943257071</v>
       </c>
       <c r="E60" s="118">
-        <v>5966300.8943257071</v>
+        <v>6220617.567549143</v>
       </c>
       <c r="F60" s="118">
-        <v>6220617.567549143</v>
+        <v>6482116.0088882605</v>
       </c>
       <c r="G60" s="302"/>
       <c r="H60" s="302"/>
@@ -18564,19 +18564,19 @@
         <v>10</v>
       </c>
       <c r="B61" s="118">
-        <v>5318640.8168270811</v>
+        <v>5555203.3815577477</v>
       </c>
       <c r="C61" s="118">
-        <v>5555203.3815577477</v>
+        <v>5798636.5094443168</v>
       </c>
       <c r="D61" s="118">
-        <v>5798636.5094443168</v>
+        <v>6049074.4452762417</v>
       </c>
       <c r="E61" s="118">
-        <v>6049074.4452762417</v>
+        <v>6306652.7422725484</v>
       </c>
       <c r="F61" s="118">
-        <v>6306652.7422725484</v>
+        <v>6571508.2620817916</v>
       </c>
       <c r="G61" s="302"/>
       <c r="H61" s="302"/>
@@ -18590,19 +18590,19 @@
         <v>15</v>
       </c>
       <c r="B62" s="118">
-        <v>5023321.2432679618</v>
+        <v>5396961.8185033593</v>
       </c>
       <c r="C62" s="284">
-        <v>5396961.8185033593</v>
+        <v>5792108.8893085411</v>
       </c>
       <c r="D62" s="118">
-        <v>5792108.8893085411</v>
+        <v>6209816.4225565288</v>
       </c>
       <c r="E62" s="118">
-        <v>6209816.4225565288</v>
+        <v>6651179.8059659954</v>
       </c>
       <c r="F62" s="118">
-        <v>6651179.8059659954</v>
+        <v>7117337.0643130448</v>
       </c>
       <c r="G62" s="302"/>
       <c r="H62" s="302"/>
@@ -18625,19 +18625,19 @@
         <v>20</v>
       </c>
       <c r="B63" s="118">
-        <v>4909228.6320150206</v>
+        <v>5364061.1430426184</v>
       </c>
       <c r="C63" s="284">
-        <v>5364061.1430426184</v>
+        <v>5853599.8591909334</v>
       </c>
       <c r="D63" s="118">
-        <v>5853599.8591909334</v>
+        <v>6380231.8284840696</v>
       </c>
       <c r="E63" s="118">
-        <v>6380231.8284840696</v>
+        <v>6946485.60456766</v>
       </c>
       <c r="F63" s="118">
-        <v>6946485.60456766</v>
+        <v>7555038.2205814561</v>
       </c>
       <c r="G63" s="302"/>
       <c r="H63" s="302"/>
@@ -18660,19 +18660,19 @@
         <v>25</v>
       </c>
       <c r="B64" s="118">
-        <v>4641486.2301515881</v>
+        <v>5187075.0610776981</v>
       </c>
       <c r="C64" s="284">
-        <v>5187075.0610776981</v>
+        <v>5789247.4213424828</v>
       </c>
       <c r="D64" s="118">
-        <v>5789247.4213424828</v>
+        <v>6453576.1043743286</v>
       </c>
       <c r="E64" s="118">
-        <v>6453576.1043743286</v>
+        <v>7186133.2801278103</v>
       </c>
       <c r="F64" s="118">
-        <v>7186133.2801278103</v>
+        <v>7993530.2762442231</v>
       </c>
       <c r="G64" s="302"/>
       <c r="H64" s="302"/>
@@ -18695,19 +18695,19 @@
         <v>30</v>
       </c>
       <c r="B65" s="118">
-        <v>4519768.9639271349</v>
+        <v>5118927.8479986088</v>
       </c>
       <c r="C65" s="284">
-        <v>5118927.8479986088</v>
+        <v>5790972.7175897965</v>
       </c>
       <c r="D65" s="118">
-        <v>5790972.7175897965</v>
+        <v>6544533.1775393505</v>
       </c>
       <c r="E65" s="118">
-        <v>6544533.1775393505</v>
+        <v>7389189.0565219279</v>
       </c>
       <c r="F65" s="118">
-        <v>7389189.0565219279</v>
+        <v>8335565.6915554032</v>
       </c>
       <c r="G65" s="302"/>
       <c r="H65" s="302"/>
@@ -18773,23 +18773,23 @@
     <row r="68" spans="1:21" ht="13.15">
       <c r="B68" s="124">
         <f>B55</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C68" s="124">
         <f>C55</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D68" s="124">
         <f>D55</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E68" s="124">
         <f>E55</f>
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F68" s="124">
         <f>F55</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G68" s="124"/>
       <c r="H68" s="124"/>
@@ -18836,23 +18836,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>6.3571498756157778</v>
+        <v>6.5699711818038571</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>6.5699711818038571</v>
+        <v>6.7848627799027819</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.7848627799027819</v>
+        <v>7.0018246699125335</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>7.0018246699125335</v>
+        <v>7.2208568518331298</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>7.2208568518331298</v>
+        <v>7.4419593256645609</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18867,23 +18867,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>6.518400176744052</v>
+        <v>6.7344626139848032</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>6.7344626139848032</v>
+        <v>6.952627593196631</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.952627593196631</v>
+        <v>7.1728951143795134</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>7.1728951143795134</v>
+        <v>7.3952651775334663</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>7.3952651775334663</v>
+        <v>7.6197377826584747</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>6.2512910395749683</v>
+        <v>6.5619754020248715</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>6.5619754020248715</v>
+        <v>6.8786885211697033</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.8786885211697033</v>
+        <v>7.2014892093722702</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>7.2014892093722702</v>
+        <v>7.5304362789954142</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>7.5304362789954142</v>
+        <v>7.865588542401956</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18930,23 +18930,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>6.3942811838587588</v>
+        <v>6.7092982906706062</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>6.7092982906706062</v>
+        <v>7.0304308062048184</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>7.0304308062048184</v>
+        <v>7.3577384007650659</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>7.3577384007650659</v>
+        <v>7.6912807446550575</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>7.6912807446550575</v>
+        <v>8.0311175081784789</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>6.1355623748800543</v>
+        <v>6.5382775311182586</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.5382775311182586</v>
+        <v>6.9526831852893691</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.9526831852893691</v>
+        <v>7.3790077035234258</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.3790077035234258</v>
+        <v>7.8174816774163567</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8174816774163567</v>
+        <v>8.2683379240299324</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>6.2623601620422349</v>
+        <v>6.6702238168983499</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>6.6702238168983499</v>
+        <v>7.0899331879305496</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>7.0899331879305496</v>
+        <v>7.5217197300629639</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>7.5217197300629639</v>
+        <v>7.9658171541170937</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>7.9658171541170937</v>
+        <v>8.4224614268117346</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>5.7531920239663412</v>
+        <v>6.3973954328681506</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>6.3973954328681506</v>
+        <v>7.0786787487122345</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>7.0786787487122345</v>
+        <v>7.7988591431268164</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>7.7988591431268164</v>
+        <v>8.5598252024946575</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>8.5598252024946575</v>
+        <v>9.3635390248553545</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>5.5564819930673988</v>
+        <v>6.3406705247833459</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>6.3406705247833459</v>
+        <v>7.1846969251106598</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>7.1846969251106598</v>
+        <v>8.0926767654734881</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>8.0926767654734881</v>
+        <v>9.0689695908090489</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>9.0689695908090489</v>
+        <v>10.118190943402293</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>5.0948603721304409</v>
+        <v>6.03552422942143</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>6.03552422942143</v>
+        <v>7.0737452175585664</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>7.0737452175585664</v>
+        <v>8.2191315342634468</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>8.2191315342634468</v>
+        <v>9.4821523652815003</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>9.4821523652815003</v>
+        <v>10.874206472112879</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>4.885004475793159</v>
+        <v>5.918029851448563</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>5.918029851448563</v>
+        <v>7.0767198455769105</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>7.0767198455769105</v>
+        <v>8.3759529837533027</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>8.3759529837533027</v>
+        <v>9.8322460971195973</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>9.8322460971195973</v>
+        <v>11.463918604875204</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -19177,15 +19177,15 @@
       </c>
       <c r="C82" s="130">
         <f>Scenarios!C29</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D82" s="133">
         <f>Scenarios!D29</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>7.2208568518331298</v>
+        <v>9.3635390248553545</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19205,15 +19205,15 @@
       </c>
       <c r="C83" s="130">
         <f>Scenarios!C22</f>
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D83" s="133">
         <f>Scenarios!D22</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>7.0018246699125335</v>
+        <v>8.5598252024946575</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19233,15 +19233,15 @@
       </c>
       <c r="C84" s="130">
         <f>Scenarios!C23</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D84" s="133">
         <f>Scenarios!D23</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.7848627799027819</v>
+        <v>7.7988591431268164</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19261,15 +19261,15 @@
       </c>
       <c r="C85" s="130">
         <f>Scenarios!C24</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D85" s="133">
         <f>Scenarios!D24</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>6.5699711818038571</v>
+        <v>7.0786787487122345</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19289,15 +19289,15 @@
       </c>
       <c r="C86" s="130">
         <f>Scenarios!C30</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D86" s="133">
         <f>Scenarios!D30</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>6.3571498756157778</v>
+        <v>6.3973954328681506</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19453,7 +19453,7 @@
       <c r="C4" s="457">
         <v>2</v>
       </c>
-      <c r="D4" s="468" t="str">
+      <c r="D4" s="471" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19463,16 +19463,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 0341.HK – 大家乐集团: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="468"/>
-      <c r="F4" s="468"/>
-      <c r="G4" s="468"/>
+      <c r="E4" s="471"/>
+      <c r="F4" s="471"/>
+      <c r="G4" s="471"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="453"/>
-      <c r="D5" s="468"/>
-      <c r="E5" s="468"/>
-      <c r="F5" s="468"/>
-      <c r="G5" s="468"/>
+      <c r="D5" s="471"/>
+      <c r="E5" s="471"/>
+      <c r="F5" s="471"/>
+      <c r="G5" s="471"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19482,10 +19482,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000 HKD</v>
       </c>
-      <c r="D6" s="468"/>
-      <c r="E6" s="468"/>
-      <c r="F6" s="468"/>
-      <c r="G6" s="468"/>
+      <c r="D6" s="471"/>
+      <c r="E6" s="471"/>
+      <c r="F6" s="471"/>
+      <c r="G6" s="471"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19495,10 +19495,10 @@
         <f>Normalized_FCF!G8</f>
         <v>398162</v>
       </c>
-      <c r="D7" s="468"/>
-      <c r="E7" s="468"/>
-      <c r="F7" s="468"/>
-      <c r="G7" s="468"/>
+      <c r="D7" s="471"/>
+      <c r="E7" s="471"/>
+      <c r="F7" s="471"/>
+      <c r="G7" s="471"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19508,10 +19508,10 @@
         <f>Normalized_FCF!G19</f>
         <v>289000.65016124537</v>
       </c>
-      <c r="D8" s="468"/>
-      <c r="E8" s="468"/>
-      <c r="F8" s="468"/>
-      <c r="G8" s="468"/>
+      <c r="D8" s="471"/>
+      <c r="E8" s="471"/>
+      <c r="F8" s="471"/>
+      <c r="G8" s="471"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19521,27 +19521,27 @@
         <f>Normalized_FCF!C19</f>
         <v>230211.62257446788</v>
       </c>
-      <c r="D9" s="468"/>
-      <c r="E9" s="468"/>
-      <c r="F9" s="468"/>
-      <c r="G9" s="468"/>
+      <c r="D9" s="471"/>
+      <c r="E9" s="471"/>
+      <c r="F9" s="471"/>
+      <c r="G9" s="471"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="456"/>
-      <c r="D10" s="468"/>
-      <c r="E10" s="468"/>
-      <c r="F10" s="468"/>
-      <c r="G10" s="468"/>
+      <c r="D10" s="471"/>
+      <c r="E10" s="471"/>
+      <c r="F10" s="471"/>
+      <c r="G10" s="471"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="456"/>
-      <c r="D11" s="468"/>
-      <c r="E11" s="468"/>
-      <c r="F11" s="468"/>
-      <c r="G11" s="468"/>
+      <c r="D11" s="471"/>
+      <c r="E11" s="471"/>
+      <c r="F11" s="471"/>
+      <c r="G11" s="471"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19551,10 +19551,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.3358728201447585E-2</v>
       </c>
-      <c r="D12" s="468"/>
-      <c r="E12" s="468"/>
-      <c r="F12" s="468"/>
-      <c r="G12" s="468"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+      <c r="G12" s="471"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19564,10 +19564,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.35590966478967423</v>
       </c>
-      <c r="D13" s="468"/>
-      <c r="E13" s="468"/>
-      <c r="F13" s="468"/>
-      <c r="G13" s="468"/>
+      <c r="D13" s="471"/>
+      <c r="E13" s="471"/>
+      <c r="F13" s="471"/>
+      <c r="G13" s="471"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19577,10 +19577,10 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.62894902211793369</v>
       </c>
-      <c r="D14" s="468"/>
-      <c r="E14" s="468"/>
-      <c r="F14" s="468"/>
-      <c r="G14" s="468"/>
+      <c r="D14" s="471"/>
+      <c r="E14" s="471"/>
+      <c r="F14" s="471"/>
+      <c r="G14" s="471"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
@@ -19605,7 +19605,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E18" s="458" t="s">
         <v>550</v>
@@ -19649,15 +19649,15 @@
         <v>450</v>
       </c>
       <c r="C22" s="331">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D22" s="332">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>7.0018246699125335</v>
+        <v>8.5598252024946575</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19673,15 +19673,15 @@
         <v>442</v>
       </c>
       <c r="C23" s="331">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D23" s="332">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>6.7848627799027819</v>
+        <v>7.7988591431268164</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19696,15 +19696,15 @@
         <v>451</v>
       </c>
       <c r="C24" s="331">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D24" s="332">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>6.5699711818038571</v>
+        <v>7.0786787487122345</v>
       </c>
       <c r="F24" s="334">
         <v>0.2</v>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.7852768382849469</v>
+        <v>7.8070162761174675</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19759,15 +19759,15 @@
         <v>449</v>
       </c>
       <c r="C29" s="331">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D29" s="332">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>7.2208568518331298</v>
+        <v>9.3635390248553545</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19782,15 +19782,15 @@
         <v>452</v>
       </c>
       <c r="C30" s="331">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D30" s="332">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>6.3571498756157778</v>
+        <v>6.3973954328681506</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>8.2639604252926629E-2</v>
+        <v>0.15535566535489756</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19866,7 +19866,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.75280838141092954</v>
+        <v>0.8684477448290957</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.7856494908288969</v>
+        <v>7.8143613713918958</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="224" t="s">
@@ -19963,7 +19963,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>2.0194760895005201E-2</v>
+        <v>3.0149622951542547E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="224" t="s">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.7890685811450933</v>
+        <v>7.8099395838685268</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.65608930105999008</v>
+        <v>0.56971924129009388</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20117,11 +20117,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.7232644668471311</v>
+        <v>4.2877154301190092</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>4.2390395011406845</v>
+        <v>4.8034904644125618</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
@@ -20129,7 +20129,7 @@
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.37529347678951996</v>
+        <v>0.38529967631162121</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.3428156741304944</v>
+        <v>5.001191277690813</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>4.918815674130494</v>
+        <v>5.5771912776908135</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.27511497893038994</v>
+        <v>0.28628956192009292</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20188,11 +20188,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.4346813909467224</v>
+        <v>6.2585850307527044</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>6.1130184841162611</v>
+        <v>6.9369221239222432</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>9.9579211632415787E-2</v>
+        <v>0.11178286983800823</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20213,11 +20213,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.8992502677806771</v>
+        <v>6.7935830571595641</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>6.6199592402379013</v>
+        <v>7.5142920296167883</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20225,7 +20225,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>2.4417743771606992E-2</v>
+        <v>3.8399726799639766E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20361,7 +20361,7 @@
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>8.2639604252926629E-2</v>
+        <v>0.15535566535489756</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>6.7856494908288969</v>
+        <v>7.8143613713918958</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>363</v>
@@ -20491,7 +20491,7 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>4.2390395011406845</v>
+        <v>4.8034904644125618</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>445</v>
@@ -20507,7 +20507,7 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>4.918815674130494</v>
+        <v>5.5771912776908135</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>446</v>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>6.1130184841162611</v>
+        <v>6.9369221239222432</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>448</v>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>6.6199592402379013</v>
+        <v>7.5142920296167883</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>447</v>
@@ -20569,13 +20569,13 @@
       <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="474"/>
+      <c r="D30" s="474"/>
+      <c r="E30" s="474"/>
+      <c r="F30" s="474"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20587,13 +20587,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="469" t="s">
+      <c r="B33" s="472" t="s">
         <v>506</v>
       </c>
-      <c r="C33" s="469"/>
-      <c r="D33" s="469"/>
-      <c r="E33" s="469"/>
-      <c r="F33" s="469"/>
+      <c r="C33" s="472"/>
+      <c r="D33" s="472"/>
+      <c r="E33" s="472"/>
+      <c r="F33" s="472"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="379" t="s">
@@ -20613,13 +20613,13 @@
       <c r="C35" s="381"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="469" t="s">
+      <c r="B36" s="472" t="s">
         <v>507</v>
       </c>
-      <c r="C36" s="469"/>
-      <c r="D36" s="469"/>
-      <c r="E36" s="469"/>
-      <c r="F36" s="469"/>
+      <c r="C36" s="472"/>
+      <c r="D36" s="472"/>
+      <c r="E36" s="472"/>
+      <c r="F36" s="472"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="379" t="s">
@@ -20648,13 +20648,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="469" t="s">
+      <c r="B40" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C40" s="469"/>
-      <c r="D40" s="469"/>
-      <c r="E40" s="469"/>
-      <c r="F40" s="469"/>
+      <c r="C40" s="472"/>
+      <c r="D40" s="472"/>
+      <c r="E40" s="472"/>
+      <c r="F40" s="472"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="379" t="s">
@@ -20670,13 +20670,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="469" t="s">
+      <c r="B43" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C43" s="469"/>
-      <c r="D43" s="469"/>
-      <c r="E43" s="469"/>
-      <c r="F43" s="469"/>
+      <c r="C43" s="472"/>
+      <c r="D43" s="472"/>
+      <c r="E43" s="472"/>
+      <c r="F43" s="472"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="379" t="s">
@@ -20740,13 +20740,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="469" t="s">
+      <c r="B51" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C51" s="469"/>
-      <c r="D51" s="469"/>
-      <c r="E51" s="469"/>
-      <c r="F51" s="469"/>
+      <c r="C51" s="472"/>
+      <c r="D51" s="472"/>
+      <c r="E51" s="472"/>
+      <c r="F51" s="472"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="379" t="s">
@@ -20762,7 +20762,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="469" t="s">
+      <c r="B54" s="472" t="s">
         <v>512</v>
       </c>
       <c r="C54" s="475"/>
@@ -20943,13 +20943,13 @@
       <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="474" t="s">
         <v>484</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="474"/>
+      <c r="D74" s="474"/>
+      <c r="E74" s="474"/>
+      <c r="F74" s="474"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -21122,23 +21122,23 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="474" t="s">
         <v>520</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="474"/>
+      <c r="D97" s="474"/>
+      <c r="E97" s="474"/>
+      <c r="F97" s="474"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="474"/>
+      <c r="D98" s="474"/>
+      <c r="E98" s="474"/>
+      <c r="F98" s="474"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21304,15 +21304,15 @@
       </c>
       <c r="C118" s="403">
         <f>DCF!C82</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D118" s="404">
         <f>DCF!D82</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.22 HKD</v>
+        <v>9.36 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21327,15 +21327,15 @@
       </c>
       <c r="C119" s="408">
         <f>DCF!C83</f>
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D119" s="409">
         <f>DCF!D83</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>7 HKD</v>
+        <v>8.56 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21349,15 +21349,15 @@
       </c>
       <c r="C120" s="408">
         <f>DCF!C84</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D120" s="409">
         <f>DCF!D84</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E120" s="405" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>7.8 HKD</v>
       </c>
       <c r="F120" s="410">
         <f>DCF!F84</f>
@@ -21371,15 +21371,15 @@
       </c>
       <c r="C121" s="408">
         <f>DCF!C85</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D121" s="409">
         <f>DCF!D85</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E121" s="405" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>6.57 HKD</v>
+        <v>7.08 HKD</v>
       </c>
       <c r="F121" s="410">
         <f>DCF!F85</f>
@@ -21393,15 +21393,15 @@
       </c>
       <c r="C122" s="408">
         <f>DCF!C86</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D122" s="409">
         <f>DCF!D86</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E122" s="405" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>6.36 HKD</v>
+        <v>6.4 HKD</v>
       </c>
       <c r="F122" s="410">
         <f>DCF!F86</f>
@@ -21409,13 +21409,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="469" t="s">
+      <c r="B124" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C124" s="469"/>
-      <c r="D124" s="469"/>
-      <c r="E124" s="469"/>
-      <c r="F124" s="469"/>
+      <c r="C124" s="472"/>
+      <c r="D124" s="472"/>
+      <c r="E124" s="472"/>
+      <c r="F124" s="472"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="379" t="s">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>6.7856494908288969</v>
+        <v>7.8143613713918958</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21431,13 +21431,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="477" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="477"/>
+      <c r="D127" s="477"/>
+      <c r="E127" s="477"/>
+      <c r="F127" s="477"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21450,13 +21450,13 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="478" t="s">
         <v>526</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="478"/>
+      <c r="D131" s="478"/>
+      <c r="E131" s="478"/>
+      <c r="F131" s="478"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
       <c r="B132" s="473" t="s">
@@ -21530,11 +21530,11 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>3.7232644668471311</v>
+        <v>4.2877154301190092</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>4.2390395011406845</v>
+        <v>4.8034904644125618</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
@@ -21551,11 +21551,11 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>4.3428156741304944</v>
+        <v>5.001191277690813</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>4.918815674130494</v>
+        <v>5.5771912776908135</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
@@ -21591,11 +21591,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>5.4346813909467224</v>
+        <v>6.2585850307527044</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>6.1130184841162611</v>
+        <v>6.9369221239222432</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21612,11 +21612,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>5.8992502677806771</v>
+        <v>6.7935830571595641</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>6.6199592402379013</v>
+        <v>7.5142920296167883</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21634,7 +21634,7 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="479" t="s">
         <v>528</v>
       </c>
       <c r="C149" s="473"/>
@@ -21677,13 +21677,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="469" t="s">
+      <c r="B158" s="472" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="469"/>
-      <c r="D158" s="469"/>
-      <c r="E158" s="469"/>
-      <c r="F158" s="469"/>
+      <c r="C158" s="472"/>
+      <c r="D158" s="472"/>
+      <c r="E158" s="472"/>
+      <c r="F158" s="472"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="350" t="s">
@@ -21691,22 +21691,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="476" t="s">
         <v>389</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="476"/>
+      <c r="D161" s="476"/>
+      <c r="E161" s="476"/>
+      <c r="F161" s="476"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="476" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="476"/>
+      <c r="D162" s="476"/>
+      <c r="E162" s="476"/>
+      <c r="F162" s="476"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21730,12 +21730,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21750,15 +21753,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21784,19 +21784,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="479" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="479" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="479" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="479"/>
+    <col min="1" max="1" width="2.59765625" style="461" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="461" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="461" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="461"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="477" t="s">
+      <c r="B2" s="459" t="s">
         <v>334</v>
       </c>
-      <c r="C2" s="478"/>
-      <c r="D2" s="478"/>
-      <c r="E2" s="478"/>
+      <c r="C2" s="460"/>
+      <c r="D2" s="460"/>
+      <c r="E2" s="460"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7B8430-5A98-47EF-BE34-2C89C2EC3507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE338B93-7E94-4963-A8EA-7C4F1138B56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,32 +22,18 @@
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
     <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$9</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$91</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$101</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$E$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$E$16</definedName>
-    <definedName name="FV_adjustments" localSheetId="7">[1]DCF!$F$7</definedName>
     <definedName name="FV_adjustments">DCF!$F$7</definedName>
-    <definedName name="Holding_Period" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="Holding_Period">Thesis!$E$21</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$7</definedName>
     <definedName name="Market_currency">Thesis!$C$7</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$8</definedName>
     <definedName name="Market_Price">Thesis!$C$8</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$E$17</definedName>
     <definedName name="Reporting_currency">Thesis!$E$17</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$17</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -4997,30 +4983,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5030,25 +5016,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5132,93 +5118,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Thesis"/>
-      <sheetName val="Data"/>
-      <sheetName val="BS"/>
-      <sheetName val="Normalized_FCF"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="投资主题"/>
-      <sheetName val="Breakdown"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="7">
-          <cell r="C7" t="str">
-            <v>HKD</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>6.5</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>580004033</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="C17">
-            <v>0</v>
-          </cell>
-          <cell r="E17" t="str">
-            <v>HKD</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="C101">
-            <v>7.2499999999999995E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="C3">
-            <v>1000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="91">
-          <cell r="C91">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="7">
-          <cell r="F7">
-            <v>-1686446.6667440513</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5539,13 +5438,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="464" t="s">
         <v>356</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="464"/>
+      <c r="D12" s="464"/>
+      <c r="E12" s="464"/>
+      <c r="F12" s="464"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5723,22 +5622,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="464"/>
+      <c r="D29" s="464"/>
+      <c r="E29" s="464"/>
+      <c r="F29" s="464"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="468" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5750,13 +5649,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="465" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="465"/>
+      <c r="D33" s="465"/>
+      <c r="E33" s="465"/>
+      <c r="F33" s="465"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5776,13 +5675,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="465" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="465"/>
+      <c r="D36" s="465"/>
+      <c r="E36" s="465"/>
+      <c r="F36" s="465"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5811,13 +5710,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="465" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="465"/>
+      <c r="D40" s="465"/>
+      <c r="E40" s="465"/>
+      <c r="F40" s="465"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5833,13 +5732,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="465" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="465"/>
+      <c r="D43" s="465"/>
+      <c r="E43" s="465"/>
+      <c r="F43" s="465"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5903,13 +5802,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="465" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="465"/>
+      <c r="D51" s="465"/>
+      <c r="E51" s="465"/>
+      <c r="F51" s="465"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5925,7 +5824,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="465" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="466"/>
@@ -5947,22 +5846,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="464" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="464"/>
+      <c r="D57" s="464"/>
+      <c r="E57" s="464"/>
+      <c r="F57" s="464"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="464" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="464"/>
+      <c r="D58" s="464"/>
+      <c r="E58" s="464"/>
+      <c r="F58" s="464"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6097,13 +5996,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="464" t="s">
         <v>483</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="464"/>
+      <c r="D73" s="464"/>
+      <c r="E73" s="464"/>
+      <c r="F73" s="464"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6122,13 +6021,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="464" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="464"/>
+      <c r="D77" s="464"/>
+      <c r="E77" s="464"/>
+      <c r="F77" s="464"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6297,31 +6196,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="464" t="s">
         <v>490</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="464"/>
+      <c r="D96" s="464"/>
+      <c r="E96" s="464"/>
+      <c r="F96" s="464"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="468" t="s">
         <v>489</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="468" t="s">
         <v>488</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6371,22 +6270,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="464" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="464"/>
+      <c r="D107" s="464"/>
+      <c r="E107" s="464"/>
+      <c r="F107" s="464"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="464" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="464"/>
+      <c r="D108" s="464"/>
+      <c r="E108" s="464"/>
+      <c r="F108" s="464"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6420,13 +6319,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="464" t="s">
         <v>496</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="464"/>
+      <c r="D114" s="464"/>
+      <c r="E114" s="464"/>
+      <c r="F114" s="464"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6561,13 +6460,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="465" t="s">
         <v>358</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="465"/>
+      <c r="D124" s="465"/>
+      <c r="E124" s="465"/>
+      <c r="F124" s="465"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6602,22 +6501,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="469" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="464" t="s">
         <v>360</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="464"/>
+      <c r="D132" s="464"/>
+      <c r="E132" s="464"/>
+      <c r="F132" s="464"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6793,13 +6692,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="469" t="s">
+      <c r="B149" s="463" t="s">
         <v>361</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="464"/>
+      <c r="D149" s="464"/>
+      <c r="E149" s="464"/>
+      <c r="F149" s="464"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6836,13 +6735,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="465" t="s">
         <v>443</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="465"/>
+      <c r="D158" s="465"/>
+      <c r="E158" s="465"/>
+      <c r="F158" s="465"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6850,22 +6749,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="468" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="468"/>
-      <c r="D161" s="468"/>
-      <c r="E161" s="468"/>
-      <c r="F161" s="468"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="468" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="468"/>
-      <c r="D162" s="468"/>
-      <c r="E162" s="468"/>
-      <c r="F162" s="468"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6889,18 +6788,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6917,6 +6804,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20369,13 +20268,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="476" t="s">
         <v>503</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="476"/>
+      <c r="D12" s="476"/>
+      <c r="E12" s="476"/>
+      <c r="F12" s="476"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20560,22 +20459,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="476" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="476"/>
+      <c r="D29" s="476"/>
+      <c r="E29" s="476"/>
+      <c r="F29" s="476"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="474" t="s">
+      <c r="B30" s="479" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="474"/>
-      <c r="D30" s="474"/>
-      <c r="E30" s="474"/>
-      <c r="F30" s="474"/>
+      <c r="C30" s="479"/>
+      <c r="D30" s="479"/>
+      <c r="E30" s="479"/>
+      <c r="F30" s="479"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20765,10 +20664,10 @@
       <c r="B54" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="478"/>
+      <c r="D54" s="478"/>
+      <c r="E54" s="478"/>
+      <c r="F54" s="478"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20784,22 +20683,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="476" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="476"/>
+      <c r="D57" s="476"/>
+      <c r="E57" s="476"/>
+      <c r="F57" s="476"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="476" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="476"/>
+      <c r="D58" s="476"/>
+      <c r="E58" s="476"/>
+      <c r="F58" s="476"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20934,22 +20833,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="476" t="s">
         <v>515</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="476"/>
+      <c r="D73" s="476"/>
+      <c r="E73" s="476"/>
+      <c r="F73" s="476"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="474" t="s">
+      <c r="B74" s="479" t="s">
         <v>484</v>
       </c>
-      <c r="C74" s="474"/>
-      <c r="D74" s="474"/>
-      <c r="E74" s="474"/>
-      <c r="F74" s="474"/>
+      <c r="C74" s="479"/>
+      <c r="D74" s="479"/>
+      <c r="E74" s="479"/>
+      <c r="F74" s="479"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20957,13 +20856,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="476" t="s">
         <v>516</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="476"/>
+      <c r="D77" s="476"/>
+      <c r="E77" s="476"/>
+      <c r="F77" s="476"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -21112,33 +21011,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="476"/>
+      <c r="D96" s="476"/>
+      <c r="E96" s="476"/>
+      <c r="F96" s="476"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="474" t="s">
+      <c r="B97" s="479" t="s">
         <v>520</v>
       </c>
-      <c r="C97" s="474"/>
-      <c r="D97" s="474"/>
-      <c r="E97" s="474"/>
-      <c r="F97" s="474"/>
+      <c r="C97" s="479"/>
+      <c r="D97" s="479"/>
+      <c r="E97" s="479"/>
+      <c r="F97" s="479"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="474" t="s">
+      <c r="B98" s="479" t="s">
         <v>521</v>
       </c>
-      <c r="C98" s="474"/>
-      <c r="D98" s="474"/>
-      <c r="E98" s="474"/>
-      <c r="F98" s="474"/>
+      <c r="C98" s="479"/>
+      <c r="D98" s="479"/>
+      <c r="E98" s="479"/>
+      <c r="F98" s="479"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21201,23 +21100,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="476" t="s">
         <v>522</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="476"/>
+      <c r="D107" s="476"/>
+      <c r="E107" s="476"/>
+      <c r="F107" s="476"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="476" t="s">
         <v>541</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="476"/>
+      <c r="D108" s="476"/>
+      <c r="E108" s="476"/>
+      <c r="F108" s="476"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21261,13 +21160,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="476"/>
+      <c r="D114" s="476"/>
+      <c r="E114" s="476"/>
+      <c r="F114" s="476"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21431,13 +21330,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="477" t="s">
+      <c r="B127" s="474" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="477"/>
-      <c r="D127" s="477"/>
-      <c r="E127" s="477"/>
-      <c r="F127" s="477"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21450,22 +21349,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="478" t="s">
+      <c r="B131" s="475" t="s">
         <v>526</v>
       </c>
-      <c r="C131" s="478"/>
-      <c r="D131" s="478"/>
-      <c r="E131" s="478"/>
-      <c r="F131" s="478"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="476" t="s">
         <v>527</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="476"/>
+      <c r="D132" s="476"/>
+      <c r="E132" s="476"/>
+      <c r="F132" s="476"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21634,13 +21533,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="479" t="s">
+      <c r="B149" s="477" t="s">
         <v>528</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="476"/>
+      <c r="D149" s="476"/>
+      <c r="E149" s="476"/>
+      <c r="F149" s="476"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21648,13 +21547,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="478" t="s">
         <v>529</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="478"/>
+      <c r="D152" s="478"/>
+      <c r="E152" s="478"/>
+      <c r="F152" s="478"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21691,22 +21590,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="476" t="s">
+      <c r="B161" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C161" s="476"/>
-      <c r="D161" s="476"/>
-      <c r="E161" s="476"/>
-      <c r="F161" s="476"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="476" t="s">
+      <c r="B162" s="473" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="476"/>
-      <c r="D162" s="476"/>
-      <c r="E162" s="476"/>
-      <c r="F162" s="476"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21730,15 +21629,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21753,12 +21649,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE338B93-7E94-4963-A8EA-7C4F1138B56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B51099-1C64-4083-9485-48866599F07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="555">
   <si>
     <t>Sales</t>
   </si>
@@ -1754,9 +1753,6 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>执行摘要</t>
@@ -3999,12 +3995,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="480">
+  <cellXfs count="477">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4978,35 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5016,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5025,22 +5024,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{6757641E-6F77-4D22-A9BB-ECA58D4E8794}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5346,7 +5335,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="436" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F3" s="437">
         <v>45930</v>
@@ -5354,13 +5343,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="429" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C4" s="428" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E4" s="438" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F4" s="439" t="s">
         <v>324</v>
@@ -5368,16 +5357,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E5" s="441" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F5" s="440" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5385,14 +5374,14 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C7" s="45" t="s">
         <v>308</v>
@@ -5402,7 +5391,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C8" s="47">
         <v>6.5</v>
@@ -5411,7 +5400,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C9" s="48">
         <v>580004033</v>
@@ -5419,14 +5408,14 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
         <v>3770.0262145000002</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
@@ -5438,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="464" t="s">
-        <v>356</v>
-      </c>
-      <c r="C12" s="464"/>
-      <c r="D12" s="464"/>
-      <c r="E12" s="464"/>
-      <c r="F12" s="464"/>
+      <c r="B12" s="459" t="s">
+        <v>355</v>
+      </c>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5458,10 +5447,10 @@
         <v>319</v>
       </c>
       <c r="C15" s="425" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E15" s="259" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5473,10 +5462,10 @@
         <v>320</v>
       </c>
       <c r="C16" s="425" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E16" s="424">
         <v>1</v>
@@ -5484,7 +5473,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C17" s="423">
         <v>0</v>
@@ -5506,7 +5495,7 @@
         <v>7.8143613713918958</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E18" s="426">
         <v>6</v>
@@ -5521,7 +5510,7 @@
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5534,7 +5523,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="260" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5556,7 +5545,7 @@
         <v>4.8034904644125618</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5571,7 +5560,7 @@
         <v>5.5771912776908135</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E23" s="451">
         <v>0.25</v>
@@ -5586,7 +5575,7 @@
         <v>6.9369221239222432</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E24" s="451">
         <v>0.1174</v>
@@ -5601,7 +5590,7 @@
         <v>7.5142920296167883</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E25" s="452">
         <v>7.2499999999999995E-2</v>
@@ -5622,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="464" t="s">
-        <v>357</v>
-      </c>
-      <c r="C29" s="464"/>
-      <c r="D29" s="464"/>
-      <c r="E29" s="464"/>
-      <c r="F29" s="464"/>
+      <c r="B29" s="459" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5649,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="465" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="465"/>
-      <c r="D33" s="465"/>
-      <c r="E33" s="465"/>
-      <c r="F33" s="465"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5675,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="465" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="465"/>
-      <c r="D36" s="465"/>
-      <c r="E36" s="465"/>
-      <c r="F36" s="465"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5710,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="465" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="465"/>
-      <c r="D40" s="465"/>
-      <c r="E40" s="465"/>
-      <c r="F40" s="465"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5732,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="465" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="465"/>
-      <c r="D43" s="465"/>
-      <c r="E43" s="465"/>
-      <c r="F43" s="465"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5802,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="465" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="465"/>
-      <c r="D51" s="465"/>
-      <c r="E51" s="465"/>
-      <c r="F51" s="465"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5824,13 +5813,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="465" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="466"/>
-      <c r="D54" s="466"/>
-      <c r="E54" s="466"/>
-      <c r="F54" s="466"/>
+      <c r="C54" s="463"/>
+      <c r="D54" s="463"/>
+      <c r="E54" s="463"/>
+      <c r="F54" s="463"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5846,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="464" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="464"/>
-      <c r="D57" s="464"/>
-      <c r="E57" s="464"/>
-      <c r="F57" s="464"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="464" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="464"/>
-      <c r="D58" s="464"/>
-      <c r="E58" s="464"/>
-      <c r="F58" s="464"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5983,7 +5972,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="202" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5996,18 +5985,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="464" t="s">
-        <v>483</v>
-      </c>
-      <c r="C73" s="464"/>
-      <c r="D73" s="464"/>
-      <c r="E73" s="464"/>
-      <c r="F73" s="464"/>
+      <c r="B73" s="459" t="s">
+        <v>482</v>
+      </c>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6021,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="464" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="464"/>
-      <c r="D77" s="464"/>
-      <c r="E77" s="464"/>
-      <c r="F77" s="464"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6083,7 +6072,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6171,7 +6160,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
@@ -6184,7 +6173,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="202" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6196,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="464" t="s">
-        <v>490</v>
-      </c>
-      <c r="C96" s="464"/>
-      <c r="D96" s="464"/>
-      <c r="E96" s="464"/>
-      <c r="F96" s="464"/>
+      <c r="B96" s="459" t="s">
+        <v>489</v>
+      </c>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="468" t="s">
-        <v>489</v>
-      </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="B97" s="461" t="s">
+        <v>488</v>
+      </c>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="468" t="s">
-        <v>488</v>
-      </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="B98" s="461" t="s">
+        <v>487</v>
+      </c>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6229,7 +6218,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C101" s="214">
         <f>E25+C103</f>
@@ -6270,31 +6259,31 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="464" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="464"/>
-      <c r="D107" s="464"/>
-      <c r="E107" s="464"/>
-      <c r="F107" s="464"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="464" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="464"/>
-      <c r="D108" s="464"/>
-      <c r="E108" s="464"/>
-      <c r="F108" s="464"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
@@ -6319,17 +6308,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="464" t="s">
-        <v>496</v>
-      </c>
-      <c r="C114" s="464"/>
-      <c r="D114" s="464"/>
-      <c r="E114" s="464"/>
-      <c r="F114" s="464"/>
+      <c r="B114" s="459" t="s">
+        <v>495</v>
+      </c>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6460,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="465" t="s">
-        <v>358</v>
-      </c>
-      <c r="C124" s="465"/>
-      <c r="D124" s="465"/>
-      <c r="E124" s="465"/>
-      <c r="F124" s="465"/>
+      <c r="B124" s="460" t="s">
+        <v>357</v>
+      </c>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,17 +6471,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="467" t="s">
-        <v>359</v>
-      </c>
-      <c r="C127" s="467"/>
-      <c r="D127" s="467"/>
-      <c r="E127" s="467"/>
-      <c r="F127" s="467"/>
+      <c r="B127" s="464" t="s">
+        <v>358</v>
+      </c>
+      <c r="C127" s="464"/>
+      <c r="D127" s="464"/>
+      <c r="E127" s="464"/>
+      <c r="F127" s="464"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="202" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6501,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="464" t="s">
-        <v>360</v>
-      </c>
-      <c r="C132" s="464"/>
-      <c r="D132" s="464"/>
-      <c r="E132" s="464"/>
-      <c r="F132" s="464"/>
+      <c r="B132" s="459" t="s">
+        <v>359</v>
+      </c>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,28 +6536,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C138" s="217"/>
       <c r="D138" s="218"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="347" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="348" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6622,21 +6611,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="347" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="348" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6683,7 +6672,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="202" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6692,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
-        <v>361</v>
-      </c>
-      <c r="C149" s="464"/>
-      <c r="D149" s="464"/>
-      <c r="E149" s="464"/>
-      <c r="F149" s="464"/>
+      <c r="B149" s="466" t="s">
+        <v>360</v>
+      </c>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6706,13 +6695,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="466" t="s">
+      <c r="B152" s="463" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="466"/>
-      <c r="D152" s="466"/>
-      <c r="E152" s="466"/>
-      <c r="F152" s="466"/>
+      <c r="C152" s="463"/>
+      <c r="D152" s="463"/>
+      <c r="E152" s="463"/>
+      <c r="F152" s="463"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6735,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="465" t="s">
-        <v>443</v>
-      </c>
-      <c r="C158" s="465"/>
-      <c r="D158" s="465"/>
-      <c r="E158" s="465"/>
-      <c r="F158" s="465"/>
+      <c r="B158" s="460" t="s">
+        <v>442</v>
+      </c>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6749,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6788,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6804,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7477,7 +7466,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9596,7 +9585,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -10779,7 +10768,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10789,7 +10778,7 @@
       <c r="E3" s="241"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11078,7 +11067,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C9" s="307">
         <f>C61</f>
@@ -11469,7 +11458,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C16" s="273">
         <f>-C4*C82</f>
@@ -12171,7 +12160,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="305" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C35" s="283">
         <f>G35</f>
@@ -12239,7 +12228,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="305" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12312,7 +12301,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="238" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -13536,7 +13525,7 @@
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="238" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
@@ -16275,15 +16264,15 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C4" s="282">
         <f>Normalized_FCF!C19</f>
@@ -16294,7 +16283,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F4" s="282">
         <f>-BS!G31</f>
@@ -16305,7 +16294,7 @@
         <v>HKD</v>
       </c>
       <c r="H4" s="315" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I4" s="312">
         <f>Normalized_FCF!C4</f>
@@ -16322,7 +16311,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F5" s="282">
         <f>BS!D66</f>
@@ -16333,7 +16322,7 @@
         <v>HKD</v>
       </c>
       <c r="H5" s="315" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I5" s="312">
         <f>Normalized_FCF!C7</f>
@@ -16354,7 +16343,7 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F6" s="291">
         <f>BS!H42</f>
@@ -16365,7 +16354,7 @@
         <v>HKD</v>
       </c>
       <c r="H6" s="315" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I6" s="312">
         <f>I7+I8</f>
@@ -16376,14 +16365,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="325" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C7" s="282">
         <f>F7</f>
         <v>-1686446.6667440513</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F7" s="290">
         <f>SUM(F4:F6)</f>
@@ -16394,7 +16383,7 @@
         <v>HKD</v>
       </c>
       <c r="H7" s="319" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I7" s="320">
         <f>Normalized_FCF!C9</f>
@@ -16406,7 +16395,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C8" s="290">
         <f>C6+C7</f>
@@ -16417,7 +16406,7 @@
         <v>HKD</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16467,7 +16456,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
@@ -16478,7 +16467,7 @@
         <v>HKD</v>
       </c>
       <c r="H10" s="315" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I10" s="313">
         <f>Normalized_FCF!C41</f>
@@ -16489,7 +16478,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16505,7 +16494,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16520,25 +16509,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C14" s="316" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F14" s="316" t="str">
         <f>IF(F17=C17,"I","II")</f>
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16553,7 +16542,7 @@
         <v>8</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16563,14 +16552,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E16" s="315" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F16" s="318">
         <f>Scenarios!C41</f>
@@ -16579,33 +16568,33 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="315" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C17" s="313">
         <f>Normalized_FCF!C32</f>
         <v>0.89099809462634716</v>
       </c>
       <c r="E17" s="315" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F17" s="318">
         <f>Scenarios!C40</f>
         <v>0.86799999999999999</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="315" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C18" s="313">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="315" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16628,41 +16617,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B20" s="121" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D20" s="121" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="121" t="s">
+        <v>395</v>
+      </c>
+      <c r="F20" s="121" t="s">
         <v>396</v>
       </c>
-      <c r="F20" s="121" t="s">
-        <v>397</v>
-      </c>
       <c r="G20" s="121" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>422</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>534</v>
+      </c>
+      <c r="K20" s="121" t="s">
+        <v>535</v>
+      </c>
+      <c r="L20" s="122" t="s">
         <v>423</v>
-      </c>
-      <c r="J20" s="121" t="s">
-        <v>535</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>536</v>
-      </c>
-      <c r="L20" s="122" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -16679,7 +16668,7 @@
       </c>
       <c r="D21" s="306">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E21" s="306">
         <f>$C$17</f>
@@ -16728,7 +16717,7 @@
       </c>
       <c r="D22" s="306">
         <f t="shared" si="1"/>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E22" s="306">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16777,7 +16766,7 @@
       </c>
       <c r="D23" s="306">
         <f t="shared" si="1"/>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E23" s="306">
         <f t="shared" si="6"/>
@@ -16834,7 +16823,7 @@
       </c>
       <c r="D24" s="306">
         <f t="shared" si="1"/>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E24" s="306">
         <f t="shared" si="6"/>
@@ -16891,7 +16880,7 @@
       </c>
       <c r="D25" s="306">
         <f t="shared" si="1"/>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E25" s="306">
         <f t="shared" si="6"/>
@@ -16948,7 +16937,7 @@
       </c>
       <c r="D26" s="306">
         <f t="shared" si="1"/>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E26" s="306">
         <f t="shared" si="6"/>
@@ -16997,7 +16986,7 @@
       </c>
       <c r="D27" s="306">
         <f t="shared" si="1"/>
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E27" s="306">
         <f t="shared" si="6"/>
@@ -18217,7 +18206,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="322" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B51" s="323">
         <f>C15+1</f>
@@ -18268,10 +18257,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="470" t="s">
-        <v>425</v>
-      </c>
-      <c r="K52" s="470"/>
+      <c r="J52" s="467" t="s">
+        <v>424</v>
+      </c>
+      <c r="K52" s="467"/>
       <c r="L52" s="324">
         <f>SUM(L21:L51)</f>
         <v>6216243.1228741389</v>
@@ -19060,7 +19049,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G81" s="330"/>
       <c r="H81" s="330"/>
@@ -19341,7 +19330,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19352,7 +19341,7 @@
       <c r="C4" s="457">
         <v>2</v>
       </c>
-      <c r="D4" s="471" t="str">
+      <c r="D4" s="468" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19362,16 +19351,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 0341.HK – 大家乐集团: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="471"/>
-      <c r="F4" s="471"/>
-      <c r="G4" s="471"/>
+      <c r="E4" s="468"/>
+      <c r="F4" s="468"/>
+      <c r="G4" s="468"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="453"/>
-      <c r="D5" s="471"/>
-      <c r="E5" s="471"/>
-      <c r="F5" s="471"/>
-      <c r="G5" s="471"/>
+      <c r="D5" s="468"/>
+      <c r="E5" s="468"/>
+      <c r="F5" s="468"/>
+      <c r="G5" s="468"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19381,10 +19370,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000 HKD</v>
       </c>
-      <c r="D6" s="471"/>
-      <c r="E6" s="471"/>
-      <c r="F6" s="471"/>
-      <c r="G6" s="471"/>
+      <c r="D6" s="468"/>
+      <c r="E6" s="468"/>
+      <c r="F6" s="468"/>
+      <c r="G6" s="468"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19394,10 +19383,10 @@
         <f>Normalized_FCF!G8</f>
         <v>398162</v>
       </c>
-      <c r="D7" s="471"/>
-      <c r="E7" s="471"/>
-      <c r="F7" s="471"/>
-      <c r="G7" s="471"/>
+      <c r="D7" s="468"/>
+      <c r="E7" s="468"/>
+      <c r="F7" s="468"/>
+      <c r="G7" s="468"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19407,10 +19396,10 @@
         <f>Normalized_FCF!G19</f>
         <v>289000.65016124537</v>
       </c>
-      <c r="D8" s="471"/>
-      <c r="E8" s="471"/>
-      <c r="F8" s="471"/>
-      <c r="G8" s="471"/>
+      <c r="D8" s="468"/>
+      <c r="E8" s="468"/>
+      <c r="F8" s="468"/>
+      <c r="G8" s="468"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19420,27 +19409,27 @@
         <f>Normalized_FCF!C19</f>
         <v>230211.62257446788</v>
       </c>
-      <c r="D9" s="471"/>
-      <c r="E9" s="471"/>
-      <c r="F9" s="471"/>
-      <c r="G9" s="471"/>
+      <c r="D9" s="468"/>
+      <c r="E9" s="468"/>
+      <c r="F9" s="468"/>
+      <c r="G9" s="468"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="456"/>
-      <c r="D10" s="471"/>
-      <c r="E10" s="471"/>
-      <c r="F10" s="471"/>
-      <c r="G10" s="471"/>
+      <c r="D10" s="468"/>
+      <c r="E10" s="468"/>
+      <c r="F10" s="468"/>
+      <c r="G10" s="468"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="456"/>
-      <c r="D11" s="471"/>
-      <c r="E11" s="471"/>
-      <c r="F11" s="471"/>
-      <c r="G11" s="471"/>
+      <c r="D11" s="468"/>
+      <c r="E11" s="468"/>
+      <c r="F11" s="468"/>
+      <c r="G11" s="468"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19450,10 +19439,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.3358728201447585E-2</v>
       </c>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-      <c r="G12" s="471"/>
+      <c r="D12" s="468"/>
+      <c r="E12" s="468"/>
+      <c r="F12" s="468"/>
+      <c r="G12" s="468"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19463,10 +19452,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.35590966478967423</v>
       </c>
-      <c r="D13" s="471"/>
-      <c r="E13" s="471"/>
-      <c r="F13" s="471"/>
-      <c r="G13" s="471"/>
+      <c r="D13" s="468"/>
+      <c r="E13" s="468"/>
+      <c r="F13" s="468"/>
+      <c r="G13" s="468"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19476,14 +19465,14 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.62894902211793369</v>
       </c>
-      <c r="D14" s="471"/>
-      <c r="E14" s="471"/>
-      <c r="F14" s="471"/>
-      <c r="G14" s="471"/>
+      <c r="D14" s="468"/>
+      <c r="E14" s="468"/>
+      <c r="F14" s="468"/>
+      <c r="G14" s="468"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19507,7 +19496,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="458" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F18" s="326"/>
     </row>
@@ -19517,35 +19506,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E20" s="326"/>
       <c r="F20" s="326"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="309" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C22" s="331">
         <v>0.04</v>
@@ -19569,7 +19558,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="309" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C23" s="331">
         <v>0.03</v>
@@ -19592,7 +19581,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="309" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C24" s="331">
         <v>0.02</v>
@@ -19615,7 +19604,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19629,33 +19618,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="309" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C29" s="331">
         <v>0.05</v>
@@ -19678,7 +19667,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="322" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C30" s="331">
         <v>0.01</v>
@@ -19705,12 +19694,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19721,7 +19710,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F33" s="222">
         <f>Holding_Period</f>
@@ -19741,7 +19730,7 @@
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
@@ -19750,7 +19739,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
@@ -19761,7 +19750,7 @@
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -19770,7 +19759,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -19781,15 +19770,15 @@
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F36" s="338" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19808,18 +19797,18 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C40" s="138">
         <v>0.86799999999999999</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C41" s="138">
         <v>0.02</v>
@@ -19862,7 +19851,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>3.0149622951542547E-2</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="224" t="s">
@@ -19981,13 +19970,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E60" s="420"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C61" s="153" t="s">
         <v>103</v>
@@ -20000,10 +19989,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -20058,7 +20047,7 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C65" s="153" t="s">
         <v>103</v>
@@ -20071,10 +20060,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -20154,7 +20143,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="352" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B2" s="352"/>
       <c r="C2" s="352"/>
@@ -20168,7 +20157,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="443" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F3" s="444">
         <f>Thesis!F3</f>
@@ -20177,7 +20166,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="430" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C4" s="431" t="str">
         <f>Thesis!C4</f>
@@ -20185,7 +20174,7 @@
       </c>
       <c r="D4" s="356"/>
       <c r="E4" s="442" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F4" s="445" t="str">
         <f>Thesis!F4</f>
@@ -20194,14 +20183,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="350" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C5" s="362" t="str">
         <f>Thesis!C5</f>
         <v>0341.HK</v>
       </c>
       <c r="E5" s="446" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F5" s="447" t="str">
         <f>Thesis!F5</f>
@@ -20210,7 +20199,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="357" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C6" s="359" t="str">
         <f>Thesis!C6</f>
@@ -20220,7 +20209,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="350" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C7" s="359" t="str">
         <f>Market_currency</f>
@@ -20231,7 +20220,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="358" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
@@ -20240,7 +20229,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="358" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C9" s="360">
         <f>Common_Shares</f>
@@ -20249,14 +20238,14 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="358" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
         <v>3770.0262145000002</v>
       </c>
       <c r="D10" s="350" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
@@ -20268,31 +20257,31 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="476" t="s">
-        <v>503</v>
-      </c>
-      <c r="C12" s="476"/>
-      <c r="D12" s="476"/>
-      <c r="E12" s="476"/>
-      <c r="F12" s="476"/>
+      <c r="B12" s="470" t="s">
+        <v>502</v>
+      </c>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C14" s="355"/>
       <c r="D14" s="356"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="350" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C15" s="365" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="358" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E15" s="351" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20301,14 +20290,14 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="350" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C16" s="365" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="358" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
@@ -20317,14 +20306,14 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="350" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C17" s="432">
         <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="D17" s="358" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E17" s="351" t="str">
         <f>Reporting_currency</f>
@@ -20341,7 +20330,7 @@
         <v>7.8143613713918958</v>
       </c>
       <c r="D18" s="357" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E18" s="434">
         <f>Thesis!E18</f>
@@ -20350,14 +20339,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="357" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C19" s="359" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="350" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E19" s="435">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20370,14 +20359,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="354" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C21" s="368" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="369" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E21" s="370">
         <f>Holding_Period</f>
@@ -20386,14 +20375,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="350" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C22" s="371">
         <f>E140</f>
         <v>4.8034904644125618</v>
       </c>
       <c r="D22" s="372" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
@@ -20402,14 +20391,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="350" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C23" s="374">
         <f>E141</f>
         <v>5.5771912776908135</v>
       </c>
       <c r="D23" s="372" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
@@ -20418,14 +20407,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="350" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C24" s="374">
         <f>E144</f>
         <v>6.9369221239222432</v>
       </c>
       <c r="D24" s="372" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E24" s="375">
         <f>Thesis!E24</f>
@@ -20434,14 +20423,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="350" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C25" s="374">
         <f>E145</f>
         <v>7.5142920296167883</v>
       </c>
       <c r="D25" s="372" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E25" s="375">
         <f>Thesis!E25</f>
@@ -20450,7 +20439,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="352" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B27" s="352"/>
       <c r="C27" s="352"/>
@@ -20459,26 +20448,26 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="476" t="s">
+      <c r="B29" s="470" t="s">
+        <v>503</v>
+      </c>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="476"/>
-      <c r="D29" s="476"/>
-      <c r="E29" s="476"/>
-      <c r="F29" s="476"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="479" t="s">
-        <v>505</v>
-      </c>
-      <c r="C30" s="479"/>
-      <c r="D30" s="479"/>
-      <c r="E30" s="479"/>
-      <c r="F30" s="479"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C32" s="377">
         <f>scaling_factor</f>
@@ -20486,13 +20475,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="472" t="s">
-        <v>506</v>
-      </c>
-      <c r="C33" s="472"/>
-      <c r="D33" s="472"/>
-      <c r="E33" s="472"/>
-      <c r="F33" s="472"/>
+      <c r="B33" s="469" t="s">
+        <v>505</v>
+      </c>
+      <c r="C33" s="469"/>
+      <c r="D33" s="469"/>
+      <c r="E33" s="469"/>
+      <c r="F33" s="469"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="379" t="s">
@@ -20512,13 +20501,13 @@
       <c r="C35" s="381"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="472" t="s">
-        <v>507</v>
-      </c>
-      <c r="C36" s="472"/>
-      <c r="D36" s="472"/>
-      <c r="E36" s="472"/>
-      <c r="F36" s="472"/>
+      <c r="B36" s="469" t="s">
+        <v>506</v>
+      </c>
+      <c r="C36" s="469"/>
+      <c r="D36" s="469"/>
+      <c r="E36" s="469"/>
+      <c r="F36" s="469"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="379" t="s">
@@ -20547,13 +20536,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="472" t="s">
-        <v>508</v>
-      </c>
-      <c r="C40" s="472"/>
-      <c r="D40" s="472"/>
-      <c r="E40" s="472"/>
-      <c r="F40" s="472"/>
+      <c r="B40" s="469" t="s">
+        <v>507</v>
+      </c>
+      <c r="C40" s="469"/>
+      <c r="D40" s="469"/>
+      <c r="E40" s="469"/>
+      <c r="F40" s="469"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="379" t="s">
@@ -20569,13 +20558,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="472" t="s">
-        <v>509</v>
-      </c>
-      <c r="C43" s="472"/>
-      <c r="D43" s="472"/>
-      <c r="E43" s="472"/>
-      <c r="F43" s="472"/>
+      <c r="B43" s="469" t="s">
+        <v>508</v>
+      </c>
+      <c r="C43" s="469"/>
+      <c r="D43" s="469"/>
+      <c r="E43" s="469"/>
+      <c r="F43" s="469"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="379" t="s">
@@ -20622,7 +20611,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="350" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20639,17 +20628,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="472" t="s">
-        <v>511</v>
-      </c>
-      <c r="C51" s="472"/>
-      <c r="D51" s="472"/>
-      <c r="E51" s="472"/>
-      <c r="F51" s="472"/>
+      <c r="B51" s="469" t="s">
+        <v>510</v>
+      </c>
+      <c r="C51" s="469"/>
+      <c r="D51" s="469"/>
+      <c r="E51" s="469"/>
+      <c r="F51" s="469"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="379" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C52" s="380">
         <f>Normalized_FCF!C12</f>
@@ -20661,13 +20650,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="472" t="s">
-        <v>512</v>
-      </c>
-      <c r="C54" s="478"/>
-      <c r="D54" s="478"/>
-      <c r="E54" s="478"/>
-      <c r="F54" s="478"/>
+      <c r="B54" s="469" t="s">
+        <v>511</v>
+      </c>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20683,26 +20672,26 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="476" t="s">
+      <c r="B57" s="470" t="s">
+        <v>512</v>
+      </c>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="476"/>
-      <c r="D57" s="476"/>
-      <c r="E57" s="476"/>
-      <c r="F57" s="476"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="476" t="s">
-        <v>514</v>
-      </c>
-      <c r="C58" s="476"/>
-      <c r="D58" s="476"/>
-      <c r="E58" s="476"/>
-      <c r="F58" s="476"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C60" s="380">
         <f>Normalized_FCF!G19</f>
@@ -20745,7 +20734,7 @@
         <v>6.1538461538461542E-2</v>
       </c>
       <c r="E63" s="379" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F63" s="387">
         <f>Normalized_FCF!C90</f>
@@ -20754,13 +20743,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="376" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C65" s="388" t="s">
         <v>327</v>
       </c>
       <c r="D65" s="388" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -20820,7 +20809,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="352" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B71" s="352"/>
       <c r="C71" s="352"/>
@@ -20833,36 +20822,36 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="476" t="s">
-        <v>515</v>
-      </c>
-      <c r="C73" s="476"/>
-      <c r="D73" s="476"/>
-      <c r="E73" s="476"/>
-      <c r="F73" s="476"/>
+      <c r="B73" s="470" t="s">
+        <v>514</v>
+      </c>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="479" t="s">
-        <v>484</v>
-      </c>
-      <c r="C74" s="479"/>
-      <c r="D74" s="479"/>
-      <c r="E74" s="479"/>
-      <c r="F74" s="479"/>
+      <c r="B74" s="471" t="s">
+        <v>483</v>
+      </c>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="476" t="s">
-        <v>516</v>
-      </c>
-      <c r="C77" s="476"/>
-      <c r="D77" s="476"/>
-      <c r="E77" s="476"/>
-      <c r="F77" s="476"/>
+      <c r="B77" s="470" t="s">
+        <v>515</v>
+      </c>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20910,7 +20899,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="350" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20928,7 +20917,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="389" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C85" s="397">
         <f>BS!C66</f>
@@ -20954,7 +20943,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="350" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20985,7 +20974,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="379" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
@@ -20998,7 +20987,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="352" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B94" s="352"/>
       <c r="C94" s="352"/>
@@ -21011,33 +21000,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="476" t="s">
-        <v>519</v>
-      </c>
-      <c r="C96" s="476"/>
-      <c r="D96" s="476"/>
-      <c r="E96" s="476"/>
-      <c r="F96" s="476"/>
+      <c r="B96" s="470" t="s">
+        <v>518</v>
+      </c>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="479" t="s">
-        <v>520</v>
-      </c>
-      <c r="C97" s="479"/>
-      <c r="D97" s="479"/>
-      <c r="E97" s="479"/>
-      <c r="F97" s="479"/>
+      <c r="B97" s="471" t="s">
+        <v>519</v>
+      </c>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="479" t="s">
-        <v>521</v>
-      </c>
-      <c r="C98" s="479"/>
-      <c r="D98" s="479"/>
-      <c r="E98" s="479"/>
-      <c r="F98" s="479"/>
+      <c r="B98" s="471" t="s">
+        <v>520</v>
+      </c>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21045,7 +21034,7 @@
     <row r="100" spans="1:6">
       <c r="A100" s="392"/>
       <c r="B100" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -21081,7 +21070,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="392"/>
       <c r="B104" s="379" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C104" s="375">
         <v>0</v>
@@ -21094,29 +21083,29 @@
     <row r="106" spans="1:6">
       <c r="A106" s="392"/>
       <c r="B106" s="400" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C106" s="399"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="476" t="s">
-        <v>522</v>
-      </c>
-      <c r="C107" s="476"/>
-      <c r="D107" s="476"/>
-      <c r="E107" s="476"/>
-      <c r="F107" s="476"/>
+      <c r="B107" s="470" t="s">
+        <v>521</v>
+      </c>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="476" t="s">
-        <v>541</v>
-      </c>
-      <c r="C108" s="476"/>
-      <c r="D108" s="476"/>
-      <c r="E108" s="476"/>
-      <c r="F108" s="476"/>
+      <c r="B108" s="470" t="s">
+        <v>540</v>
+      </c>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21124,13 +21113,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="392"/>
       <c r="B110" s="376" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="392"/>
       <c r="B111" s="382" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
@@ -21144,7 +21133,7 @@
     <row r="112" spans="1:6">
       <c r="A112" s="392"/>
       <c r="B112" s="379" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
@@ -21160,13 +21149,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="476" t="s">
-        <v>523</v>
-      </c>
-      <c r="C114" s="476"/>
-      <c r="D114" s="476"/>
-      <c r="E114" s="476"/>
-      <c r="F114" s="476"/>
+      <c r="B114" s="470" t="s">
+        <v>522</v>
+      </c>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21174,25 +21163,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="392"/>
       <c r="B116" s="376" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="392"/>
       <c r="B117" s="349" t="s">
+        <v>378</v>
+      </c>
+      <c r="C117" s="349" t="s">
         <v>379</v>
-      </c>
-      <c r="C117" s="349" t="s">
-        <v>380</v>
       </c>
       <c r="D117" s="349" t="s">
         <v>99</v>
       </c>
       <c r="E117" s="349" t="s">
+        <v>380</v>
+      </c>
+      <c r="F117" s="349" t="s">
         <v>381</v>
-      </c>
-      <c r="F117" s="349" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21308,13 +21297,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="472" t="s">
-        <v>524</v>
-      </c>
-      <c r="C124" s="472"/>
-      <c r="D124" s="472"/>
-      <c r="E124" s="472"/>
-      <c r="F124" s="472"/>
+      <c r="B124" s="469" t="s">
+        <v>523</v>
+      </c>
+      <c r="C124" s="469"/>
+      <c r="D124" s="469"/>
+      <c r="E124" s="469"/>
+      <c r="F124" s="469"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="379" t="s">
@@ -21331,7 +21320,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="B127" s="474" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C127" s="474"/>
       <c r="D127" s="474"/>
@@ -21340,7 +21329,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B129" s="352"/>
       <c r="C129" s="352"/>
@@ -21350,7 +21339,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="475" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C131" s="475"/>
       <c r="D131" s="475"/>
@@ -21358,22 +21347,22 @@
       <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="476" t="s">
-        <v>527</v>
-      </c>
-      <c r="C132" s="476"/>
-      <c r="D132" s="476"/>
-      <c r="E132" s="476"/>
-      <c r="F132" s="476"/>
+      <c r="B132" s="470" t="s">
+        <v>526</v>
+      </c>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="350" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C135" s="412">
         <f>E21</f>
@@ -21382,7 +21371,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="350" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C136" s="413">
         <f>Scenarios!C58</f>
@@ -21395,28 +21384,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="376" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C138" s="414"/>
       <c r="D138" s="414"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="347" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="348" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21463,21 +21452,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="347" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="348" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21524,7 +21513,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="352" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B147" s="352"/>
       <c r="C147" s="352"/>
@@ -21533,65 +21522,65 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
-        <v>528</v>
-      </c>
-      <c r="C149" s="476"/>
-      <c r="D149" s="476"/>
-      <c r="E149" s="476"/>
-      <c r="F149" s="476"/>
+      <c r="B149" s="476" t="s">
+        <v>527</v>
+      </c>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="478" t="s">
-        <v>529</v>
-      </c>
-      <c r="C152" s="478"/>
-      <c r="D152" s="478"/>
-      <c r="E152" s="478"/>
-      <c r="F152" s="478"/>
+      <c r="B152" s="472" t="s">
+        <v>528</v>
+      </c>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="419" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="419" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="350" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="472" t="s">
-        <v>444</v>
-      </c>
-      <c r="C158" s="472"/>
-      <c r="D158" s="472"/>
-      <c r="E158" s="472"/>
-      <c r="F158" s="472"/>
+      <c r="B158" s="469" t="s">
+        <v>443</v>
+      </c>
+      <c r="C158" s="469"/>
+      <c r="D158" s="469"/>
+      <c r="E158" s="469"/>
+      <c r="F158" s="469"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="350" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="473" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C161" s="473"/>
       <c r="D161" s="473"/>
@@ -21600,7 +21589,7 @@
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="473" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C162" s="473"/>
       <c r="D162" s="473"/>
@@ -21609,32 +21598,35 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="419" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="419" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="419" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21649,15 +21641,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21676,28 +21665,4 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA9E8A69-327E-47E0-B9FB-0AC135518E27}">
-  <dimension ref="B2:E2"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="461" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="461" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="461" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="461"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="459" t="s">
-        <v>334</v>
-      </c>
-      <c r="C2" s="460"/>
-      <c r="D2" s="460"/>
-      <c r="E2" s="460"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B51099-1C64-4083-9485-48866599F07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1323F58D-DF45-41A8-8209-AFC4B58FBD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.5</v>
+        <v>6.66</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3770.0262145000002</v>
+        <v>3862.8268597800002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.15535566535489756</v>
+        <v>0.11183056447009664</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5533,7 +5533,7 @@
         <v>316</v>
       </c>
       <c r="E21" s="450">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>4.8034904644125618</v>
+        <v>5.1203191959855099</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E22" s="79">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>5.5771912776908135</v>
+        <v>5.9046863925539546</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
       </c>
       <c r="E23" s="451">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>6.9369221239222432</v>
+        <v>6.5660659780940076</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>7.5142920296167883</v>
+        <v>7.3792932677079612</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1063666265514203E-2</v>
+        <v>5.9596671280156499E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.006006006006006E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C135" s="204">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
         <v>475</v>
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="340">
         <f>Scenarios!C62</f>
-        <v>0.51577503429355298</v>
+        <v>0.8168965684352435</v>
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>4.2877154301190092</v>
+        <v>4.3034226275502663</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>4.8034904644125618</v>
+        <v>5.1203191959855099</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="340">
         <f>Scenarios!C63</f>
-        <v>0.57600000000000007</v>
+        <v>0.89835581614662341</v>
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>5.001191277690813</v>
+        <v>5.0063305764073309</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>5.5771912776908135</v>
+        <v>5.9046863925539546</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
         <v>475</v>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="340">
         <f>Scenarios!C66</f>
-        <v>0.67833709316953872</v>
+        <v>0.96504125037545974</v>
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>6.2585850307527044</v>
+        <v>5.6010247277185474</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>6.9369221239222432</v>
+        <v>6.5660659780940076</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="340">
         <f>Scenarios!C67</f>
-        <v>0.72070897245722421</v>
+        <v>1.0449500908692064</v>
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>6.7935830571595641</v>
+        <v>6.3343431768387548</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>7.5142920296167883</v>
+        <v>7.3792932677079612</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -14229,24 +14229,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.006006006006006E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.006006006006006E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7692307692307681E-2</v>
+        <v>8.5585585585585572E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8461538461538461E-2</v>
+        <v>5.7057057057057055E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8461538461538461E-2</v>
+        <v>5.7057057057057055E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15428,50 +15428,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1063666265514203E-2</v>
+        <v>5.9596671280156499E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6657464356537391E-2</v>
+        <v>7.4815843591215167E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.2090452702739689E-2</v>
+        <v>8.9878069454625828E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8889462596864448E-2</v>
+        <v>2.8195421453396232E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.333143803744533E-3</v>
+        <v>-6.1809962048557749E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.152418398124112E-2</v>
+        <v>-3.0766846227938027E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.533489374626735E-2</v>
+        <v>5.40055269295402E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14795520462288819</v>
+        <v>0.14440072523254852</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12204159170840694</v>
+        <v>0.11910966157727404</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13722875400976869</v>
+        <v>0.13393196712665112</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13379482563277015</v>
+        <v>0.13058053552747836</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15485,43 +15485,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2363226837981449E-2</v>
+        <v>6.0865011178210117E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8385327061762262E-2</v>
+        <v>8.6261955841059265E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.949236787064256E-2</v>
+        <v>2.8783842516392887E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0609658129473993E-3</v>
+        <v>5.9153570246483628E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5635939774975268E-2</v>
+        <v>9.333837966026115E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9730897284984915E-2</v>
+        <v>1.9256881734594885E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15705726334810874</v>
+        <v>0.15328411588028631</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1218280653416926</v>
+        <v>0.11890126497312341</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13364628555157756</v>
+        <v>0.13043556397676487</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13736244008284204</v>
+        <v>0.13406244152229327</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19714,7 +19714,7 @@
       </c>
       <c r="F33" s="222">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.5</v>
+        <v>6.66</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15535566535489756</v>
+        <v>0.11183056447009664</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.8684477448290957</v>
+        <v>0.56386844863399943</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C57" s="222">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" s="126"/>
     </row>
@@ -20001,23 +20001,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.51577503429355298</v>
+        <v>0.8168965684352435</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>4.2877154301190092</v>
+        <v>4.3034226275502663</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>4.8034904644125618</v>
+        <v>5.1203191959855099</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.38529967631162121</v>
+        <v>0.34475525860234468</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20026,23 +20026,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.57600000000000007</v>
+        <v>0.89835581614662341</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>5.001191277690813</v>
+        <v>5.0063305764073309</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>5.5771912776908135</v>
+        <v>5.9046863925539546</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.28628956192009292</v>
+        <v>0.24438017236177412</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20072,15 +20072,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>0.67833709316953872</v>
+        <v>0.96504125037545974</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>6.2585850307527044</v>
+        <v>5.6010247277185474</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>6.9369221239222432</v>
+        <v>6.5660659780940076</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.11178286983800823</v>
+        <v>0.15926801896697729</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20097,15 +20097,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>0.72070897245722421</v>
+        <v>1.0449500908692064</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.7935830571595641</v>
+        <v>6.3343431768387548</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>7.5142920296167883</v>
+        <v>7.3792932677079612</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>3.8399726799639766E-2</v>
+        <v>5.567545228669657E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>6.5</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20242,14 +20242,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3770.0262145000002</v>
+        <v>3862.8268597800002</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.15535566535489756</v>
+        <v>0.11183056447009664</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E21" s="370">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -20379,14 +20379,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>4.8034904644125618</v>
+        <v>5.1203191959855099</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20395,14 +20395,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>5.5771912776908135</v>
+        <v>5.9046863925539546</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>6.9369221239222432</v>
+        <v>6.5660659780940076</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>447</v>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>7.5142920296167883</v>
+        <v>7.3792932677079612</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>446</v>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>6.1063666265514203E-2</v>
+        <v>5.9596671280156499E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.006006006006006E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="C135" s="412">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
         <v>475</v>
@@ -21414,19 +21414,19 @@
       </c>
       <c r="C140" s="416">
         <f>Scenarios!C62</f>
-        <v>0.51577503429355298</v>
+        <v>0.8168965684352435</v>
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>4.2877154301190092</v>
+        <v>4.3034226275502663</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>4.8034904644125618</v>
+        <v>5.1203191959855099</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21435,19 +21435,19 @@
       </c>
       <c r="C141" s="416">
         <f>Scenarios!C63</f>
-        <v>0.57600000000000007</v>
+        <v>0.89835581614662341</v>
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>5.001191277690813</v>
+        <v>5.0063305764073309</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>5.5771912776908135</v>
+        <v>5.9046863925539546</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
         <v>475</v>
@@ -21475,15 +21475,15 @@
       </c>
       <c r="C144" s="416">
         <f>Scenarios!C66</f>
-        <v>0.67833709316953872</v>
+        <v>0.96504125037545974</v>
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>6.2585850307527044</v>
+        <v>5.6010247277185474</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>6.9369221239222432</v>
+        <v>6.5660659780940076</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21496,15 +21496,15 @@
       </c>
       <c r="C145" s="416">
         <f>Scenarios!C67</f>
-        <v>0.72070897245722421</v>
+        <v>1.0449500908692064</v>
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>6.7935830571595641</v>
+        <v>6.3343431768387548</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>7.5142920296167883</v>
+        <v>7.3792932677079612</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1323F58D-DF45-41A8-8209-AFC4B58FBD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1763135-3536-41DA-B96E-B5D4791F1265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3862.8268597800002</v>
+        <v>3897.6271017599997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.11183056447009664</v>
+        <v>0.10832958200820168</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>5.1203191959855099</v>
+        <v>4.6766451060685625</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E22" s="79">
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>5.9046863925539546</v>
+        <v>5.5505413533150421</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
       </c>
       <c r="E23" s="451">
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.9596671280156499E-2</v>
+        <v>5.9064558143726541E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.006006006006006E-2</v>
+        <v>5.9523809523809527E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="340">
         <f>Scenarios!C62</f>
-        <v>0.8168965684352435</v>
+        <v>0.76946442037261453</v>
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>4.3034226275502663</v>
+        <v>3.9071806856959479</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>5.1203191959855099</v>
+        <v>4.6766451060685625</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="340">
         <f>Scenarios!C63</f>
-        <v>0.89835581614662341</v>
+        <v>0.86192453047990469</v>
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>5.0063305764073309</v>
+        <v>4.6886168228351375</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>5.9046863925539546</v>
+        <v>5.5505413533150421</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14229,24 +14229,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.006006006006006E-2</v>
+        <v>5.9523809523809527E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.006006006006006E-2</v>
+        <v>5.9523809523809527E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.5585585585585572E-2</v>
+        <v>8.4821428571428562E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7057057057057055E-2</v>
+        <v>5.6547619047619048E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7057057057057055E-2</v>
+        <v>5.6547619047619048E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15428,50 +15428,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9596671280156499E-2</v>
+        <v>5.9064558143726541E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.4815843591215167E-2</v>
+        <v>7.4147844987722186E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.9878069454625828E-2</v>
+        <v>8.9075586691638106E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8195421453396232E-2</v>
+        <v>2.7943676618990911E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.1809962048557749E-3</v>
+        <v>-6.1258087387409919E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.0766846227938027E-2</v>
+        <v>-3.0492142243760012E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.40055269295402E-2</v>
+        <v>5.3523334724812167E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14440072523254852</v>
+        <v>0.14311143304297219</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.11910966157727404</v>
+        <v>0.11804618245604838</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13393196712665112</v>
+        <v>0.13273614599159175</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13058053552747836</v>
+        <v>0.12941463788884019</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15485,43 +15485,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0865011178210117E-2</v>
+        <v>6.0321573578404675E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6261955841059265E-2</v>
+        <v>8.54917598067641E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8783842516392887E-2</v>
+        <v>2.8526843922496527E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9153570246483628E-3</v>
+        <v>5.8625413369282888E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.333837966026115E-2</v>
+        <v>9.2505001270437398E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9256881734594885E-2</v>
+        <v>1.9084945290536004E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15328411588028631</v>
+        <v>0.15191550770278375</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11890126497312341</v>
+        <v>0.11783964653586339</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13043556397676487</v>
+        <v>0.12927096072697236</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13406244152229327</v>
+        <v>0.13286545543727279</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.11183056447009664</v>
+        <v>0.10832958200820168</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20001,23 +20001,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.8168965684352435</v>
+        <v>0.76946442037261453</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>4.3034226275502663</v>
+        <v>3.9071806856959479</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>5.1203191959855099</v>
+        <v>4.6766451060685625</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.34475525860234468</v>
+        <v>0.40153201473512645</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20026,23 +20026,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.89835581614662341</v>
+        <v>0.86192453047990469</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>5.0063305764073309</v>
+        <v>4.6886168228351375</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>5.9046863925539546</v>
+        <v>5.5505413533150421</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.24438017236177412</v>
+        <v>0.2896999396987987</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20224,7 +20224,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20242,14 +20242,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3862.8268597800002</v>
+        <v>3897.6271017599997</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.11183056447009664</v>
+        <v>0.10832958200820168</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20257,13 +20257,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20379,14 +20379,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>5.1203191959855099</v>
+        <v>4.6766451060685625</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20395,14 +20395,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>5.9046863925539546</v>
+        <v>5.5505413533150421</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20448,22 +20448,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>504</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20653,10 +20653,10 @@
       <c r="B54" s="469" t="s">
         <v>511</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20672,22 +20672,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>5.9596671280156499E-2</v>
+        <v>5.9064558143726541E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.006006006006006E-2</v>
+        <v>5.9523809523809527E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20822,22 +20822,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>514</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20845,13 +20845,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -21000,33 +21000,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21089,23 +21089,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>540</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21149,13 +21149,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>522</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21319,13 +21319,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>524</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21338,22 +21338,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21414,19 +21414,19 @@
       </c>
       <c r="C140" s="416">
         <f>Scenarios!C62</f>
-        <v>0.8168965684352435</v>
+        <v>0.76946442037261453</v>
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>4.3034226275502663</v>
+        <v>3.9071806856959479</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>5.1203191959855099</v>
+        <v>4.6766451060685625</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21435,19 +21435,19 @@
       </c>
       <c r="C141" s="416">
         <f>Scenarios!C63</f>
-        <v>0.89835581614662341</v>
+        <v>0.86192453047990469</v>
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>5.0063305764073309</v>
+        <v>4.6886168228351375</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>5.9046863925539546</v>
+        <v>5.5505413533150421</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21522,13 +21522,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>527</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21536,13 +21536,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>528</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21579,22 +21579,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21618,15 +21618,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21641,12 +21638,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1763135-3536-41DA-B96E-B5D4791F1265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2CBB97-716F-48C2-882B-A18CC50E9CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5015,16 +5024,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.72</v>
+        <v>6.51</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3897.6271017599997</v>
+        <v>3775.8262548299999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.10832958200820168</v>
+        <v>0.1207769498377638</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="459" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="459" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.9064558143726541E-2</v>
+        <v>6.0969866470943525E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.9523809523809527E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="459" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="459" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="461" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="459" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="466" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="460" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14229,24 +14229,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.9523809523809527E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.9523809523809527E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.4821428571428562E-2</v>
+        <v>8.755760368663594E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.6547619047619048E-2</v>
+        <v>5.8371735791090631E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.6547619047619048E-2</v>
+        <v>5.8371735791090631E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15428,50 +15428,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9064558143726541E-2</v>
+        <v>6.0969866470943525E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.4147844987722186E-2</v>
+        <v>7.6539710955068063E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.9075586691638106E-2</v>
+        <v>9.1948992713949004E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.7943676618990911E-2</v>
+        <v>2.8845085542184169E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.1258087387409919E-3</v>
+        <v>-6.3234154722487659E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.0492142243760012E-2</v>
+        <v>-3.1475759735494206E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.3523334724812167E-2</v>
+        <v>5.5249893909483531E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14311143304297219</v>
+        <v>0.14772793088306807</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.11804618245604838</v>
+        <v>0.12185412382559832</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13273614599159175</v>
+        <v>0.13701795715261084</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.12941463788884019</v>
+        <v>0.13358930362718988</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15485,43 +15485,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0321573578404675E-2</v>
+        <v>6.2267430790611276E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.54917598067641E-2</v>
+        <v>8.8249558510208104E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8526843922496527E-2</v>
+        <v>2.9447064694189961E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8625413369282888E-3</v>
+        <v>6.0516555736033944E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2505001270437398E-2</v>
+        <v>9.5489033569483753E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9084945290536004E-2</v>
+        <v>1.9700588687004906E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15191550770278375</v>
+        <v>0.15681600795126066</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11783964653586339</v>
+        <v>0.1216409254563751</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12927096072697236</v>
+        <v>0.13344099171816501</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13286545543727279</v>
+        <v>0.13715143787073322</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.72</v>
+        <v>6.51</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.10832958200820168</v>
+        <v>0.1207769498377638</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20224,7 +20224,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>6.72</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20242,14 +20242,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3897.6271017599997</v>
+        <v>3775.8262548299999</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.10832958200820168</v>
+        <v>0.1207769498377638</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20257,13 +20257,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20448,22 +20448,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20653,10 +20653,10 @@
       <c r="B54" s="469" t="s">
         <v>511</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20672,22 +20672,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>5.9064558143726541E-2</v>
+        <v>6.0969866470943525E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>5.9523809523809527E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20822,22 +20822,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="471" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20845,13 +20845,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="470" t="s">
         <v>515</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -21000,33 +21000,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="470" t="s">
         <v>518</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="471" t="s">
         <v>520</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21089,23 +21089,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="470" t="s">
         <v>540</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21149,13 +21149,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="470" t="s">
         <v>522</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21319,13 +21319,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21338,22 +21338,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="475" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="470" t="s">
         <v>526</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21522,13 +21522,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="476" t="s">
         <v>527</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21536,13 +21536,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="472" t="s">
         <v>528</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21579,22 +21579,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="473" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21618,12 +21618,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21638,15 +21641,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2CBB97-716F-48C2-882B-A18CC50E9CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A97901-4164-4D8A-94FD-8DCEFCD7C473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3775.8262548299999</v>
+        <v>3770.0262145000002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.1207769498377638</v>
+        <v>0.12138349206304627</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>4.6766451060685625</v>
+        <v>4.333028820025568</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E22" s="79">
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>5.5505413533150421</v>
+        <v>5.3553121183397749</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
       </c>
       <c r="E23" s="451">
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.0969866470943525E-2</v>
+        <v>6.1063666265514203E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="340">
         <f>Scenarios!C62</f>
-        <v>0.76946442037261453</v>
+        <v>0.73194063044404789</v>
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>3.9071806856959479</v>
+        <v>3.6010881895815197</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>4.6766451060685625</v>
+        <v>4.333028820025568</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="340">
         <f>Scenarios!C63</f>
-        <v>0.86192453047990469</v>
+        <v>0.84160157890763132</v>
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>4.6886168228351375</v>
+        <v>4.513710539432144</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>5.5505413533150421</v>
+        <v>5.3553121183397749</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14229,24 +14229,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.755760368663594E-2</v>
+        <v>8.7692307692307681E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8371735791090631E-2</v>
+        <v>5.8461538461538461E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8371735791090631E-2</v>
+        <v>5.8461538461538461E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15428,50 +15428,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0969866470943525E-2</v>
+        <v>6.1063666265514203E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6539710955068063E-2</v>
+        <v>7.6657464356537391E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.1948992713949004E-2</v>
+        <v>9.2090452702739689E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8845085542184169E-2</v>
+        <v>2.8889462596864448E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3234154722487659E-3</v>
+        <v>-6.333143803744533E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1475759735494206E-2</v>
+        <v>-3.152418398124112E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5249893909483531E-2</v>
+        <v>5.533489374626735E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14772793088306807</v>
+        <v>0.14795520462288819</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12185412382559832</v>
+        <v>0.12204159170840694</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13701795715261084</v>
+        <v>0.13722875400976869</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13358930362718988</v>
+        <v>0.13379482563277015</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15485,43 +15485,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2267430790611276E-2</v>
+        <v>6.2363226837981449E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8249558510208104E-2</v>
+        <v>8.8385327061762262E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9447064694189961E-2</v>
+        <v>2.949236787064256E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0516555736033944E-3</v>
+        <v>6.0609658129473993E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5489033569483753E-2</v>
+        <v>9.5635939774975268E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9700588687004906E-2</v>
+        <v>1.9730897284984915E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15681600795126066</v>
+        <v>0.15705726334810874</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1216409254563751</v>
+        <v>0.1218280653416926</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13344099171816501</v>
+        <v>0.13364628555157756</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13715143787073322</v>
+        <v>0.13736244008284204</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1207769498377638</v>
+        <v>0.12138349206304627</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20001,23 +20001,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.76946442037261453</v>
+        <v>0.73194063044404789</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.9071806856959479</v>
+        <v>3.6010881895815197</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>4.6766451060685625</v>
+        <v>4.333028820025568</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.40153201473512645</v>
+        <v>0.44550442267891077</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20026,23 +20026,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.86192453047990469</v>
+        <v>0.84160157890763132</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.6886168228351375</v>
+        <v>4.513710539432144</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>5.5505413533150421</v>
+        <v>5.3553121183397749</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.2896999396987987</v>
+        <v>0.31468332934468768</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20224,7 +20224,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20242,14 +20242,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3775.8262548299999</v>
+        <v>3770.0262145000002</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.1207769498377638</v>
+        <v>0.12138349206304627</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20257,13 +20257,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20379,14 +20379,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>4.6766451060685625</v>
+        <v>4.333028820025568</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20395,14 +20395,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>5.5505413533150421</v>
+        <v>5.3553121183397749</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20448,22 +20448,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>504</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20653,10 +20653,10 @@
       <c r="B54" s="469" t="s">
         <v>511</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20672,22 +20672,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>6.0969866470943525E-2</v>
+        <v>6.1063666265514203E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20822,22 +20822,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>514</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20845,13 +20845,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -21000,33 +21000,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21089,23 +21089,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>540</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21149,13 +21149,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>522</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21319,13 +21319,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>524</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21338,22 +21338,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21414,19 +21414,19 @@
       </c>
       <c r="C140" s="416">
         <f>Scenarios!C62</f>
-        <v>0.76946442037261453</v>
+        <v>0.73194063044404789</v>
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>3.9071806856959479</v>
+        <v>3.6010881895815197</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>4.6766451060685625</v>
+        <v>4.333028820025568</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21435,19 +21435,19 @@
       </c>
       <c r="C141" s="416">
         <f>Scenarios!C63</f>
-        <v>0.86192453047990469</v>
+        <v>0.84160157890763132</v>
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>4.6886168228351375</v>
+        <v>4.513710539432144</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>5.5505413533150421</v>
+        <v>5.3553121183397749</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21522,13 +21522,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>527</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21536,13 +21536,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>528</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21579,22 +21579,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21618,15 +21618,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21641,12 +21638,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A97901-4164-4D8A-94FD-8DCEFCD7C473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E1FC3F-D3E2-49FF-A3FF-2C2D1C3A6769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5015,16 +5024,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3770.0262145000002</v>
+        <v>3758.4261338400001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.12138349206304627</v>
+        <v>0.12260045445698151</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="459" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="459" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1063666265514203E-2</v>
+        <v>6.1252134371271964E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="459" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="459" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="461" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="459" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="466" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="460" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14229,24 +14229,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7692307692307681E-2</v>
+        <v>8.7962962962962951E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8461538461538461E-2</v>
+        <v>5.8641975308641972E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8461538461538461E-2</v>
+        <v>5.8641975308641972E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15428,50 +15428,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1063666265514203E-2</v>
+        <v>6.1252134371271964E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6657464356537391E-2</v>
+        <v>7.6894061468748928E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.2090452702739689E-2</v>
+        <v>9.2374682495032098E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8889462596864448E-2</v>
+        <v>2.8978627604879462E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.333143803744533E-3</v>
+        <v>-6.3526905438795467E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.152418398124112E-2</v>
+        <v>-3.1621480845380752E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.533489374626735E-2</v>
+        <v>5.5505680455360765E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14795520462288819</v>
+        <v>0.1484118564890082</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12204159170840694</v>
+        <v>0.12241826328775386</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13722875400976869</v>
+        <v>0.13765229954683589</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13379482563277015</v>
+        <v>0.13420777262546388</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15485,43 +15485,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2363226837981449E-2</v>
+        <v>6.2555705933160399E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8385327061762262E-2</v>
+        <v>8.8658121281088687E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.949236787064256E-2</v>
+        <v>2.9583393697403801E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0609658129473993E-3</v>
+        <v>6.0796724975552621E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5635939774975268E-2</v>
+        <v>9.5931112428601736E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9730897284984915E-2</v>
+        <v>1.979179511611141E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15705726334810874</v>
+        <v>0.15754200798807202</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1218280653416926</v>
+        <v>0.1222040778890435</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13364628555157756</v>
+        <v>0.13405877408723058</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13736244008284204</v>
+        <v>0.13778639823124586</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12138349206304627</v>
+        <v>0.12260045445698151</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20224,7 +20224,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20242,14 +20242,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3770.0262145000002</v>
+        <v>3758.4261338400001</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.12138349206304627</v>
+        <v>0.12260045445698151</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20257,13 +20257,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20448,22 +20448,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20653,10 +20653,10 @@
       <c r="B54" s="469" t="s">
         <v>511</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20672,22 +20672,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>6.1063666265514203E-2</v>
+        <v>6.1252134371271964E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.1538461538461542E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20822,22 +20822,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="471" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20845,13 +20845,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="470" t="s">
         <v>515</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -21000,33 +21000,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="470" t="s">
         <v>518</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="471" t="s">
         <v>520</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21089,23 +21089,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="470" t="s">
         <v>540</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21149,13 +21149,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="470" t="s">
         <v>522</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21319,13 +21319,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21338,22 +21338,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="475" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="470" t="s">
         <v>526</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21522,13 +21522,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="476" t="s">
         <v>527</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21536,13 +21536,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="472" t="s">
         <v>528</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21579,22 +21579,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="473" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21618,12 +21618,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21638,15 +21641,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E1FC3F-D3E2-49FF-A3FF-2C2D1C3A6769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B2BFE4-AA3F-4C74-9279-7572CD3818FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.48</v>
+        <v>6.58</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3758.4261338400001</v>
+        <v>3816.4265371399997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.12260045445698151</v>
+        <v>0.11656690703965478</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0321250870188803E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.0790273556231005E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14229,24 +14229,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.0790273556231005E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.0790273556231005E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7962962962962951E-2</v>
+        <v>8.6626139817629177E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8641975308641972E-2</v>
+        <v>5.7750759878419454E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8641975308641972E-2</v>
+        <v>5.7750759878419454E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15428,50 +15428,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0321250870188803E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6894061468748928E-2</v>
+        <v>7.5725458710865209E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.2374682495032098E-2</v>
+        <v>9.0970811940396357E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8978627604879462E-2</v>
+        <v>2.8538222930033271E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3526905438795467E-3</v>
+        <v>-6.2561450948844166E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1621480845380752E-2</v>
+        <v>-3.1140911227669796E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5505680455360765E-2</v>
+        <v>5.4662129080659233E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1484118564890082</v>
+        <v>0.14615635715026948</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12241826328775386</v>
+        <v>0.12055780335936855</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13765229954683589</v>
+        <v>0.13556031931056178</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13420777262546388</v>
+        <v>0.13216814082264527</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15485,43 +15485,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2555705933160399E-2</v>
+        <v>6.1605011314115415E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8658121281088687E-2</v>
+        <v>8.7310733419673978E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9583393697403801E-2</v>
+        <v>2.913379804850709E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0796724975552621E-3</v>
+        <v>5.9872762589905926E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5931112428601736E-2</v>
+        <v>9.4473192786829682E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.979179511611141E-2</v>
+        <v>1.9491007956292088E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15754200798807202</v>
+        <v>0.15514775254752383</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1222040778890435</v>
+        <v>0.12034687305790302</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13405877408723058</v>
+        <v>0.13202140669988666</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13778639823124586</v>
+        <v>0.13569238002104456</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.48</v>
+        <v>6.58</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12260045445698151</v>
+        <v>0.11656690703965478</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20224,7 +20224,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>6.48</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20242,14 +20242,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3758.4261338400001</v>
+        <v>3816.4265371399997</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.12260045445698151</v>
+        <v>0.11656690703965478</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20257,13 +20257,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20448,22 +20448,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>504</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20653,10 +20653,10 @@
       <c r="B54" s="469" t="s">
         <v>511</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20672,22 +20672,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0321250870188803E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.0790273556231005E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20822,22 +20822,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>514</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20845,13 +20845,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -21000,33 +21000,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21089,23 +21089,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>540</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21149,13 +21149,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>522</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21319,13 +21319,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>524</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21338,22 +21338,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21522,13 +21522,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>527</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21536,13 +21536,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>528</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21579,22 +21579,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21618,15 +21618,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21641,12 +21638,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB65637-7354-449D-9967-7339D8F18A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E2A09B-C837-490A-8282-619FD0B737CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$89:$M$89</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
@@ -2086,9 +2086,6 @@
     <t>Try obtain this number by reverse engineering.</t>
   </si>
   <si>
-    <t>CNS_01</t>
-  </si>
-  <si>
     <t>Assets held for sale</t>
   </si>
   <si>
@@ -3246,19 +3243,22 @@
     <t>Implied Return</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
+  </si>
+  <si>
     <t>大家乐集团</t>
   </si>
   <si>
     <t>0341.HK</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
+    <t>CNS_01</t>
   </si>
 </sst>
 </file>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5032,14 +5032,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="433" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F3" s="434">
         <v>45930</v>
@@ -5339,13 +5339,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="426" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C4" s="425" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E4" s="435" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F4" s="436" t="s">
         <v>324</v>
@@ -5356,13 +5356,13 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F5" s="437" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5370,7 +5370,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>404</v>
+        <v>555</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3758.4261338400001</v>
+        <v>3781.6262951599997</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.12260045445698151</v>
+        <v>0.12017169390553457</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5443,7 +5443,7 @@
         <v>319</v>
       </c>
       <c r="C15" s="422" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>353</v>
@@ -5458,7 +5458,7 @@
         <v>320</v>
       </c>
       <c r="C16" s="422" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C17" s="420">
         <v>0</v>
@@ -5519,7 +5519,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C21" s="257" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5541,7 +5541,7 @@
         <v>4.333028820025568</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E22" s="79">
         <v>0.29465259038036606</v>
@@ -5556,7 +5556,7 @@
         <v>5.3553121183397749</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E23" s="448">
         <v>0.20075184365903009</v>
@@ -5571,7 +5571,7 @@
         <v>6.5660659780940076</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E24" s="448">
         <v>0.1174</v>
@@ -5586,7 +5586,7 @@
         <v>7.3792932677079612</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E25" s="449">
         <v>7.2499999999999995E-2</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0876354405804044E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5968,7 +5968,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5981,18 +5981,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
-        <v>482</v>
-      </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="B73" s="456" t="s">
+        <v>481</v>
+      </c>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6068,7 +6068,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6156,7 +6156,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
-        <v>489</v>
-      </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="B96" s="456" t="s">
+        <v>488</v>
+      </c>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
-        <v>488</v>
-      </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="B97" s="458" t="s">
+        <v>487</v>
+      </c>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
-        <v>487</v>
-      </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="B98" s="458" t="s">
+        <v>486</v>
+      </c>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6255,31 +6255,31 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
@@ -6304,17 +6304,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
-        <v>495</v>
-      </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="B114" s="456" t="s">
+        <v>494</v>
+      </c>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6331,127 +6331,127 @@
         <v>124</v>
       </c>
       <c r="F117" s="346" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
-        <f>DCF!B82&amp;" ("&amp;DCF!D82&amp;"yrs)"</f>
+        <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (15yrs)</v>
       </c>
       <c r="C118" s="206">
-        <f>DCF!C82</f>
+        <f>DCF!C90</f>
         <v>0.05</v>
       </c>
       <c r="D118" s="207" t="str">
-        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
         <v>9.36 HKD</v>
       </c>
       <c r="E118" s="208">
-        <f>DCF!F82</f>
+        <f>DCF!F90</f>
         <v>0.05</v>
       </c>
       <c r="F118" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E82,C$18)</f>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
         <v>-1.3162728985041415E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
-        <f>DCF!B83&amp;" ("&amp;DCF!D83&amp;"yrs)"</f>
+        <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (15yrs)</v>
       </c>
       <c r="C119" s="198">
-        <f>DCF!C83</f>
+        <f>DCF!C91</f>
         <v>0.04</v>
       </c>
       <c r="D119" s="207" t="str">
-        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
         <v>8.56 HKD</v>
       </c>
       <c r="E119" s="199">
-        <f>DCF!F83</f>
+        <f>DCF!F91</f>
         <v>0.18</v>
       </c>
       <c r="F119" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E83,C$18)</f>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
         <v>1.8223005300290952E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
-        <f>DCF!B84&amp;" ("&amp;DCF!D84&amp;"yrs)"</f>
+        <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (15yrs)</v>
       </c>
       <c r="C120" s="198">
-        <f>DCF!C84</f>
+        <f>DCF!C92</f>
         <v>0.03</v>
       </c>
       <c r="D120" s="207" t="str">
-        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
         <v>7.8 HKD</v>
       </c>
       <c r="E120" s="199">
-        <f>DCF!F84</f>
+        <f>DCF!F92</f>
         <v>0.53999999999999992</v>
       </c>
       <c r="F120" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E84,C$18)</f>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
         <v>5.191889800512979E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
-        <f>DCF!B85&amp;" ("&amp;DCF!D85&amp;"yrs)"</f>
+        <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (15yrs)</v>
       </c>
       <c r="C121" s="198">
-        <f>DCF!C85</f>
+        <f>DCF!C93</f>
         <v>0.02</v>
       </c>
       <c r="D121" s="207" t="str">
-        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
         <v>7.08 HKD</v>
       </c>
       <c r="E121" s="199">
-        <f>DCF!F85</f>
+        <f>DCF!F93</f>
         <v>0.18</v>
       </c>
       <c r="F121" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E85,C$18)</f>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
         <v>8.8265281842590304E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
-        <f>DCF!B86&amp;" ("&amp;DCF!D86&amp;"yrs)"</f>
+        <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (15yrs)</v>
       </c>
       <c r="C122" s="198">
-        <f>DCF!C86</f>
+        <f>DCF!C94</f>
         <v>0.01</v>
       </c>
       <c r="D122" s="207" t="str">
-        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
         <v>6.4 HKD</v>
       </c>
       <c r="E122" s="199">
-        <f>DCF!F86</f>
+        <f>DCF!F94</f>
         <v>0.05</v>
       </c>
       <c r="F122" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E86,C$18)</f>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
         <v>0.12768233742292004</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6477,7 +6477,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6532,28 +6532,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="344" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C139" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E139" s="345" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="345" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6607,21 +6607,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="344" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C143" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E143" s="345" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="345" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6668,7 +6668,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
-        <v>442</v>
-      </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="B158" s="457" t="s">
+        <v>441</v>
+      </c>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7462,7 +7462,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9581,7 +9581,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -10774,7 +10774,7 @@
       <c r="E3" s="238"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11063,7 +11063,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C9" s="304">
         <f>C61</f>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="235" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
@@ -14225,24 +14225,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7962962962962951E-2</v>
+        <v>8.7423312883435578E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8641975308641972E-2</v>
+        <v>5.8282208588957059E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8641975308641972E-2</v>
+        <v>5.8282208588957059E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15424,50 +15424,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0876354405804044E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6894061468748928E-2</v>
+        <v>7.6422318760351701E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.2374682495032098E-2</v>
+        <v>9.18079666515043E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8978627604879462E-2</v>
+        <v>2.8800844613438487E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3526905438795467E-3</v>
+        <v>-6.3137169822606544E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1621480845380752E-2</v>
+        <v>-3.1427484030378421E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5505680455360765E-2</v>
+        <v>5.5165154808395366E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1484118564890082</v>
+        <v>0.1475013543019591</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12241826328775386</v>
+        <v>0.12166723099764495</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13765229954683589</v>
+        <v>0.13680780691157923</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13420777262546388</v>
+        <v>0.13338441205720952</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15481,43 +15481,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2555705933160399E-2</v>
+        <v>6.2171928596147154E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8658121281088687E-2</v>
+        <v>8.8114206426603489E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9583393697403801E-2</v>
+        <v>2.9401900484536298E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0796724975552621E-3</v>
+        <v>6.0423738932757817E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5931112428601736E-2</v>
+        <v>9.534257799652443E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.979179511611141E-2</v>
+        <v>1.9670373060184349E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15754200798807202</v>
+        <v>0.15657549260164216</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1222040778890435</v>
+        <v>0.12145435961978557</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13405877408723058</v>
+        <v>0.13323632762043777</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13778639823124586</v>
+        <v>0.1369410829046738</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16226,7 +16226,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U110"/>
+  <dimension ref="A2:U118"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -16260,10 +16260,10 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="2:15">
@@ -16279,7 +16279,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F4" s="279">
         <f>-BS!G31</f>
@@ -16307,7 +16307,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
@@ -16339,7 +16339,7 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F6" s="288">
         <f>BS!H42</f>
@@ -16350,7 +16350,7 @@
         <v>HKD</v>
       </c>
       <c r="H6" s="312" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
@@ -16361,14 +16361,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="322" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C7" s="279">
         <f>F7</f>
         <v>-1686446.6667440513</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
@@ -16379,7 +16379,7 @@
         <v>HKD</v>
       </c>
       <c r="H7" s="316" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I7" s="317">
         <f>Normalized_FCF!C9</f>
@@ -16391,7 +16391,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
@@ -16402,7 +16402,7 @@
         <v>HKD</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16452,7 +16452,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
@@ -16474,7 +16474,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16490,7 +16490,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16508,7 +16508,7 @@
         <v>400</v>
       </c>
       <c r="C14" s="313" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E14" s="106" t="s">
         <v>400</v>
@@ -16518,12 +16518,12 @@
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16538,7 +16538,7 @@
         <v>8</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16548,7 +16548,7 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
@@ -16578,19 +16578,19 @@
         <v>0.86799999999999999</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="312" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C18" s="310">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="312" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16631,23 +16631,23 @@
         <v>396</v>
       </c>
       <c r="G20" s="121" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>421</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>533</v>
+      </c>
+      <c r="K20" s="121" t="s">
+        <v>534</v>
+      </c>
+      <c r="L20" s="122" t="s">
         <v>422</v>
-      </c>
-      <c r="J20" s="121" t="s">
-        <v>534</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>535</v>
-      </c>
-      <c r="L20" s="122" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18202,7 +18202,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="319" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B51" s="320">
         <f>C15+1</f>
@@ -18254,7 +18254,7 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="464" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K52" s="464"/>
       <c r="L52" s="321">
@@ -18286,23 +18286,23 @@
         <v>6216243.1228741389</v>
       </c>
       <c r="B55" s="123">
-        <f>C86</f>
+        <f>C94</f>
         <v>0.01</v>
       </c>
       <c r="C55" s="123">
-        <f>C85</f>
+        <f>C93</f>
         <v>0.02</v>
       </c>
       <c r="D55" s="123">
-        <f>C84</f>
+        <f>C92</f>
         <v>0.03</v>
       </c>
       <c r="E55" s="123">
-        <f>C83</f>
+        <f>C91</f>
         <v>0.04</v>
       </c>
       <c r="F55" s="123">
-        <f>C82</f>
+        <f>C90</f>
         <v>0.05</v>
       </c>
       <c r="G55" s="123"/>
@@ -18314,23 +18314,23 @@
     </row>
     <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B56" s="118">
-        <f t="dataTable" ref="B56:F65" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>5497056.4488840643</v>
+        <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
+        <v>5322146.0032817367</v>
       </c>
       <c r="C56" s="118">
-        <v>5621694.4424392562</v>
+        <v>5322146.0032817367</v>
       </c>
       <c r="D56" s="118">
-        <v>5747533.213652215</v>
+        <v>5322146.0032817367</v>
       </c>
       <c r="E56" s="118">
-        <v>5874572.7625229498</v>
+        <v>5322146.0032817367</v>
       </c>
       <c r="F56" s="118">
-        <v>6002813.0890514571</v>
+        <v>5322146.0032817367</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18341,22 +18341,22 @@
     </row>
     <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>5592462.1429429594</v>
+        <v>5441083.9420132637</v>
       </c>
       <c r="C57" s="118">
-        <v>5718998.710745181</v>
+        <v>5441083.9420132637</v>
       </c>
       <c r="D57" s="118">
-        <v>5846754.7613701653</v>
+        <v>5441083.9420132637</v>
       </c>
       <c r="E57" s="118">
-        <v>5975730.2948179226</v>
+        <v>5441083.9420132637</v>
       </c>
       <c r="F57" s="118">
-        <v>6105925.3110884447</v>
+        <v>5441083.9420132637</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18367,22 +18367,22 @@
     </row>
     <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>5492418.8643652732</v>
+        <v>5490862.7347770724</v>
       </c>
       <c r="C58" s="118">
-        <v>5676113.7507732855</v>
+        <v>5554199.7438838035</v>
       </c>
       <c r="D58" s="118">
-        <v>5863339.45178595</v>
+        <v>5617536.7529905308</v>
       </c>
       <c r="E58" s="118">
-        <v>6054130.0788109051</v>
+        <v>5680873.7620972618</v>
       </c>
       <c r="F58" s="118">
-        <v>6248519.7432557773</v>
+        <v>5744210.7712039873</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18393,22 +18393,22 @@
     </row>
     <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>5577866.7339330092</v>
+        <v>5597386.7067017779</v>
       </c>
       <c r="C59" s="118">
-        <v>5764124.8880702872</v>
+        <v>5661778.4085998451</v>
       </c>
       <c r="D59" s="118">
-        <v>5953964.6129467599</v>
+        <v>5726170.1104979031</v>
       </c>
       <c r="E59" s="118">
-        <v>6147420.5175792277</v>
+        <v>5790561.8123959685</v>
       </c>
       <c r="F59" s="118">
-        <v>6344527.2109844796</v>
+        <v>5854953.5142940283</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18419,22 +18419,22 @@
     </row>
     <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>5478674.0036659241</v>
+        <v>5497056.4488840643</v>
       </c>
       <c r="C60" s="118">
-        <v>5719030.9543831721</v>
+        <v>5621694.4424392562</v>
       </c>
       <c r="D60" s="118">
-        <v>5966300.8943257071</v>
+        <v>5747533.213652215</v>
       </c>
       <c r="E60" s="118">
-        <v>6220617.567549143</v>
+        <v>5874572.7625229498</v>
       </c>
       <c r="F60" s="118">
-        <v>6482116.0088882605</v>
+        <v>6002813.0890514571</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18445,22 +18445,22 @@
     </row>
     <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>5555203.3815577477</v>
+        <v>5592462.1429429594</v>
       </c>
       <c r="C61" s="118">
-        <v>5798636.5094443168</v>
+        <v>5718998.710745181</v>
       </c>
       <c r="D61" s="118">
-        <v>6049074.4452762417</v>
+        <v>5846754.7613701653</v>
       </c>
       <c r="E61" s="118">
-        <v>6306652.7422725484</v>
+        <v>5975730.2948179226</v>
       </c>
       <c r="F61" s="118">
-        <v>6571508.2620817916</v>
+        <v>6105925.3110884447</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18471,22 +18471,22 @@
     </row>
     <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>5396961.8185033593</v>
-      </c>
-      <c r="C62" s="281">
-        <v>5792108.8893085411</v>
+        <v>5492418.8643652732</v>
+      </c>
+      <c r="C62" s="118">
+        <v>5676113.7507732855</v>
       </c>
       <c r="D62" s="118">
-        <v>6209816.4225565288</v>
+        <v>5863339.45178595</v>
       </c>
       <c r="E62" s="118">
-        <v>6651179.8059659954</v>
+        <v>6054130.0788109051</v>
       </c>
       <c r="F62" s="118">
-        <v>7117337.0643130448</v>
+        <v>6248519.7432557773</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18494,34 +18494,25 @@
       <c r="J62" s="299"/>
       <c r="K62" s="299"/>
       <c r="L62" s="299"/>
-      <c r="M62" s="279"/>
-      <c r="N62" s="279"/>
-      <c r="O62" s="279"/>
-      <c r="P62" s="279"/>
-      <c r="Q62" s="279"/>
-      <c r="R62" s="279"/>
-      <c r="S62" s="279"/>
-      <c r="T62" s="279"/>
-      <c r="U62" s="279"/>
     </row>
     <row r="63" spans="1:21" ht="13.15">
-      <c r="A63" s="132">
-        <v>20</v>
+      <c r="A63" s="131">
+        <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>5364061.1430426184</v>
-      </c>
-      <c r="C63" s="281">
-        <v>5853599.8591909334</v>
+        <v>5577866.7339330092</v>
+      </c>
+      <c r="C63" s="118">
+        <v>5764124.8880702872</v>
       </c>
       <c r="D63" s="118">
-        <v>6380231.8284840696</v>
+        <v>5953964.6129467599</v>
       </c>
       <c r="E63" s="118">
-        <v>6946485.60456766</v>
+        <v>6147420.5175792277</v>
       </c>
       <c r="F63" s="118">
-        <v>7555038.2205814561</v>
+        <v>6344527.2109844796</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18529,34 +18520,25 @@
       <c r="J63" s="299"/>
       <c r="K63" s="299"/>
       <c r="L63" s="299"/>
-      <c r="M63" s="279"/>
-      <c r="N63" s="279"/>
-      <c r="O63" s="279"/>
-      <c r="P63" s="279"/>
-      <c r="Q63" s="279"/>
-      <c r="R63" s="279"/>
-      <c r="S63" s="279"/>
-      <c r="T63" s="279"/>
-      <c r="U63" s="279"/>
     </row>
     <row r="64" spans="1:21" ht="13.15">
-      <c r="A64" s="132">
-        <v>25</v>
+      <c r="A64" s="131">
+        <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>5187075.0610776981</v>
-      </c>
-      <c r="C64" s="281">
-        <v>5789247.4213424828</v>
+        <v>5478674.0036659241</v>
+      </c>
+      <c r="C64" s="118">
+        <v>5719030.9543831721</v>
       </c>
       <c r="D64" s="118">
-        <v>6453576.1043743286</v>
+        <v>5966300.8943257071</v>
       </c>
       <c r="E64" s="118">
-        <v>7186133.2801278103</v>
+        <v>6220617.567549143</v>
       </c>
       <c r="F64" s="118">
-        <v>7993530.2762442231</v>
+        <v>6482116.0088882605</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18564,34 +18546,25 @@
       <c r="J64" s="299"/>
       <c r="K64" s="299"/>
       <c r="L64" s="299"/>
-      <c r="M64" s="279"/>
-      <c r="N64" s="279"/>
-      <c r="O64" s="279"/>
-      <c r="P64" s="279"/>
-      <c r="Q64" s="279"/>
-      <c r="R64" s="279"/>
-      <c r="S64" s="279"/>
-      <c r="T64" s="279"/>
-      <c r="U64" s="279"/>
     </row>
     <row r="65" spans="1:21" ht="13.15">
-      <c r="A65" s="132">
-        <v>30</v>
+      <c r="A65" s="131">
+        <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>5118927.8479986088</v>
-      </c>
-      <c r="C65" s="281">
-        <v>5790972.7175897965</v>
+        <v>5555203.3815577477</v>
+      </c>
+      <c r="C65" s="118">
+        <v>5798636.5094443168</v>
       </c>
       <c r="D65" s="118">
-        <v>6544533.1775393505</v>
+        <v>6049074.4452762417</v>
       </c>
       <c r="E65" s="118">
-        <v>7389189.0565219279</v>
+        <v>6306652.7422725484</v>
       </c>
       <c r="F65" s="118">
-        <v>8335565.6915554032</v>
+        <v>6571508.2620817916</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18599,27 +18572,32 @@
       <c r="J65" s="299"/>
       <c r="K65" s="299"/>
       <c r="L65" s="299"/>
-      <c r="M65" s="279"/>
-      <c r="N65" s="279"/>
-      <c r="O65" s="279"/>
-      <c r="P65" s="279"/>
-      <c r="Q65" s="279"/>
-      <c r="R65" s="279"/>
-      <c r="S65" s="279"/>
-      <c r="T65" s="279"/>
-      <c r="U65" s="279"/>
-    </row>
-    <row r="66" spans="1:21">
-      <c r="C66" s="279"/>
-      <c r="D66" s="111"/>
-      <c r="E66" s="111"/>
-      <c r="F66" s="111"/>
-      <c r="G66" s="111"/>
-      <c r="H66" s="111"/>
-      <c r="I66" s="111"/>
-      <c r="J66" s="111"/>
-      <c r="K66" s="111"/>
-      <c r="L66" s="111"/>
+    </row>
+    <row r="66" spans="1:21" ht="13.15">
+      <c r="A66" s="131">
+        <v>15</v>
+      </c>
+      <c r="B66" s="118">
+        <v>5396961.8185033593</v>
+      </c>
+      <c r="C66" s="281">
+        <v>5792108.8893085411</v>
+      </c>
+      <c r="D66" s="118">
+        <v>6209816.4225565288</v>
+      </c>
+      <c r="E66" s="118">
+        <v>6651179.8059659954</v>
+      </c>
+      <c r="F66" s="118">
+        <v>7117337.0643130448</v>
+      </c>
+      <c r="G66" s="299"/>
+      <c r="H66" s="299"/>
+      <c r="I66" s="299"/>
+      <c r="J66" s="299"/>
+      <c r="K66" s="299"/>
+      <c r="L66" s="299"/>
       <c r="M66" s="279"/>
       <c r="N66" s="279"/>
       <c r="O66" s="279"/>
@@ -18631,19 +18609,30 @@
       <c r="U66" s="279"/>
     </row>
     <row r="67" spans="1:21" ht="13.15">
-      <c r="B67" s="115" t="s">
-        <v>109</v>
-      </c>
-      <c r="C67" s="279"/>
-      <c r="D67" s="111"/>
-      <c r="E67" s="111"/>
-      <c r="F67" s="111"/>
-      <c r="G67" s="111"/>
-      <c r="H67" s="111"/>
-      <c r="I67" s="111"/>
-      <c r="J67" s="111"/>
-      <c r="K67" s="111"/>
-      <c r="L67" s="111"/>
+      <c r="A67" s="132">
+        <v>20</v>
+      </c>
+      <c r="B67" s="118">
+        <v>5364061.1430426184</v>
+      </c>
+      <c r="C67" s="281">
+        <v>5853599.8591909334</v>
+      </c>
+      <c r="D67" s="118">
+        <v>6380231.8284840696</v>
+      </c>
+      <c r="E67" s="118">
+        <v>6946485.60456766</v>
+      </c>
+      <c r="F67" s="118">
+        <v>7555038.2205814561</v>
+      </c>
+      <c r="G67" s="299"/>
+      <c r="H67" s="299"/>
+      <c r="I67" s="299"/>
+      <c r="J67" s="299"/>
+      <c r="K67" s="299"/>
+      <c r="L67" s="299"/>
       <c r="M67" s="279"/>
       <c r="N67" s="279"/>
       <c r="O67" s="279"/>
@@ -18655,182 +18644,171 @@
       <c r="U67" s="279"/>
     </row>
     <row r="68" spans="1:21" ht="13.15">
-      <c r="B68" s="124">
+      <c r="A68" s="132">
+        <v>25</v>
+      </c>
+      <c r="B68" s="118">
+        <v>5187075.0610776981</v>
+      </c>
+      <c r="C68" s="281">
+        <v>5789247.4213424828</v>
+      </c>
+      <c r="D68" s="118">
+        <v>6453576.1043743286</v>
+      </c>
+      <c r="E68" s="118">
+        <v>7186133.2801278103</v>
+      </c>
+      <c r="F68" s="118">
+        <v>7993530.2762442231</v>
+      </c>
+      <c r="G68" s="299"/>
+      <c r="H68" s="299"/>
+      <c r="I68" s="299"/>
+      <c r="J68" s="299"/>
+      <c r="K68" s="299"/>
+      <c r="L68" s="299"/>
+      <c r="M68" s="279"/>
+      <c r="N68" s="279"/>
+      <c r="O68" s="279"/>
+      <c r="P68" s="279"/>
+      <c r="Q68" s="279"/>
+      <c r="R68" s="279"/>
+      <c r="S68" s="279"/>
+      <c r="T68" s="279"/>
+      <c r="U68" s="279"/>
+    </row>
+    <row r="69" spans="1:21" ht="13.15">
+      <c r="A69" s="132">
+        <v>30</v>
+      </c>
+      <c r="B69" s="118">
+        <v>5118927.8479986088</v>
+      </c>
+      <c r="C69" s="281">
+        <v>5790972.7175897965</v>
+      </c>
+      <c r="D69" s="118">
+        <v>6544533.1775393505</v>
+      </c>
+      <c r="E69" s="118">
+        <v>7389189.0565219279</v>
+      </c>
+      <c r="F69" s="118">
+        <v>8335565.6915554032</v>
+      </c>
+      <c r="G69" s="299"/>
+      <c r="H69" s="299"/>
+      <c r="I69" s="299"/>
+      <c r="J69" s="299"/>
+      <c r="K69" s="299"/>
+      <c r="L69" s="299"/>
+      <c r="M69" s="279"/>
+      <c r="N69" s="279"/>
+      <c r="O69" s="279"/>
+      <c r="P69" s="279"/>
+      <c r="Q69" s="279"/>
+      <c r="R69" s="279"/>
+      <c r="S69" s="279"/>
+      <c r="T69" s="279"/>
+      <c r="U69" s="279"/>
+    </row>
+    <row r="70" spans="1:21">
+      <c r="C70" s="279"/>
+      <c r="D70" s="111"/>
+      <c r="E70" s="111"/>
+      <c r="F70" s="111"/>
+      <c r="G70" s="111"/>
+      <c r="H70" s="111"/>
+      <c r="I70" s="111"/>
+      <c r="J70" s="111"/>
+      <c r="K70" s="111"/>
+      <c r="L70" s="111"/>
+      <c r="M70" s="279"/>
+      <c r="N70" s="279"/>
+      <c r="O70" s="279"/>
+      <c r="P70" s="279"/>
+      <c r="Q70" s="279"/>
+      <c r="R70" s="279"/>
+      <c r="S70" s="279"/>
+      <c r="T70" s="279"/>
+      <c r="U70" s="279"/>
+    </row>
+    <row r="71" spans="1:21" ht="13.15">
+      <c r="B71" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" s="279"/>
+      <c r="D71" s="111"/>
+      <c r="E71" s="111"/>
+      <c r="F71" s="111"/>
+      <c r="G71" s="111"/>
+      <c r="H71" s="111"/>
+      <c r="I71" s="111"/>
+      <c r="J71" s="111"/>
+      <c r="K71" s="111"/>
+      <c r="L71" s="111"/>
+      <c r="M71" s="279"/>
+      <c r="N71" s="279"/>
+      <c r="O71" s="279"/>
+      <c r="P71" s="279"/>
+      <c r="Q71" s="279"/>
+      <c r="R71" s="279"/>
+      <c r="S71" s="279"/>
+      <c r="T71" s="279"/>
+      <c r="U71" s="279"/>
+    </row>
+    <row r="72" spans="1:21" ht="13.15">
+      <c r="B72" s="124">
         <f>B55</f>
         <v>0.01</v>
       </c>
-      <c r="C68" s="124">
+      <c r="C72" s="124">
         <f>C55</f>
         <v>0.02</v>
       </c>
-      <c r="D68" s="124">
+      <c r="D72" s="124">
         <f>D55</f>
         <v>0.03</v>
       </c>
-      <c r="E68" s="124">
+      <c r="E72" s="124">
         <f>E55</f>
         <v>0.04</v>
       </c>
-      <c r="F68" s="124">
+      <c r="F72" s="124">
         <f>F55</f>
         <v>0.05</v>
       </c>
-      <c r="G68" s="124"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="124"/>
-      <c r="K68" s="124"/>
-      <c r="L68" s="124"/>
-    </row>
-    <row r="69" spans="1:21" ht="13.15">
-      <c r="A69" s="131">
-        <v>0</v>
-      </c>
-      <c r="B69" s="119">
+      <c r="G72" s="124"/>
+      <c r="H72" s="124"/>
+      <c r="I72" s="124"/>
+      <c r="J72" s="124"/>
+      <c r="K72" s="124"/>
+      <c r="L72" s="124"/>
+    </row>
+    <row r="73" spans="1:21" ht="13.15">
+      <c r="A73" s="131">
+        <v>0</v>
+      </c>
+      <c r="B73" s="119">
         <f>C11</f>
         <v>2.5670270786220946</v>
       </c>
-      <c r="C69" s="119">
+      <c r="C73" s="119">
         <f>C11</f>
         <v>2.5670270786220946</v>
       </c>
-      <c r="D69" s="119">
+      <c r="D73" s="119">
         <f>C11</f>
         <v>2.5670270786220946</v>
       </c>
-      <c r="E69" s="119">
+      <c r="E73" s="119">
         <f>C11</f>
         <v>2.5670270786220946</v>
       </c>
-      <c r="F69" s="119">
+      <c r="F73" s="119">
         <f>C11</f>
         <v>2.5670270786220946</v>
-      </c>
-      <c r="G69" s="300"/>
-      <c r="H69" s="300"/>
-      <c r="I69" s="300"/>
-      <c r="J69" s="300"/>
-      <c r="K69" s="300"/>
-      <c r="L69" s="300"/>
-    </row>
-    <row r="70" spans="1:21" ht="13.15">
-      <c r="A70" s="131">
-        <f>A56</f>
-        <v>5</v>
-      </c>
-      <c r="B70" s="119">
-        <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>6.5699711818038571</v>
-      </c>
-      <c r="C70" s="119">
-        <f t="shared" si="11"/>
-        <v>6.7848627799027819</v>
-      </c>
-      <c r="D70" s="119">
-        <f t="shared" si="11"/>
-        <v>7.0018246699125335</v>
-      </c>
-      <c r="E70" s="119">
-        <f t="shared" si="11"/>
-        <v>7.2208568518331298</v>
-      </c>
-      <c r="F70" s="119">
-        <f t="shared" si="11"/>
-        <v>7.4419593256645609</v>
-      </c>
-      <c r="G70" s="300"/>
-      <c r="H70" s="300"/>
-      <c r="I70" s="300"/>
-      <c r="J70" s="300"/>
-      <c r="K70" s="300"/>
-      <c r="L70" s="300"/>
-    </row>
-    <row r="71" spans="1:21" ht="13.15">
-      <c r="A71" s="131">
-        <v>6</v>
-      </c>
-      <c r="B71" s="119">
-        <f t="shared" si="11"/>
-        <v>6.7344626139848032</v>
-      </c>
-      <c r="C71" s="119">
-        <f t="shared" si="11"/>
-        <v>6.952627593196631</v>
-      </c>
-      <c r="D71" s="119">
-        <f t="shared" si="11"/>
-        <v>7.1728951143795134</v>
-      </c>
-      <c r="E71" s="119">
-        <f t="shared" si="11"/>
-        <v>7.3952651775334663</v>
-      </c>
-      <c r="F71" s="119">
-        <f t="shared" si="11"/>
-        <v>7.6197377826584747</v>
-      </c>
-      <c r="G71" s="300"/>
-      <c r="H71" s="300"/>
-      <c r="I71" s="300"/>
-      <c r="J71" s="300"/>
-      <c r="K71" s="300"/>
-      <c r="L71" s="300"/>
-    </row>
-    <row r="72" spans="1:21" ht="13.15">
-      <c r="A72" s="131">
-        <f t="shared" ref="A72" si="12">A58</f>
-        <v>7</v>
-      </c>
-      <c r="B72" s="119">
-        <f t="shared" si="11"/>
-        <v>6.5619754020248715</v>
-      </c>
-      <c r="C72" s="119">
-        <f t="shared" si="11"/>
-        <v>6.8786885211697033</v>
-      </c>
-      <c r="D72" s="119">
-        <f t="shared" si="11"/>
-        <v>7.2014892093722702</v>
-      </c>
-      <c r="E72" s="119">
-        <f t="shared" si="11"/>
-        <v>7.5304362789954142</v>
-      </c>
-      <c r="F72" s="119">
-        <f t="shared" si="11"/>
-        <v>7.865588542401956</v>
-      </c>
-      <c r="G72" s="300"/>
-      <c r="H72" s="300"/>
-      <c r="I72" s="300"/>
-      <c r="J72" s="300"/>
-      <c r="K72" s="300"/>
-      <c r="L72" s="300"/>
-    </row>
-    <row r="73" spans="1:21" ht="13.15">
-      <c r="A73" s="131">
-        <v>8</v>
-      </c>
-      <c r="B73" s="119">
-        <f t="shared" si="11"/>
-        <v>6.7092982906706062</v>
-      </c>
-      <c r="C73" s="119">
-        <f t="shared" si="11"/>
-        <v>7.0304308062048184</v>
-      </c>
-      <c r="D73" s="119">
-        <f t="shared" si="11"/>
-        <v>7.3577384007650659</v>
-      </c>
-      <c r="E73" s="119">
-        <f t="shared" si="11"/>
-        <v>7.6912807446550575</v>
-      </c>
-      <c r="F73" s="119">
-        <f t="shared" si="11"/>
-        <v>8.0311175081784789</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18841,28 +18819,27 @@
     </row>
     <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
-        <f t="shared" ref="A74" si="13">A60</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B74" s="119">
-        <f t="shared" si="11"/>
-        <v>6.5382775311182586</v>
+        <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
+        <v>6.2684035449417044</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.9526831852893691</v>
+        <v>6.2684035449417044</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.3790077035234258</v>
+        <v>6.2684035449417044</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8174816774163567</v>
+        <v>6.2684035449417044</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>8.2683379240299324</v>
+        <v>6.2684035449417044</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18873,28 +18850,27 @@
     </row>
     <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
-        <f t="shared" ref="A75:A79" si="14">A61</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B75" s="119">
-        <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>6.6702238168983499</v>
+        <f t="shared" si="11"/>
+        <v>6.4734675306459675</v>
       </c>
       <c r="C75" s="119">
-        <f t="shared" si="15"/>
-        <v>7.0899331879305496</v>
+        <f t="shared" si="11"/>
+        <v>6.4734675306459675</v>
       </c>
       <c r="D75" s="119">
-        <f t="shared" si="15"/>
-        <v>7.5217197300629639</v>
+        <f t="shared" si="11"/>
+        <v>6.4734675306459675</v>
       </c>
       <c r="E75" s="119">
-        <f t="shared" si="15"/>
-        <v>7.9658171541170937</v>
+        <f t="shared" si="11"/>
+        <v>6.4734675306459675</v>
       </c>
       <c r="F75" s="119">
-        <f t="shared" si="15"/>
-        <v>8.4224614268117346</v>
+        <f t="shared" si="11"/>
+        <v>6.4734675306459675</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18905,28 +18881,27 @@
     </row>
     <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
-        <f t="shared" si="14"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B76" s="119">
-        <f t="shared" si="15"/>
-        <v>6.3973954328681506</v>
+        <f t="shared" si="11"/>
+        <v>6.5592924386320961</v>
       </c>
       <c r="C76" s="119">
-        <f t="shared" si="15"/>
-        <v>7.0786787487122345</v>
+        <f t="shared" si="11"/>
+        <v>6.6684934191479179</v>
       </c>
       <c r="D76" s="119">
-        <f t="shared" si="15"/>
-        <v>7.7988591431268164</v>
+        <f t="shared" si="11"/>
+        <v>6.7776943996637335</v>
       </c>
       <c r="E76" s="119">
-        <f t="shared" si="15"/>
-        <v>8.5598252024946575</v>
+        <f t="shared" si="11"/>
+        <v>6.8868953801795554</v>
       </c>
       <c r="F76" s="119">
-        <f t="shared" si="15"/>
-        <v>9.3635390248553545</v>
+        <f t="shared" si="11"/>
+        <v>6.9960963606953674</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18936,29 +18911,28 @@
       <c r="L76" s="300"/>
     </row>
     <row r="77" spans="1:21" ht="13.15">
-      <c r="A77" s="132">
-        <f t="shared" si="14"/>
-        <v>20</v>
+      <c r="A77" s="131">
+        <v>4</v>
       </c>
       <c r="B77" s="119">
-        <f t="shared" si="15"/>
-        <v>6.3406705247833459</v>
+        <f t="shared" si="11"/>
+        <v>6.7429531821164534</v>
       </c>
       <c r="C77" s="119">
-        <f t="shared" si="15"/>
-        <v>7.1846969251106598</v>
+        <f t="shared" si="11"/>
+        <v>6.8539725858350948</v>
       </c>
       <c r="D77" s="119">
-        <f t="shared" si="15"/>
-        <v>8.0926767654734881</v>
+        <f t="shared" si="11"/>
+        <v>6.9649919895537202</v>
       </c>
       <c r="E77" s="119">
-        <f t="shared" si="15"/>
-        <v>9.0689695908090489</v>
+        <f t="shared" si="11"/>
+        <v>7.0760113932723581</v>
       </c>
       <c r="F77" s="119">
-        <f t="shared" si="15"/>
-        <v>10.118190943402293</v>
+        <f t="shared" si="11"/>
+        <v>7.187030796990987</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18968,29 +18942,28 @@
       <c r="L77" s="300"/>
     </row>
     <row r="78" spans="1:21" ht="13.15">
-      <c r="A78" s="132">
-        <f t="shared" si="14"/>
-        <v>25</v>
+      <c r="A78" s="131">
+        <v>5</v>
       </c>
       <c r="B78" s="119">
-        <f t="shared" si="15"/>
-        <v>6.03552422942143</v>
+        <f t="shared" si="11"/>
+        <v>6.5699711818038571</v>
       </c>
       <c r="C78" s="119">
-        <f t="shared" si="15"/>
-        <v>7.0737452175585664</v>
+        <f t="shared" si="11"/>
+        <v>6.7848627799027819</v>
       </c>
       <c r="D78" s="119">
-        <f t="shared" si="15"/>
-        <v>8.2191315342634468</v>
+        <f t="shared" si="11"/>
+        <v>7.0018246699125335</v>
       </c>
       <c r="E78" s="119">
-        <f t="shared" si="15"/>
-        <v>9.4821523652815003</v>
+        <f t="shared" si="11"/>
+        <v>7.2208568518331298</v>
       </c>
       <c r="F78" s="119">
-        <f t="shared" si="15"/>
-        <v>10.874206472112879</v>
+        <f t="shared" si="11"/>
+        <v>7.4419593256645609</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19000,29 +18973,28 @@
       <c r="L78" s="300"/>
     </row>
     <row r="79" spans="1:21" ht="13.15">
-      <c r="A79" s="132">
-        <f t="shared" si="14"/>
-        <v>30</v>
+      <c r="A79" s="131">
+        <v>6</v>
       </c>
       <c r="B79" s="119">
-        <f t="shared" si="15"/>
-        <v>5.918029851448563</v>
+        <f t="shared" si="11"/>
+        <v>6.7344626139848032</v>
       </c>
       <c r="C79" s="119">
-        <f t="shared" si="15"/>
-        <v>7.0767198455769105</v>
+        <f t="shared" si="11"/>
+        <v>6.952627593196631</v>
       </c>
       <c r="D79" s="119">
-        <f t="shared" si="15"/>
-        <v>8.3759529837533027</v>
+        <f t="shared" si="11"/>
+        <v>7.1728951143795134</v>
       </c>
       <c r="E79" s="119">
-        <f t="shared" si="15"/>
-        <v>9.8322460971195973</v>
+        <f t="shared" si="11"/>
+        <v>7.3952651775334663</v>
       </c>
       <c r="F79" s="119">
-        <f t="shared" si="15"/>
-        <v>11.463918604875204</v>
+        <f t="shared" si="11"/>
+        <v>7.6197377826584747</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19031,269 +19003,524 @@
       <c r="K79" s="300"/>
       <c r="L79" s="300"/>
     </row>
-    <row r="81" spans="2:12" ht="13.15">
-      <c r="B81" s="153" t="s">
+    <row r="80" spans="1:21" ht="13.15">
+      <c r="A80" s="131">
+        <f t="shared" ref="A80" si="12">A62</f>
+        <v>7</v>
+      </c>
+      <c r="B80" s="119">
+        <f t="shared" si="11"/>
+        <v>6.5619754020248715</v>
+      </c>
+      <c r="C80" s="119">
+        <f t="shared" si="11"/>
+        <v>6.8786885211697033</v>
+      </c>
+      <c r="D80" s="119">
+        <f t="shared" si="11"/>
+        <v>7.2014892093722702</v>
+      </c>
+      <c r="E80" s="119">
+        <f t="shared" si="11"/>
+        <v>7.5304362789954142</v>
+      </c>
+      <c r="F80" s="119">
+        <f t="shared" si="11"/>
+        <v>7.865588542401956</v>
+      </c>
+      <c r="G80" s="300"/>
+      <c r="H80" s="300"/>
+      <c r="I80" s="300"/>
+      <c r="J80" s="300"/>
+      <c r="K80" s="300"/>
+      <c r="L80" s="300"/>
+    </row>
+    <row r="81" spans="1:12" ht="13.15">
+      <c r="A81" s="131">
+        <v>8</v>
+      </c>
+      <c r="B81" s="119">
+        <f t="shared" si="11"/>
+        <v>6.7092982906706062</v>
+      </c>
+      <c r="C81" s="119">
+        <f t="shared" si="11"/>
+        <v>7.0304308062048184</v>
+      </c>
+      <c r="D81" s="119">
+        <f t="shared" si="11"/>
+        <v>7.3577384007650659</v>
+      </c>
+      <c r="E81" s="119">
+        <f t="shared" si="11"/>
+        <v>7.6912807446550575</v>
+      </c>
+      <c r="F81" s="119">
+        <f t="shared" si="11"/>
+        <v>8.0311175081784789</v>
+      </c>
+      <c r="G81" s="300"/>
+      <c r="H81" s="300"/>
+      <c r="I81" s="300"/>
+      <c r="J81" s="300"/>
+      <c r="K81" s="300"/>
+      <c r="L81" s="300"/>
+    </row>
+    <row r="82" spans="1:12" ht="13.15">
+      <c r="A82" s="131">
+        <f t="shared" ref="A82" si="13">A64</f>
+        <v>9</v>
+      </c>
+      <c r="B82" s="119">
+        <f t="shared" si="11"/>
+        <v>6.5382775311182586</v>
+      </c>
+      <c r="C82" s="119">
+        <f t="shared" si="11"/>
+        <v>6.9526831852893691</v>
+      </c>
+      <c r="D82" s="119">
+        <f t="shared" si="11"/>
+        <v>7.3790077035234258</v>
+      </c>
+      <c r="E82" s="119">
+        <f t="shared" si="11"/>
+        <v>7.8174816774163567</v>
+      </c>
+      <c r="F82" s="119">
+        <f t="shared" si="11"/>
+        <v>8.2683379240299324</v>
+      </c>
+      <c r="G82" s="300"/>
+      <c r="H82" s="300"/>
+      <c r="I82" s="300"/>
+      <c r="J82" s="300"/>
+      <c r="K82" s="300"/>
+      <c r="L82" s="300"/>
+    </row>
+    <row r="83" spans="1:12" ht="13.15">
+      <c r="A83" s="131">
+        <f t="shared" ref="A83:A87" si="14">A65</f>
+        <v>10</v>
+      </c>
+      <c r="B83" s="119">
+        <f t="shared" si="11"/>
+        <v>6.6702238168983499</v>
+      </c>
+      <c r="C83" s="119">
+        <f t="shared" si="11"/>
+        <v>7.0899331879305496</v>
+      </c>
+      <c r="D83" s="119">
+        <f t="shared" si="11"/>
+        <v>7.5217197300629639</v>
+      </c>
+      <c r="E83" s="119">
+        <f t="shared" si="11"/>
+        <v>7.9658171541170937</v>
+      </c>
+      <c r="F83" s="119">
+        <f t="shared" si="11"/>
+        <v>8.4224614268117346</v>
+      </c>
+      <c r="G83" s="300"/>
+      <c r="H83" s="300"/>
+      <c r="I83" s="300"/>
+      <c r="J83" s="300"/>
+      <c r="K83" s="300"/>
+      <c r="L83" s="300"/>
+    </row>
+    <row r="84" spans="1:12" ht="13.15">
+      <c r="A84" s="131">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="B84" s="119">
+        <f t="shared" si="11"/>
+        <v>6.3973954328681506</v>
+      </c>
+      <c r="C84" s="119">
+        <f t="shared" si="11"/>
+        <v>7.0786787487122345</v>
+      </c>
+      <c r="D84" s="119">
+        <f t="shared" si="11"/>
+        <v>7.7988591431268164</v>
+      </c>
+      <c r="E84" s="119">
+        <f t="shared" si="11"/>
+        <v>8.5598252024946575</v>
+      </c>
+      <c r="F84" s="119">
+        <f t="shared" si="11"/>
+        <v>9.3635390248553545</v>
+      </c>
+      <c r="G84" s="300"/>
+      <c r="H84" s="300"/>
+      <c r="I84" s="300"/>
+      <c r="J84" s="300"/>
+      <c r="K84" s="300"/>
+      <c r="L84" s="300"/>
+    </row>
+    <row r="85" spans="1:12" ht="13.15">
+      <c r="A85" s="132">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="B85" s="119">
+        <f t="shared" si="11"/>
+        <v>6.3406705247833459</v>
+      </c>
+      <c r="C85" s="119">
+        <f t="shared" si="11"/>
+        <v>7.1846969251106598</v>
+      </c>
+      <c r="D85" s="119">
+        <f t="shared" si="11"/>
+        <v>8.0926767654734881</v>
+      </c>
+      <c r="E85" s="119">
+        <f t="shared" si="11"/>
+        <v>9.0689695908090489</v>
+      </c>
+      <c r="F85" s="119">
+        <f t="shared" si="11"/>
+        <v>10.118190943402293</v>
+      </c>
+      <c r="G85" s="300"/>
+      <c r="H85" s="300"/>
+      <c r="I85" s="300"/>
+      <c r="J85" s="300"/>
+      <c r="K85" s="300"/>
+      <c r="L85" s="300"/>
+    </row>
+    <row r="86" spans="1:12" ht="13.15">
+      <c r="A86" s="132">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+      <c r="B86" s="119">
+        <f t="shared" si="11"/>
+        <v>6.03552422942143</v>
+      </c>
+      <c r="C86" s="119">
+        <f t="shared" si="11"/>
+        <v>7.0737452175585664</v>
+      </c>
+      <c r="D86" s="119">
+        <f t="shared" si="11"/>
+        <v>8.2191315342634468</v>
+      </c>
+      <c r="E86" s="119">
+        <f t="shared" si="11"/>
+        <v>9.4821523652815003</v>
+      </c>
+      <c r="F86" s="119">
+        <f t="shared" si="11"/>
+        <v>10.874206472112879</v>
+      </c>
+      <c r="G86" s="300"/>
+      <c r="H86" s="300"/>
+      <c r="I86" s="300"/>
+      <c r="J86" s="300"/>
+      <c r="K86" s="300"/>
+      <c r="L86" s="300"/>
+    </row>
+    <row r="87" spans="1:12" ht="13.15">
+      <c r="A87" s="132">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="B87" s="119">
+        <f t="shared" si="11"/>
+        <v>5.918029851448563</v>
+      </c>
+      <c r="C87" s="119">
+        <f t="shared" si="11"/>
+        <v>7.0767198455769105</v>
+      </c>
+      <c r="D87" s="119">
+        <f t="shared" si="11"/>
+        <v>8.3759529837533027</v>
+      </c>
+      <c r="E87" s="119">
+        <f t="shared" si="11"/>
+        <v>9.8322460971195973</v>
+      </c>
+      <c r="F87" s="119">
+        <f t="shared" si="11"/>
+        <v>11.463918604875204</v>
+      </c>
+      <c r="G87" s="300"/>
+      <c r="H87" s="300"/>
+      <c r="I87" s="300"/>
+      <c r="J87" s="300"/>
+      <c r="K87" s="300"/>
+      <c r="L87" s="300"/>
+    </row>
+    <row r="89" spans="1:12" ht="13.15">
+      <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="C81" s="153" t="s">
+      <c r="C89" s="153" t="s">
         <v>110</v>
       </c>
-      <c r="D81" s="153" t="s">
+      <c r="D89" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="E81" s="154" t="s">
+      <c r="E89" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="F81" s="154" t="s">
-        <v>461</v>
-      </c>
-      <c r="G81" s="327"/>
-      <c r="H81" s="327"/>
-      <c r="I81" s="327"/>
-      <c r="J81" s="327"/>
-      <c r="K81" s="327"/>
-      <c r="L81" s="327"/>
-    </row>
-    <row r="82" spans="2:12">
-      <c r="B82" s="120" t="str">
+      <c r="F89" s="154" t="s">
+        <v>460</v>
+      </c>
+      <c r="G89" s="327"/>
+      <c r="H89" s="327"/>
+      <c r="I89" s="327"/>
+      <c r="J89" s="327"/>
+      <c r="K89" s="327"/>
+      <c r="L89" s="327"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C82" s="130">
+      <c r="C90" s="130">
         <f>Scenarios!C29</f>
         <v>0.05</v>
       </c>
-      <c r="D82" s="133">
+      <c r="D90" s="133">
         <f>Scenarios!D29</f>
         <v>15</v>
       </c>
-      <c r="E82" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
+      <c r="E90" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
         <v>9.3635390248553545</v>
       </c>
-      <c r="F82" s="130">
+      <c r="F90" s="130">
         <f>Scenarios!F29</f>
         <v>0.05</v>
       </c>
-      <c r="G82" s="301"/>
-      <c r="H82" s="301"/>
-      <c r="I82" s="301"/>
-      <c r="J82" s="301"/>
-      <c r="K82" s="301"/>
-      <c r="L82" s="301"/>
-    </row>
-    <row r="83" spans="2:12">
-      <c r="B83" s="120" t="str">
+      <c r="G90" s="301"/>
+      <c r="H90" s="301"/>
+      <c r="I90" s="301"/>
+      <c r="J90" s="301"/>
+      <c r="K90" s="301"/>
+      <c r="L90" s="301"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
       </c>
-      <c r="C83" s="130">
+      <c r="C91" s="130">
         <f>Scenarios!C22</f>
         <v>0.04</v>
       </c>
-      <c r="D83" s="133">
+      <c r="D91" s="133">
         <f>Scenarios!D22</f>
         <v>15</v>
       </c>
-      <c r="E83" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
+      <c r="E91" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
         <v>8.5598252024946575</v>
       </c>
-      <c r="F83" s="130">
-        <f>Scenarios!F22*(1-F$82-F$86)</f>
+      <c r="F91" s="130">
+        <f>Scenarios!F22*(1-F$90-F$94)</f>
         <v>0.18</v>
       </c>
-      <c r="G83" s="301"/>
-      <c r="H83" s="301"/>
-      <c r="I83" s="301"/>
-      <c r="J83" s="301"/>
-      <c r="K83" s="301"/>
-      <c r="L83" s="301"/>
-    </row>
-    <row r="84" spans="2:12">
-      <c r="B84" s="120" t="str">
+      <c r="G91" s="301"/>
+      <c r="H91" s="301"/>
+      <c r="I91" s="301"/>
+      <c r="J91" s="301"/>
+      <c r="K91" s="301"/>
+      <c r="L91" s="301"/>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
       </c>
-      <c r="C84" s="130">
+      <c r="C92" s="130">
         <f>Scenarios!C23</f>
         <v>0.03</v>
       </c>
-      <c r="D84" s="133">
+      <c r="D92" s="133">
         <f>Scenarios!D23</f>
         <v>15</v>
       </c>
-      <c r="E84" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
+      <c r="E92" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
         <v>7.7988591431268164</v>
       </c>
-      <c r="F84" s="130">
-        <f>Scenarios!F23*(1-F$82-F$86)</f>
+      <c r="F92" s="130">
+        <f>Scenarios!F23*(1-F$90-F$94)</f>
         <v>0.53999999999999992</v>
       </c>
-      <c r="G84" s="301"/>
-      <c r="H84" s="301"/>
-      <c r="I84" s="301"/>
-      <c r="J84" s="301"/>
-      <c r="K84" s="301"/>
-      <c r="L84" s="301"/>
-    </row>
-    <row r="85" spans="2:12">
-      <c r="B85" s="120" t="str">
+      <c r="G92" s="301"/>
+      <c r="H92" s="301"/>
+      <c r="I92" s="301"/>
+      <c r="J92" s="301"/>
+      <c r="K92" s="301"/>
+      <c r="L92" s="301"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C85" s="130">
+      <c r="C93" s="130">
         <f>Scenarios!C24</f>
         <v>0.02</v>
       </c>
-      <c r="D85" s="133">
+      <c r="D93" s="133">
         <f>Scenarios!D24</f>
         <v>15</v>
       </c>
-      <c r="E85" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
+      <c r="E93" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
         <v>7.0786787487122345</v>
       </c>
-      <c r="F85" s="130">
-        <f>Scenarios!F24*(1-F$82-F$86)</f>
+      <c r="F93" s="130">
+        <f>Scenarios!F24*(1-F$90-F$94)</f>
         <v>0.18</v>
       </c>
-      <c r="G85" s="301"/>
-      <c r="H85" s="301"/>
-      <c r="I85" s="301"/>
-      <c r="J85" s="301"/>
-      <c r="K85" s="301"/>
-      <c r="L85" s="301"/>
-    </row>
-    <row r="86" spans="2:12">
-      <c r="B86" s="120" t="str">
+      <c r="G93" s="301"/>
+      <c r="H93" s="301"/>
+      <c r="I93" s="301"/>
+      <c r="J93" s="301"/>
+      <c r="K93" s="301"/>
+      <c r="L93" s="301"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C86" s="130">
+      <c r="C94" s="130">
         <f>Scenarios!C30</f>
         <v>0.01</v>
       </c>
-      <c r="D86" s="133">
+      <c r="D94" s="133">
         <f>Scenarios!D30</f>
         <v>15</v>
       </c>
-      <c r="E86" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
+      <c r="E94" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
         <v>6.3973954328681506</v>
       </c>
-      <c r="F86" s="130">
+      <c r="F94" s="130">
         <f>Scenarios!F30</f>
         <v>0.05</v>
       </c>
-      <c r="G86" s="301"/>
-      <c r="H86" s="301"/>
-      <c r="I86" s="301"/>
-      <c r="J86" s="301"/>
-      <c r="K86" s="301"/>
-      <c r="L86" s="301"/>
-    </row>
-    <row r="87" spans="2:12">
-      <c r="B87" s="141"/>
-      <c r="C87" s="141"/>
-      <c r="D87" s="141"/>
-      <c r="E87" s="141"/>
-      <c r="F87" s="142"/>
-      <c r="G87" s="142"/>
-      <c r="H87" s="142"/>
-      <c r="I87" s="142"/>
-      <c r="J87" s="142"/>
-      <c r="K87" s="142"/>
-      <c r="L87" s="142"/>
-    </row>
-    <row r="97" spans="3:21">
-      <c r="C97" s="112"/>
-    </row>
-    <row r="98" spans="3:21">
-      <c r="C98" s="112"/>
-    </row>
-    <row r="99" spans="3:21">
-      <c r="C99" s="112"/>
-    </row>
-    <row r="106" spans="3:21">
-      <c r="C106" s="279"/>
-      <c r="M106" s="279"/>
-      <c r="N106" s="279"/>
-      <c r="O106" s="279"/>
-      <c r="P106" s="279"/>
-      <c r="Q106" s="279"/>
-      <c r="R106" s="279"/>
-      <c r="S106" s="279"/>
-      <c r="T106" s="279"/>
-      <c r="U106" s="279"/>
-    </row>
-    <row r="107" spans="3:21">
-      <c r="C107" s="279"/>
-      <c r="M107" s="279"/>
-      <c r="N107" s="279"/>
-      <c r="O107" s="279"/>
-      <c r="P107" s="279"/>
-      <c r="Q107" s="279"/>
-      <c r="R107" s="279"/>
-      <c r="S107" s="279"/>
-      <c r="T107" s="279"/>
-      <c r="U107" s="279"/>
-    </row>
-    <row r="108" spans="3:21">
-      <c r="C108" s="279"/>
-      <c r="M108" s="279"/>
-      <c r="N108" s="279"/>
-      <c r="O108" s="279"/>
-      <c r="P108" s="279"/>
-      <c r="Q108" s="279"/>
-      <c r="R108" s="279"/>
-      <c r="S108" s="279"/>
-      <c r="T108" s="279"/>
-      <c r="U108" s="279"/>
-    </row>
-    <row r="109" spans="3:21">
-      <c r="C109" s="279"/>
-      <c r="M109" s="279"/>
-      <c r="N109" s="279"/>
-      <c r="O109" s="279"/>
-      <c r="P109" s="279"/>
-      <c r="Q109" s="279"/>
-      <c r="R109" s="279"/>
-      <c r="S109" s="279"/>
-      <c r="T109" s="279"/>
-      <c r="U109" s="279"/>
-    </row>
-    <row r="110" spans="3:21">
-      <c r="C110" s="279"/>
-      <c r="M110" s="279"/>
-      <c r="N110" s="279"/>
-      <c r="O110" s="279"/>
-      <c r="P110" s="279"/>
-      <c r="Q110" s="279"/>
-      <c r="R110" s="279"/>
-      <c r="S110" s="279"/>
-      <c r="T110" s="279"/>
-      <c r="U110" s="279"/>
+      <c r="G94" s="301"/>
+      <c r="H94" s="301"/>
+      <c r="I94" s="301"/>
+      <c r="J94" s="301"/>
+      <c r="K94" s="301"/>
+      <c r="L94" s="301"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="B95" s="141"/>
+      <c r="C95" s="141"/>
+      <c r="D95" s="141"/>
+      <c r="E95" s="141"/>
+      <c r="F95" s="142"/>
+      <c r="G95" s="142"/>
+      <c r="H95" s="142"/>
+      <c r="I95" s="142"/>
+      <c r="J95" s="142"/>
+      <c r="K95" s="142"/>
+      <c r="L95" s="142"/>
+    </row>
+    <row r="105" spans="3:3">
+      <c r="C105" s="112"/>
+    </row>
+    <row r="106" spans="3:3">
+      <c r="C106" s="112"/>
+    </row>
+    <row r="107" spans="3:3">
+      <c r="C107" s="112"/>
+    </row>
+    <row r="114" spans="3:21">
+      <c r="C114" s="279"/>
+      <c r="M114" s="279"/>
+      <c r="N114" s="279"/>
+      <c r="O114" s="279"/>
+      <c r="P114" s="279"/>
+      <c r="Q114" s="279"/>
+      <c r="R114" s="279"/>
+      <c r="S114" s="279"/>
+      <c r="T114" s="279"/>
+      <c r="U114" s="279"/>
+    </row>
+    <row r="115" spans="3:21">
+      <c r="C115" s="279"/>
+      <c r="M115" s="279"/>
+      <c r="N115" s="279"/>
+      <c r="O115" s="279"/>
+      <c r="P115" s="279"/>
+      <c r="Q115" s="279"/>
+      <c r="R115" s="279"/>
+      <c r="S115" s="279"/>
+      <c r="T115" s="279"/>
+      <c r="U115" s="279"/>
+    </row>
+    <row r="116" spans="3:21">
+      <c r="C116" s="279"/>
+      <c r="M116" s="279"/>
+      <c r="N116" s="279"/>
+      <c r="O116" s="279"/>
+      <c r="P116" s="279"/>
+      <c r="Q116" s="279"/>
+      <c r="R116" s="279"/>
+      <c r="S116" s="279"/>
+      <c r="T116" s="279"/>
+      <c r="U116" s="279"/>
+    </row>
+    <row r="117" spans="3:21">
+      <c r="C117" s="279"/>
+      <c r="M117" s="279"/>
+      <c r="N117" s="279"/>
+      <c r="O117" s="279"/>
+      <c r="P117" s="279"/>
+      <c r="Q117" s="279"/>
+      <c r="R117" s="279"/>
+      <c r="S117" s="279"/>
+      <c r="T117" s="279"/>
+      <c r="U117" s="279"/>
+    </row>
+    <row r="118" spans="3:21">
+      <c r="C118" s="279"/>
+      <c r="M118" s="279"/>
+      <c r="N118" s="279"/>
+      <c r="O118" s="279"/>
+      <c r="P118" s="279"/>
+      <c r="Q118" s="279"/>
+      <c r="R118" s="279"/>
+      <c r="S118" s="279"/>
+      <c r="T118" s="279"/>
+      <c r="U118" s="279"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J52:K52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C21:L50">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>0</formula>
+  <conditionalFormatting sqref="B74:L87">
+    <cfRule type="expression" dxfId="1" priority="21">
+      <formula>ISNUMBER(MATCH(B74, $E$90:$E$94, 0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70:L79">
-    <cfRule type="expression" dxfId="0" priority="19">
-      <formula>ISNUMBER(MATCH(C70, $E$82:$E$86, 0))</formula>
+  <conditionalFormatting sqref="C21:L50">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{A06882BF-7451-4B05-ADA9-B8AC5ACC7F23}">
-      <formula1>$A$56:$A$65</formula1>
+      <formula1>$A$56:$A$69</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19326,7 +19553,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19468,7 +19695,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19492,7 +19719,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="455" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F18" s="323"/>
     </row>
@@ -19502,35 +19729,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E20" s="323"/>
       <c r="F20" s="323"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C21" s="153" t="s">
         <v>379</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="306" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C22" s="328">
         <v>0.04</v>
@@ -19540,7 +19767,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="330">
-        <f>DCF!E83</f>
+        <f>DCF!E91</f>
         <v>8.5598252024946575</v>
       </c>
       <c r="F22" s="332">
@@ -19554,7 +19781,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="306" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C23" s="328">
         <v>0.03</v>
@@ -19564,7 +19791,7 @@
         <v>15</v>
       </c>
       <c r="E23" s="330">
-        <f>DCF!E84</f>
+        <f>DCF!E92</f>
         <v>7.7988591431268164</v>
       </c>
       <c r="F23" s="331">
@@ -19577,7 +19804,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="306" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C24" s="328">
         <v>0.02</v>
@@ -19587,7 +19814,7 @@
         <v>15</v>
       </c>
       <c r="E24" s="330">
-        <f>DCF!E85</f>
+        <f>DCF!E93</f>
         <v>7.0786787487122345</v>
       </c>
       <c r="F24" s="331">
@@ -19600,7 +19827,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19614,33 +19841,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C28" s="153" t="s">
         <v>379</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="306" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C29" s="328">
         <v>0.05</v>
@@ -19650,7 +19877,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="330">
-        <f>DCF!E82</f>
+        <f>DCF!E90</f>
         <v>9.3635390248553545</v>
       </c>
       <c r="F29" s="331">
@@ -19663,7 +19890,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="319" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C30" s="328">
         <v>0.01</v>
@@ -19673,7 +19900,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="330">
-        <f>DCF!E86</f>
+        <f>DCF!E94</f>
         <v>6.3973954328681506</v>
       </c>
       <c r="F30" s="331">
@@ -19690,12 +19917,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19706,7 +19933,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F33" s="219">
         <f>Holding_Period</f>
@@ -19719,23 +19946,23 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12260045445698151</v>
+        <v>0.12017169390553457</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
@@ -19746,7 +19973,7 @@
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -19755,7 +19982,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -19766,15 +19993,15 @@
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F36" s="335" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19966,13 +20193,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E60" s="417"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C61" s="153" t="s">
         <v>103</v>
@@ -19985,10 +20212,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -20043,7 +20270,7 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C65" s="153" t="s">
         <v>103</v>
@@ -20056,10 +20283,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -20153,7 +20380,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="440" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F3" s="441">
         <f>Thesis!F3</f>
@@ -20162,7 +20389,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="427" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C4" s="428" t="str">
         <f>Thesis!C4</f>
@@ -20170,7 +20397,7 @@
       </c>
       <c r="D4" s="353"/>
       <c r="E4" s="439" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F4" s="442" t="str">
         <f>Thesis!F4</f>
@@ -20186,7 +20413,7 @@
         <v>0341.HK</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F5" s="444" t="str">
         <f>Thesis!F5</f>
@@ -20220,7 +20447,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20238,14 +20465,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3758.4261338400001</v>
+        <v>3781.6262951599997</v>
       </c>
       <c r="D10" s="347" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.12260045445698151</v>
+        <v>0.12017169390553457</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20253,13 +20480,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
-        <v>502</v>
-      </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="B12" s="467" t="s">
+        <v>501</v>
+      </c>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20302,7 +20529,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="347" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C17" s="429">
         <f>Terminal_Growth</f>
@@ -20355,7 +20582,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="351" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C21" s="365" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -20378,7 +20605,7 @@
         <v>4.333028820025568</v>
       </c>
       <c r="D22" s="369" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
@@ -20394,7 +20621,7 @@
         <v>5.3553121183397749</v>
       </c>
       <c r="D23" s="369" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
@@ -20410,7 +20637,7 @@
         <v>6.5660659780940076</v>
       </c>
       <c r="D24" s="369" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E24" s="372">
         <f>Thesis!E24</f>
@@ -20426,7 +20653,7 @@
         <v>7.3792932677079612</v>
       </c>
       <c r="D25" s="369" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E25" s="372">
         <f>Thesis!E25</f>
@@ -20444,22 +20671,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
+        <v>502</v>
+      </c>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
-        <v>504</v>
-      </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20472,7 +20699,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="466" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C33" s="466"/>
       <c r="D33" s="466"/>
@@ -20498,7 +20725,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="466" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C36" s="466"/>
       <c r="D36" s="466"/>
@@ -20533,7 +20760,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="466" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C40" s="466"/>
       <c r="D40" s="466"/>
@@ -20555,7 +20782,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="466" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C43" s="466"/>
       <c r="D43" s="466"/>
@@ -20607,7 +20834,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="347" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20625,7 +20852,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="466" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C51" s="466"/>
       <c r="D51" s="466"/>
@@ -20634,7 +20861,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="376" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
@@ -20647,12 +20874,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="466" t="s">
-        <v>511</v>
-      </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+        <v>510</v>
+      </c>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20668,22 +20895,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
+        <v>511</v>
+      </c>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
-        <v>513</v>
-      </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20717,7 +20944,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0876354405804044E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20727,7 +20954,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -20805,7 +21032,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="349" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B71" s="349"/>
       <c r="C71" s="349"/>
@@ -20818,22 +21045,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
-        <v>514</v>
-      </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="B73" s="467" t="s">
+        <v>513</v>
+      </c>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
-        <v>483</v>
-      </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="B74" s="468" t="s">
+        <v>482</v>
+      </c>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20841,13 +21068,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
-        <v>515</v>
-      </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="B77" s="467" t="s">
+        <v>514</v>
+      </c>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20895,7 +21122,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="347" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20913,7 +21140,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="386" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C85" s="394">
         <f>BS!C66</f>
@@ -20939,7 +21166,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="347" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20970,7 +21197,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="376" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
@@ -20983,7 +21210,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="349" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B94" s="349"/>
       <c r="C94" s="349"/>
@@ -20996,33 +21223,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
-        <v>518</v>
-      </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="B96" s="467" t="s">
+        <v>517</v>
+      </c>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
-        <v>519</v>
-      </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="B97" s="468" t="s">
+        <v>518</v>
+      </c>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
-        <v>520</v>
-      </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="B98" s="468" t="s">
+        <v>519</v>
+      </c>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21066,7 +21293,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="389"/>
       <c r="B104" s="376" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C104" s="372">
         <v>0</v>
@@ -21085,23 +21312,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
-        <v>521</v>
-      </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="B107" s="467" t="s">
+        <v>520</v>
+      </c>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
-        <v>540</v>
-      </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="B108" s="467" t="s">
+        <v>539</v>
+      </c>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21109,13 +21336,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="389"/>
       <c r="B110" s="373" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="389"/>
       <c r="B111" s="379" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
@@ -21145,13 +21372,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
-        <v>522</v>
-      </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="B114" s="467" t="s">
+        <v>521</v>
+      </c>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21159,7 +21386,7 @@
     <row r="116" spans="1:6">
       <c r="A116" s="389"/>
       <c r="B116" s="373" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -21183,118 +21410,118 @@
     <row r="118" spans="1:6">
       <c r="A118" s="389"/>
       <c r="B118" s="399" t="str">
-        <f>DCF!B82</f>
+        <f>DCF!B90</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C118" s="400">
-        <f>DCF!C82</f>
+        <f>DCF!C90</f>
         <v>0.05</v>
       </c>
       <c r="D118" s="401">
-        <f>DCF!D82</f>
+        <f>DCF!D90</f>
         <v>15</v>
       </c>
       <c r="E118" s="402" t="str">
-        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
         <v>9.36 HKD</v>
       </c>
       <c r="F118" s="403">
-        <f>DCF!F82</f>
+        <f>DCF!F90</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="389"/>
       <c r="B119" s="404" t="str">
-        <f>DCF!B83</f>
+        <f>DCF!B91</f>
         <v>Optimistic</v>
       </c>
       <c r="C119" s="405">
-        <f>DCF!C83</f>
+        <f>DCF!C91</f>
         <v>0.04</v>
       </c>
       <c r="D119" s="406">
-        <f>DCF!D83</f>
+        <f>DCF!D91</f>
         <v>15</v>
       </c>
       <c r="E119" s="402" t="str">
-        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
         <v>8.56 HKD</v>
       </c>
       <c r="F119" s="407">
-        <f>DCF!F83</f>
+        <f>DCF!F91</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="B120" s="404" t="str">
-        <f>DCF!B84</f>
+        <f>DCF!B92</f>
         <v>Base</v>
       </c>
       <c r="C120" s="405">
-        <f>DCF!C84</f>
+        <f>DCF!C92</f>
         <v>0.03</v>
       </c>
       <c r="D120" s="406">
-        <f>DCF!D84</f>
+        <f>DCF!D92</f>
         <v>15</v>
       </c>
       <c r="E120" s="402" t="str">
-        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
         <v>7.8 HKD</v>
       </c>
       <c r="F120" s="407">
-        <f>DCF!F84</f>
+        <f>DCF!F92</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="404" t="str">
-        <f>DCF!B85</f>
+        <f>DCF!B93</f>
         <v>Pessimistic</v>
       </c>
       <c r="C121" s="405">
-        <f>DCF!C85</f>
+        <f>DCF!C93</f>
         <v>0.02</v>
       </c>
       <c r="D121" s="406">
-        <f>DCF!D85</f>
+        <f>DCF!D93</f>
         <v>15</v>
       </c>
       <c r="E121" s="402" t="str">
-        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
         <v>7.08 HKD</v>
       </c>
       <c r="F121" s="407">
-        <f>DCF!F85</f>
+        <f>DCF!F93</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="404" t="str">
-        <f>DCF!B86</f>
+        <f>DCF!B94</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C122" s="405">
-        <f>DCF!C86</f>
+        <f>DCF!C94</f>
         <v>0.01</v>
       </c>
       <c r="D122" s="406">
-        <f>DCF!D86</f>
+        <f>DCF!D94</f>
         <v>15</v>
       </c>
       <c r="E122" s="402" t="str">
-        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
         <v>6.4 HKD</v>
       </c>
       <c r="F122" s="407">
-        <f>DCF!F86</f>
+        <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="466" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C124" s="466"/>
       <c r="D124" s="466"/>
@@ -21315,17 +21542,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
-        <v>524</v>
-      </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="B127" s="471" t="s">
+        <v>523</v>
+      </c>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B129" s="349"/>
       <c r="C129" s="349"/>
@@ -21334,22 +21561,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
+        <v>524</v>
+      </c>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
-        <v>526</v>
-      </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21380,28 +21607,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="373" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C138" s="411"/>
       <c r="D138" s="411"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="344" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C139" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E139" s="345" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="345" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21448,21 +21675,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="344" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C143" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E143" s="345" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="345" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21509,7 +21736,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="349" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B147" s="349"/>
       <c r="C147" s="349"/>
@@ -21518,13 +21745,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
-        <v>527</v>
-      </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="B149" s="473" t="s">
+        <v>526</v>
+      </c>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21532,13 +21759,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
-        <v>528</v>
-      </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="B152" s="469" t="s">
+        <v>527</v>
+      </c>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21557,12 +21784,12 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="347" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="466" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C158" s="466"/>
       <c r="D158" s="466"/>
@@ -21571,30 +21798,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="347" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21614,12 +21841,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21634,15 +21864,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E2A09B-C837-490A-8282-619FD0B737CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CDC3B9-4C42-4C57-AB91-25AA39798D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.52</v>
+        <v>6.48</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3781.6262951599997</v>
+        <v>3758.4261338400001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.12017169390553457</v>
+        <v>0.12260045445698151</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.0876354405804044E-2</v>
+        <v>6.1252134371271964E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14225,24 +14225,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7423312883435578E-2</v>
+        <v>8.7962962962962951E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8282208588957059E-2</v>
+        <v>5.8641975308641972E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8282208588957059E-2</v>
+        <v>5.8641975308641972E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15424,50 +15424,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0876354405804044E-2</v>
+        <v>6.1252134371271964E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6422318760351701E-2</v>
+        <v>7.6894061468748928E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.18079666515043E-2</v>
+        <v>9.2374682495032098E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8800844613438487E-2</v>
+        <v>2.8978627604879462E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3137169822606544E-3</v>
+        <v>-6.3526905438795467E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1427484030378421E-2</v>
+        <v>-3.1621480845380752E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5165154808395366E-2</v>
+        <v>5.5505680455360765E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1475013543019591</v>
+        <v>0.1484118564890082</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12166723099764495</v>
+        <v>0.12241826328775386</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13680780691157923</v>
+        <v>0.13765229954683589</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13338441205720952</v>
+        <v>0.13420777262546388</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15481,43 +15481,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2171928596147154E-2</v>
+        <v>6.2555705933160399E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8114206426603489E-2</v>
+        <v>8.8658121281088687E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9401900484536298E-2</v>
+        <v>2.9583393697403801E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0423738932757817E-3</v>
+        <v>6.0796724975552621E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.534257799652443E-2</v>
+        <v>9.5931112428601736E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9670373060184349E-2</v>
+        <v>1.979179511611141E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15657549260164216</v>
+        <v>0.15754200798807202</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12145435961978557</v>
+        <v>0.1222040778890435</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13323632762043777</v>
+        <v>0.13405877408723058</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1369410829046738</v>
+        <v>0.13778639823124586</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.52</v>
+        <v>6.48</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12017169390553457</v>
+        <v>0.12260045445698151</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20447,7 +20447,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.52</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3781.6262951599997</v>
+        <v>3758.4261338400001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.12017169390553457</v>
+        <v>0.12260045445698151</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20480,13 +20480,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20671,22 +20671,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20876,10 +20876,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20895,22 +20895,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>6.0876354405804044E-2</v>
+        <v>6.1252134371271964E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21045,22 +21045,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21068,13 +21068,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21223,33 +21223,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21312,23 +21312,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21372,13 +21372,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21542,13 +21542,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21561,22 +21561,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21745,13 +21745,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21759,13 +21759,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21802,22 +21802,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21841,15 +21841,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21864,12 +21861,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CDC3B9-4C42-4C57-AB91-25AA39798D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369C8DB7-373B-4050-A13A-BFE306FB3EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3758.4261338400001</v>
+        <v>3781.6262951599997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.12260045445698151</v>
+        <v>0.12017169390553457</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0876354405804044E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14225,24 +14225,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7962962962962951E-2</v>
+        <v>8.7423312883435578E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8641975308641972E-2</v>
+        <v>5.8282208588957059E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8641975308641972E-2</v>
+        <v>5.8282208588957059E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15424,50 +15424,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0876354405804044E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6894061468748928E-2</v>
+        <v>7.6422318760351701E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.2374682495032098E-2</v>
+        <v>9.18079666515043E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8978627604879462E-2</v>
+        <v>2.8800844613438487E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3526905438795467E-3</v>
+        <v>-6.3137169822606544E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1621480845380752E-2</v>
+        <v>-3.1427484030378421E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5505680455360765E-2</v>
+        <v>5.5165154808395366E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1484118564890082</v>
+        <v>0.1475013543019591</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12241826328775386</v>
+        <v>0.12166723099764495</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13765229954683589</v>
+        <v>0.13680780691157923</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13420777262546388</v>
+        <v>0.13338441205720952</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15481,43 +15481,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2555705933160399E-2</v>
+        <v>6.2171928596147154E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8658121281088687E-2</v>
+        <v>8.8114206426603489E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9583393697403801E-2</v>
+        <v>2.9401900484536298E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0796724975552621E-3</v>
+        <v>6.0423738932757817E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5931112428601736E-2</v>
+        <v>9.534257799652443E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.979179511611141E-2</v>
+        <v>1.9670373060184349E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15754200798807202</v>
+        <v>0.15657549260164216</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1222040778890435</v>
+        <v>0.12145435961978557</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13405877408723058</v>
+        <v>0.13323632762043777</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13778639823124586</v>
+        <v>0.1369410829046738</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12260045445698151</v>
+        <v>0.12017169390553457</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20447,7 +20447,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3758.4261338400001</v>
+        <v>3781.6262951599997</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.12260045445698151</v>
+        <v>0.12017169390553457</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20480,13 +20480,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20671,22 +20671,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20876,10 +20876,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20895,22 +20895,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>6.1252134371271964E-2</v>
+        <v>6.0876354405804044E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.1349693251533749E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21045,22 +21045,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21068,13 +21068,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21223,33 +21223,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21312,23 +21312,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21372,13 +21372,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21542,13 +21542,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21561,22 +21561,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21745,13 +21745,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21759,13 +21759,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21802,22 +21802,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21841,12 +21841,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21861,15 +21864,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369C8DB7-373B-4050-A13A-BFE306FB3EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0C40E7-FB07-410C-91FE-24A1BEE1499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3781.6262951599997</v>
+        <v>3775.8262548299999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.12017169390553457</v>
+        <v>0.1207769498377638</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.0876354405804044E-2</v>
+        <v>6.0969866470943525E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14225,24 +14225,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.7423312883435578E-2</v>
+        <v>8.755760368663594E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8282208588957059E-2</v>
+        <v>5.8371735791090631E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8282208588957059E-2</v>
+        <v>5.8371735791090631E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15424,50 +15424,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0876354405804044E-2</v>
+        <v>6.0969866470943525E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6422318760351701E-2</v>
+        <v>7.6539710955068063E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.18079666515043E-2</v>
+        <v>9.1948992713949004E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8800844613438487E-2</v>
+        <v>2.8845085542184169E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3137169822606544E-3</v>
+        <v>-6.3234154722487659E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1427484030378421E-2</v>
+        <v>-3.1475759735494206E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5165154808395366E-2</v>
+        <v>5.5249893909483531E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1475013543019591</v>
+        <v>0.14772793088306807</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12166723099764495</v>
+        <v>0.12185412382559832</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13680780691157923</v>
+        <v>0.13701795715261084</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13338441205720952</v>
+        <v>0.13358930362718988</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15481,43 +15481,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2171928596147154E-2</v>
+        <v>6.2267430790611276E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8114206426603489E-2</v>
+        <v>8.8249558510208104E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9401900484536298E-2</v>
+        <v>2.9447064694189961E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0423738932757817E-3</v>
+        <v>6.0516555736033944E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.534257799652443E-2</v>
+        <v>9.5489033569483753E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9670373060184349E-2</v>
+        <v>1.9700588687004906E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15657549260164216</v>
+        <v>0.15681600795126066</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12145435961978557</v>
+        <v>0.1216409254563751</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13323632762043777</v>
+        <v>0.13344099171816501</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1369410829046738</v>
+        <v>0.13715143787073322</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12017169390553457</v>
+        <v>0.1207769498377638</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20447,7 +20447,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3781.6262951599997</v>
+        <v>3775.8262548299999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.12017169390553457</v>
+        <v>0.1207769498377638</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20480,13 +20480,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20671,22 +20671,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20876,10 +20876,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20895,22 +20895,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>6.0876354405804044E-2</v>
+        <v>6.0969866470943525E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.1349693251533749E-2</v>
+        <v>6.1443932411674354E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21045,22 +21045,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21068,13 +21068,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21223,33 +21223,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21312,23 +21312,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21372,13 +21372,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21542,13 +21542,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21561,22 +21561,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21745,13 +21745,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21759,13 +21759,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21802,22 +21802,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21841,15 +21841,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21864,12 +21861,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0C40E7-FB07-410C-91FE-24A1BEE1499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2526484-518A-40DB-87E1-E607066F7F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.51</v>
+        <v>6.27</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3775.8262548299999</v>
+        <v>3636.6252869099999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.1207769498377638</v>
+        <v>0.19480295483917651</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>7.8143613713918958</v>
+        <v>9.245456706985749</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v>Low Growth Asset Play</v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="1" t="s">
         <v>348</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>4.333028820025568</v>
+        <v>4.9925197580872513</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>5.3553121183397749</v>
+        <v>6.181937582942723</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>6.5660659780940076</v>
+        <v>7.5918184332759076</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>7.3792932677079612</v>
+        <v>8.5393431481257664</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C34" s="289">
         <f>Normalized_FCF!C8</f>
-        <v>399119.96227138769</v>
+        <v>439469.87884546071</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>6692.5186674405113</v>
+        <v>6967.3739452954487</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-78679.881332559497</v>
+        <v>-78405.026054704562</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C49" s="289">
         <f>Normalized_FCF!C13</f>
-        <v>-37355.845009453624</v>
+        <v>-39042.598999519083</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-52872.613354906651</v>
+        <v>-59575.700710474768</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>289000.65016124537</v>
+        <v>290217.63448334695</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>230211.62257446788</v>
+        <v>262446.55308076233</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.0969866470943525E-2</v>
+        <v>7.216760935624475E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,14 +5890,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.3795853269537489E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>1.0077754137932506</v>
+        <v>0.88399565731239171</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5917,11 +5917,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.1167471410506614</v>
+        <v>0.13154811711973616</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.11792742550148552</v>
+        <v>0.11837081398114316</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>3.9086921133773919E-2</v>
+        <v>4.2139530177368108E-2</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>3.7776339292914275E-2</v>
+        <v>3.791837235752913E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="C68" s="268">
         <f>Normalized_FCF!C117</f>
-        <v>1.3708738209065539</v>
+        <v>1.4327738230803833</v>
       </c>
       <c r="D68" s="268">
         <f>Normalized_FCF!G117</f>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C81" s="342">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>5.3475400925918697</v>
+        <v>4.8565558249568426</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>384381.13325594889</v>
+        <v>356895.60547045514</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.66272148362104388</v>
+        <v>0.61533297212513538</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-2.9076464486309033</v>
+        <v>-2.9550349601268113</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6337,7 +6337,7 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (15yrs)</v>
+        <v>Snowball Scenario (20yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>9.36 HKD</v>
+        <v>11.43 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,13 +6353,13 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-1.3162728985041415E-2</v>
+        <v>-3.0574909747230136E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (15yrs)</v>
+        <v>Optimistic (20yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>8.56 HKD</v>
+        <v>10.28 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,13 +6375,13 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.8223005300290952E-2</v>
+        <v>5.496734932037171E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (15yrs)</v>
+        <v>Base (20yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>7.8 HKD</v>
+        <v>9.22 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,13 +6397,13 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.191889800512979E-2</v>
+        <v>4.4376065079678513E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (15yrs)</v>
+        <v>Pessimistic (20yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>7.08 HKD</v>
+        <v>8.23 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,13 +6419,13 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>8.8265281842590304E-2</v>
+        <v>8.6505401148917249E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (15yrs)</v>
+        <v>Devil's advocate (20yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>6.4 HKD</v>
+        <v>7.31 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.12768233742292004</v>
+        <v>0.13244054457715634</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>7.8143613713918958</v>
+        <v>9.245456706985749</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>3.6010881895815197</v>
+        <v>4.2605791276432035</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>4.333028820025568</v>
+        <v>4.9925197580872513</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>4.513710539432144</v>
+        <v>5.340336004035092</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>5.3553121183397749</v>
+        <v>6.181937582942723</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>5.6010247277185474</v>
+        <v>6.6267771829004483</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>6.5660659780940076</v>
+        <v>7.5918184332759076</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>6.3343431768387548</v>
+        <v>7.4943930572565609</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>7.3792932677079612</v>
+        <v>8.5393431481257664</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
-        <v>5.3475400925918697</v>
+        <v>4.8565558249568426</v>
       </c>
       <c r="D50" s="92">
         <f>G31/Normalized_FCF!G8</f>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
-        <v>8.897587277630245E-2</v>
+        <v>9.7971085702254657E-2</v>
       </c>
       <c r="D54" s="89">
         <f>Normalized_FCF!G8/G35</f>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>384381.13325594889</v>
+        <v>356895.60547045514</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-669251.86674405111</v>
+        <v>-696737.39452954486</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.5743445066892159</v>
+        <v>1.5122383386805875</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10473,7 +10473,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>669251.86674405111</v>
+        <v>696737.39452954486</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10605,11 +10605,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>384381.13325594889</v>
+        <v>356895.60547045514</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.66272148362104388</v>
+        <v>0.61533297212513538</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10639,11 +10639,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2582173.333255949</v>
+        <v>2554687.8054704554</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>4.4519920316760082</v>
+        <v>4.4046035201800997</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10787,8 +10787,8 @@
         <v>0</v>
       </c>
       <c r="C4" s="269">
-        <f>AVERAGE(G4:J4)</f>
-        <v>8198140.75</v>
+        <f>G4</f>
+        <v>8568317</v>
       </c>
       <c r="D4" s="54"/>
       <c r="E4" s="236"/>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="C5" s="270">
         <f>C26</f>
-        <v>-7304527.7877286123</v>
+        <v>-7634354.1211545393</v>
       </c>
       <c r="E5" s="238"/>
       <c r="G5" s="274">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="C6" s="271">
         <f>C4+C5</f>
-        <v>893612.96227138769</v>
+        <v>933962.87884546071</v>
       </c>
       <c r="E6" s="238"/>
       <c r="G6" s="271">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="C8" s="272">
         <f>C6+C7</f>
-        <v>399119.96227138769</v>
+        <v>439469.87884546071</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="244"/>
@@ -11124,24 +11124,24 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-78679.881332559497</v>
+        <v>-78405.026054704562</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>-74482.349838754599</v>
+        <v>-73265.365516653022</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-79815.579205498987</v>
+        <v>-78633.759396519948</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>-73832.968687003769</v>
+        <v>-72819.588982796442</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>-83179.118160315134</v>
+        <v>-82979.322161794684</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
@@ -11179,24 +11179,24 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>320440.08093882818</v>
+        <v>361064.85279075615</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>323679.65016124537</v>
+        <v>324896.63448334695</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>406257.42079450103</v>
+        <v>407439.24060348002</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>142737.03131299623</v>
+        <v>143750.41101720356</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>5698.8818396848656</v>
+        <v>5898.6778382053162</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-52872.613354906651</v>
+        <v>-59575.700710474768</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="C13" s="270">
         <f>-C4*C79</f>
-        <v>-37355.845009453624</v>
+        <v>-39042.598999519083</v>
       </c>
       <c r="D13" s="57"/>
       <c r="E13" s="245"/>
@@ -11346,26 +11346,26 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>230211.62257446788</v>
+        <v>262446.55308076233</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>289000.65016124537</v>
+        <v>290217.63448334695</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>347183.42079450103</v>
+        <v>348365.24060348002</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>108914.03131299623</v>
+        <v>109927.41101720356</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>-23876.118160315134</v>
+        <v>-23676.322161794684</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
@@ -11564,26 +11564,26 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>230211.62257446788</v>
+        <v>262446.55308076233</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>289000.65016124537</v>
+        <v>290217.63448334695</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>347183.42079450103</v>
+        <v>348365.24060348002</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>108914.03131299623</v>
+        <v>109927.41101720356</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>-23876.118160315134</v>
+        <v>-23676.322161794684</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="C23" s="278">
         <f>-C4*C29</f>
-        <v>-7304527.7877286123</v>
+        <v>-7634354.1211545393</v>
       </c>
       <c r="D23" s="55"/>
       <c r="E23" s="237"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C26" s="271">
         <f>SUM(C23:C25)</f>
-        <v>-7304527.7877286123</v>
+        <v>-7634354.1211545393</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="243"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
-        <v>6.0317700693294389E-2</v>
+        <v>5.7711800345388718E-2</v>
       </c>
       <c r="E38" s="238"/>
       <c r="G38" s="29">
@@ -12302,19 +12302,19 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>9.9827097514172861E-2</v>
+        <v>9.9453169317628612E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.13861408338060871</v>
+        <v>0.13821201884382026</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>0.23111731900645427</v>
+        <v>0.22948803948847138</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.902540671302102</v>
+        <v>4.7364851524931719</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
@@ -12440,24 +12440,24 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>6692.5186674405113</v>
+        <v>6967.3739452954487</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>29632.650161245398</v>
+        <v>30849.634483346978</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>28776.420794501017</v>
+        <v>29958.240603480055</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>24675.031312996227</v>
+        <v>25688.411017203551</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>4864.8818396848692</v>
+        <v>5064.677838205318</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
@@ -12552,24 +12552,24 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-78679.881332559497</v>
+        <v>-78405.026054704562</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-74482.349838754599</v>
+        <v>-73265.365516653022</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>-79815.579205498987</v>
+        <v>-78633.759396519948</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>-73832.968687003769</v>
+        <v>-72819.588982796442</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>-83179.118160315134</v>
+        <v>-82979.322161794684</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>4.6750467630216281</v>
+        <v>5.1476809700261521</v>
       </c>
       <c r="E53" s="238"/>
       <c r="G53" s="40">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
-        <v>0.10900190537365288</v>
+        <v>0.10900190537365281</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="235"/>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="C73" s="74">
         <f t="shared" si="22"/>
-        <v>6.0317700693294389E-2</v>
+        <v>5.7711800345388718E-2</v>
       </c>
       <c r="D73" s="26"/>
       <c r="E73" s="235"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
-        <v>4.8684204680358494E-2</v>
+        <v>5.1290105028264095E-2</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="235"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>9.5972835465845709E-3</v>
+        <v>9.1505748508959889E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235" t="s">
@@ -13526,19 +13526,19 @@
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>8.6927630990723849E-3</v>
+        <v>8.5507300344575283E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1832304608240791E-3</v>
+        <v>9.0472554572338798E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2014660795733134E-3</v>
+        <v>9.0751731898275293E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>1.1077620766099928E-2</v>
+        <v>1.1051012353422025E-2</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
@@ -13576,26 +13576,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>3.9086921133773919E-2</v>
+        <v>4.2139530177368108E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>3.7776339292914275E-2</v>
+        <v>3.791837235752913E-2</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>4.6742196933388325E-2</v>
+        <v>4.6878171936978519E-2</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>1.7788665081222912E-2</v>
+        <v>1.79149579709687E-2</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>7.5896514903138587E-4</v>
+        <v>7.8557356170929E-4</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>6.4493419870726969E-3</v>
+        <v>6.9530224792657379E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13748,26 +13748,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>2.8080955132963274E-2</v>
+        <v>3.0629883684364423E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>3.3728986703134976E-2</v>
+        <v>3.3871019767749831E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>3.9945401600412205E-2</v>
+        <v>4.0081376604002399E-2</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>1.3573458883450318E-2</v>
+        <v>1.3699751773196104E-2</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>3.1797714161479456E-3</v>
+        <v>3.1531630034700416E-3</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="C81" s="74">
         <f>ABS(C15/C$4)</f>
-        <v>4.6165711414505782E-2</v>
+        <v>4.4171218221734795E-2</v>
       </c>
       <c r="D81" s="26"/>
       <c r="E81" s="235"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G76:J76),C81)</f>
-        <v>4.6165711414505782E-2</v>
+        <v>4.4171218221734795E-2</v>
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="236"/>
@@ -13969,26 +13969,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>2.8080955132963274E-2</v>
+        <v>3.0629883684364423E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>3.3728986703134976E-2</v>
+        <v>3.3871019767749831E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>3.9945401600412205E-2</v>
+        <v>4.0081376604002399E-2</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>1.3573458883450318E-2</v>
+        <v>1.3699751773196104E-2</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>3.1797714161479456E-3</v>
+        <v>3.1531630034700416E-3</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
@@ -14149,24 +14149,24 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>1.0077754137932506</v>
+        <v>0.88399565731239171</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.802771942106555</v>
+        <v>0.79940563781734142</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.95224103171010732</v>
+        <v>0.94901057934853383</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>2.0236284515684848</v>
+        <v>2.0049733774363823</v>
       </c>
       <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v>-9.2310454764934455</v>
+        <v>-9.308942961405176</v>
       </c>
       <c r="K90" s="152">
         <f t="shared" si="37"/>
@@ -14225,24 +14225,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.3795853269537489E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.3795853269537489E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.755760368663594E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8371735791090631E-2</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8371735791090631E-2</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="C95" s="74">
         <f>C4/G4-1</f>
-        <v>-4.3202912543968686E-2</v>
+        <v>0</v>
       </c>
       <c r="D95" s="26"/>
       <c r="E95" s="235"/>
@@ -14362,26 +14362,26 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-1.0008566250004791E-2</v>
+        <v>0.11132223134574537</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-0.20326464553376444</v>
+        <v>-0.20258874917858871</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>1.8461949716724368</v>
+        <v>1.8343518305121167</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>24.04649777418253</v>
+        <v>23.369937630114734</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.0651814784193805</v>
+        <v>-1.0674666632911132</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="C107" s="91">
         <f>C101/C$4</f>
-        <v>1.5188199836651987E-2</v>
+        <v>1.4532025367408791E-2</v>
       </c>
       <c r="D107" s="25"/>
       <c r="E107" s="239"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="C108" s="91">
         <f>C102/C$4</f>
-        <v>2.691305342616861E-2</v>
+        <v>2.5750331132706691E-2</v>
       </c>
       <c r="D108" s="25"/>
       <c r="E108" s="239"/>
@@ -14973,19 +14973,19 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>5.2283584800136307</v>
+        <v>5.2064341392966007</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>4.7904188402603074</v>
+        <v>4.7741674718145966</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>15.5984034336013</v>
+        <v>15.454607584036758</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-48.77011380918006</v>
+        <v>-49.181667323272073</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -15081,24 +15081,24 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>3.9086921133773919E-2</v>
+        <v>4.2139530177368108E-2</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>3.7776339292914275E-2</v>
+        <v>3.791837235752913E-2</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>4.6742196933388325E-2</v>
+        <v>4.6878171936978519E-2</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>1.7788665081222912E-2</v>
+        <v>1.79149579709687E-2</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>7.5896514903138587E-4</v>
+        <v>7.8557356170929E-4</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="C117" s="40">
         <f>C4/C100</f>
-        <v>1.3708738209065539</v>
+        <v>1.4327738230803833</v>
       </c>
       <c r="E117" s="238"/>
       <c r="G117" s="40">
@@ -15246,26 +15246,26 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.1167471410506614</v>
+        <v>0.13154811711973616</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.11792742550148552</v>
+        <v>0.11837081398114316</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.13958275424109118</v>
+        <v>0.13998880630441438</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>5.1122425000079234E-2</v>
+        <v>5.1485375157080467E-2</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>2.0163211970682122E-3</v>
+        <v>2.0870110127616838E-3</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
@@ -15367,26 +15367,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.39691383072584235</v>
+        <v>0.45249091066365454</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.49827351831749306</v>
+        <v>0.50037175255873945</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.59858794256780801</v>
+        <v>0.6006255487597274</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.18778150687961892</v>
+        <v>0.18952870111715853</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-4.1165434724339464E-2</v>
+        <v>-4.0820961260099868E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
@@ -15424,50 +15424,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0969866470943525E-2</v>
+        <v>7.216760935624475E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6539710955068063E-2</v>
+        <v>7.9804107266146646E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.1948992713949004E-2</v>
+        <v>9.5793548446527502E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>2.8845085542184169E-2</v>
+        <v>3.0227863017090677E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.3234154722487659E-3</v>
+        <v>-6.5105201371770125E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.1475759735494206E-2</v>
+        <v>-3.268057350527389E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.5249893909483531E-2</v>
+        <v>5.7364722384487685E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14772793088306807</v>
+        <v>0.15338258852452524</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12185412382559832</v>
+        <v>0.12651839650791788</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.13701795715261084</v>
+        <v>0.14226266364649068</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13358930362718988</v>
+        <v>0.13870276979473781</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15481,43 +15481,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2267430790611276E-2</v>
+        <v>6.4650873117524627E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8249558510208104E-2</v>
+        <v>9.1627532041699322E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9447064694189961E-2</v>
+        <v>3.0574225065259433E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0516555736033944E-3</v>
+        <v>6.2832978922102234E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5489033569483753E-2</v>
+        <v>9.914411619415299E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9700588687004906E-2</v>
+        <v>2.0454678206124711E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15681600795126066</v>
+        <v>0.16281853457140461</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1216409254563751</v>
+        <v>0.1262970374355665</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13344099171816501</v>
+        <v>0.13854878087484118</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13715143787073322</v>
+        <v>0.14240125367439765</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>230211.62257446788</v>
+        <v>262446.55308076233</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="I4" s="309">
         <f>Normalized_FCF!C4</f>
-        <v>8198140.75</v>
+        <v>8568317</v>
       </c>
       <c r="J4" s="309"/>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>384381.13325594889</v>
+        <v>356895.60547045514</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3175332.7251650742</v>
+        <v>3619952.4562863773</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-78679.881332559497</v>
+        <v>-78405.026054704562</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16365,14 +16365,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>-1686446.6667440513</v>
+        <v>-1713932.1945295448</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>-1686446.6667440513</v>
+        <v>-1713932.1945295448</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>1488886.058421023</v>
+        <v>1906020.2617568325</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-2.9076464486309033</v>
+        <v>-2.9550349601268113</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-78679.881332559497</v>
+        <v>-78405.026054704562</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>1488886.058421023</v>
+        <v>1906020.2617568325</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15" s="312" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
@@ -16535,7 +16535,7 @@
       </c>
       <c r="F15" s="314">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>432</v>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.8099395838685268</v>
+        <v>9.232538014143703</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="C21" s="281">
         <f>I4*(1+D21)</f>
-        <v>8445311.6025161762</v>
+        <v>8826648.526879292</v>
       </c>
       <c r="D21" s="303">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>332473.397313744</v>
+        <v>374314.70393650717</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16684,11 +16684,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>239133.17710545129</v>
+        <v>272333.05914858059</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>3.8753710308859324E-2</v>
+        <v>3.767055025781163E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>222967.99730112008</v>
+        <v>253923.59827373479</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C22" s="281">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>8699934.5630403273</v>
+        <v>9092768.6518904921</v>
       </c>
       <c r="D22" s="303">
         <f t="shared" si="1"/>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>344869.51364022063</v>
+        <v>387964.03309846646</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16733,11 +16733,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>248323.71314168588</v>
+        <v>282517.63964665163</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>3.8432709954678623E-2</v>
+        <v>3.7397518060833246E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>215885.55866719777</v>
+        <v>245612.783800698</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C23" s="281">
         <f t="shared" si="5"/>
-        <v>8962234.3098190855</v>
+        <v>9366912.1983305961</v>
       </c>
       <c r="D23" s="303">
         <f t="shared" si="1"/>
@@ -16774,7 +16774,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>357639.36820000387</v>
+        <v>402024.88438820012</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16782,11 +16782,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>257791.34037413541</v>
+        <v>293009.28140665893</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>3.8126150389220292E-2</v>
+        <v>3.7136236070531181E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>208966.38129958435</v>
+        <v>237514.14277096602</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="C24" s="281">
         <f t="shared" si="5"/>
-        <v>9232442.2950635087</v>
+        <v>9649321.0693304688</v>
       </c>
       <c r="D24" s="303">
         <f t="shared" si="1"/>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G24" s="281">
         <f t="shared" si="8"/>
-        <v>370794.22905991052</v>
+        <v>416509.66504269699</v>
       </c>
       <c r="H24" s="303">
         <f t="shared" si="2"/>
@@ -16839,11 +16839,11 @@
       </c>
       <c r="I24" s="281">
         <f t="shared" si="9"/>
-        <v>267544.41299788898</v>
+        <v>303817.24220987322</v>
       </c>
       <c r="J24" s="303">
         <f t="shared" si="10"/>
-        <v>3.7833204985081359E-2</v>
+        <v>3.6886069790445397E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16851,7 +16851,7 @@
       </c>
       <c r="L24" s="281">
         <f t="shared" si="4"/>
-        <v>202211.88740166169</v>
+        <v>229627.13847779363</v>
       </c>
       <c r="N24" s="279"/>
       <c r="O24" s="279"/>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="C25" s="281">
         <f t="shared" si="5"/>
-        <v>9510796.9491815474</v>
+        <v>9940244.4613091573</v>
       </c>
       <c r="D25" s="303">
         <f t="shared" si="1"/>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="G25" s="281">
         <f t="shared" si="8"/>
-        <v>384345.70401472354</v>
+        <v>431431.15637246298</v>
       </c>
       <c r="H25" s="303">
         <f t="shared" si="2"/>
@@ -16896,11 +16896,11 @@
       </c>
       <c r="I25" s="281">
         <f t="shared" si="9"/>
-        <v>277591.53708386794</v>
+        <v>314951.05895617965</v>
       </c>
       <c r="J25" s="303">
         <f t="shared" si="10"/>
-        <v>3.7553107438869304E-2</v>
+        <v>3.6646428179396562E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="L25" s="281">
         <f t="shared" si="4"/>
-        <v>195622.91108128006</v>
+        <v>221950.72532966008</v>
       </c>
       <c r="N25" s="279"/>
       <c r="O25" s="279"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="C26" s="281">
         <f t="shared" si="5"/>
-        <v>9797543.8911680523</v>
+        <v>10239939.083863787</v>
       </c>
       <c r="D26" s="303">
         <f t="shared" si="1"/>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="G26" s="281">
         <f t="shared" si="8"/>
-        <v>398305.75082986127</v>
+        <v>446802.52503969567</v>
       </c>
       <c r="H26" s="303">
         <f t="shared" si="2"/>
@@ -16953,11 +16953,11 @@
       </c>
       <c r="I26" s="281">
         <f t="shared" si="9"/>
-        <v>287941.57817278628</v>
+        <v>326420.55607939838</v>
       </c>
       <c r="J26" s="303">
         <f t="shared" si="10"/>
-        <v>3.7285146361617283E-2</v>
+        <v>3.6416759991953374E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="L26" s="281">
         <f t="shared" si="4"/>
-        <v>189199.75753159091</v>
+        <v>214483.4047776506</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="C27" s="281">
         <f t="shared" si="5"/>
-        <v>10092936.145337958</v>
+        <v>10548669.386289045</v>
       </c>
       <c r="D27" s="303">
         <f t="shared" si="1"/>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="G27" s="281">
         <f t="shared" si="8"/>
-        <v>412686.68779286148</v>
+        <v>462637.33467649494</v>
       </c>
       <c r="H27" s="303">
         <f t="shared" si="2"/>
@@ -17002,11 +17002,11 @@
       </c>
       <c r="I27" s="281">
         <f t="shared" si="9"/>
-        <v>298603.66909806867</v>
+        <v>338235.85421632626</v>
       </c>
       <c r="J27" s="303">
         <f t="shared" si="10"/>
-        <v>3.7028660441960737E-2</v>
+        <v>3.619655048334014E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -17014,36 +17014,36 @@
       </c>
       <c r="L27" s="281">
         <f t="shared" si="4"/>
-        <v>182942.2574442233</v>
+        <v>207223.27661214315</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B28" s="117">
         <v>8</v>
       </c>
       <c r="C28" s="281">
         <f t="shared" si="5"/>
-        <v>10294794.868244717</v>
+        <v>10866707.79092614</v>
       </c>
       <c r="D28" s="303">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E28" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.89099809462634716</v>
       </c>
       <c r="F28" s="281">
         <f t="shared" si="7"/>
-        <v>-620958.35556164815</v>
+        <v>-627137.27044160955</v>
       </c>
       <c r="G28" s="281">
         <f t="shared" si="8"/>
-        <v>659274.68571409502</v>
+        <v>478949.55785335309</v>
       </c>
       <c r="H28" s="303">
         <f t="shared" si="2"/>
@@ -17051,11 +17051,11 @@
       </c>
       <c r="I28" s="281">
         <f t="shared" si="9"/>
-        <v>503584.85305811919</v>
+        <v>350407.3791371425</v>
       </c>
       <c r="J28" s="303">
         <f t="shared" si="10"/>
-        <v>0.68646572421295238</v>
+        <v>3.598531843709174E-2</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -17063,36 +17063,36 @@
       </c>
       <c r="L28" s="281">
         <f t="shared" si="4"/>
-        <v>287669.78712337941</v>
+        <v>200168.08597539266</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B29" s="117">
         <v>9</v>
       </c>
       <c r="C29" s="281">
         <f t="shared" si="5"/>
-        <v>10500690.765609611</v>
+        <v>11194334.933547152</v>
       </c>
       <c r="D29" s="303">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>3.0149622951542498E-2</v>
       </c>
       <c r="E29" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.89099809462634716</v>
       </c>
       <c r="F29" s="281">
         <f t="shared" si="7"/>
-        <v>-633377.52267288114</v>
+        <v>-646045.22268428362</v>
       </c>
       <c r="G29" s="281">
         <f t="shared" si="8"/>
-        <v>674033.77705502813</v>
+        <v>495753.58840849495</v>
       </c>
       <c r="H29" s="303">
         <f t="shared" si="2"/>
@@ -17100,11 +17100,11 @@
       </c>
       <c r="I29" s="281">
         <f t="shared" si="9"/>
-        <v>514970.50413753535</v>
+        <v>362945.87094506674</v>
       </c>
       <c r="J29" s="303">
         <f t="shared" si="10"/>
-        <v>2.2609200833334286E-2</v>
+        <v>3.5782613479200975E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="L29" s="281">
         <f t="shared" si="4"/>
-        <v>274287.8984747174</v>
+        <v>193315.26641186164</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="C30" s="281">
         <f t="shared" si="5"/>
-        <v>10710704.580921803</v>
+        <v>11418221.632218095</v>
       </c>
       <c r="D30" s="303">
         <f t="shared" si="1"/>
@@ -17137,11 +17137,11 @@
       </c>
       <c r="F30" s="281">
         <f t="shared" si="7"/>
-        <v>-646045.07312633877</v>
+        <v>-658966.12713796936</v>
       </c>
       <c r="G30" s="281">
         <f t="shared" si="8"/>
-        <v>689088.05022277974</v>
+        <v>769834.10226011451</v>
       </c>
       <c r="H30" s="303">
         <f t="shared" si="2"/>
@@ -17149,11 +17149,11 @@
       </c>
       <c r="I30" s="281">
         <f t="shared" si="9"/>
-        <v>526583.86823853967</v>
+        <v>590782.93250364857</v>
       </c>
       <c r="J30" s="303">
         <f t="shared" si="10"/>
-        <v>2.2551513159873471E-2</v>
+        <v>0.62774391389361162</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="L30" s="281">
         <f t="shared" si="4"/>
-        <v>261513.75816015297</v>
+        <v>293396.50197168294</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="C31" s="281">
         <f t="shared" si="5"/>
-        <v>10924918.672540238</v>
+        <v>11646586.064862456</v>
       </c>
       <c r="D31" s="303">
         <f t="shared" si="1"/>
@@ -17186,11 +17186,11 @@
       </c>
       <c r="F31" s="281">
         <f t="shared" si="7"/>
-        <v>-658965.97458886553</v>
+        <v>-672145.44968072872</v>
       </c>
       <c r="G31" s="281">
         <f t="shared" si="8"/>
-        <v>704443.40885388653</v>
+        <v>786798.88482641091</v>
       </c>
       <c r="H31" s="303">
         <f t="shared" si="2"/>
@@ -17198,11 +17198,11 @@
       </c>
       <c r="I31" s="281">
         <f t="shared" si="9"/>
-        <v>538429.49962156429</v>
+        <v>603907.95508883509</v>
       </c>
       <c r="J31" s="303">
         <f t="shared" si="10"/>
-        <v>2.2495241684195699E-2</v>
+        <v>2.2216319841138032E-2</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="L31" s="281">
         <f t="shared" si="4"/>
-        <v>249320.81431581159</v>
+        <v>279640.73892751231</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="C32" s="281">
         <f t="shared" si="5"/>
-        <v>11143417.045991043</v>
+        <v>11879517.786159705</v>
       </c>
       <c r="D32" s="303">
         <f t="shared" si="1"/>
@@ -17235,11 +17235,11 @@
       </c>
       <c r="F32" s="281">
         <f t="shared" si="7"/>
-        <v>-672145.29408064287</v>
+        <v>-685588.35867434333</v>
       </c>
       <c r="G32" s="281">
         <f t="shared" si="8"/>
-        <v>720105.8746576152</v>
+        <v>804102.96304403327</v>
       </c>
       <c r="H32" s="303">
         <f t="shared" si="2"/>
@@ -17247,11 +17247,11 @@
       </c>
       <c r="I32" s="281">
         <f t="shared" si="9"/>
-        <v>550512.04363224912</v>
+        <v>617295.47812572541</v>
       </c>
       <c r="J32" s="303">
         <f t="shared" si="10"/>
-        <v>2.2440345521887339E-2</v>
+        <v>2.2168151494081689E-2</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="L32" s="281">
         <f t="shared" si="4"/>
-        <v>237683.598633899</v>
+        <v>266517.34936314618</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="C33" s="281">
         <f t="shared" si="5"/>
-        <v>11366285.386910863</v>
+        <v>12117108.1418829</v>
       </c>
       <c r="D33" s="303">
         <f t="shared" si="1"/>
@@ -17284,11 +17284,11 @@
       </c>
       <c r="F33" s="281">
         <f t="shared" si="7"/>
-        <v>-685588.19996225578</v>
+        <v>-699300.1258478302</v>
       </c>
       <c r="G33" s="281">
         <f t="shared" si="8"/>
-        <v>736081.58977741865</v>
+        <v>821753.12282600813</v>
       </c>
       <c r="H33" s="303">
         <f t="shared" si="2"/>
@@ -17296,11 +17296,11 @@
       </c>
       <c r="I33" s="281">
         <f t="shared" si="9"/>
-        <v>562836.23852314777</v>
+        <v>630950.75162335357</v>
       </c>
       <c r="J33" s="303">
         <f t="shared" si="10"/>
-        <v>2.2386785236494067E-2</v>
+        <v>2.2121129963707631E-2</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="L33" s="281">
         <f t="shared" si="4"/>
-        <v>226577.68793543417</v>
+        <v>253998.14851840667</v>
       </c>
       <c r="N33" s="279"/>
       <c r="O33" s="279"/>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="C34" s="281">
         <f t="shared" si="5"/>
-        <v>11593611.09464908</v>
+        <v>12359450.304720558</v>
       </c>
       <c r="D34" s="303">
         <f t="shared" si="1"/>
@@ -17341,11 +17341,11 @@
       </c>
       <c r="F34" s="281">
         <f t="shared" si="7"/>
-        <v>-699299.96396150091</v>
+        <v>-713286.12836478685</v>
       </c>
       <c r="G34" s="281">
         <f t="shared" si="8"/>
-        <v>752376.81919961818</v>
+        <v>839756.28580362245</v>
       </c>
       <c r="H34" s="303">
         <f t="shared" si="2"/>
@@ -17353,11 +17353,11 @@
       </c>
       <c r="I34" s="281">
         <f t="shared" si="9"/>
-        <v>575406.91731186444</v>
+        <v>644879.13059093431</v>
       </c>
       <c r="J34" s="303">
         <f t="shared" si="10"/>
-        <v>2.2334522776467747E-2</v>
+        <v>2.2075223671173871E-2</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="L34" s="281">
         <f t="shared" si="4"/>
-        <v>215979.6666361469</v>
+        <v>242056.14401772915</v>
       </c>
       <c r="N34" s="279"/>
       <c r="O34" s="279"/>
@@ -17386,7 +17386,7 @@
       </c>
       <c r="C35" s="281">
         <f t="shared" si="5"/>
-        <v>11825483.316542063</v>
+        <v>12606639.310814969</v>
       </c>
       <c r="D35" s="303">
         <f t="shared" si="1"/>
@@ -17398,11 +17398,11 @@
       </c>
       <c r="F35" s="281">
         <f t="shared" si="7"/>
-        <v>-713285.96324073093</v>
+        <v>-727551.85093208263</v>
       </c>
       <c r="G35" s="281">
         <f t="shared" si="8"/>
-        <v>768997.953210262</v>
+        <v>858119.51204078877</v>
       </c>
       <c r="H35" s="303">
         <f t="shared" si="2"/>
@@ -17410,11 +17410,11 @@
       </c>
       <c r="I35" s="281">
         <f t="shared" si="9"/>
-        <v>588229.00967635564</v>
+        <v>659086.07713786629</v>
       </c>
       <c r="J35" s="303">
         <f t="shared" si="10"/>
-        <v>2.2283521415405128E-2</v>
+        <v>2.2030402090874812E-2</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="L35" s="281">
         <f t="shared" si="4"/>
-        <v>205867.09012860191</v>
+        <v>230665.49016224375</v>
       </c>
       <c r="N35" s="279"/>
       <c r="O35" s="279"/>
@@ -17436,30 +17436,30 @@
     <row r="36" spans="1:21">
       <c r="A36" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B36" s="117">
         <v>16</v>
       </c>
       <c r="C36" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12858772.097031269</v>
       </c>
       <c r="D36" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E36" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F36" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-742102.88795072434</v>
       </c>
       <c r="G36" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>876850.00280269876</v>
       </c>
       <c r="H36" s="303">
         <f t="shared" si="2"/>
@@ -17467,48 +17467,48 @@
       </c>
       <c r="I36" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>673577.1626157373</v>
       </c>
       <c r="J36" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.1986635707432534E-2</v>
       </c>
       <c r="K36" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.32631961978921564</v>
       </c>
       <c r="L36" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>219801.44360346606</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B37" s="117">
         <v>17</v>
       </c>
       <c r="C37" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13115947.538971895</v>
       </c>
       <c r="D37" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E37" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F37" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-756944.94570973888</v>
       </c>
       <c r="G37" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>895955.10337984678</v>
       </c>
       <c r="H37" s="303">
         <f t="shared" si="2"/>
@@ -17516,48 +17516,48 @@
       </c>
       <c r="I37" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>688358.0698031655</v>
       </c>
       <c r="J37" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.1943895974781524E-2</v>
       </c>
       <c r="K37" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.30426071775218239</v>
       </c>
       <c r="L37" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>209440.32038881801</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B38" s="117">
         <v>18</v>
       </c>
       <c r="C38" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13378266.489751333</v>
       </c>
       <c r="D38" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E38" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F38" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-772083.84462393366</v>
       </c>
       <c r="G38" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>915442.30596853781</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="2"/>
@@ -17565,48 +17565,48 @@
       </c>
       <c r="I38" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>703434.59513434244</v>
       </c>
       <c r="J38" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.1902155277249813E-2</v>
       </c>
       <c r="K38" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.28369297692511181</v>
       </c>
       <c r="L38" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>199559.45436577237</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B39" s="117">
         <v>19</v>
       </c>
       <c r="C39" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13645831.819546361</v>
       </c>
       <c r="D39" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E39" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F39" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-787525.52151641238</v>
       </c>
       <c r="G39" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>935319.25260900275</v>
       </c>
       <c r="H39" s="303">
         <f t="shared" si="2"/>
@@ -17614,48 +17614,48 @@
       </c>
       <c r="I39" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>718812.65097214293</v>
       </c>
       <c r="J39" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.1861386892499279E-2</v>
       </c>
       <c r="K39" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.26451559620057047</v>
       </c>
       <c r="L39" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>190137.15692840895</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B40" s="117">
         <v>20</v>
       </c>
       <c r="C40" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13918748.455937289</v>
       </c>
       <c r="D40" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E40" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F40" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-803276.0319467407</v>
       </c>
       <c r="G40" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>955593.73818227684</v>
       </c>
       <c r="H40" s="303">
         <f t="shared" si="2"/>
@@ -17663,19 +17663,19 @@
       </c>
       <c r="I40" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>734498.26792669925</v>
       </c>
       <c r="J40" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.1821564956240769E-2</v>
       </c>
       <c r="K40" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.2466345885320004</v>
       </c>
       <c r="L40" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>181152.67808756846</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -18206,11 +18206,11 @@
       </c>
       <c r="B51" s="320">
         <f>C15+1</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C51" s="281">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>11825483.316542063</v>
+        <v>13918748.455937289</v>
       </c>
       <c r="D51" s="305">
         <f>Terminal_Growth</f>
@@ -18222,11 +18222,11 @@
       </c>
       <c r="F51" s="281">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-713285.96324073093</v>
+        <v>-803276.0319467407</v>
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>768997.953210262</v>
+        <v>955593.73818227684</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>8113503.5817428371</v>
+        <v>10131010.592092404</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18242,11 +18242,11 @@
       </c>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.34997779222393377</v>
+        <v>0.2466345885320004</v>
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>2839546.0707393372</v>
+        <v>2498657.628794048</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18259,7 +18259,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>6216243.1228741389</v>
+        <v>7068841.4775587041</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18283,7 +18283,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>6216243.1228741389</v>
+        <v>7068841.4775587041</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18318,19 +18318,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>5322146.0032817367</v>
+        <v>5868845.4418163244</v>
       </c>
       <c r="C56" s="118">
-        <v>5322146.0032817367</v>
+        <v>5868845.4418163244</v>
       </c>
       <c r="D56" s="118">
-        <v>5322146.0032817367</v>
+        <v>5868845.4418163244</v>
       </c>
       <c r="E56" s="118">
-        <v>5322146.0032817367</v>
+        <v>5868845.4418163244</v>
       </c>
       <c r="F56" s="118">
-        <v>5322146.0032817367</v>
+        <v>5868845.4418163244</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18344,19 +18344,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>5441083.9420132637</v>
+        <v>5998045.2832838027</v>
       </c>
       <c r="C57" s="118">
-        <v>5441083.9420132637</v>
+        <v>5998045.2832838027</v>
       </c>
       <c r="D57" s="118">
-        <v>5441083.9420132637</v>
+        <v>5998045.2832838027</v>
       </c>
       <c r="E57" s="118">
-        <v>5441083.9420132637</v>
+        <v>5998045.2832838027</v>
       </c>
       <c r="F57" s="118">
-        <v>5441083.9420132637</v>
+        <v>5998045.2832838027</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18370,19 +18370,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>5490862.7347770724</v>
+        <v>6052058.5955419457</v>
       </c>
       <c r="C58" s="118">
-        <v>5554199.7438838035</v>
+        <v>6120920.6569871418</v>
       </c>
       <c r="D58" s="118">
-        <v>5617536.7529905308</v>
+        <v>6189782.718432337</v>
       </c>
       <c r="E58" s="118">
-        <v>5680873.7620972618</v>
+        <v>6258644.7798775379</v>
       </c>
       <c r="F58" s="118">
-        <v>5744210.7712039873</v>
+        <v>6327506.8413227359</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18396,19 +18396,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>5597386.7067017779</v>
+        <v>6167773.3996821512</v>
       </c>
       <c r="C59" s="118">
-        <v>5661778.4085998451</v>
+        <v>6237781.1522574499</v>
       </c>
       <c r="D59" s="118">
-        <v>5726170.1104979031</v>
+        <v>6307788.9048327459</v>
       </c>
       <c r="E59" s="118">
-        <v>5790561.8123959685</v>
+        <v>6377796.6574080484</v>
       </c>
       <c r="F59" s="118">
-        <v>5854953.5142940283</v>
+        <v>6447804.409983349</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18422,19 +18422,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>5497056.4488840643</v>
+        <v>6064528.6063984428</v>
       </c>
       <c r="C60" s="118">
-        <v>5621694.4424392562</v>
+        <v>6200094.9329497013</v>
       </c>
       <c r="D60" s="118">
-        <v>5747533.213652215</v>
+        <v>6336966.7653764896</v>
       </c>
       <c r="E60" s="118">
-        <v>5874572.7625229498</v>
+        <v>6475144.103678802</v>
       </c>
       <c r="F60" s="118">
-        <v>6002813.0890514571</v>
+        <v>6614626.9478566507</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18448,19 +18448,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>5592462.1429429594</v>
+        <v>6168165.8535120673</v>
       </c>
       <c r="C61" s="118">
-        <v>5718998.710745181</v>
+        <v>6305794.5622968376</v>
       </c>
       <c r="D61" s="118">
-        <v>5846754.7613701653</v>
+        <v>6444749.0959939221</v>
       </c>
       <c r="E61" s="118">
-        <v>5975730.2948179226</v>
+        <v>6585029.4546033144</v>
       </c>
       <c r="F61" s="118">
-        <v>6105925.3110884447</v>
+        <v>6726635.6381250275</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18474,19 +18474,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>5492418.8643652732</v>
+        <v>6064898.1899585528</v>
       </c>
       <c r="C62" s="118">
-        <v>5676113.7507732855</v>
+        <v>6264779.0152249224</v>
       </c>
       <c r="D62" s="118">
-        <v>5863339.45178595</v>
+        <v>6468499.6296151876</v>
       </c>
       <c r="E62" s="118">
-        <v>6054130.0788109051</v>
+        <v>6676097.1191408839</v>
       </c>
       <c r="F62" s="118">
-        <v>6248519.7432557773</v>
+        <v>6887608.5698135383</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18500,19 +18500,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>5577866.7339330092</v>
+        <v>6157718.4567264616</v>
       </c>
       <c r="C63" s="118">
-        <v>5764124.8880702872</v>
+        <v>6360383.7071122844</v>
       </c>
       <c r="D63" s="118">
-        <v>5953964.6129467599</v>
+        <v>6566943.8819691092</v>
       </c>
       <c r="E63" s="118">
-        <v>6147420.5175792277</v>
+        <v>6777436.6078510936</v>
       </c>
       <c r="F63" s="118">
-        <v>6344527.2109844796</v>
+        <v>6991899.5113123851</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18526,19 +18526,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>5478674.0036659241</v>
+        <v>6055059.6158294491</v>
       </c>
       <c r="C64" s="118">
-        <v>5719030.9543831721</v>
+        <v>6316695.9641403118</v>
       </c>
       <c r="D64" s="118">
-        <v>5966300.8943257071</v>
+        <v>6585852.19796432</v>
       </c>
       <c r="E64" s="118">
-        <v>6220617.567549143</v>
+        <v>6862673.7525932696</v>
       </c>
       <c r="F64" s="118">
-        <v>6482116.0088882605</v>
+        <v>7147307.4666403215</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18552,19 +18552,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>5555203.3815577477</v>
+        <v>6138191.9081550092</v>
       </c>
       <c r="C65" s="118">
-        <v>5798636.5094443168</v>
+        <v>6403169.8445818331</v>
       </c>
       <c r="D65" s="118">
-        <v>6049074.4452762417</v>
+        <v>6675767.4073126987</v>
       </c>
       <c r="E65" s="118">
-        <v>6306652.7422725484</v>
+        <v>6956131.9968964783</v>
       </c>
       <c r="F65" s="118">
-        <v>6571508.2620817916</v>
+        <v>7244412.4363766424</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18578,19 +18578,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>5396961.8185033593</v>
+        <v>5979861.5836562309</v>
       </c>
       <c r="C66" s="281">
-        <v>5792108.8893085411</v>
+        <v>6410464.0632768515</v>
       </c>
       <c r="D66" s="118">
-        <v>6209816.4225565288</v>
+        <v>6865625.8549388181</v>
       </c>
       <c r="E66" s="118">
-        <v>6651179.8059659954</v>
+        <v>7346538.7647476587</v>
       </c>
       <c r="F66" s="118">
-        <v>7117337.0643130448</v>
+        <v>7854440.974044906</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18613,19 +18613,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>5364061.1430426184</v>
+        <v>5951898.8282217141</v>
       </c>
       <c r="C67" s="281">
-        <v>5853599.8591909334</v>
+        <v>6485715.1590054734</v>
       </c>
       <c r="D67" s="118">
-        <v>6380231.8284840696</v>
+        <v>7059929.3351791268</v>
       </c>
       <c r="E67" s="118">
-        <v>6946485.60456766</v>
+        <v>7677293.4042476285</v>
       </c>
       <c r="F67" s="118">
-        <v>7555038.2205814561</v>
+        <v>8340720.9542961139</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18648,19 +18648,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>5187075.0610776981</v>
+        <v>5769689.0023798207</v>
       </c>
       <c r="C68" s="281">
-        <v>5789247.4213424828</v>
+        <v>6427002.8823416922</v>
       </c>
       <c r="D68" s="118">
-        <v>6453576.1043743286</v>
+        <v>7152058.4742696658</v>
       </c>
       <c r="E68" s="118">
-        <v>7186133.2801278103</v>
+        <v>7951468.1674427968</v>
       </c>
       <c r="F68" s="118">
-        <v>7993530.2762442231</v>
+        <v>8832431.1842891984</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18683,19 +18683,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>5118927.8479986088</v>
+        <v>5701421.8997263089</v>
       </c>
       <c r="C69" s="281">
-        <v>5790972.7175897965</v>
+        <v>6435455.3327843975</v>
       </c>
       <c r="D69" s="118">
-        <v>6544533.1775393505</v>
+        <v>7258366.806684792</v>
       </c>
       <c r="E69" s="118">
-        <v>7389189.0565219279</v>
+        <v>8180591.7129682312</v>
       </c>
       <c r="F69" s="118">
-        <v>8335565.6915554032</v>
+        <v>9213703.6846195087</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>6.2684035449417044</v>
+        <v>7.1635937181264051</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.2684035449417044</v>
+        <v>7.1635937181264051</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.2684035449417044</v>
+        <v>7.1635937181264051</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>6.2684035449417044</v>
+        <v>7.1635937181264051</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>6.2684035449417044</v>
+        <v>7.1635937181264051</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18854,23 +18854,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>6.4734675306459675</v>
+        <v>7.3863505165562495</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>6.4734675306459675</v>
+        <v>7.3863505165562495</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>6.4734675306459675</v>
+        <v>7.3863505165562495</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>6.4734675306459675</v>
+        <v>7.3863505165562495</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.4734675306459675</v>
+        <v>7.3863505165562495</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>6.5592924386320961</v>
+        <v>7.4794762694562182</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>6.6684934191479179</v>
+        <v>7.5982031360419819</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7776943996637335</v>
+        <v>7.7169300026277448</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.8868953801795554</v>
+        <v>7.8356568692135173</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.9960963606953674</v>
+        <v>7.9543837357992846</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7429531821164534</v>
+        <v>7.6789831651956915</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>6.8539725858350948</v>
+        <v>7.7996853475808594</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.9649919895537202</v>
+        <v>7.920387529966022</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>7.0760113932723581</v>
+        <v>8.0410897123511962</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>7.187030796990987</v>
+        <v>8.1617918947363659</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18947,23 +18947,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>6.5699711818038571</v>
+        <v>7.5009761386760871</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>6.7848627799027819</v>
+        <v>7.7347095592008701</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>7.0018246699125335</v>
+        <v>7.9706938362736262</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>7.2208568518331298</v>
+        <v>8.2089289698943482</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>7.4419593256645609</v>
+        <v>8.4494149600630557</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18978,23 +18978,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>6.7344626139848032</v>
+        <v>7.6796598050250502</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>6.952627593196631</v>
+        <v>7.9169490322618037</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>7.1728951143795134</v>
+        <v>8.1565241486249747</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>7.3952651775334663</v>
+        <v>8.3983851541145569</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.6197377826584747</v>
+        <v>8.642532048730569</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19010,23 +19010,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>6.5619754020248715</v>
+        <v>7.5016133472799638</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>6.8786885211697033</v>
+        <v>7.8462330635128161</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>7.2014892093722702</v>
+        <v>8.1974730597875745</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>7.5304362789954142</v>
+        <v>8.5553972770588302</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.865588542401956</v>
+        <v>8.9200696562811554</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19041,23 +19041,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>6.7092982906706062</v>
+        <v>7.6616471771962953</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>7.0304308062048184</v>
+        <v>8.0110675930123065</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>7.3577384007650659</v>
+        <v>8.3672033491525131</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>7.6912807446550575</v>
+        <v>8.7301193185350652</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>8.0311175081784789</v>
+        <v>9.0998803740780883</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19073,23 +19073,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>6.5382775311182586</v>
+        <v>7.4846504063876136</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9526831852893691</v>
+        <v>7.9357444219888169</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>7.3790077035234258</v>
+        <v>8.3998036672872161</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>7.8174816774163567</v>
+        <v>8.8770788910423413</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>8.2683379240299324</v>
+        <v>9.367823261516488</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19105,23 +19105,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>6.6702238168983499</v>
+        <v>7.6279809482384486</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>7.0899331879305496</v>
+        <v>8.0848362825992428</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>7.5217197300629639</v>
+        <v>8.5548288123423344</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.9658171541170937</v>
+        <v>9.0382126745779612</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.4224614268117346</v>
+        <v>9.535244458976198</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19137,23 +19137,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>6.3973954328681506</v>
+        <v>7.3549995282992908</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>7.0786787487122345</v>
+        <v>8.0974124342809652</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>7.7988591431268164</v>
+        <v>8.8821686872809629</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.5598252024946575</v>
+        <v>9.71132311112415</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.3635390248553545</v>
+        <v>10.58701048638288</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19169,23 +19169,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>6.3406705247833459</v>
+        <v>7.3067882162332642</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>7.1846969251106598</v>
+        <v>8.2271548006217543</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>8.0926767654734881</v>
+        <v>9.2171723582645892</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.0689695908090489</v>
+        <v>10.281585765659813</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.118190943402293</v>
+        <v>11.425418415610515</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19201,23 +19201,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>6.03552422942143</v>
+        <v>6.9926355285365336</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>7.0737452175585664</v>
+        <v>8.125927441287546</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>8.2191315342634468</v>
+        <v>9.3760145970228486</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.4821523652815003</v>
+        <v>10.754297587639796</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>10.874206472112879</v>
+        <v>12.273188779291909</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19233,23 +19233,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.918029851448563</v>
+        <v>6.8749344458381803</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>7.0767198455769105</v>
+        <v>8.1405005303727815</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>8.3759529837533027</v>
+        <v>9.5593035508345281</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.8322460971195973</v>
+        <v>11.149335436498054</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.463918604875204</v>
+        <v>12.930550588240417</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19292,11 +19292,11 @@
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>9.3635390248553545</v>
+        <v>11.425418415610515</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19320,11 +19320,11 @@
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>8.5598252024946575</v>
+        <v>10.281585765659813</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19348,11 +19348,11 @@
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>7.7988591431268164</v>
+        <v>9.2171723582645892</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19376,11 +19376,11 @@
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>7.0786787487122345</v>
+        <v>8.2271548006217543</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19404,11 +19404,11 @@
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>6.3973954328681506</v>
+        <v>7.3067882162332642</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>289000.65016124537</v>
+        <v>290217.63448334695</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19630,7 +19630,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>230211.62257446788</v>
+        <v>262446.55308076233</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.62894902211793369</v>
+        <v>0.62483362929826525</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19716,7 +19716,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" s="455" t="s">
         <v>548</v>
@@ -19764,11 +19764,11 @@
       </c>
       <c r="D22" s="329">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>8.5598252024946575</v>
+        <v>10.281585765659813</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19788,11 +19788,11 @@
       </c>
       <c r="D23" s="329">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>7.7988591431268164</v>
+        <v>9.2171723582645892</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19811,11 +19811,11 @@
       </c>
       <c r="D24" s="329">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>7.0786787487122345</v>
+        <v>8.2271548006217543</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>7.8070162761174675</v>
+        <v>9.2320515282150666</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19874,11 +19874,11 @@
       </c>
       <c r="D29" s="329">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>9.3635390248553545</v>
+        <v>11.425418415610515</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19897,11 +19897,11 @@
       </c>
       <c r="D30" s="329">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>6.3973954328681506</v>
+        <v>7.3067882162332642</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.51</v>
+        <v>6.27</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1207769498377638</v>
+        <v>0.19480295483917651</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19966,7 +19966,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.56386844863399943</v>
+        <v>0.50264149520909396</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>7.8143613713918958</v>
+        <v>9.245456706985749</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20062,7 +20062,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.8099395838685268</v>
+        <v>9.232538014143703</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20143,14 +20143,14 @@
       </c>
       <c r="C53" s="217" t="str">
         <f>IF(F53&gt;50%,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E53" s="126" t="s">
         <v>273</v>
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.56971924129009388</v>
+        <v>0.47640734901197879</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20228,11 +20228,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.6010881895815197</v>
+        <v>4.2605791276432035</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>4.333028820025568</v>
+        <v>4.9925197580872513</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.44550442267891077</v>
+        <v>0.46000290560930679</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20253,11 +20253,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.513710539432144</v>
+        <v>5.340336004035092</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>5.3553121183397749</v>
+        <v>6.181937582942723</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20265,7 +20265,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.31468332934468768</v>
+        <v>0.33135400674455273</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20299,11 +20299,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.6010247277185474</v>
+        <v>6.6267771829004483</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>6.5660659780940076</v>
+        <v>7.5918184332759076</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20311,7 +20311,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.15974375050888412</v>
+        <v>0.17885955514348728</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20324,11 +20324,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.3343431768387548</v>
+        <v>7.4943930572565609</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>7.3792932677079612</v>
+        <v>8.5393431481257664</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>5.567545228669657E-2</v>
+        <v>7.6374113387654763E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20447,7 +20447,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.51</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20465,14 +20465,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3775.8262548299999</v>
+        <v>3636.6252869099999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.1207769498377638</v>
+        <v>0.19480295483917651</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>7.8143613713918958</v>
+        <v>9.245456706985749</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="C19" s="356" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v>Low Growth Asset Play</v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="347" t="s">
         <v>363</v>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>4.333028820025568</v>
+        <v>4.9925197580872513</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>5.3553121183397749</v>
+        <v>6.181937582942723</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>6.5660659780940076</v>
+        <v>7.5918184332759076</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>7.3792932677079612</v>
+        <v>8.5393431481257664</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C34" s="377">
         <f>Normalized_FCF!C8</f>
-        <v>399119.96227138769</v>
+        <v>439469.87884546071</v>
       </c>
       <c r="D34" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20795,7 +20795,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>6692.5186674405113</v>
+        <v>6967.3739452954487</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-78679.881332559497</v>
+        <v>-78405.026054704562</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="C49" s="377">
         <f>Normalized_FCF!C13</f>
-        <v>-37355.845009453624</v>
+        <v>-39042.598999519083</v>
       </c>
       <c r="D49" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-52872.613354906651</v>
+        <v>-59575.700710474768</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>289000.65016124537</v>
+        <v>290217.63448334695</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20931,7 +20931,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>230211.62257446788</v>
+        <v>262446.55308076233</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>6.0969866470943525E-2</v>
+        <v>7.216760935624475E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20954,14 +20954,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.1443932411674354E-2</v>
+        <v>6.3795853269537489E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>1.0077754137932506</v>
+        <v>0.88399565731239171</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20981,11 +20981,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.1167471410506614</v>
+        <v>0.13154811711973616</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>0.11792742550148552</v>
+        <v>0.11837081398114316</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20995,11 +20995,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>3.9086921133773919E-2</v>
+        <v>4.2139530177368108E-2</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>3.7776339292914275E-2</v>
+        <v>3.791837235752913E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="C68" s="388">
         <f>Normalized_FCF!C117</f>
-        <v>1.3708738209065539</v>
+        <v>1.4327738230803833</v>
       </c>
       <c r="D68" s="388">
         <f>Normalized_FCF!G117</f>
@@ -21117,7 +21117,7 @@
       </c>
       <c r="C81" s="393">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>5.3475400925918697</v>
+        <v>4.8565558249568426</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>384381.13325594889</v>
+        <v>356895.60547045514</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.66272148362104388</v>
+        <v>0.61533297212513538</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-2.9076464486309033</v>
+        <v>-2.9550349601268113</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>2.5670270786220946</v>
+        <v>3.2862189800615274</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21419,11 +21419,11 @@
       </c>
       <c r="D118" s="401">
         <f>DCF!D90</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>9.36 HKD</v>
+        <v>11.43 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21442,11 +21442,11 @@
       </c>
       <c r="D119" s="406">
         <f>DCF!D91</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>8.56 HKD</v>
+        <v>10.28 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21464,11 +21464,11 @@
       </c>
       <c r="D120" s="406">
         <f>DCF!D92</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>7.8 HKD</v>
+        <v>9.22 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21486,11 +21486,11 @@
       </c>
       <c r="D121" s="406">
         <f>DCF!D93</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>7.08 HKD</v>
+        <v>8.23 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21508,11 +21508,11 @@
       </c>
       <c r="D122" s="406">
         <f>DCF!D94</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>6.4 HKD</v>
+        <v>7.31 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21534,7 +21534,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>7.8143613713918958</v>
+        <v>9.245456706985749</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21641,11 +21641,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>3.6010881895815197</v>
+        <v>4.2605791276432035</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>4.333028820025568</v>
+        <v>4.9925197580872513</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21662,11 +21662,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>4.513710539432144</v>
+        <v>5.340336004035092</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>5.3553121183397749</v>
+        <v>6.181937582942723</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21702,11 +21702,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>5.6010247277185474</v>
+        <v>6.6267771829004483</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>6.5660659780940076</v>
+        <v>7.5918184332759076</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21723,11 +21723,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>6.3343431768387548</v>
+        <v>7.4943930572565609</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>7.3792932677079612</v>
+        <v>8.5393431481257664</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2526484-518A-40DB-87E1-E607066F7F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7247D33B-698B-4F72-94A0-DD2881351624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.27</v>
+        <v>6.18</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3636.6252869099999</v>
+        <v>3584.4249239400001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.19480295483917651</v>
+        <v>0.16611853030232007</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,18 +5423,18 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
-        <v>2-stage DCF Valuation Conclusion</v>
+        <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>9.245456706985749</v>
+        <v>8.3894050049409827</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>348</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>4.9925197580872513</v>
+        <v>4.5980258861772203</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>6.181937582942723</v>
+        <v>5.6874672857327493</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>7.5918184332759076</v>
+        <v>6.9782344788773099</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>8.5393431481257664</v>
+        <v>7.8454252449020769</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C34" s="289">
         <f>Normalized_FCF!C8</f>
-        <v>439469.87884546071</v>
+        <v>533705.04</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>6967.3739452954487</v>
+        <v>6888.8446443333341</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-78405.026054704562</v>
+        <v>-78483.555355666671</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-59575.700710474768</v>
+        <v>-75111.544966315007</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>290217.63448334695</v>
+        <v>289869.92812368623</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>262446.55308076233</v>
+        <v>341067.34067849925</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.216760935624475E-2</v>
+        <v>9.5152597115522236E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,14 +5890,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.3795853269537489E-2</v>
+        <v>6.4724919093851141E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.88399565731239171</v>
+        <v>0.68022230665202266</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5917,11 +5917,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.13154811711973616</v>
+        <v>0.1658525572748466</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.11837081398114316</v>
+        <v>0.11824413281411626</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>4.2139530177368108E-2</v>
+        <v>5.3128459724860015E-2</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>3.791837235752913E-2</v>
+        <v>3.7877791884180549E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C81" s="342">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>4.8565558249568426</v>
+        <v>3.999044116203212</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>356895.60547045514</v>
+        <v>364748.53556666663</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.61533297212513538</v>
+        <v>0.62887241262797666</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-2.9550349601268113</v>
+        <v>-2.9414955196239703</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6337,15 +6337,15 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (20yrs)</v>
+        <v>Snowball Scenario (30yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>11.43 HKD</v>
+        <v>12.86 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,21 +6353,21 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-3.0574909747230136E-2</v>
+        <v>-9.6804914114679869E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (20yrs)</v>
+        <v>Optimistic (30yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>10.28 HKD</v>
+        <v>10.31 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,21 +6375,21 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>5.496734932037171E-3</v>
+        <v>-2.4979569163920998E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (20yrs)</v>
+        <v>Base (30yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>9.22 HKD</v>
+        <v>8.24 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,21 +6397,21 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>4.4376065079678513E-2</v>
+        <v>5.4111240073368816E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (20yrs)</v>
+        <v>Pessimistic (30yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>8.23 HKD</v>
+        <v>6.55 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,21 +6419,21 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>8.6505401148917249E-2</v>
+        <v>0.14222478353438384</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (20yrs)</v>
+        <v>Devil's advocate (30yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>7.31 HKD</v>
+        <v>5.17 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.13244054457715634</v>
+        <v>0.2419679577668665</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>9.245456706985749</v>
+        <v>8.3894050049409827</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>4.2605791276432035</v>
+        <v>3.8660852557331729</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>4.9925197580872513</v>
+        <v>4.5980258861772203</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>5.340336004035092</v>
+        <v>4.8458657068251183</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>6.181937582942723</v>
+        <v>5.6874672857327493</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>6.6267771829004483</v>
+        <v>6.0131932285018506</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>7.5918184332759076</v>
+        <v>6.9782344788773099</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>7.4943930572565609</v>
+        <v>6.8004751540328705</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>8.5393431481257664</v>
+        <v>7.8454252449020769</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
-        <v>4.8565558249568426</v>
+        <v>3.999044116203212</v>
       </c>
       <c r="D50" s="92">
         <f>G31/Normalized_FCF!G8</f>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
-        <v>9.7971085702254657E-2</v>
+        <v>0.11897894424739897</v>
       </c>
       <c r="D54" s="89">
         <f>Normalized_FCF!G8/G35</f>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>356895.60547045514</v>
+        <v>364748.53556666663</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-696737.39452954486</v>
+        <v>-688884.46443333337</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.5122383386805875</v>
+        <v>1.5294770812790845</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10473,7 +10473,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>696737.39452954486</v>
+        <v>688884.46443333337</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10605,11 +10605,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>356895.60547045514</v>
+        <v>364748.53556666663</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.61533297212513538</v>
+        <v>0.62887241262797666</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10639,11 +10639,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2554687.8054704554</v>
+        <v>2562540.7355666668</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>4.4046035201800997</v>
+        <v>4.4181429606829417</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="C5" s="270">
         <f>C26</f>
-        <v>-7634354.1211545393</v>
+        <v>-7540118.96</v>
       </c>
       <c r="E5" s="238"/>
       <c r="G5" s="274">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="C6" s="271">
         <f>C4+C5</f>
-        <v>933962.87884546071</v>
+        <v>1028198.04</v>
       </c>
       <c r="E6" s="238"/>
       <c r="G6" s="271">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="C8" s="272">
         <f>C6+C7</f>
-        <v>439469.87884546071</v>
+        <v>533705.04</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="244"/>
@@ -11124,24 +11124,24 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-78405.026054704562</v>
+        <v>-78483.555355666671</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>-73265.365516653022</v>
+        <v>-73613.071876313799</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-78633.759396519948</v>
+        <v>-78971.418852021772</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>-72819.588982796442</v>
+        <v>-73109.123171121537</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>-82979.322161794684</v>
+        <v>-83036.406166952918</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
@@ -11179,24 +11179,24 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>361064.85279075615</v>
+        <v>455221.48464433337</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>324896.63448334695</v>
+        <v>324548.92812368623</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>407439.24060348002</v>
+        <v>407101.5811479782</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>143750.41101720356</v>
+        <v>143460.87682887848</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>5898.6778382053162</v>
+        <v>5841.5938330470817</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-59575.700710474768</v>
+        <v>-75111.544966315007</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11346,26 +11346,26 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>262446.55308076233</v>
+        <v>341067.34067849925</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>290217.63448334695</v>
+        <v>289869.92812368623</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>348365.24060348002</v>
+        <v>348027.5811479782</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>109927.41101720356</v>
+        <v>109637.87682887848</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>-23676.322161794684</v>
+        <v>-23733.406166952918</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
@@ -11564,26 +11564,26 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>262446.55308076233</v>
+        <v>341067.34067849925</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>290217.63448334695</v>
+        <v>289869.92812368623</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>348365.24060348002</v>
+        <v>348027.5811479782</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>109927.41101720356</v>
+        <v>109637.87682887848</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>-23676.322161794684</v>
+        <v>-23733.406166952918</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="C23" s="278">
         <f>-C4*C29</f>
-        <v>-7634354.1211545393</v>
+        <v>-7540118.96</v>
       </c>
       <c r="D23" s="55"/>
       <c r="E23" s="237"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C26" s="271">
         <f>SUM(C23:C25)</f>
-        <v>-7634354.1211545393</v>
+        <v>-7540118.96</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="243"/>
@@ -11922,8 +11922,7 @@
         <v>40</v>
       </c>
       <c r="C29" s="60">
-        <f>AVERAGE(G29:H29)</f>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="236"/>
@@ -12094,7 +12093,7 @@
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="E32" s="238"/>
       <c r="G32" s="29">
@@ -12302,19 +12301,19 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>9.9453169317628612E-2</v>
+        <v>9.9559718735801314E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.13821201884382026</v>
+        <v>0.13832665508496433</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>0.22948803948847138</v>
+        <v>0.22995119456400367</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.7364851524931719</v>
+        <v>4.7827700450420583</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
@@ -12440,24 +12439,24 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>6967.3739452954487</v>
+        <v>6888.8446443333341</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>30849.634483346978</v>
+        <v>30501.928123686208</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>29958.240603480055</v>
+        <v>29620.581147978221</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>25688.411017203551</v>
+        <v>25398.876828878463</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>5064.677838205318</v>
+        <v>5007.5938330470863</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
@@ -12552,24 +12551,24 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-78405.026054704562</v>
+        <v>-78483.555355666671</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-73265.365516653022</v>
+        <v>-73613.071876313799</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>-78633.759396519948</v>
+        <v>-78971.418852021772</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>-72819.588982796442</v>
+        <v>-73109.123171121537</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>-82979.322161794684</v>
+        <v>-83036.406166952918</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
@@ -12669,7 +12668,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>5.1476809700261521</v>
+        <v>6.2514939254372601</v>
       </c>
       <c r="E53" s="238"/>
       <c r="G53" s="40">
@@ -13232,7 +13231,7 @@
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="235"/>
@@ -13289,7 +13288,7 @@
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
-        <v>0.10900190537365281</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="235"/>
@@ -13403,7 +13402,7 @@
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
-        <v>5.1290105028264095E-2</v>
+        <v>6.2288199654611291E-2</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="235"/>
@@ -13517,7 +13516,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>9.1505748508959889E-3</v>
+        <v>9.159739929751276E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235" t="s">
@@ -13526,19 +13525,19 @@
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>8.5507300344575283E-3</v>
+        <v>8.5913105078061179E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>9.0472554572338798E-3</v>
+        <v>9.086105073161193E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>9.0751731898275293E-3</v>
+        <v>9.1112565149345567E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>1.1051012353422025E-2</v>
+        <v>1.1058614681685883E-2</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
@@ -13576,26 +13575,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>4.2139530177368108E-2</v>
+        <v>5.3128459724860015E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>3.791837235752913E-2</v>
+        <v>3.7877791884180549E-2</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>4.6878171936978519E-2</v>
+        <v>4.6839322321051209E-2</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>1.79149579709687E-2</v>
+        <v>1.7878874645861673E-2</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>7.8557356170929E-4</v>
+        <v>7.7797123344543119E-4</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
@@ -13633,7 +13632,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>6.9530224792657379E-3</v>
+        <v>8.7661958546019023E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13748,26 +13747,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>3.0629883684364423E-2</v>
+        <v>3.9805639856520164E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>3.3871019767749831E-2</v>
+        <v>3.383043929440125E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>4.0081376604002399E-2</v>
+        <v>4.0042526988075082E-2</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>1.3699751773196104E-2</v>
+        <v>1.3663668448089078E-2</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>3.1531630034700416E-3</v>
+        <v>3.1607653317339002E-3</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
@@ -13969,26 +13968,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>3.0629883684364423E-2</v>
+        <v>3.9805639856520164E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>3.3871019767749831E-2</v>
+        <v>3.383043929440125E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>4.0081376604002399E-2</v>
+        <v>4.0042526988075082E-2</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>1.3699751773196104E-2</v>
+        <v>1.3663668448089078E-2</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>3.1531630034700416E-3</v>
+        <v>3.1607653317339002E-3</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
@@ -14149,24 +14148,24 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.88399565731239171</v>
+        <v>0.68022230665202266</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.79940563781734142</v>
+        <v>0.80036454523494382</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.94901057934853383</v>
+        <v>0.94993131785561225</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>2.0049733774363823</v>
+        <v>2.0102681565422884</v>
       </c>
       <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v>-9.308942961405176</v>
+        <v>-9.2865529283737391</v>
       </c>
       <c r="K90" s="152">
         <f t="shared" si="37"/>
@@ -14225,24 +14224,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3795853269537489E-2</v>
+        <v>6.4724919093851141E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.3795853269537489E-2</v>
+        <v>6.4724919093851141E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.0909090909090912E-2</v>
+        <v>9.2233009708737865E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.0606060606060608E-2</v>
+        <v>6.1488673139158581E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.0606060606060608E-2</v>
+        <v>6.1488673139158581E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -14362,26 +14361,26 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.11132223134574537</v>
+        <v>0.40262821780402724</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-0.20258874917858871</v>
+        <v>-0.20278146007564812</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>1.8343518305121167</v>
+        <v>1.8377184787011509</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>23.369937630114734</v>
+        <v>23.558516207903942</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.0674666632911132</v>
+        <v>-1.0668137597996945</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
@@ -14973,19 +14972,19 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>5.2064341392966007</v>
+        <v>5.2126793896166532</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>4.7741674718145966</v>
+        <v>4.7787994115697456</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>15.454607584036758</v>
+        <v>15.495420461777091</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-49.181667323272073</v>
+        <v>-49.063374713630502</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -15081,24 +15080,24 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>4.2139530177368108E-2</v>
+        <v>5.3128459724860015E-2</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>3.791837235752913E-2</v>
+        <v>3.7877791884180549E-2</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>4.6878171936978519E-2</v>
+        <v>4.6839322321051209E-2</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>1.79149579709687E-2</v>
+        <v>1.7878874645861673E-2</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>7.8557356170929E-4</v>
+        <v>7.7797123344543119E-4</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
@@ -15246,26 +15245,26 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.13154811711973616</v>
+        <v>0.1658525572748466</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.11837081398114316</v>
+        <v>0.11824413281411626</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.13998880630441438</v>
+        <v>0.13987279257917012</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>5.1485375157080467E-2</v>
+        <v>5.1381676140143856E-2</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>2.0870110127616838E-3</v>
+        <v>2.0668141227660726E-3</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
@@ -15367,26 +15366,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.45249091066365454</v>
+        <v>0.58804305017392744</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.50037175255873945</v>
+        <v>0.49977226300370614</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.6006255487597274</v>
+        <v>0.60004338133279533</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.18952870111715853</v>
+        <v>0.18902950771185151</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-4.0820961260099868E-2</v>
+        <v>-4.0919381274290068E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
@@ -15424,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.216760935624475E-2</v>
+        <v>9.5152597115522236E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.9804107266146646E-2</v>
+        <v>8.0869298220664423E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.5793548446527502E-2</v>
+        <v>9.7094398273915111E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.0227863017090677E-2</v>
+        <v>3.0587298982500247E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.5105201371770125E-3</v>
+        <v>-6.6212591058721799E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.268057350527389E-2</v>
+        <v>-3.3156504187389531E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.7364722384487685E-2</v>
+        <v>5.8200130962902552E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15338258852452524</v>
+        <v>0.15561631554187269</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12651839650791788</v>
+        <v>0.1283608974279361</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.14226266364649068</v>
+        <v>0.14433445001027453</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13870276979473781</v>
+        <v>0.14072271304417575</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15481,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4650873117524627E-2</v>
+        <v>6.5592390687197313E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1627532041699322E-2</v>
+        <v>9.2961913576287164E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0574225065259433E-2</v>
+        <v>3.1019480770093307E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2832978922102234E-3</v>
+        <v>6.3748022304462937E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.914411619415299E-2</v>
+        <v>0.10058796254649502</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0454678206124711E-2</v>
+        <v>2.0752561869320701E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16281853457140461</v>
+        <v>0.16518967827875514</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1262970374355665</v>
+        <v>0.12813631467977377</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13854878087484118</v>
+        <v>0.14056648156719323</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14240125367439765</v>
+        <v>0.14447505833955876</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16272,7 +16271,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>262446.55308076233</v>
+        <v>341067.34067849925</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16311,7 +16310,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>356895.60547045514</v>
+        <v>364748.53556666663</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16332,7 +16331,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3619952.4562863773</v>
+        <v>4704377.1128068864</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16354,7 +16353,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-78405.026054704562</v>
+        <v>-78483.555355666671</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16365,14 +16364,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>-1713932.1945295448</v>
+        <v>-1706079.2644333334</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>-1713932.1945295448</v>
+        <v>-1706079.2644333334</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16395,7 +16394,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>1906020.2617568325</v>
+        <v>2998297.8483735528</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16406,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-2.9550349601268113</v>
+        <v>-2.9414955196239703</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16418,7 +16417,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-78405.026054704562</v>
+        <v>-78483.555355666671</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16456,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>1906020.2617568325</v>
+        <v>2998297.8483735528</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16478,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16515,7 +16514,7 @@
       </c>
       <c r="F14" s="313" t="str">
         <f>IF(F17=C17,"I","II")</f>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
         <v>415</v>
@@ -16527,15 +16526,15 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E15" s="312" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
-        <v>Change year</v>
+        <v>Terminal Year</v>
       </c>
       <c r="F15" s="314">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>432</v>
@@ -16552,7 +16551,7 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E16" s="312" t="s">
         <v>401</v>
@@ -16568,14 +16567,14 @@
       </c>
       <c r="C17" s="310">
         <f>Normalized_FCF!C32</f>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="E17" s="312" t="s">
         <v>402</v>
       </c>
       <c r="F17" s="315">
         <f>Scenarios!C40</f>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>414</v>
@@ -16601,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>9.232538014143703</v>
+        <v>8.2435802828925357</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16660,23 +16659,23 @@
       </c>
       <c r="C21" s="281">
         <f>I4*(1+D21)</f>
-        <v>8826648.526879292</v>
+        <v>8739683.3399999999</v>
       </c>
       <c r="D21" s="303">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E21" s="303">
         <f>$C$17</f>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F21" s="281">
         <f>I5*(1+D21)</f>
-        <v>-509401.77750217711</v>
+        <v>-504382.86</v>
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>374314.70393650717</v>
+        <v>465895.58544433338</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16684,11 +16683,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>272333.05914858059</v>
+        <v>349199.36286650889</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>3.767055025781163E-2</v>
+        <v>2.3842863910195078E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16696,7 +16695,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>253923.59827373479</v>
+        <v>325593.81153054442</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16709,23 +16708,23 @@
       </c>
       <c r="C22" s="281">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>9092768.6518904921</v>
+        <v>8914477.0067999996</v>
       </c>
       <c r="D22" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E22" s="303">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F22" s="281">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
-        <v>-524760.04902471334</v>
+        <v>-514470.5172</v>
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>387964.03309846646</v>
+        <v>476783.16826033324</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16733,11 +16732,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>282517.63964665163</v>
+        <v>357494.02549827856</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>3.7397518060833246E-2</v>
+        <v>2.3753372754407032E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16745,7 +16744,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>245612.783800698</v>
+        <v>310795.11673879501</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16758,23 +16757,23 @@
       </c>
       <c r="C23" s="281">
         <f t="shared" si="5"/>
-        <v>9366912.1983305961</v>
+        <v>9092766.5469359998</v>
       </c>
       <c r="D23" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E23" s="303">
         <f t="shared" si="6"/>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F23" s="281">
         <f t="shared" si="7"/>
-        <v>-540581.36664284149</v>
+        <v>-524759.92754399998</v>
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>402024.88438820012</v>
+        <v>487888.50273265329</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16782,11 +16781,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>293009.28140665893</v>
+        <v>365954.58138268383</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>3.7136236070531181E-2</v>
+        <v>2.3666286094188305E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16794,7 +16793,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>237514.14277096602</v>
+        <v>296643.80688877573</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -16815,23 +16814,23 @@
       </c>
       <c r="C24" s="281">
         <f t="shared" si="5"/>
-        <v>9649321.0693304688</v>
+        <v>9274621.8778747208</v>
       </c>
       <c r="D24" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E24" s="303">
         <f t="shared" si="6"/>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F24" s="281">
         <f t="shared" si="7"/>
-        <v>-556879.69102175278</v>
+        <v>-535255.12609487993</v>
       </c>
       <c r="G24" s="281">
         <f t="shared" si="8"/>
-        <v>416509.66504269699</v>
+        <v>499215.94389441994</v>
       </c>
       <c r="H24" s="303">
         <f t="shared" si="2"/>
@@ -16839,11 +16838,11 @@
       </c>
       <c r="I24" s="281">
         <f t="shared" si="9"/>
-        <v>303817.24220987322</v>
+        <v>374584.34838477738</v>
       </c>
       <c r="J24" s="303">
         <f t="shared" si="10"/>
-        <v>3.6886069790445397E-2</v>
+        <v>2.3581524705846624E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16851,7 +16850,7 @@
       </c>
       <c r="L24" s="281">
         <f t="shared" si="4"/>
-        <v>229627.13847779363</v>
+        <v>283113.39874103473</v>
       </c>
       <c r="N24" s="279"/>
       <c r="O24" s="279"/>
@@ -16872,23 +16871,23 @@
       </c>
       <c r="C25" s="281">
         <f t="shared" si="5"/>
-        <v>9940244.4613091573</v>
+        <v>9460114.3154322151</v>
       </c>
       <c r="D25" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E25" s="303">
         <f t="shared" si="6"/>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F25" s="281">
         <f t="shared" si="7"/>
-        <v>-573669.4037354301</v>
+        <v>-545960.22861677757</v>
       </c>
       <c r="G25" s="281">
         <f t="shared" si="8"/>
-        <v>431431.15637246298</v>
+        <v>510769.93387942156</v>
       </c>
       <c r="H25" s="303">
         <f t="shared" si="2"/>
@@ -16896,11 +16895,11 @@
       </c>
       <c r="I25" s="281">
         <f t="shared" si="9"/>
-        <v>314951.05895617965</v>
+        <v>383386.71072691242</v>
       </c>
       <c r="J25" s="303">
         <f t="shared" si="10"/>
-        <v>3.6646428179396562E-2</v>
+        <v>2.3499012652533846E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16908,7 +16907,7 @@
       </c>
       <c r="L25" s="281">
         <f t="shared" si="4"/>
-        <v>221950.72532966008</v>
+        <v>270178.3534546874</v>
       </c>
       <c r="N25" s="279"/>
       <c r="O25" s="279"/>
@@ -16929,23 +16928,23 @@
       </c>
       <c r="C26" s="281">
         <f t="shared" si="5"/>
-        <v>10239939.083863787</v>
+        <v>9649316.6017408594</v>
       </c>
       <c r="D26" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E26" s="303">
         <f t="shared" si="6"/>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F26" s="281">
         <f t="shared" si="7"/>
-        <v>-590965.31995688961</v>
+        <v>-556879.43318911316</v>
       </c>
       <c r="G26" s="281">
         <f t="shared" si="8"/>
-        <v>446802.52503969567</v>
+        <v>522555.00366412336</v>
       </c>
       <c r="H26" s="303">
         <f t="shared" si="2"/>
@@ -16953,11 +16952,11 @@
       </c>
       <c r="I26" s="281">
         <f t="shared" si="9"/>
-        <v>326420.55607939838</v>
+        <v>392365.12031589029</v>
       </c>
       <c r="J26" s="303">
         <f t="shared" si="10"/>
-        <v>3.6416759991953374E-2</v>
+        <v>2.341867711573653E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16965,7 +16964,7 @@
       </c>
       <c r="L26" s="281">
         <f t="shared" si="4"/>
-        <v>214483.4047776506</v>
+        <v>257814.05415189188</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16978,23 +16977,23 @@
       </c>
       <c r="C27" s="281">
         <f t="shared" si="5"/>
-        <v>10548669.386289045</v>
+        <v>9842302.9337756764</v>
       </c>
       <c r="D27" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E27" s="303">
         <f t="shared" si="6"/>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F27" s="281">
         <f t="shared" si="7"/>
-        <v>-608782.70153102756</v>
+        <v>-568017.02185289538</v>
       </c>
       <c r="G27" s="281">
         <f t="shared" si="8"/>
-        <v>462637.33467649494</v>
+        <v>534575.7748445191</v>
       </c>
       <c r="H27" s="303">
         <f t="shared" si="2"/>
@@ -17002,11 +17001,11 @@
       </c>
       <c r="I27" s="281">
         <f t="shared" si="9"/>
-        <v>338235.85421632626</v>
+        <v>401523.09809664771</v>
       </c>
       <c r="J27" s="303">
         <f t="shared" si="10"/>
-        <v>3.619655048334014E-2</v>
+        <v>2.334044823705117E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -17014,7 +17013,7 @@
       </c>
       <c r="L27" s="281">
         <f t="shared" si="4"/>
-        <v>207223.27661214315</v>
+        <v>245996.78297212912</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -17027,23 +17026,23 @@
       </c>
       <c r="C28" s="281">
         <f t="shared" si="5"/>
-        <v>10866707.79092614</v>
+        <v>10039148.992451191</v>
       </c>
       <c r="D28" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E28" s="303">
         <f t="shared" si="6"/>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F28" s="281">
         <f t="shared" si="7"/>
-        <v>-627137.27044160955</v>
+        <v>-579377.36228995328</v>
       </c>
       <c r="G28" s="281">
         <f t="shared" si="8"/>
-        <v>478949.55785335309</v>
+        <v>546836.96144852298</v>
       </c>
       <c r="H28" s="303">
         <f t="shared" si="2"/>
@@ -17051,11 +17050,11 @@
       </c>
       <c r="I28" s="281">
         <f t="shared" si="9"/>
-        <v>350407.3791371425</v>
+        <v>410864.23543302045</v>
       </c>
       <c r="J28" s="303">
         <f t="shared" si="10"/>
-        <v>3.598531843709174E-2</v>
+        <v>2.3264258969540874E-2</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -17063,7 +17062,7 @@
       </c>
       <c r="L28" s="281">
         <f t="shared" si="4"/>
-        <v>200168.08597539266</v>
+        <v>234703.69774999219</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -17076,23 +17075,23 @@
       </c>
       <c r="C29" s="281">
         <f t="shared" si="5"/>
-        <v>11194334.933547152</v>
+        <v>10239931.972300215</v>
       </c>
       <c r="D29" s="303">
         <f t="shared" si="1"/>
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E29" s="303">
         <f t="shared" si="6"/>
-        <v>0.89099809462634716</v>
+        <v>0.88</v>
       </c>
       <c r="F29" s="281">
         <f t="shared" si="7"/>
-        <v>-646045.22268428362</v>
+        <v>-590964.90953575238</v>
       </c>
       <c r="G29" s="281">
         <f t="shared" si="8"/>
-        <v>495753.58840849495</v>
+        <v>559343.37178460672</v>
       </c>
       <c r="H29" s="303">
         <f t="shared" si="2"/>
@@ -17100,11 +17099,11 @@
       </c>
       <c r="I29" s="281">
         <f t="shared" si="9"/>
-        <v>362945.87094506674</v>
+        <v>420392.19551612041</v>
       </c>
       <c r="J29" s="303">
         <f t="shared" si="10"/>
-        <v>3.5782613479200975E-2</v>
+        <v>2.3190044937978493E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17112,20 +17111,20 @@
       </c>
       <c r="L29" s="281">
         <f t="shared" si="4"/>
-        <v>193315.26641186164</v>
+        <v>223912.80843629298</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B30" s="117">
         <v>10</v>
       </c>
       <c r="C30" s="281">
         <f t="shared" si="5"/>
-        <v>11418221.632218095</v>
+        <v>10444730.61174622</v>
       </c>
       <c r="D30" s="303">
         <f t="shared" si="1"/>
@@ -17133,15 +17132,15 @@
       </c>
       <c r="E30" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F30" s="281">
         <f t="shared" si="7"/>
-        <v>-658966.12713796936</v>
+        <v>-602784.2077264674</v>
       </c>
       <c r="G30" s="281">
         <f t="shared" si="8"/>
-        <v>769834.10226011451</v>
+        <v>572099.91032741219</v>
       </c>
       <c r="H30" s="303">
         <f t="shared" si="2"/>
@@ -17149,11 +17148,11 @@
       </c>
       <c r="I30" s="281">
         <f t="shared" si="9"/>
-        <v>590782.93250364857</v>
+        <v>430110.7148008825</v>
       </c>
       <c r="J30" s="303">
         <f t="shared" si="10"/>
-        <v>0.62774391389361162</v>
+        <v>2.3117744307385557E-2</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17161,20 +17160,20 @@
       </c>
       <c r="L30" s="281">
         <f t="shared" si="4"/>
-        <v>293396.50197168294</v>
+        <v>213602.95336957747</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B31" s="117">
         <v>11</v>
       </c>
       <c r="C31" s="281">
         <f t="shared" si="5"/>
-        <v>11646586.064862456</v>
+        <v>10653625.223981144</v>
       </c>
       <c r="D31" s="303">
         <f t="shared" si="1"/>
@@ -17182,15 +17181,15 @@
       </c>
       <c r="E31" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F31" s="281">
         <f t="shared" si="7"/>
-        <v>-672145.44968072872</v>
+        <v>-614839.89188099676</v>
       </c>
       <c r="G31" s="281">
         <f t="shared" si="8"/>
-        <v>786798.88482641091</v>
+        <v>585111.57964107371</v>
       </c>
       <c r="H31" s="303">
         <f t="shared" si="2"/>
@@ -17198,11 +17197,11 @@
       </c>
       <c r="I31" s="281">
         <f t="shared" si="9"/>
-        <v>603907.95508883509</v>
+        <v>440023.60447133973</v>
       </c>
       <c r="J31" s="303">
         <f t="shared" si="10"/>
-        <v>2.2216319841138032E-2</v>
+        <v>2.3047297659269717E-2</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17210,20 +17209,20 @@
       </c>
       <c r="L31" s="281">
         <f t="shared" si="4"/>
-        <v>279640.73892751231</v>
+        <v>203753.77549350605</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B32" s="117">
         <v>12</v>
       </c>
       <c r="C32" s="281">
         <f t="shared" si="5"/>
-        <v>11879517.786159705</v>
+        <v>10866697.728460766</v>
       </c>
       <c r="D32" s="303">
         <f t="shared" si="1"/>
@@ -17231,15 +17230,15 @@
       </c>
       <c r="E32" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F32" s="281">
         <f t="shared" si="7"/>
-        <v>-685588.35867434333</v>
+        <v>-627136.68971861666</v>
       </c>
       <c r="G32" s="281">
         <f t="shared" si="8"/>
-        <v>804102.96304403327</v>
+        <v>598383.48234100849</v>
       </c>
       <c r="H32" s="303">
         <f t="shared" si="2"/>
@@ -17247,11 +17246,11 @@
       </c>
       <c r="I32" s="281">
         <f t="shared" si="9"/>
-        <v>617295.47812572541</v>
+        <v>450134.75193520612</v>
       </c>
       <c r="J32" s="303">
         <f t="shared" si="10"/>
-        <v>2.2168151494081689E-2</v>
+        <v>2.2978647875070868E-2</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
@@ -17259,20 +17258,20 @@
       </c>
       <c r="L32" s="281">
         <f t="shared" si="4"/>
-        <v>266517.34936314618</v>
+        <v>194345.69860493013</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B33" s="117">
         <v>13</v>
       </c>
       <c r="C33" s="281">
         <f t="shared" si="5"/>
-        <v>12117108.1418829</v>
+        <v>11084031.683029981</v>
       </c>
       <c r="D33" s="303">
         <f t="shared" si="1"/>
@@ -17280,15 +17279,15 @@
       </c>
       <c r="E33" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F33" s="281">
         <f t="shared" si="7"/>
-        <v>-699300.1258478302</v>
+        <v>-639679.42351298896</v>
       </c>
       <c r="G33" s="281">
         <f t="shared" si="8"/>
-        <v>821753.12282600813</v>
+        <v>611920.82309494214</v>
       </c>
       <c r="H33" s="303">
         <f t="shared" si="2"/>
@@ -17296,11 +17295,11 @@
       </c>
       <c r="I33" s="281">
         <f t="shared" si="9"/>
-        <v>630950.75162335357</v>
+        <v>460448.12234835001</v>
       </c>
       <c r="J33" s="303">
         <f t="shared" si="10"/>
-        <v>2.2121129963707631E-2</v>
+        <v>2.2911740026303029E-2</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
@@ -17308,7 +17307,7 @@
       </c>
       <c r="L33" s="281">
         <f t="shared" si="4"/>
-        <v>253998.14851840667</v>
+        <v>185359.9037077823</v>
       </c>
       <c r="N33" s="279"/>
       <c r="O33" s="279"/>
@@ -17322,14 +17321,14 @@
     <row r="34" spans="1:21">
       <c r="A34" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B34" s="117">
         <v>14</v>
       </c>
       <c r="C34" s="281">
         <f t="shared" si="5"/>
-        <v>12359450.304720558</v>
+        <v>11305712.316690581</v>
       </c>
       <c r="D34" s="303">
         <f t="shared" si="1"/>
@@ -17337,15 +17336,15 @@
       </c>
       <c r="E34" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F34" s="281">
         <f t="shared" si="7"/>
-        <v>-713286.12836478685</v>
+        <v>-652473.01198324875</v>
       </c>
       <c r="G34" s="281">
         <f t="shared" si="8"/>
-        <v>839756.28580362245</v>
+        <v>625728.91066395433</v>
       </c>
       <c r="H34" s="303">
         <f t="shared" si="2"/>
@@ -17353,11 +17352,11 @@
       </c>
       <c r="I34" s="281">
         <f t="shared" si="9"/>
-        <v>644879.13059093431</v>
+        <v>470967.76016975672</v>
       </c>
       <c r="J34" s="303">
         <f t="shared" si="10"/>
-        <v>2.2075223671173871E-2</v>
+        <v>2.2846521270963427E-2</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17365,7 +17364,7 @@
       </c>
       <c r="L34" s="281">
         <f t="shared" si="4"/>
-        <v>242056.14401772915</v>
+        <v>176778.3055390451</v>
       </c>
       <c r="N34" s="279"/>
       <c r="O34" s="279"/>
@@ -17379,14 +17378,14 @@
     <row r="35" spans="1:21">
       <c r="A35" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="281">
         <f t="shared" si="5"/>
-        <v>12606639.310814969</v>
+        <v>11531826.563024392</v>
       </c>
       <c r="D35" s="303">
         <f t="shared" si="1"/>
@@ -17394,15 +17393,15 @@
       </c>
       <c r="E35" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F35" s="281">
         <f t="shared" si="7"/>
-        <v>-727551.85093208263</v>
+        <v>-665522.47222291376</v>
       </c>
       <c r="G35" s="281">
         <f t="shared" si="8"/>
-        <v>858119.51204078877</v>
+        <v>639813.15998434671</v>
       </c>
       <c r="H35" s="303">
         <f t="shared" si="2"/>
@@ -17410,11 +17409,11 @@
       </c>
       <c r="I35" s="281">
         <f t="shared" si="9"/>
-        <v>659086.07713786629</v>
+        <v>481697.79074759141</v>
       </c>
       <c r="J35" s="303">
         <f t="shared" si="10"/>
-        <v>2.2030402090874812E-2</v>
+        <v>2.2782940755790015E-2</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
@@ -17422,7 +17421,7 @@
       </c>
       <c r="L35" s="281">
         <f t="shared" si="4"/>
-        <v>230665.49016224375</v>
+        <v>168583.52932498849</v>
       </c>
       <c r="N35" s="279"/>
       <c r="O35" s="279"/>
@@ -17436,14 +17435,14 @@
     <row r="36" spans="1:21">
       <c r="A36" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B36" s="117">
         <v>16</v>
       </c>
       <c r="C36" s="281">
         <f t="shared" si="5"/>
-        <v>12858772.097031269</v>
+        <v>11762463.094284881</v>
       </c>
       <c r="D36" s="303">
         <f t="shared" si="1"/>
@@ -17451,15 +17450,15 @@
       </c>
       <c r="E36" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F36" s="281">
         <f t="shared" si="7"/>
-        <v>-742102.88795072434</v>
+        <v>-678832.92166737199</v>
       </c>
       <c r="G36" s="281">
         <f t="shared" si="8"/>
-        <v>876850.00280269876</v>
+        <v>654179.09429114696</v>
       </c>
       <c r="H36" s="303">
         <f t="shared" si="2"/>
@@ -17467,11 +17466,11 @@
       </c>
       <c r="I36" s="281">
         <f t="shared" si="9"/>
-        <v>673577.1626157373</v>
+        <v>492642.42193698289</v>
       </c>
       <c r="J36" s="303">
         <f t="shared" si="10"/>
-        <v>2.1986635707432534E-2</v>
+        <v>2.2720949523985734E-2</v>
       </c>
       <c r="K36" s="119">
         <f t="shared" si="3"/>
@@ -17479,20 +17478,20 @@
       </c>
       <c r="L36" s="281">
         <f t="shared" si="4"/>
-        <v>219801.44360346606</v>
+        <v>160758.8878185146</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B37" s="117">
         <v>17</v>
       </c>
       <c r="C37" s="281">
         <f t="shared" si="5"/>
-        <v>13115947.538971895</v>
+        <v>11997712.356170578</v>
       </c>
       <c r="D37" s="303">
         <f t="shared" si="1"/>
@@ -17500,15 +17499,15 @@
       </c>
       <c r="E37" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F37" s="281">
         <f t="shared" si="7"/>
-        <v>-756944.94570973888</v>
+        <v>-692409.58010071947</v>
       </c>
       <c r="G37" s="281">
         <f t="shared" si="8"/>
-        <v>895955.10337984678</v>
+        <v>668832.34728408314</v>
       </c>
       <c r="H37" s="303">
         <f t="shared" si="2"/>
@@ -17516,11 +17515,11 @@
       </c>
       <c r="I37" s="281">
         <f t="shared" si="9"/>
-        <v>688358.0698031655</v>
+        <v>503805.94575016206</v>
       </c>
       <c r="J37" s="303">
         <f t="shared" si="10"/>
-        <v>2.1943895974781524E-2</v>
+        <v>2.2660500428051122E-2</v>
       </c>
       <c r="K37" s="119">
         <f t="shared" si="3"/>
@@ -17528,20 +17527,20 @@
       </c>
       <c r="L37" s="281">
         <f t="shared" si="4"/>
-        <v>209440.32038881801</v>
+        <v>153288.35866176136</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B38" s="117">
         <v>18</v>
       </c>
       <c r="C38" s="281">
         <f t="shared" si="5"/>
-        <v>13378266.489751333</v>
+        <v>12237666.603293989</v>
       </c>
       <c r="D38" s="303">
         <f t="shared" si="1"/>
@@ -17549,15 +17548,15 @@
       </c>
       <c r="E38" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F38" s="281">
         <f t="shared" si="7"/>
-        <v>-772083.84462393366</v>
+        <v>-706257.77170273382</v>
       </c>
       <c r="G38" s="281">
         <f t="shared" si="8"/>
-        <v>915442.30596853781</v>
+        <v>683778.66533687804</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="2"/>
@@ -17565,11 +17564,11 @@
       </c>
       <c r="I38" s="281">
         <f t="shared" si="9"/>
-        <v>703434.59513434244</v>
+        <v>515192.74003960483</v>
       </c>
       <c r="J38" s="303">
         <f t="shared" si="10"/>
-        <v>2.1902155277249813E-2</v>
+        <v>2.2601548047409326E-2</v>
       </c>
       <c r="K38" s="119">
         <f t="shared" si="3"/>
@@ -17577,20 +17576,20 @@
       </c>
       <c r="L38" s="281">
         <f t="shared" si="4"/>
-        <v>199559.45436577237</v>
+        <v>146156.56211204073</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B39" s="117">
         <v>19</v>
       </c>
       <c r="C39" s="281">
         <f t="shared" si="5"/>
-        <v>13645831.819546361</v>
+        <v>12482419.935359869</v>
       </c>
       <c r="D39" s="303">
         <f t="shared" si="1"/>
@@ -17598,15 +17597,15 @@
       </c>
       <c r="E39" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F39" s="281">
         <f t="shared" si="7"/>
-        <v>-787525.52151641238</v>
+        <v>-720382.92713678849</v>
       </c>
       <c r="G39" s="281">
         <f t="shared" si="8"/>
-        <v>935319.25260900275</v>
+        <v>699023.90975072898</v>
       </c>
       <c r="H39" s="303">
         <f t="shared" si="2"/>
@@ -17614,11 +17613,11 @@
       </c>
       <c r="I39" s="281">
         <f t="shared" si="9"/>
-        <v>718812.65097214293</v>
+        <v>526807.2702148367</v>
       </c>
       <c r="J39" s="303">
         <f t="shared" si="10"/>
-        <v>2.1861386892499279E-2</v>
+        <v>2.2544048610504408E-2</v>
       </c>
       <c r="K39" s="119">
         <f t="shared" si="3"/>
@@ -17626,20 +17625,20 @@
       </c>
       <c r="L39" s="281">
         <f t="shared" si="4"/>
-        <v>190137.15692840895</v>
+        <v>139348.73916367255</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B40" s="117">
         <v>20</v>
       </c>
       <c r="C40" s="281">
         <f t="shared" si="5"/>
-        <v>13918748.455937289</v>
+        <v>12732068.334067067</v>
       </c>
       <c r="D40" s="303">
         <f t="shared" si="1"/>
@@ -17647,15 +17646,15 @@
       </c>
       <c r="E40" s="303">
         <f t="shared" si="6"/>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F40" s="281">
         <f t="shared" si="7"/>
-        <v>-803276.0319467407</v>
+        <v>-734790.58567952423</v>
       </c>
       <c r="G40" s="281">
         <f t="shared" si="8"/>
-        <v>955593.73818227684</v>
+        <v>714574.05905285699</v>
       </c>
       <c r="H40" s="303">
         <f t="shared" si="2"/>
@@ -17663,11 +17662,11 @@
       </c>
       <c r="I40" s="281">
         <f t="shared" si="9"/>
-        <v>734498.26792669925</v>
+        <v>538654.09099357307</v>
       </c>
       <c r="J40" s="303">
         <f t="shared" si="10"/>
-        <v>2.1821564956240769E-2</v>
+        <v>2.2487959921101863E-2</v>
       </c>
       <c r="K40" s="119">
         <f t="shared" si="3"/>
@@ -17675,36 +17674,36 @@
       </c>
       <c r="L40" s="281">
         <f t="shared" si="4"/>
-        <v>181152.67808756846</v>
+        <v>132850.7300932786</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B41" s="117">
         <v>21</v>
       </c>
       <c r="C41" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12986709.700748408</v>
       </c>
       <c r="D41" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E41" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F41" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-749486.39739311475</v>
       </c>
       <c r="G41" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>730435.21134102752</v>
       </c>
       <c r="H41" s="303">
         <f t="shared" si="2"/>
@@ -17712,48 +17711,48 @@
       </c>
       <c r="I41" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>550737.8481878842</v>
       </c>
       <c r="J41" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2433241288527306E-2</v>
       </c>
       <c r="K41" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.22996232030955746</v>
       </c>
       <c r="L41" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>126648.95345157865</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B42" s="117">
         <v>22</v>
       </c>
       <c r="C42" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13246443.894763377</v>
       </c>
       <c r="D42" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E42" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F42" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-764476.1253409771</v>
       </c>
       <c r="G42" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>746613.58667496138</v>
       </c>
       <c r="H42" s="303">
         <f t="shared" si="2"/>
@@ -17761,48 +17760,48 @@
       </c>
       <c r="I42" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>563063.28052608145</v>
       </c>
       <c r="J42" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.237985346159177E-2</v>
       </c>
       <c r="K42" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.21441708187371325</v>
       </c>
       <c r="L42" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120730.38552064238</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B43" s="117">
         <v>23</v>
       </c>
       <c r="C43" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13511372.772658644</v>
       </c>
       <c r="D43" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E43" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F43" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-779765.64784779667</v>
       </c>
       <c r="G43" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>763115.52951557387</v>
       </c>
       <c r="H43" s="303">
         <f t="shared" si="2"/>
@@ -17810,48 +17809,48 @@
       </c>
       <c r="I43" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>575635.22151104279</v>
       </c>
       <c r="J43" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.232775856599134E-2</v>
       </c>
       <c r="K43" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.19992268706173733</v>
       </c>
       <c r="L43" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>115082.54025186606</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B44" s="117">
         <v>24</v>
       </c>
       <c r="C44" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13781600.228111817</v>
       </c>
       <c r="D44" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E44" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F44" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-795360.96080475266</v>
       </c>
       <c r="G44" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>779947.51121299865</v>
       </c>
       <c r="H44" s="303">
         <f t="shared" si="2"/>
@@ -17859,48 +17858,48 @@
       </c>
       <c r="I44" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>588458.60131570313</v>
       </c>
       <c r="J44" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2276920044953075E-2</v>
       </c>
       <c r="K44" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.18640809982446369</v>
       </c>
       <c r="L44" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>109693.44969662187</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B45" s="117">
         <v>25</v>
       </c>
       <c r="C45" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14057232.232674053</v>
       </c>
       <c r="D45" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E45" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F45" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-811268.18002084771</v>
       </c>
       <c r="G45" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>797116.13254437188</v>
       </c>
       <c r="H45" s="303">
         <f t="shared" si="2"/>
@@ -17908,48 +17907,48 @@
       </c>
       <c r="I45" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>601538.44871645677</v>
       </c>
       <c r="J45" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.222730260295136E-2</v>
       </c>
       <c r="K45" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.17380708608341602</v>
       </c>
       <c r="L45" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>104551.64493854574</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B46" s="117">
         <v>26</v>
       </c>
       <c r="C46" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14338376.877327533</v>
       </c>
       <c r="D46" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E46" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F46" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-827493.54362126463</v>
       </c>
       <c r="G46" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>814628.12630237266</v>
       </c>
       <c r="H46" s="303">
         <f t="shared" si="2"/>
@@ -17957,48 +17956,48 @@
       </c>
       <c r="I46" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>614879.89306522557</v>
       </c>
       <c r="J46" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2178872152289308E-2</v>
       </c>
       <c r="K46" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.16205788912206626</v>
       </c>
       <c r="L46" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>99646.137533752277</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B47" s="117">
         <v>27</v>
       </c>
       <c r="C47" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14625144.414874084</v>
       </c>
       <c r="D47" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E47" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F47" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-844043.4144936899</v>
       </c>
       <c r="G47" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>832490.35993553337</v>
       </c>
       <c r="H47" s="303">
         <f t="shared" si="2"/>
@@ -18006,19 +18005,19 @@
       </c>
       <c r="I47" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>628488.16630096966</v>
       </c>
       <c r="J47" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2131595762394873E-2</v>
       </c>
       <c r="K47" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.15110292692034147</v>
       </c>
       <c r="L47" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>94966.401462874841</v>
       </c>
       <c r="N47" s="279"/>
       <c r="O47" s="279"/>
@@ -18032,30 +18031,30 @@
     <row r="48" spans="1:21">
       <c r="A48" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B48" s="117">
         <v>28</v>
       </c>
       <c r="C48" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14917647.303171566</v>
       </c>
       <c r="D48" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E48" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F48" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-860924.28278356371</v>
       </c>
       <c r="G48" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>850709.83824135736</v>
       </c>
       <c r="H48" s="303">
         <f t="shared" si="2"/>
@@ -18063,19 +18062,19 @@
       </c>
       <c r="I48" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>642368.60500142863</v>
       </c>
       <c r="J48" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2085441611659373E-2</v>
       </c>
       <c r="K48" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.14088850994903634</v>
       </c>
       <c r="L48" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90502.355596692374</v>
       </c>
       <c r="N48" s="279"/>
       <c r="O48" s="279"/>
@@ -18089,30 +18088,30 @@
     <row r="49" spans="1:21">
       <c r="A49" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B49" s="117">
         <v>29</v>
       </c>
       <c r="C49" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15216000.249234997</v>
       </c>
       <c r="D49" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E49" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F49" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-878142.76843923505</v>
       </c>
       <c r="G49" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>869293.70611329784</v>
       </c>
       <c r="H49" s="303">
         <f t="shared" si="2"/>
@@ -18120,19 +18119,19 @@
       </c>
       <c r="I49" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>656526.65247589687</v>
       </c>
       <c r="J49" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.204037894167743E-2</v>
       </c>
       <c r="K49" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1313645780410595</v>
       </c>
       <c r="L49" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>86244.34667520551</v>
       </c>
       <c r="N49" s="279"/>
       <c r="O49" s="279"/>
@@ -18146,30 +18145,30 @@
     <row r="50" spans="1:21">
       <c r="A50" s="306" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B50" s="117">
         <v>30</v>
       </c>
       <c r="C50" s="281">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15520320.254219698</v>
       </c>
       <c r="D50" s="303">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E50" s="303">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F50" s="281">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-895705.62380801979</v>
       </c>
       <c r="G50" s="281">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>888249.25134267728</v>
       </c>
       <c r="H50" s="303">
         <f t="shared" si="2"/>
@@ -18177,19 +18176,19 @@
       </c>
       <c r="I50" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>670967.86089985457</v>
       </c>
       <c r="J50" s="303">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.1996378013743989E-2</v>
       </c>
       <c r="K50" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.12248445504993893</v>
       </c>
       <c r="L50" s="281">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>82183.132798341918</v>
       </c>
       <c r="N50" s="279"/>
       <c r="O50" s="279"/>
@@ -18206,11 +18205,11 @@
       </c>
       <c r="B51" s="320">
         <f>C15+1</f>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C51" s="281">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>13918748.455937289</v>
+        <v>15520320.254219698</v>
       </c>
       <c r="D51" s="305">
         <f>Terminal_Growth</f>
@@ -18218,15 +18217,15 @@
       </c>
       <c r="E51" s="305">
         <f>F17</f>
-        <v>0.86799999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F51" s="281">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-803276.0319467407</v>
+        <v>-895705.62380801979</v>
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>955593.73818227684</v>
+        <v>888249.25134267728</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18234,7 +18233,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>10131010.592092404</v>
+        <v>9254729.1158600636</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18242,11 +18241,11 @@
       </c>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.2466345885320004</v>
+        <v>0.12248445504993893</v>
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>2498657.628794048</v>
+        <v>1133560.4523909232</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18259,7 +18258,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>7068841.4775587041</v>
+        <v>6487389.0748702856</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18283,27 +18282,27 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>7068841.4775587041</v>
+        <v>6487389.0748702856</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C55" s="123">
         <f>C93</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D55" s="123">
         <f>C92</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E55" s="123">
         <f>C91</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F55" s="123">
         <f>C90</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G55" s="123"/>
       <c r="H55" s="123"/>
@@ -18318,19 +18317,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>5868845.4418163244</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C56" s="118">
-        <v>5868845.4418163244</v>
+        <v>4760460.0244483305</v>
       </c>
       <c r="D56" s="118">
-        <v>5868845.4418163244</v>
+        <v>4816542.9360897783</v>
       </c>
       <c r="E56" s="118">
-        <v>5868845.4418163244</v>
+        <v>4872625.8477312233</v>
       </c>
       <c r="F56" s="118">
-        <v>5868845.4418163244</v>
+        <v>4928708.7593726683</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18344,19 +18343,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>5998045.2832838027</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C57" s="118">
-        <v>5998045.2832838027</v>
+        <v>4813274.7011456359</v>
       </c>
       <c r="D57" s="118">
-        <v>5998045.2832838027</v>
+        <v>4923218.1246665129</v>
       </c>
       <c r="E57" s="118">
-        <v>5998045.2832838027</v>
+        <v>5034207.3833695147</v>
       </c>
       <c r="F57" s="118">
-        <v>5998045.2832838027</v>
+        <v>5146242.4772546375</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18370,19 +18369,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>6052058.5955419457</v>
+        <v>4704377.1128068864</v>
       </c>
       <c r="C58" s="118">
-        <v>6120920.6569871418</v>
+        <v>4863011.5994806308</v>
       </c>
       <c r="D58" s="118">
-        <v>6189782.718432337</v>
+        <v>5024671.4508653665</v>
       </c>
       <c r="E58" s="118">
-        <v>6258644.7798775379</v>
+        <v>5189385.9210920688</v>
       </c>
       <c r="F58" s="118">
-        <v>6327506.8413227359</v>
+        <v>5357184.2642917018</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18396,19 +18395,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>6167773.3996821512</v>
+        <v>4704377.1128068846</v>
       </c>
       <c r="C59" s="118">
-        <v>6237781.1522574499</v>
+        <v>4909850.0771667287</v>
       </c>
       <c r="D59" s="118">
-        <v>6307788.9048327459</v>
+        <v>5121158.5303272158</v>
       </c>
       <c r="E59" s="118">
-        <v>6377796.6574080484</v>
+        <v>5338415.1927510248</v>
       </c>
       <c r="F59" s="118">
-        <v>6447804.409983349</v>
+        <v>5561733.8759640045</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18422,19 +18421,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>6064528.6063984428</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C60" s="118">
-        <v>6200094.9329497013</v>
+        <v>4953959.0398361553</v>
       </c>
       <c r="D60" s="118">
-        <v>6336966.7653764896</v>
+        <v>5212922.4660391808</v>
       </c>
       <c r="E60" s="118">
-        <v>6475144.103678802</v>
+        <v>5481538.8755563637</v>
       </c>
       <c r="F60" s="118">
-        <v>6614626.9478566507</v>
+        <v>5760085.0145553295</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18448,19 +18447,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>6168165.8535120673</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C61" s="118">
-        <v>6305794.5622968376</v>
+        <v>4995497.5501355687</v>
       </c>
       <c r="D61" s="118">
-        <v>6444749.0959939221</v>
+        <v>5300194.4608421698</v>
       </c>
       <c r="E61" s="118">
-        <v>6585029.4546033144</v>
+        <v>5618990.9905116074</v>
       </c>
       <c r="F61" s="118">
-        <v>6726635.6381250275</v>
+        <v>5952425.51258328</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18474,19 +18473,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>6064898.1899585528</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C62" s="118">
-        <v>6264779.0152249224</v>
+        <v>5034615.4013266275</v>
       </c>
       <c r="D62" s="118">
-        <v>6468499.6296151876</v>
+        <v>5383194.3999555018</v>
       </c>
       <c r="E62" s="118">
-        <v>6676097.1191408839</v>
+        <v>5750996.2850607</v>
       </c>
       <c r="F62" s="118">
-        <v>6887608.5698135383</v>
+        <v>6138937.5106709916</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18500,19 +18499,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>6157718.4567264616</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C63" s="118">
-        <v>6360383.7071122844</v>
+        <v>5071453.6574599277</v>
       </c>
       <c r="D63" s="118">
-        <v>6566943.8819691092</v>
+        <v>5462131.4049863638</v>
       </c>
       <c r="E63" s="118">
-        <v>6777436.6078510936</v>
+        <v>5877770.6005717162</v>
       </c>
       <c r="F63" s="118">
-        <v>6991899.5113123851</v>
+        <v>6319797.6300287694</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18526,19 +18525,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>6055059.6158294491</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C64" s="118">
-        <v>6316695.9641403118</v>
+        <v>5106145.1620703116</v>
       </c>
       <c r="D64" s="118">
-        <v>6585852.19796432</v>
+        <v>5537204.3608199097</v>
       </c>
       <c r="E64" s="118">
-        <v>6862673.7525932696</v>
+        <v>5999521.2252582852</v>
       </c>
       <c r="F64" s="118">
-        <v>7147307.4666403215</v>
+        <v>6495177.1397090415</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18552,19 +18551,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>6138191.9081550092</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C65" s="118">
-        <v>6403169.8445818331</v>
+        <v>5138815.0172278732</v>
       </c>
       <c r="D65" s="118">
-        <v>6675767.4073126987</v>
+        <v>5608602.4167175479</v>
       </c>
       <c r="E65" s="118">
-        <v>6956131.9968964783</v>
+        <v>6116447.233115783</v>
       </c>
       <c r="F65" s="118">
-        <v>7244412.4363766424</v>
+        <v>6665242.1187929399</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18578,19 +18577,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>5979861.5836562309</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C66" s="281">
-        <v>6410464.0632768515</v>
+        <v>5275730.9100739127</v>
       </c>
       <c r="D66" s="118">
-        <v>6865625.8549388181</v>
+        <v>5916466.0563589875</v>
       </c>
       <c r="E66" s="118">
-        <v>7346538.7647476587</v>
+        <v>6635140.5628965255</v>
       </c>
       <c r="F66" s="118">
-        <v>7854440.974044906</v>
+        <v>7441317.946202103</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18613,19 +18612,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>5951898.8282217141</v>
+        <v>4704377.1128068855</v>
       </c>
       <c r="C67" s="281">
-        <v>6485715.1590054734</v>
+        <v>5377139.3794040922</v>
       </c>
       <c r="D67" s="118">
-        <v>7059929.3351791268</v>
+        <v>6156003.137908808</v>
       </c>
       <c r="E67" s="118">
-        <v>7677293.4042476285</v>
+        <v>7058891.1202103924</v>
       </c>
       <c r="F67" s="118">
-        <v>8340720.9542961139</v>
+        <v>8106720.3244954431</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18648,19 +18647,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>5769689.0023798207</v>
+        <v>4704377.1128068846</v>
       </c>
       <c r="C68" s="281">
-        <v>6427002.8823416922</v>
+        <v>5452248.83118595</v>
       </c>
       <c r="D68" s="118">
-        <v>7152058.4742696658</v>
+        <v>6342377.9027372645</v>
       </c>
       <c r="E68" s="118">
-        <v>7951468.1674427968</v>
+        <v>7405077.4397833021</v>
       </c>
       <c r="F68" s="118">
-        <v>8832431.1842891984</v>
+        <v>8677232.0057013053</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18683,19 +18682,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>5701421.8997263089</v>
+        <v>4704377.1128068846</v>
       </c>
       <c r="C69" s="281">
-        <v>6435455.3327843975</v>
+        <v>5507879.5865285154</v>
       </c>
       <c r="D69" s="118">
-        <v>7258366.806684792</v>
+        <v>6487389.0748702856</v>
       </c>
       <c r="E69" s="118">
-        <v>8180591.7129682312</v>
+        <v>7687897.0509694852</v>
       </c>
       <c r="F69" s="118">
-        <v>9213703.6846195087</v>
+        <v>9166385.0189910345</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18761,23 +18760,23 @@
     <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C72" s="124">
         <f>C55</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D72" s="124">
         <f>D55</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E72" s="124">
         <f>E55</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F72" s="124">
         <f>F55</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G72" s="124"/>
       <c r="H72" s="124"/>
@@ -18792,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18823,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>7.1635937181264051</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>7.1635937181264051</v>
+        <v>5.2661371063518043</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.1635937181264051</v>
+        <v>5.3628311092389334</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.1635937181264051</v>
+        <v>5.4595251121260553</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.1635937181264051</v>
+        <v>5.556219115013179</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18854,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>7.3863505165562495</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>7.3863505165562495</v>
+        <v>5.357196260585833</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.3863505165562495</v>
+        <v>5.546752569275978</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.3863505165562495</v>
+        <v>5.738112029535114</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>7.3863505165562495</v>
+        <v>5.9312746413632329</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18885,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>7.4794762694562182</v>
+        <v>5.1694431034646842</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>7.5982031360419819</v>
+        <v>5.4429489373004021</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>7.7169300026277448</v>
+        <v>5.7216708809196035</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.8356568692135173</v>
+        <v>6.0056593721284264</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9543837357992846</v>
+        <v>6.2949648487329881</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18916,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>7.6789831651956915</v>
+        <v>5.1694431034646806</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>7.7996853475808594</v>
+        <v>5.5237043717821788</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>7.920387529966022</v>
+        <v>5.8880267577275314</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0410897123511962</v>
+        <v>6.2626046055746851</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.1617918947363659</v>
+        <v>6.6476341407278987</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18947,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>7.5009761386760871</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>7.7347095592008701</v>
+        <v>5.5997537786135041</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>7.9706938362736262</v>
+        <v>6.0462393398665331</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.2089289698943482</v>
+        <v>6.5093678600731897</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>8.4494149600630557</v>
+        <v>6.9896164844805417</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18978,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>7.6796598050250502</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>7.9169490322618037</v>
+        <v>5.6713714018299513</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>8.1565241486249747</v>
+        <v>6.1967072501525804</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.3983851541145569</v>
+        <v>6.7463526173071857</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>8.642532048730569</v>
+        <v>7.3212357269073438</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19010,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>7.5016133472799638</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>7.8462330635128161</v>
+        <v>5.7388155038799429</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>8.1974730597875745</v>
+        <v>6.339809598396652</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.5553972770588302</v>
+        <v>6.973946370175268</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>8.9200696562811554</v>
+        <v>7.6428059013818235</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19041,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>7.6616471771962953</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>8.0110675930123065</v>
+        <v>5.8023292969526548</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3672033491525131</v>
+        <v>6.4759069365868189</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.7301193185350652</v>
+        <v>7.1925212563795782</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.0998803740780883</v>
+        <v>7.954631525114646</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19073,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>7.4846504063876136</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9357444219888169</v>
+        <v>5.8621418200327895</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>8.3998036672872161</v>
+        <v>6.6053421673131298</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.8770788910423413</v>
+        <v>7.4024346669067933</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>9.367823261516488</v>
+        <v>8.2570078875222368</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19105,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>7.6279809482384486</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>8.0848362825992428</v>
+        <v>5.9184687648448469</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5548288123423344</v>
+        <v>6.7284414077241665</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>9.0382126745779612</v>
+        <v>7.604029830396799</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>9.535244458976198</v>
+        <v>8.5502213298568677</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19137,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>7.3549995282992908</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>8.0974124342809652</v>
+        <v>6.1545290076294679</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8821686872809629</v>
+        <v>7.2592370955559442</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>9.71132311112415</v>
+        <v>8.498322456428836</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>10.58701048638288</v>
+        <v>9.8882737971733548</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19169,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>7.3067882162332642</v>
+        <v>5.1694431034646824</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>8.2271548006217543</v>
+        <v>6.3293699803821166</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>9.2171723582645892</v>
+        <v>7.6722291920261085</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>10.281585765659813</v>
+        <v>9.2289217854060315</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>11.425418415610515</v>
+        <v>11.035511299732823</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19201,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>6.9926355285365336</v>
+        <v>5.1694431034646806</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>8.125927441287546</v>
+        <v>6.4588681347197054</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3760145970228486</v>
+        <v>7.9935627590781433</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>10.754297587639796</v>
+        <v>9.8257905998904818</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>12.273188779291909</v>
+        <v>12.019145289750032</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19233,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>6.8749344458381803</v>
+        <v>5.1694431034646806</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>8.1405005303727815</v>
+        <v>6.5547825632019041</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>9.5593035508345281</v>
+        <v>8.2435802828925357</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>11.149335436498054</v>
+        <v>10.313407228559997</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>12.930550588240417</v>
+        <v>12.862506689772795</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19288,15 +19287,15 @@
       </c>
       <c r="C90" s="130">
         <f>Scenarios!C29</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>11.425418415610515</v>
+        <v>12.862506689772795</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19316,15 +19315,15 @@
       </c>
       <c r="C91" s="130">
         <f>Scenarios!C22</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>10.281585765659813</v>
+        <v>10.313407228559997</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19344,15 +19343,15 @@
       </c>
       <c r="C92" s="130">
         <f>Scenarios!C23</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>9.2171723582645892</v>
+        <v>8.2435802828925357</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19372,15 +19371,15 @@
       </c>
       <c r="C93" s="130">
         <f>Scenarios!C24</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>8.2271548006217543</v>
+        <v>6.5547825632019041</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19400,15 +19399,15 @@
       </c>
       <c r="C94" s="130">
         <f>Scenarios!C30</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>7.3067882162332642</v>
+        <v>5.1694431034646806</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19617,7 +19616,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>290217.63448334695</v>
+        <v>289869.92812368623</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19630,7 +19629,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>262446.55308076233</v>
+        <v>341067.34067849925</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19686,7 +19685,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.62483362929826525</v>
+        <v>0.62600273988199584</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19716,7 +19715,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E18" s="455" t="s">
         <v>548</v>
@@ -19760,15 +19759,15 @@
         <v>448</v>
       </c>
       <c r="C22" s="328">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D22" s="329">
         <f>C18</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>10.281585765659813</v>
+        <v>10.313407228559997</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19784,15 +19783,15 @@
         <v>440</v>
       </c>
       <c r="C23" s="328">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D23" s="329">
         <f>C18</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>9.2171723582645892</v>
+        <v>8.2435802828925357</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19807,15 +19806,15 @@
         <v>449</v>
       </c>
       <c r="C24" s="328">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D24" s="329">
         <f>C18</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>8.2271548006217543</v>
+        <v>6.5547825632019041</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19831,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>9.2320515282150666</v>
+        <v>8.3197861280879017</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19870,15 +19869,15 @@
         <v>447</v>
       </c>
       <c r="C29" s="328">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D29" s="329">
         <f>C18</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>11.425418415610515</v>
+        <v>12.862506689772795</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19893,15 +19892,15 @@
         <v>450</v>
       </c>
       <c r="C30" s="328">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D30" s="329">
         <f>C18</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>7.3067882162332642</v>
+        <v>5.1694431034646806</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19946,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.27</v>
+        <v>6.18</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19480295483917651</v>
+        <v>0.16611853030232007</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19966,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19977,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.50264149520909396</v>
+        <v>0.24196795776686636</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19986,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>9.245456706985749</v>
+        <v>8.3894050049409827</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20012,7 +20011,7 @@
     <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="418" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
-        <v>2-stage DCF</v>
+        <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
         <v>251</v>
@@ -20023,7 +20022,8 @@
         <v>402</v>
       </c>
       <c r="C40" s="138">
-        <v>0.86799999999999999</v>
+        <f>DCF!C17</f>
+        <v>0.88</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>403</v>
@@ -20034,6 +20034,7 @@
         <v>401</v>
       </c>
       <c r="C41" s="138">
+        <f>DCF!C16</f>
         <v>0.02</v>
       </c>
       <c r="E41" s="97"/>
@@ -20062,7 +20063,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -20074,7 +20075,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>3.0149622951542498E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
@@ -20087,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>9.232538014143703</v>
+        <v>8.2435802828925357</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20143,14 +20144,14 @@
       </c>
       <c r="C53" s="217" t="str">
         <f>IF(F53&gt;50%,"Y","N")</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E53" s="126" t="s">
         <v>273</v>
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.47640734901197879</v>
+        <v>0.52663364780706778</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20228,11 +20229,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>4.2605791276432035</v>
+        <v>3.8660852557331729</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>4.9925197580872513</v>
+        <v>4.5980258861772203</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20240,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46000290560930679</v>
+        <v>0.45192467362474575</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20253,11 +20254,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>5.340336004035092</v>
+        <v>4.8458657068251183</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>6.181937582942723</v>
+        <v>5.6874672857327493</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20265,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33135400674455273</v>
+        <v>0.32206547634986193</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20299,11 +20300,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>6.6267771829004483</v>
+        <v>6.0131932285018506</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>7.5918184332759076</v>
+        <v>6.9782344788773099</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20311,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.17885955514348728</v>
+        <v>0.16820865427674037</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20324,11 +20325,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>7.4943930572565609</v>
+        <v>6.8004751540328705</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>8.5393431481257664</v>
+        <v>7.8454252449020769</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20336,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>7.6374113387654763E-2</v>
+        <v>6.4841280128748791E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20447,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.27</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20465,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3636.6252869099999</v>
+        <v>3584.4249239400001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.19480295483917651</v>
+        <v>0.16611853030232007</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20480,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20550,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>9.245456706985749</v>
+        <v>8.3894050049409827</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20566,7 +20567,7 @@
       </c>
       <c r="C19" s="356" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="347" t="s">
         <v>363</v>
@@ -20602,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>4.9925197580872513</v>
+        <v>4.5980258861772203</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20618,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>6.181937582942723</v>
+        <v>5.6874672857327493</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20634,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>7.5918184332759076</v>
+        <v>6.9782344788773099</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20650,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>8.5393431481257664</v>
+        <v>7.8454252449020769</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20671,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20712,7 +20713,7 @@
       </c>
       <c r="C34" s="377">
         <f>Normalized_FCF!C8</f>
-        <v>439469.87884546071</v>
+        <v>533705.04</v>
       </c>
       <c r="D34" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20795,7 +20796,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>6967.3739452954487</v>
+        <v>6888.8446443333341</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20825,7 +20826,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-78405.026054704562</v>
+        <v>-78483.555355666671</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20865,7 +20866,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-59575.700710474768</v>
+        <v>-75111.544966315007</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20876,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20895,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20918,7 +20919,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>290217.63448334695</v>
+        <v>289869.92812368623</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20931,7 +20932,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>262446.55308076233</v>
+        <v>341067.34067849925</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20944,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>7.216760935624475E-2</v>
+        <v>9.5152597115522236E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20954,14 +20955,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.3795853269537489E-2</v>
+        <v>6.4724919093851141E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.88399565731239171</v>
+        <v>0.68022230665202266</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20981,11 +20982,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.13154811711973616</v>
+        <v>0.1658525572748466</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>0.11837081398114316</v>
+        <v>0.11824413281411626</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20995,11 +20996,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>4.2139530177368108E-2</v>
+        <v>5.3128459724860015E-2</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>3.791837235752913E-2</v>
+        <v>3.7877791884180549E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21045,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21068,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21117,7 +21118,7 @@
       </c>
       <c r="C81" s="393">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>4.8565558249568426</v>
+        <v>3.999044116203212</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -21131,7 +21132,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>356895.60547045514</v>
+        <v>364748.53556666663</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21157,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.61533297212513538</v>
+        <v>0.62887241262797666</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21201,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-2.9550349601268113</v>
+        <v>-2.9414955196239703</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21223,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21312,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21360,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>3.2862189800615274</v>
+        <v>5.1694431034646833</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21372,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21415,15 +21416,15 @@
       </c>
       <c r="C118" s="400">
         <f>DCF!C90</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D118" s="401">
         <f>DCF!D90</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>11.43 HKD</v>
+        <v>12.86 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21438,15 +21439,15 @@
       </c>
       <c r="C119" s="405">
         <f>DCF!C91</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D119" s="406">
         <f>DCF!D91</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>10.28 HKD</v>
+        <v>10.31 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21460,15 +21461,15 @@
       </c>
       <c r="C120" s="405">
         <f>DCF!C92</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D120" s="406">
         <f>DCF!D92</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>9.22 HKD</v>
+        <v>8.24 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21482,15 +21483,15 @@
       </c>
       <c r="C121" s="405">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D121" s="406">
         <f>DCF!D93</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>8.23 HKD</v>
+        <v>6.55 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21504,15 +21505,15 @@
       </c>
       <c r="C122" s="405">
         <f>DCF!C94</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D122" s="406">
         <f>DCF!D94</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>7.31 HKD</v>
+        <v>5.17 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21534,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>9.245456706985749</v>
+        <v>8.3894050049409827</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21542,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21561,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21641,11 +21642,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>4.2605791276432035</v>
+        <v>3.8660852557331729</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>4.9925197580872513</v>
+        <v>4.5980258861772203</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21662,11 +21663,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>5.340336004035092</v>
+        <v>4.8458657068251183</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>6.181937582942723</v>
+        <v>5.6874672857327493</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21702,11 +21703,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>6.6267771829004483</v>
+        <v>6.0131932285018506</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>7.5918184332759076</v>
+        <v>6.9782344788773099</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21723,11 +21724,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>7.4943930572565609</v>
+        <v>6.8004751540328705</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>8.5393431481257664</v>
+        <v>7.8454252449020769</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21745,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21759,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21802,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21841,12 +21842,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21861,15 +21865,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7247D33B-698B-4F72-94A0-DD2881351624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2E25D6-E4AA-49FD-A307-EFA7BF5776DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.18</v>
+        <v>6.28</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3584.4249239400001</v>
+        <v>3642.4253272400001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16611853030232007</v>
+        <v>0.15955100724787913</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.5152597115522236E-2</v>
+        <v>9.3637428371644488E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.4724919093851141E-2</v>
+        <v>6.3694267515923567E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14224,24 +14224,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4724919093851141E-2</v>
+        <v>6.3694267515923567E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.4724919093851141E-2</v>
+        <v>6.3694267515923567E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.2233009708737865E-2</v>
+        <v>9.0764331210191077E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.1488673139158581E-2</v>
+        <v>6.0509554140127389E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.1488673139158581E-2</v>
+        <v>6.0509554140127389E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.5152597115522236E-2</v>
+        <v>9.3637428371644488E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.0869298220664423E-2</v>
+        <v>7.9581570541991414E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.7094398273915111E-2</v>
+        <v>9.554830912942601E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.0587298982500247E-2</v>
+        <v>3.0100240081505015E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.6212591058721799E-3</v>
+        <v>-6.5158250436767621E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.3156504187389531E-2</v>
+        <v>-3.2628534375488419E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.8200130962902552E-2</v>
+        <v>5.7273377285149321E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15561631554187269</v>
+        <v>0.15313834873388107</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.1283608974279361</v>
+        <v>0.12631693409309636</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.14433445001027453</v>
+        <v>0.142036130742595</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.14072271304417575</v>
+        <v>0.13848190551162515</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5592390687197313E-2</v>
+        <v>6.4547925867337486E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2961913576287164E-2</v>
+        <v>9.1481628328257111E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1019480770093307E-2</v>
+        <v>3.0525539993499464E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3748022304462937E-3</v>
+        <v>6.2732926407895054E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10058796254649502</v>
+        <v>9.8986243397665485E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0752561869320701E-2</v>
+        <v>2.0422107062484384E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16518967827875514</v>
+        <v>0.16255926938896603</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12813631467977377</v>
+        <v>0.12609592750334425</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14056648156719323</v>
+        <v>0.13832816179701499</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14447505833955876</v>
+        <v>0.14217450008574412</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.18</v>
+        <v>6.28</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16611853030232007</v>
+        <v>0.15955100724787913</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.18</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3584.4249239400001</v>
+        <v>3642.4253272400001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16611853030232007</v>
+        <v>0.15955100724787913</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.5152597115522236E-2</v>
+        <v>9.3637428371644488E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.4724919093851141E-2</v>
+        <v>6.3694267515923567E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,15 +21842,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21865,12 +21862,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2E25D6-E4AA-49FD-A307-EFA7BF5776DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7570E15-5408-4804-BD31-A8296FD26F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.28</v>
+        <v>6.03</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3642.4253272400001</v>
+        <v>3497.4243189900003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15955100724787913</v>
+        <v>0.17625020018811974</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.3637428371644488E-2</v>
+        <v>9.7519577143271544E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.3694267515923567E-2</v>
+        <v>6.633499170812604E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14224,24 +14224,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3694267515923567E-2</v>
+        <v>6.633499170812604E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.3694267515923567E-2</v>
+        <v>6.633499170812604E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.0764331210191077E-2</v>
+        <v>9.4527363184079588E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.0509554140127389E-2</v>
+        <v>6.3018242122719739E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.0509554140127389E-2</v>
+        <v>6.3018242122719739E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.3637428371644488E-2</v>
+        <v>9.7519577143271544E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.9581570541991414E-2</v>
+        <v>8.2880972305755571E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.554830912942601E-2</v>
+        <v>9.9509681813067213E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.0100240081505015E-2</v>
+        <v>3.1348177066642037E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.5158250436767621E-3</v>
+        <v>-6.7859670438291985E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.2628534375488419E-2</v>
+        <v>-3.3981292848767372E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.7273377285149321E-2</v>
+        <v>5.9647895414716046E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15313834873388107</v>
+        <v>0.15948736816729239</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12631693409309636</v>
+        <v>0.13155395457788474</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.142036130742595</v>
+        <v>0.14792485921451021</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.13848190551162515</v>
+        <v>0.14422327804527463</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4547925867337486E-2</v>
+        <v>6.7224042196829079E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1481628328257111E-2</v>
+        <v>9.5274398988632616E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0525539993499464E-2</v>
+        <v>3.1791109644971248E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2732926407895054E-3</v>
+        <v>6.5333794003578933E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8986243397665485E-2</v>
+        <v>0.10309015066954216</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0422107062484384E-2</v>
+        <v>2.126879475164211E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16255926938896603</v>
+        <v>0.16929887425583859</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12609592750334425</v>
+        <v>0.13132378519419599</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13832816179701499</v>
+        <v>0.1440631602131433</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14217450008574412</v>
+        <v>0.14806896526342839</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.28</v>
+        <v>6.03</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15955100724787913</v>
+        <v>0.17625020018811974</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.28</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3642.4253272400001</v>
+        <v>3497.4243189900003</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15955100724787913</v>
+        <v>0.17625020018811974</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.3637428371644488E-2</v>
+        <v>9.7519577143271544E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.3694267515923567E-2</v>
+        <v>6.633499170812604E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,12 +21842,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21862,15 +21865,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7570E15-5408-4804-BD31-A8296FD26F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82363EFC-02B3-48B7-8445-D2CC8FAD8AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.03</v>
+        <v>5.71</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3497.4243189900003</v>
+        <v>3311.8230284299998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.17625020018811974</v>
+        <v>0.19907787595736612</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.7519577143271544E-2</v>
+        <v>0.10298477235970709</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.633499170812604E-2</v>
+        <v>7.0052539404553416E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14224,24 +14224,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.633499170812604E-2</v>
+        <v>7.0052539404553416E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.633499170812604E-2</v>
+        <v>7.0052539404553416E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.4527363184079588E-2</v>
+        <v>9.982486865148861E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.3018242122719739E-2</v>
+        <v>6.6549912434325745E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.3018242122719739E-2</v>
+        <v>6.6549912434325745E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.7519577143271544E-2</v>
+        <v>0.10298477235970709</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2880972305755571E-2</v>
+        <v>8.7525790368424894E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.9509681813067213E-2</v>
+        <v>0.10508640653814279</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.1348177066642037E-2</v>
+        <v>3.3104992594019528E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-6.7859670438291985E-3</v>
+        <v>-7.1662664228178755E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.3981292848767372E-2</v>
+        <v>-3.5885673533812133E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>5.9647895414716046E-2</v>
+        <v>6.2990684649866513E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15948736816729239</v>
+        <v>0.16842536428174662</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13155395457788474</v>
+        <v>0.13892650544739843</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.14792485921451021</v>
+        <v>0.15621486883774019</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.14422327804527463</v>
+        <v>0.15230584353993101</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7224042196829079E-2</v>
+        <v>7.099141408877048E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5274398988632616E-2</v>
+        <v>0.10061376986014969</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1791109644971248E-2</v>
+        <v>3.3572748013866317E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5333794003578933E-3</v>
+        <v>6.8995232546686693E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10309015066954216</v>
+        <v>0.10886753214314174</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.126879475164211E-2</v>
+        <v>2.2460741217583527E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16929887425583859</v>
+        <v>0.17878672710380156</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13132378519419599</v>
+        <v>0.13868343690385324</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1440631602131433</v>
+        <v>0.15213675237920388</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14806896526342839</v>
+        <v>0.15636705088239461</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.03</v>
+        <v>5.71</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17625020018811974</v>
+        <v>0.19907787595736612</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.03</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3497.4243189900003</v>
+        <v>3311.8230284299998</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.17625020018811974</v>
+        <v>0.19907787595736612</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20481,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20672,22 +20672,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20877,10 +20877,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20896,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.7519577143271544E-2</v>
+        <v>0.10298477235970709</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.633499170812604E-2</v>
+        <v>7.0052539404553416E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21046,22 +21046,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21069,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21224,33 +21224,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21313,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21373,13 +21373,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21543,13 +21543,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21562,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21746,13 +21746,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21760,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21803,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,15 +21842,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21865,12 +21862,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82363EFC-02B3-48B7-8445-D2CC8FAD8AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26A08C4-22C8-4C4E-B00B-8DA363CDDC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>5.71</v>
+        <v>5.66</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3311.8230284299998</v>
+        <v>3282.82282678</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.19907787595736612</v>
+        <v>0.20280486606948164</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10298477235970709</v>
+        <v>0.10389453183284937</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>7.0052539404553416E-2</v>
+        <v>7.0671378091872794E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -14224,24 +14224,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>7.0052539404553416E-2</v>
+        <v>7.0671378091872794E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.0052539404553416E-2</v>
+        <v>7.0671378091872794E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.982486865148861E-2</v>
+        <v>0.10070671378091872</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6549912434325745E-2</v>
+        <v>6.7137809187279157E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6549912434325745E-2</v>
+        <v>6.7137809187279157E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10298477235970709</v>
+        <v>0.10389453183284937</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.7525790368424894E-2</v>
+        <v>8.8298986396414508E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10508640653814279</v>
+        <v>0.10601473168423946</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3104992594019528E-2</v>
+        <v>3.3397439525062106E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-7.1662664228178755E-3</v>
+        <v>-7.2295726633021321E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.5885673533812133E-2</v>
+        <v>-3.6202684784110824E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>6.2990684649866513E-2</v>
+        <v>6.3547139461261087E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.16842536428174662</v>
+        <v>0.16991322085667371</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13892650544739843</v>
+        <v>0.14015377139658039</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.15621486883774019</v>
+        <v>0.15759485884514074</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.15230584353993101</v>
+        <v>0.15365130152173251</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.099141408877048E-2</v>
+        <v>7.1618546722063497E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10061376986014969</v>
+        <v>0.1015025840815291</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3572748013866317E-2</v>
+        <v>3.3869327059925201E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8995232546686693E-3</v>
+        <v>6.9604731067417127E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10886753214314174</v>
+        <v>0.10982925945889385</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2460741217583527E-2</v>
+        <v>2.2659157659434971E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17878672710380156</v>
+        <v>0.18036611515242168</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13868343690385324</v>
+        <v>0.13990855560441728</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15213675237920388</v>
+        <v>0.15348071662283641</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15636705088239461</v>
+        <v>0.15774838525414719</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>5.71</v>
+        <v>5.66</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19907787595736612</v>
+        <v>0.20280486606948164</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>5.71</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3311.8230284299998</v>
+        <v>3282.82282678</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.19907787595736612</v>
+        <v>0.20280486606948164</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10298477235970709</v>
+        <v>0.10389453183284937</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>7.0052539404553416E-2</v>
+        <v>7.0671378091872794E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26A08C4-22C8-4C4E-B00B-8DA363CDDC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A68F5AB-BA7D-4768-90DA-97EF76884F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>5.66</v>
+        <v>5.69</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3282.82282678</v>
+        <v>3300.2229477700002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.20280486606948164</v>
+        <v>0.20056322920543154</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10389453183284937</v>
+        <v>0.1033467574998115</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>7.0671378091872794E-2</v>
+        <v>7.0298769771528991E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -14224,24 +14224,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>7.0671378091872794E-2</v>
+        <v>7.0298769771528991E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.0671378091872794E-2</v>
+        <v>7.0298769771528991E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>0.10070671378091872</v>
+        <v>0.10017574692442881</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7137809187279157E-2</v>
+        <v>6.6783831282952538E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7137809187279157E-2</v>
+        <v>6.6783831282952538E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10389453183284937</v>
+        <v>0.1033467574998115</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.8298986396414508E-2</v>
+        <v>8.7833438137733935E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10601473168423946</v>
+        <v>0.1054557787931099</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3397439525062106E-2</v>
+        <v>3.3221354606652286E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-7.2295726633021321E-3</v>
+        <v>-7.1914554084868305E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6202684784110824E-2</v>
+        <v>-3.6011809468904615E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>6.3547139461261087E-2</v>
+        <v>6.3212093031764102E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.16991322085667371</v>
+        <v>0.16901736907711301</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.14015377139658039</v>
+        <v>0.13941482356847892</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.15759485884514074</v>
+        <v>0.15676395449270589</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.15365130152173251</v>
+        <v>0.15284118921142459</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1618546722063497E-2</v>
+        <v>7.1240944542509552E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1015025840815291</v>
+        <v>0.10096742107231189</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3869327059925201E-2</v>
+        <v>3.3690754158027525E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9604731067417127E-3</v>
+        <v>6.923774654509331E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10982925945889385</v>
+        <v>0.10925019482202797</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2659157659434971E-2</v>
+        <v>2.2539689341371162E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18036611515242168</v>
+        <v>0.17941515145214529</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13990855560441728</v>
+        <v>0.13917090065395463</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15348071662283641</v>
+        <v>0.15267150370566854</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15774838525414719</v>
+        <v>0.15691667144788629</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>5.66</v>
+        <v>5.69</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20280486606948164</v>
+        <v>0.20056322920543154</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>5.66</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3282.82282678</v>
+        <v>3300.2229477700002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.20280486606948164</v>
+        <v>0.20056322920543154</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10389453183284937</v>
+        <v>0.1033467574998115</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>7.0671378091872794E-2</v>
+        <v>7.0298769771528991E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A68F5AB-BA7D-4768-90DA-97EF76884F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD971B09-6B9D-4D4C-94AF-513852F53153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>5.69</v>
+        <v>5.6</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3300.2229477700002</v>
+        <v>3248.0225847999995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.20056322920543154</v>
+        <v>0.19957778695608511</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>8.3894050049409827</v>
+        <v>8.3930917865501833</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>4.5980258861772203</v>
+        <v>4.5082322850718066</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>5.6874672857327493</v>
+        <v>5.5843966373132385</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>6.9782344788773099</v>
+        <v>6.8602468616155488</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>7.8454252449020769</v>
+        <v>7.7177949990241954</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>6888.8446443333341</v>
+        <v>6864.677809625</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-78483.555355666671</v>
+        <v>-78507.722190375003</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-75111.544966315007</v>
+        <v>-75107.557438588134</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>289869.92812368623</v>
+        <v>289762.92396067944</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>341067.34067849925</v>
+        <v>341047.16137151787</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.1033467574998115</v>
+        <v>0.10500147473343946</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,14 +5890,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>7.0298769771528991E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.68022230665202266</v>
+        <v>0.59522973518862243</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5917,11 +5917,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.1658525572748466</v>
+        <v>0.16584375248097633</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.11824413281411626</v>
+        <v>0.11820514758456895</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>5.3128459724860015E-2</v>
+        <v>5.3125639236926585E-2</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>3.7877791884180549E-2</v>
+        <v>3.7865303531682992E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>364748.53556666663</v>
+        <v>367165.21903749998</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.62887241262797666</v>
+        <v>0.63303907929464343</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-2.9414955196239703</v>
+        <v>-2.9373288529573038</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>12.86 HKD</v>
+        <v>12.87 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-9.6804914114679869E-2</v>
+        <v>-0.10125201658765973</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>10.31 HKD</v>
+        <v>10.32 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-2.4979569163920998E-2</v>
+        <v>-3.015046515037512E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>8.24 HKD</v>
+        <v>8.25 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.4111240073368816E-2</v>
+        <v>4.8057775524901515E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.55 HKD</v>
+        <v>6.56 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.14222478353438384</v>
+        <v>0.13507645584940894</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.2419679577668665</v>
+        <v>0.23342996477283839</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>8.3894050049409827</v>
+        <v>8.3930917865501833</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6562,15 +6562,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>0.73194063044404789</v>
+        <v>0.64044805163854179</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>3.8660852557331729</v>
+        <v>3.8677842334332651</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>4.5980258861772203</v>
+        <v>4.5082322850718066</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6583,15 +6583,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>0.84160157890763132</v>
+        <v>0.73640138154417734</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>4.8458657068251183</v>
+        <v>4.8479952557690611</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>5.6874672857327493</v>
+        <v>5.5843966373132385</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6630,15 +6630,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>0.96504125037545974</v>
+        <v>0.8444110940785271</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>6.0131932285018506</v>
+        <v>6.0158357675370215</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>6.9782344788773099</v>
+        <v>6.8602468616155488</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6651,15 +6651,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.0449500908692064</v>
+        <v>0.91433132951055562</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>6.8004751540328705</v>
+        <v>6.8034636695136399</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>7.8454252449020769</v>
+        <v>7.7177949990241954</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -7435,8 +7435,8 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="37">
-        <f>0.25+0.15</f>
-        <v>0.4</v>
+        <f>0.25+0.1</f>
+        <v>0.35</v>
       </c>
       <c r="D25" s="37">
         <f>0.42+0.15</f>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>364748.53556666663</v>
+        <v>367165.21903749998</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10440,11 +10440,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-700179.71776666667</v>
+        <v>-697763.03429583332</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-688884.46443333337</v>
+        <v>-686467.78096250002</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>1.5048036572106489</v>
+        <v>1.5100155041364474</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.5294770812790845</v>
+        <v>1.5348615466303397</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10473,7 +10473,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>688884.46443333337</v>
+        <v>686467.78096250002</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10605,11 +10605,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>364748.53556666663</v>
+        <v>367165.21903749998</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.62887241262797666</v>
+        <v>0.63303907929464343</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10639,11 +10639,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2562540.7355666668</v>
+        <v>2564957.4190375004</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>4.4181429606829417</v>
+        <v>4.4223096273496081</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11124,24 +11124,24 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-78483.555355666671</v>
+        <v>-78507.722190375003</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>-73613.071876313799</v>
+        <v>-73720.076039320571</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-78971.418852021772</v>
+        <v>-79075.331151620063</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>-73109.123171121537</v>
+        <v>-73198.225261499756</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>-83036.406166952918</v>
+        <v>-83053.973364167803</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
@@ -11179,24 +11179,24 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>455221.48464433337</v>
+        <v>455197.31780962506</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>324548.92812368623</v>
+        <v>324441.92396067944</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>407101.5811479782</v>
+        <v>406997.66884837992</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>143460.87682887848</v>
+        <v>143371.77473850024</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>5841.5938330470817</v>
+        <v>5824.0266358321969</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-75111.544966315007</v>
+        <v>-75107.557438588134</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11346,26 +11346,26 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>341067.34067849925</v>
+        <v>341047.16137151787</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>289869.92812368623</v>
+        <v>289762.92396067944</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>348027.5811479782</v>
+        <v>347923.66884837992</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>109637.87682887848</v>
+        <v>109548.77473850024</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>-23733.406166952918</v>
+        <v>-23750.973364167803</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
@@ -11564,26 +11564,26 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>341067.34067849925</v>
+        <v>341047.16137151787</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>289869.92812368623</v>
+        <v>289762.92396067944</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>348027.5811479782</v>
+        <v>347923.66884837992</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>109637.87682887848</v>
+        <v>109548.77473850024</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>-23733.406166952918</v>
+        <v>-23750.973364167803</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
@@ -12301,19 +12301,19 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>9.9559718735801314E-2</v>
+        <v>9.959255451806541E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.13832665508496433</v>
+        <v>0.13836197184947133</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>0.22995119456400367</v>
+        <v>0.23009410366977429</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.7827700450420583</v>
+        <v>4.7971964668063007</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
@@ -12439,24 +12439,24 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>6888.8446443333341</v>
+        <v>6864.677809625</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>30501.928123686208</v>
+        <v>30394.923960679429</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>29620.581147978221</v>
+        <v>29516.668848379937</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>25398.876828878463</v>
+        <v>25309.774738500251</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>5007.5938330470863</v>
+        <v>4990.0266358321987</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
@@ -12551,24 +12551,24 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-78483.555355666671</v>
+        <v>-78507.722190375003</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-73613.071876313799</v>
+        <v>-73720.076039320571</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>-78971.418852021772</v>
+        <v>-79075.331151620063</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>-73109.123171121537</v>
+        <v>-73198.225261499756</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>-83036.406166952918</v>
+        <v>-83053.973364167803</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>9.159739929751276E-3</v>
+        <v>9.1625604176847099E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235" t="s">
@@ -13525,19 +13525,19 @@
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>8.5913105078061179E-3</v>
+        <v>8.6037988603036714E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>9.086105073161193E-3</v>
+        <v>9.0980607665787448E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1112565149345567E-3</v>
+        <v>9.1223609019965186E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>1.1058614681685883E-2</v>
+        <v>1.1060954244222416E-2</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
@@ -13575,26 +13575,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>5.3128459724860015E-2</v>
+        <v>5.3125639236926585E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>3.7877791884180549E-2</v>
+        <v>3.7865303531682992E-2</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>4.6839322321051209E-2</v>
+        <v>4.6827366627633656E-2</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>1.7878874645861673E-2</v>
+        <v>1.7867770258799709E-2</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>7.7797123344543119E-4</v>
+        <v>7.7563167090889749E-4</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>8.7661958546019023E-3</v>
+        <v>8.7657304740928858E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13747,26 +13747,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>3.9805639856520164E-2</v>
+        <v>3.9803284749095752E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>3.383043929440125E-2</v>
+        <v>3.3817950941903693E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>4.0042526988075082E-2</v>
+        <v>4.0030571294657535E-2</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>1.3663668448089078E-2</v>
+        <v>1.3652564061027113E-2</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>3.1607653317339002E-3</v>
+        <v>3.1631048942704337E-3</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
@@ -13968,26 +13968,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>3.9805639856520164E-2</v>
+        <v>3.9803284749095752E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>3.383043929440125E-2</v>
+        <v>3.3817950941903693E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>4.0042526988075082E-2</v>
+        <v>4.0030571294657535E-2</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>1.3663668448089078E-2</v>
+        <v>1.3652564061027113E-2</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>3.1607653317339002E-3</v>
+        <v>3.1631048942704337E-3</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
@@ -14037,12 +14037,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14093,12 +14093,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>232001.61320000002</v>
+        <v>203001.41154999999</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>232001.61320000002</v>
+        <v>203001.41154999999</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14148,24 +14148,24 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.68022230665202266</v>
+        <v>0.59522973518862243</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.80036454523494382</v>
+        <v>0.70057759210611448</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.94993131785561225</v>
+        <v>0.95021502821089077</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>2.0102681565422884</v>
+        <v>2.0119032190557333</v>
       </c>
       <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v>-9.2865529283737391</v>
+        <v>-9.2796842117010456</v>
       </c>
       <c r="K90" s="152">
         <f t="shared" si="37"/>
@@ -14224,24 +14224,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>7.0298769771528991E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.0298769771528991E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>0.10017574692442881</v>
+        <v>0.10178571428571428</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6783831282952538E-2</v>
+        <v>6.7857142857142866E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6783831282952538E-2</v>
+        <v>6.7857142857142866E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -14361,26 +14361,26 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.40262821780402724</v>
+        <v>0.40301633109780366</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-0.20278146007564812</v>
+        <v>-0.20284082982906526</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>1.8377184787011509</v>
+        <v>1.8387572769515774</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>23.558516207903942</v>
+        <v>23.617293790589578</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.0668137597996945</v>
+        <v>-1.0666128333866958</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
@@ -14972,19 +14972,19 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>5.2126793896166532</v>
+        <v>5.2146043370443111</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>4.7787994115697456</v>
+        <v>4.7802266672601066</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>15.495420461777091</v>
+        <v>15.508023746092499</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-49.063374713630502</v>
+        <v>-49.027085422812533</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -15080,24 +15080,24 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>5.3128459724860015E-2</v>
+        <v>5.3125639236926585E-2</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>3.7877791884180549E-2</v>
+        <v>3.7865303531682992E-2</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>4.6839322321051209E-2</v>
+        <v>4.6827366627633656E-2</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>1.7878874645861673E-2</v>
+        <v>1.7867770258799709E-2</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>7.7797123344543119E-4</v>
+        <v>7.7563167090889749E-4</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
@@ -15245,26 +15245,26 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.1658525572748466</v>
+        <v>0.16584375248097633</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.11824413281411626</v>
+        <v>0.11820514758456895</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.13987279257917012</v>
+        <v>0.13983709017907836</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>5.1381676140143856E-2</v>
+        <v>5.1349763504082914E-2</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>2.0668141227660726E-3</v>
+        <v>2.0605986732947766E-3</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
@@ -15366,26 +15366,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.58804305017392744</v>
+        <v>0.58800825850726091</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.49977226300370614</v>
+        <v>0.49958777435031987</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.60004338133279533</v>
+        <v>0.59986422344132206</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.18902950771185151</v>
+        <v>0.18887588448630707</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-4.0919381274290068E-2</v>
+        <v>-4.0949669334743748E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
@@ -15423,50 +15423,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1033467574998115</v>
+        <v>0.10500147473343946</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.7833438137733935E-2</v>
+        <v>8.9212102562557127E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.1054557787931099</v>
+        <v>0.10711861132880751</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3221354606652286E-2</v>
+        <v>3.3727836515411981E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-7.1914554084868305E-3</v>
+        <v>-7.3124409526328128E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6011809468904615E-2</v>
+        <v>-3.6590570692512016E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>6.3212093031764102E-2</v>
+        <v>6.4228001669774604E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.16901736907711301</v>
+        <v>0.17173371965156664</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13941482356847892</v>
+        <v>0.14165541894725805</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.15676395449270589</v>
+        <v>0.15928337518991012</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.15284118921142459</v>
+        <v>0.15529756546660822</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15480,43 +15480,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1240944542509552E-2</v>
+        <v>7.2385888294085612E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10096742107231189</v>
+        <v>0.10259011176811693</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3690754158027525E-2</v>
+        <v>3.4232212706995835E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.923774654509331E-3</v>
+        <v>7.0350496043139468E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10925019482202797</v>
+        <v>0.11100600152452487</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2539689341371162E-2</v>
+        <v>2.2901934348643203E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17941515145214529</v>
+        <v>0.18229860924334051</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13917090065395463</v>
+        <v>0.14140757584303607</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15267150370566854</v>
+        <v>0.15512515287236683</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15691667144788629</v>
+        <v>0.15943854652472736</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>341067.34067849925</v>
+        <v>341047.16137151787</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>364748.53556666663</v>
+        <v>367165.21903749998</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>4704377.1128068864</v>
+        <v>4704098.7775381776</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-78483.555355666671</v>
+        <v>-78507.722190375003</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16364,14 +16364,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>-1706079.2644333334</v>
+        <v>-1703662.5809625001</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>-1706079.2644333334</v>
+        <v>-1703662.5809625001</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>2998297.8483735528</v>
+        <v>3000436.1965756775</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-2.9414955196239703</v>
+        <v>-2.9373288529573038</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-78483.555355666671</v>
+        <v>-78507.722190375003</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>2998297.8483735528</v>
+        <v>3000436.1965756775</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.2435802828925357</v>
+        <v>8.2472670645017345</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16675,7 +16675,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>465895.58544433338</v>
+        <v>465871.41860962508</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16683,11 +16683,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>349199.36286650889</v>
+        <v>349179.18355952745</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>2.3842863910195078E-2</v>
+        <v>2.3844274660744125E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16695,7 +16695,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>325593.81153054442</v>
+        <v>325574.99632589973</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>476783.16826033324</v>
+        <v>476759.00142562494</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16732,11 +16732,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>357494.02549827856</v>
+        <v>357473.84619129717</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>2.3753372754407032E-2</v>
+        <v>2.3754745478278716E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16744,7 +16744,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>310795.11673879501</v>
+        <v>310777.57342444104</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>487888.50273265329</v>
+        <v>487864.33589794498</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>365954.58138268383</v>
+        <v>365934.40207570238</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>2.3666286094188305E-2</v>
+        <v>2.3667622049971415E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>296643.80688877573</v>
+        <v>296627.44948611461</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="G24" s="281">
         <f t="shared" si="8"/>
-        <v>499215.94389441994</v>
+        <v>499191.77705971163</v>
       </c>
       <c r="H24" s="303">
         <f t="shared" si="2"/>
@@ -16838,11 +16838,11 @@
       </c>
       <c r="I24" s="281">
         <f t="shared" si="9"/>
-        <v>374584.34838477738</v>
+        <v>374564.16907779593</v>
       </c>
       <c r="J24" s="303">
         <f t="shared" si="10"/>
-        <v>2.3581524705846624E-2</v>
+        <v>2.3582825099642601E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="L24" s="281">
         <f t="shared" si="4"/>
-        <v>283113.39874103473</v>
+        <v>283098.14708354184</v>
       </c>
       <c r="N24" s="279"/>
       <c r="O24" s="279"/>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="G25" s="281">
         <f t="shared" si="8"/>
-        <v>510769.93387942156</v>
+        <v>510745.76704471326</v>
       </c>
       <c r="H25" s="303">
         <f t="shared" si="2"/>
@@ -16895,11 +16895,11 @@
       </c>
       <c r="I25" s="281">
         <f t="shared" si="9"/>
-        <v>383386.71072691242</v>
+        <v>383366.53141993098</v>
       </c>
       <c r="J25" s="303">
         <f t="shared" si="10"/>
-        <v>2.3499012652533846E-2</v>
+        <v>2.3500278640658845E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="L25" s="281">
         <f t="shared" si="4"/>
-        <v>270178.3534546874</v>
+        <v>270164.13279502036</v>
       </c>
       <c r="N25" s="279"/>
       <c r="O25" s="279"/>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="G26" s="281">
         <f t="shared" si="8"/>
-        <v>522555.00366412336</v>
+        <v>522530.83682941506</v>
       </c>
       <c r="H26" s="303">
         <f t="shared" si="2"/>
@@ -16952,11 +16952,11 @@
       </c>
       <c r="I26" s="281">
         <f t="shared" si="9"/>
-        <v>392365.12031589029</v>
+        <v>392344.94100890891</v>
       </c>
       <c r="J26" s="303">
         <f t="shared" si="10"/>
-        <v>2.341867711573653E-2</v>
+        <v>2.3419909807262718E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="L26" s="281">
         <f t="shared" si="4"/>
-        <v>257814.05415189188</v>
+        <v>257800.79479555905</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="G27" s="281">
         <f t="shared" si="8"/>
-        <v>534575.7748445191</v>
+        <v>534551.60800981079</v>
       </c>
       <c r="H27" s="303">
         <f t="shared" si="2"/>
@@ -17001,11 +17001,11 @@
       </c>
       <c r="I27" s="281">
         <f t="shared" si="9"/>
-        <v>401523.09809664771</v>
+        <v>401502.91878966626</v>
       </c>
       <c r="J27" s="303">
         <f t="shared" si="10"/>
-        <v>2.334044823705117E-2</v>
+        <v>2.3341648696189932E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="L27" s="281">
         <f t="shared" si="4"/>
-        <v>245996.78297212912</v>
+        <v>245984.41993592129</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="G28" s="281">
         <f t="shared" si="8"/>
-        <v>546836.96144852298</v>
+        <v>546812.79461381468</v>
       </c>
       <c r="H28" s="303">
         <f t="shared" si="2"/>
@@ -17050,11 +17050,11 @@
       </c>
       <c r="I28" s="281">
         <f t="shared" si="9"/>
-        <v>410864.23543302045</v>
+        <v>410844.05612603901</v>
       </c>
       <c r="J28" s="303">
         <f t="shared" si="10"/>
-        <v>2.3264258969540874E-2</v>
+        <v>2.326542821788613E-2</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -17062,7 +17062,7 @@
       </c>
       <c r="L28" s="281">
         <f t="shared" si="4"/>
-        <v>234703.69774999219</v>
+        <v>234692.17044350473</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G29" s="281">
         <f t="shared" si="8"/>
-        <v>559343.37178460672</v>
+        <v>559319.20494989841</v>
       </c>
       <c r="H29" s="303">
         <f t="shared" si="2"/>
@@ -17099,11 +17099,11 @@
       </c>
       <c r="I29" s="281">
         <f t="shared" si="9"/>
-        <v>420392.19551612041</v>
+        <v>420372.01620913902</v>
       </c>
       <c r="J29" s="303">
         <f t="shared" si="10"/>
-        <v>2.3190044937978493E-2</v>
+        <v>2.3191183956613015E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="L29" s="281">
         <f t="shared" si="4"/>
-        <v>223912.80843629298</v>
+        <v>223902.06036497603</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="G30" s="281">
         <f t="shared" si="8"/>
-        <v>572099.91032741219</v>
+        <v>572075.74349270388</v>
       </c>
       <c r="H30" s="303">
         <f t="shared" si="2"/>
@@ -17148,11 +17148,11 @@
       </c>
       <c r="I30" s="281">
         <f t="shared" si="9"/>
-        <v>430110.7148008825</v>
+        <v>430090.53549390106</v>
       </c>
       <c r="J30" s="303">
         <f t="shared" si="10"/>
-        <v>2.3117744307385557E-2</v>
+        <v>2.3118854038864045E-2</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="L30" s="281">
         <f t="shared" si="4"/>
-        <v>213602.95336957747</v>
+        <v>213592.93185785998</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="G31" s="281">
         <f t="shared" si="8"/>
-        <v>585111.57964107371</v>
+        <v>585087.41280636541</v>
       </c>
       <c r="H31" s="303">
         <f t="shared" si="2"/>
@@ -17197,11 +17197,11 @@
       </c>
       <c r="I31" s="281">
         <f t="shared" si="9"/>
-        <v>440023.60447133973</v>
+        <v>440003.42516435834</v>
       </c>
       <c r="J31" s="303">
         <f t="shared" si="10"/>
-        <v>2.3047297659269717E-2</v>
+        <v>2.3048379009488418E-2</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L31" s="281">
         <f t="shared" si="4"/>
-        <v>203753.77549350605</v>
+        <v>203744.43142663664</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="G32" s="281">
         <f t="shared" si="8"/>
-        <v>598383.48234100849</v>
+        <v>598359.31550630019</v>
       </c>
       <c r="H32" s="303">
         <f t="shared" si="2"/>
@@ -17246,11 +17246,11 @@
       </c>
       <c r="I32" s="281">
         <f t="shared" si="9"/>
-        <v>450134.75193520612</v>
+        <v>450114.57262822468</v>
       </c>
       <c r="J32" s="303">
         <f t="shared" si="10"/>
-        <v>2.2978647875070868E-2</v>
+        <v>2.2979701715025058E-2</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="L32" s="281">
         <f t="shared" si="4"/>
-        <v>194345.69860493013</v>
+        <v>194336.98618826864</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="G33" s="281">
         <f t="shared" si="8"/>
-        <v>611920.82309494214</v>
+        <v>611896.65626023384</v>
       </c>
       <c r="H33" s="303">
         <f t="shared" si="2"/>
@@ -17295,11 +17295,11 @@
       </c>
       <c r="I33" s="281">
         <f t="shared" si="9"/>
-        <v>460448.12234835001</v>
+        <v>460427.94304136856</v>
       </c>
       <c r="J33" s="303">
         <f t="shared" si="10"/>
-        <v>2.2911740026303029E-2</v>
+        <v>2.2912767193747907E-2</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="L33" s="281">
         <f t="shared" si="4"/>
-        <v>185359.9037077823</v>
+        <v>185351.78024236366</v>
       </c>
       <c r="N33" s="279"/>
       <c r="O33" s="279"/>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="G34" s="281">
         <f t="shared" si="8"/>
-        <v>625728.91066395433</v>
+        <v>625704.74382924603</v>
       </c>
       <c r="H34" s="303">
         <f t="shared" si="2"/>
@@ -17352,11 +17352,11 @@
       </c>
       <c r="I34" s="281">
         <f t="shared" si="9"/>
-        <v>470967.76016975672</v>
+        <v>470947.58086277527</v>
       </c>
       <c r="J34" s="303">
         <f t="shared" si="10"/>
-        <v>2.2846521270963427E-2</v>
+        <v>2.2847522571977308E-2</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="L34" s="281">
         <f t="shared" si="4"/>
-        <v>176778.3055390451</v>
+        <v>176770.73121231445</v>
       </c>
       <c r="N34" s="279"/>
       <c r="O34" s="279"/>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="G35" s="281">
         <f t="shared" si="8"/>
-        <v>639813.15998434671</v>
+        <v>639788.99314963841</v>
       </c>
       <c r="H35" s="303">
         <f t="shared" si="2"/>
@@ -17409,11 +17409,11 @@
       </c>
       <c r="I35" s="281">
         <f t="shared" si="9"/>
-        <v>481697.79074759141</v>
+        <v>481677.61144060991</v>
       </c>
       <c r="J35" s="303">
         <f t="shared" si="10"/>
-        <v>2.2782940755790015E-2</v>
+        <v>2.2783916966251816E-2</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
@@ -17421,7 +17421,7 @@
       </c>
       <c r="L35" s="281">
         <f t="shared" si="4"/>
-        <v>168583.52932498849</v>
+        <v>168576.46701568249</v>
       </c>
       <c r="N35" s="279"/>
       <c r="O35" s="279"/>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="G36" s="281">
         <f t="shared" si="8"/>
-        <v>654179.09429114696</v>
+        <v>654154.92745643866</v>
       </c>
       <c r="H36" s="303">
         <f t="shared" si="2"/>
@@ -17466,11 +17466,11 @@
       </c>
       <c r="I36" s="281">
         <f t="shared" si="9"/>
-        <v>492642.42193698289</v>
+        <v>492622.24263000139</v>
       </c>
       <c r="J36" s="303">
         <f t="shared" si="10"/>
-        <v>2.2720949523985734E-2</v>
+        <v>2.2721901390969856E-2</v>
       </c>
       <c r="K36" s="119">
         <f t="shared" si="3"/>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="L36" s="281">
         <f t="shared" si="4"/>
-        <v>160758.8878185146</v>
+        <v>160752.30291473281</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G37" s="281">
         <f t="shared" si="8"/>
-        <v>668832.34728408314</v>
+        <v>668808.18044937484</v>
       </c>
       <c r="H37" s="303">
         <f t="shared" si="2"/>
@@ -17515,11 +17515,11 @@
       </c>
       <c r="I37" s="281">
         <f t="shared" si="9"/>
-        <v>503805.94575016206</v>
+        <v>503785.76644318056</v>
       </c>
       <c r="J37" s="303">
         <f t="shared" si="10"/>
-        <v>2.2660500428051122E-2</v>
+        <v>2.2661428671144845E-2</v>
       </c>
       <c r="K37" s="119">
         <f t="shared" si="3"/>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="L37" s="281">
         <f t="shared" si="4"/>
-        <v>153288.35866176136</v>
+        <v>153282.21889133545</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="G38" s="281">
         <f t="shared" si="8"/>
-        <v>683778.66533687804</v>
+        <v>683754.49850216974</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="2"/>
@@ -17564,11 +17564,11 @@
       </c>
       <c r="I38" s="281">
         <f t="shared" si="9"/>
-        <v>515192.74003960483</v>
+        <v>515172.56073262345</v>
       </c>
       <c r="J38" s="303">
         <f t="shared" si="10"/>
-        <v>2.2601548047409326E-2</v>
+        <v>2.2602453359958474E-2</v>
       </c>
       <c r="K38" s="119">
         <f t="shared" si="3"/>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="L38" s="281">
         <f t="shared" si="4"/>
-        <v>146156.56211204073</v>
+        <v>146150.83738437091</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="G39" s="281">
         <f t="shared" si="8"/>
-        <v>699023.90975072898</v>
+        <v>698999.74291602068</v>
       </c>
       <c r="H39" s="303">
         <f t="shared" si="2"/>
@@ -17613,11 +17613,11 @@
       </c>
       <c r="I39" s="281">
         <f t="shared" si="9"/>
-        <v>526807.2702148367</v>
+        <v>526787.09090785519</v>
       </c>
       <c r="J39" s="303">
         <f t="shared" si="10"/>
-        <v>2.2544048610504408E-2</v>
+        <v>2.2544931660791079E-2</v>
       </c>
       <c r="K39" s="119">
         <f t="shared" si="3"/>
@@ -17625,7 +17625,7 @@
       </c>
       <c r="L39" s="281">
         <f t="shared" si="4"/>
-        <v>139348.73916367255</v>
+        <v>139343.40142225544</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="G40" s="281">
         <f t="shared" si="8"/>
-        <v>714574.05905285699</v>
+        <v>714549.89221814869</v>
       </c>
       <c r="H40" s="303">
         <f t="shared" si="2"/>
@@ -17662,11 +17662,11 @@
       </c>
       <c r="I40" s="281">
         <f t="shared" si="9"/>
-        <v>538654.09099357307</v>
+        <v>538633.91168659169</v>
       </c>
       <c r="J40" s="303">
         <f t="shared" si="10"/>
-        <v>2.2487959921101863E-2</v>
+        <v>2.248882135346153E-2</v>
       </c>
       <c r="K40" s="119">
         <f t="shared" si="3"/>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="L40" s="281">
         <f t="shared" si="4"/>
-        <v>132850.7300932786</v>
+        <v>132845.75317820438</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="G41" s="281">
         <f t="shared" si="8"/>
-        <v>730435.21134102752</v>
+        <v>730411.04450631922</v>
       </c>
       <c r="H41" s="303">
         <f t="shared" si="2"/>
@@ -17711,11 +17711,11 @@
       </c>
       <c r="I41" s="281">
         <f t="shared" si="9"/>
-        <v>550737.8481878842</v>
+        <v>550717.66888090281</v>
       </c>
       <c r="J41" s="303">
         <f t="shared" si="10"/>
-        <v>2.2433241288527306E-2</v>
+        <v>2.2434081724401533E-2</v>
       </c>
       <c r="K41" s="119">
         <f t="shared" si="3"/>
@@ -17723,7 +17723,7 @@
       </c>
       <c r="L41" s="281">
         <f t="shared" si="4"/>
-        <v>126648.95345157865</v>
+        <v>126644.31297132297</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="G42" s="281">
         <f t="shared" si="8"/>
-        <v>746613.58667496138</v>
+        <v>746589.41984025307</v>
       </c>
       <c r="H42" s="303">
         <f t="shared" si="2"/>
@@ -17760,11 +17760,11 @@
       </c>
       <c r="I42" s="281">
         <f t="shared" si="9"/>
-        <v>563063.28052608145</v>
+        <v>563043.10121910006</v>
       </c>
       <c r="J42" s="303">
         <f t="shared" si="10"/>
-        <v>2.237985346159177E-2</v>
+        <v>2.2380673500531412E-2</v>
       </c>
       <c r="K42" s="119">
         <f t="shared" si="3"/>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="L42" s="281">
         <f t="shared" si="4"/>
-        <v>120730.38552064238</v>
+        <v>120726.0587325252</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="G43" s="281">
         <f t="shared" si="8"/>
-        <v>763115.52951557387</v>
+        <v>763091.36268086557</v>
       </c>
       <c r="H43" s="303">
         <f t="shared" si="2"/>
@@ -17809,11 +17809,11 @@
       </c>
       <c r="I43" s="281">
         <f t="shared" si="9"/>
-        <v>575635.22151104279</v>
+        <v>575615.04220406129</v>
       </c>
       <c r="J43" s="303">
         <f t="shared" si="10"/>
-        <v>2.232775856599134E-2</v>
+        <v>2.2328558786601782E-2</v>
       </c>
       <c r="K43" s="119">
         <f t="shared" si="3"/>
@@ -17821,7 +17821,7 @@
       </c>
       <c r="L43" s="281">
         <f t="shared" si="4"/>
-        <v>115082.54025186606</v>
+        <v>115078.50595059126</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="G44" s="281">
         <f t="shared" si="8"/>
-        <v>779947.51121299865</v>
+        <v>779923.34437829035</v>
       </c>
       <c r="H44" s="303">
         <f t="shared" si="2"/>
@@ -17858,11 +17858,11 @@
       </c>
       <c r="I44" s="281">
         <f t="shared" si="9"/>
-        <v>588458.60131570313</v>
+        <v>588438.42200872174</v>
       </c>
       <c r="J44" s="303">
         <f t="shared" si="10"/>
-        <v>2.2276920044953075E-2</v>
+        <v>2.2277701005795514E-2</v>
       </c>
       <c r="K44" s="119">
         <f t="shared" si="3"/>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="L44" s="281">
         <f t="shared" si="4"/>
-        <v>109693.44969662187</v>
+        <v>109689.68811035169</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="G45" s="281">
         <f t="shared" si="8"/>
-        <v>797116.13254437188</v>
+        <v>797091.96570966358</v>
       </c>
       <c r="H45" s="303">
         <f t="shared" si="2"/>
@@ -17907,11 +17907,11 @@
       </c>
       <c r="I45" s="281">
         <f t="shared" si="9"/>
-        <v>601538.44871645677</v>
+        <v>601518.26940947538</v>
       </c>
       <c r="J45" s="303">
         <f t="shared" si="10"/>
-        <v>2.222730260295136E-2</v>
+        <v>2.2228064843392792E-2</v>
       </c>
       <c r="K45" s="119">
         <f t="shared" si="3"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="L45" s="281">
         <f t="shared" si="4"/>
-        <v>104551.64493854574</v>
+        <v>104548.13763200011</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="G46" s="281">
         <f t="shared" si="8"/>
-        <v>814628.12630237266</v>
+        <v>814603.95946766436</v>
       </c>
       <c r="H46" s="303">
         <f t="shared" si="2"/>
@@ -17956,11 +17956,11 @@
       </c>
       <c r="I46" s="281">
         <f t="shared" si="9"/>
-        <v>614879.89306522557</v>
+        <v>614859.71375824418</v>
       </c>
       <c r="J46" s="303">
         <f t="shared" si="10"/>
-        <v>2.2178872152289308E-2</v>
+        <v>2.2179616193314322E-2</v>
       </c>
       <c r="K46" s="119">
         <f t="shared" si="3"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="L46" s="281">
         <f t="shared" si="4"/>
-        <v>99646.137533752277</v>
+        <v>99642.867317858938</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="G47" s="281">
         <f t="shared" si="8"/>
-        <v>832490.35993553337</v>
+        <v>832466.19310082507</v>
       </c>
       <c r="H47" s="303">
         <f t="shared" si="2"/>
@@ -18005,11 +18005,11 @@
       </c>
       <c r="I47" s="281">
         <f t="shared" si="9"/>
-        <v>628488.16630096966</v>
+        <v>628467.98699398816</v>
       </c>
       <c r="J47" s="303">
         <f t="shared" si="10"/>
-        <v>2.2131595762394873E-2</v>
+        <v>2.2132322107371927E-2</v>
       </c>
       <c r="K47" s="119">
         <f t="shared" si="3"/>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="L47" s="281">
         <f t="shared" si="4"/>
-        <v>94966.401462874841</v>
+        <v>94963.352310526709</v>
       </c>
       <c r="N47" s="279"/>
       <c r="O47" s="279"/>
@@ -18054,7 +18054,7 @@
       </c>
       <c r="G48" s="281">
         <f t="shared" si="8"/>
-        <v>850709.83824135736</v>
+        <v>850685.67140664905</v>
       </c>
       <c r="H48" s="303">
         <f t="shared" si="2"/>
@@ -18062,11 +18062,11 @@
       </c>
       <c r="I48" s="281">
         <f t="shared" si="9"/>
-        <v>642368.60500142863</v>
+        <v>642348.42569444724</v>
       </c>
       <c r="J48" s="303">
         <f t="shared" si="10"/>
-        <v>2.2085441611659373E-2</v>
+        <v>2.2086150747073541E-2</v>
       </c>
       <c r="K48" s="119">
         <f t="shared" si="3"/>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="L48" s="281">
         <f t="shared" si="4"/>
-        <v>90502.355596692374</v>
+        <v>90499.512564199962</v>
       </c>
       <c r="N48" s="279"/>
       <c r="O48" s="279"/>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="G49" s="281">
         <f t="shared" si="8"/>
-        <v>869293.70611329784</v>
+        <v>869269.53927858954</v>
       </c>
       <c r="H49" s="303">
         <f t="shared" si="2"/>
@@ -18119,11 +18119,11 @@
       </c>
       <c r="I49" s="281">
         <f t="shared" si="9"/>
-        <v>656526.65247589687</v>
+        <v>656506.47316891549</v>
       </c>
       <c r="J49" s="303">
         <f t="shared" si="10"/>
-        <v>2.204037894167743E-2</v>
+        <v>2.2041071337820961E-2</v>
       </c>
       <c r="K49" s="119">
         <f t="shared" si="3"/>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L49" s="281">
         <f t="shared" si="4"/>
-        <v>86244.34667520551</v>
+        <v>86241.695829058735</v>
       </c>
       <c r="N49" s="279"/>
       <c r="O49" s="279"/>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="G50" s="281">
         <f t="shared" si="8"/>
-        <v>888249.25134267728</v>
+        <v>888225.08450796898</v>
       </c>
       <c r="H50" s="303">
         <f t="shared" si="2"/>
@@ -18176,11 +18176,11 @@
       </c>
       <c r="I50" s="281">
         <f t="shared" si="9"/>
-        <v>670967.86089985457</v>
+        <v>670947.68159287318</v>
       </c>
       <c r="J50" s="303">
         <f t="shared" si="10"/>
-        <v>2.1996378013743989E-2</v>
+        <v>2.1997054125378002E-2</v>
       </c>
       <c r="K50" s="119">
         <f t="shared" si="3"/>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="L50" s="281">
         <f t="shared" si="4"/>
-        <v>82183.132798341918</v>
+        <v>82180.661146923012</v>
       </c>
       <c r="N50" s="279"/>
       <c r="O50" s="279"/>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>888249.25134267728</v>
+        <v>888225.08450796898</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>9254729.1158600636</v>
+        <v>9254450.7805913556</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18245,7 +18245,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>1133560.4523909232</v>
+        <v>1133526.3606472141</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18258,7 +18258,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>6487389.0748702856</v>
+        <v>6487110.7396015767</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18282,7 +18282,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>6487389.0748702856</v>
+        <v>6487110.7396015767</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18317,19 +18317,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381757</v>
       </c>
       <c r="C56" s="118">
-        <v>4760460.0244483305</v>
+        <v>4760181.6891796207</v>
       </c>
       <c r="D56" s="118">
-        <v>4816542.9360897783</v>
+        <v>4816264.6008210685</v>
       </c>
       <c r="E56" s="118">
-        <v>4872625.8477312233</v>
+        <v>4872347.5124625135</v>
       </c>
       <c r="F56" s="118">
-        <v>4928708.7593726683</v>
+        <v>4928430.4241039604</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18343,19 +18343,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C57" s="118">
-        <v>4813274.7011456359</v>
+        <v>4812996.365876927</v>
       </c>
       <c r="D57" s="118">
-        <v>4923218.1246665129</v>
+        <v>4922939.7893978031</v>
       </c>
       <c r="E57" s="118">
-        <v>5034207.3833695147</v>
+        <v>5033929.0481008049</v>
       </c>
       <c r="F57" s="118">
-        <v>5146242.4772546375</v>
+        <v>5145964.1419859277</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18369,19 +18369,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>4704377.1128068864</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C58" s="118">
-        <v>4863011.5994806308</v>
+        <v>4862733.264211921</v>
       </c>
       <c r="D58" s="118">
-        <v>5024671.4508653665</v>
+        <v>5024393.1155966567</v>
       </c>
       <c r="E58" s="118">
-        <v>5189385.9210920688</v>
+        <v>5189107.585823359</v>
       </c>
       <c r="F58" s="118">
-        <v>5357184.2642917018</v>
+        <v>5356905.929022993</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18395,19 +18395,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>4704377.1128068846</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C59" s="118">
-        <v>4909850.0771667287</v>
+        <v>4909571.7418980189</v>
       </c>
       <c r="D59" s="118">
-        <v>5121158.5303272158</v>
+        <v>5120880.195058506</v>
       </c>
       <c r="E59" s="118">
-        <v>5338415.1927510248</v>
+        <v>5338136.857482315</v>
       </c>
       <c r="F59" s="118">
-        <v>5561733.8759640045</v>
+        <v>5561455.5406952957</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18421,19 +18421,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C60" s="118">
-        <v>4953959.0398361553</v>
+        <v>4953680.7045674454</v>
       </c>
       <c r="D60" s="118">
-        <v>5212922.4660391808</v>
+        <v>5212644.1307704709</v>
       </c>
       <c r="E60" s="118">
-        <v>5481538.8755563637</v>
+        <v>5481260.5402876548</v>
       </c>
       <c r="F60" s="118">
-        <v>5760085.0145553295</v>
+        <v>5759806.6792866206</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18447,19 +18447,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C61" s="118">
-        <v>4995497.5501355687</v>
+        <v>4995219.2148668598</v>
       </c>
       <c r="D61" s="118">
-        <v>5300194.4608421698</v>
+        <v>5299916.12557346</v>
       </c>
       <c r="E61" s="118">
-        <v>5618990.9905116074</v>
+        <v>5618712.6552428985</v>
       </c>
       <c r="F61" s="118">
-        <v>5952425.51258328</v>
+        <v>5952147.177314572</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18473,19 +18473,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C62" s="118">
-        <v>5034615.4013266275</v>
+        <v>5034337.0660579177</v>
       </c>
       <c r="D62" s="118">
-        <v>5383194.3999555018</v>
+        <v>5382916.064686792</v>
       </c>
       <c r="E62" s="118">
-        <v>5750996.2850607</v>
+        <v>5750717.9497919912</v>
       </c>
       <c r="F62" s="118">
-        <v>6138937.5106709916</v>
+        <v>6138659.1754022818</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18499,19 +18499,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C63" s="118">
-        <v>5071453.6574599277</v>
+        <v>5071175.3221912179</v>
       </c>
       <c r="D63" s="118">
-        <v>5462131.4049863638</v>
+        <v>5461853.069717655</v>
       </c>
       <c r="E63" s="118">
-        <v>5877770.6005717162</v>
+        <v>5877492.2653030064</v>
       </c>
       <c r="F63" s="118">
-        <v>6319797.6300287694</v>
+        <v>6319519.2947600596</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18525,19 +18525,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C64" s="118">
-        <v>5106145.1620703116</v>
+        <v>5105866.8268016009</v>
       </c>
       <c r="D64" s="118">
-        <v>5537204.3608199097</v>
+        <v>5536926.0255511999</v>
       </c>
       <c r="E64" s="118">
-        <v>5999521.2252582852</v>
+        <v>5999242.8899895754</v>
       </c>
       <c r="F64" s="118">
-        <v>6495177.1397090415</v>
+        <v>6494898.8044403326</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18551,19 +18551,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381766</v>
       </c>
       <c r="C65" s="118">
-        <v>5138815.0172278732</v>
+        <v>5138536.6819591634</v>
       </c>
       <c r="D65" s="118">
-        <v>5608602.4167175479</v>
+        <v>5608324.081448839</v>
       </c>
       <c r="E65" s="118">
-        <v>6116447.233115783</v>
+        <v>6116168.8978470732</v>
       </c>
       <c r="F65" s="118">
-        <v>6665242.1187929399</v>
+        <v>6664963.7835242301</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18577,19 +18577,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381757</v>
       </c>
       <c r="C66" s="281">
-        <v>5275730.9100739127</v>
+        <v>5275452.5748052029</v>
       </c>
       <c r="D66" s="118">
-        <v>5916466.0563589875</v>
+        <v>5916187.7210902767</v>
       </c>
       <c r="E66" s="118">
-        <v>6635140.5628965255</v>
+        <v>6634862.2276278175</v>
       </c>
       <c r="F66" s="118">
-        <v>7441317.946202103</v>
+        <v>7441039.6109333932</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18612,19 +18612,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>4704377.1128068855</v>
+        <v>4704098.7775381748</v>
       </c>
       <c r="C67" s="281">
-        <v>5377139.3794040922</v>
+        <v>5376861.0441353805</v>
       </c>
       <c r="D67" s="118">
-        <v>6156003.137908808</v>
+        <v>6155724.8026400981</v>
       </c>
       <c r="E67" s="118">
-        <v>7058891.1202103924</v>
+        <v>7058612.7849416845</v>
       </c>
       <c r="F67" s="118">
-        <v>8106720.3244954431</v>
+        <v>8106441.9892267343</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18647,19 +18647,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>4704377.1128068846</v>
+        <v>4704098.7775381748</v>
       </c>
       <c r="C68" s="281">
-        <v>5452248.83118595</v>
+        <v>5451970.4959172383</v>
       </c>
       <c r="D68" s="118">
-        <v>6342377.9027372645</v>
+        <v>6342099.5674685556</v>
       </c>
       <c r="E68" s="118">
-        <v>7405077.4397833021</v>
+        <v>7404799.1045145933</v>
       </c>
       <c r="F68" s="118">
-        <v>8677232.0057013053</v>
+        <v>8676953.6704325955</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18682,19 +18682,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>4704377.1128068846</v>
+        <v>4704098.7775381748</v>
       </c>
       <c r="C69" s="281">
-        <v>5507879.5865285154</v>
+        <v>5507601.2512598056</v>
       </c>
       <c r="D69" s="118">
-        <v>6487389.0748702856</v>
+        <v>6487110.7396015767</v>
       </c>
       <c r="E69" s="118">
-        <v>7687897.0509694852</v>
+        <v>7687618.7157007772</v>
       </c>
       <c r="F69" s="118">
-        <v>9166385.0189910345</v>
+        <v>9166106.6837223265</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738785</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.2661371063518043</v>
+        <v>5.2698238879610004</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.3628311092389334</v>
+        <v>5.3665178908481295</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.4595251121260553</v>
+        <v>5.4632118937352514</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.556219115013179</v>
+        <v>5.5599058966223787</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.357196260585833</v>
+        <v>5.3608830421950309</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.546752569275978</v>
+        <v>5.5504393508851742</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.738112029535114</v>
+        <v>5.7417988111443092</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9312746413632329</v>
+        <v>5.934961422972429</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18884,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646842</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4429489373004021</v>
+        <v>5.4466357189095973</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.7216708809196035</v>
+        <v>5.7253576625287996</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.0056593721284264</v>
+        <v>6.0093461537376225</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.2949648487329881</v>
+        <v>6.2986516303421851</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18915,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646806</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.5237043717821788</v>
+        <v>5.5273911533913749</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8880267577275314</v>
+        <v>5.8917135393367266</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2626046055746851</v>
+        <v>6.2662913871838795</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.6476341407278987</v>
+        <v>6.6513209223370957</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18946,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.5997537786135041</v>
+        <v>5.6034405602227002</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.0462393398665331</v>
+        <v>6.0499261214757292</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.5093678600731897</v>
+        <v>6.5130546416823876</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9896164844805417</v>
+        <v>6.9933032660897387</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18977,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6713714018299513</v>
+        <v>5.6750581834391483</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.1967072501525804</v>
+        <v>6.2003940317617756</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.7463526173071857</v>
+        <v>6.7500393989163836</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.3212357269073438</v>
+        <v>7.3249225085165444</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19009,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.7388155038799429</v>
+        <v>5.7425022854891381</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.339809598396652</v>
+        <v>6.3434963800058464</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.973946370175268</v>
+        <v>6.9776331517844659</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.6428059013818235</v>
+        <v>7.6464926829910205</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19040,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.8023292969526548</v>
+        <v>5.80601607856185</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.4759069365868189</v>
+        <v>6.4795937181960159</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>7.1925212563795782</v>
+        <v>7.1962080379887743</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.954631525114646</v>
+        <v>7.958318306723843</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19072,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8621418200327895</v>
+        <v>5.8658286016419838</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.6053421673131298</v>
+        <v>6.609028948922326</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>7.4024346669067933</v>
+        <v>7.4061214485159894</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>8.2570078875222368</v>
+        <v>8.2606946691314356</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19104,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738794</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>5.9184687648448469</v>
+        <v>5.9221555464540421</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.7284414077241665</v>
+        <v>6.7321281893333644</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.604029830396799</v>
+        <v>7.6077166120059951</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5502213298568677</v>
+        <v>8.5539081114660647</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19136,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738785</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1545290076294679</v>
+        <v>6.158215789238664</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>7.2592370955559442</v>
+        <v>7.2629238771651377</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.498322456428836</v>
+        <v>8.5020092380380365</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.8882737971733548</v>
+        <v>9.8919605787825517</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19168,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646824</v>
+        <v>5.1731298850738767</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.3293699803821166</v>
+        <v>6.3330567619913092</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.6722291920261085</v>
+        <v>7.6759159736353038</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.2289217854060315</v>
+        <v>9.232608567015232</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>11.035511299732823</v>
+        <v>11.039198081342022</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19200,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646806</v>
+        <v>5.1731298850738767</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.4588681347197054</v>
+        <v>6.462554916328898</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.9935627590781433</v>
+        <v>7.9972495406873421</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.8257905998904818</v>
+        <v>9.8294773814996788</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>12.019145289750032</v>
+        <v>12.022832071359229</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19232,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.1694431034646806</v>
+        <v>5.1731298850738767</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.5547825632019041</v>
+        <v>6.5584693448110993</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>8.2435802828925357</v>
+        <v>8.2472670645017345</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>10.313407228559997</v>
+        <v>10.317094010169198</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>12.862506689772795</v>
+        <v>12.866193471381994</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>12.862506689772795</v>
+        <v>12.866193471381994</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>10.313407228559997</v>
+        <v>10.317094010169198</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>8.2435802828925357</v>
+        <v>8.2472670645017345</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.5547825632019041</v>
+        <v>6.5584693448110993</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.1694431034646806</v>
+        <v>5.1731298850738767</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>289869.92812368623</v>
+        <v>289762.92396067944</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>341067.34067849925</v>
+        <v>341047.16137151787</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19685,7 +19685,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.62600273988199584</v>
+        <v>0.62636359906346839</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>10.313407228559997</v>
+        <v>10.317094010169198</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>8.2435802828925357</v>
+        <v>8.2472670645017345</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>6.5547825632019041</v>
+        <v>6.5584693448110993</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>8.3197861280879017</v>
+        <v>8.3234729096970987</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>12.862506689772795</v>
+        <v>12.866193471381994</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>5.1694431034646806</v>
+        <v>5.1731298850738767</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19925,7 +19925,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>5.69</v>
+        <v>5.6</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20056322920543154</v>
+        <v>0.19957778695608511</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.24196795776686636</v>
+        <v>0.23342996477283787</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>8.3894050049409827</v>
+        <v>8.3930917865501833</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>8.2435802828925357</v>
+        <v>8.2472670645017345</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.52663364780706778</v>
+        <v>0.52689875671755426</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20225,15 +20225,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.73194063044404789</v>
+        <v>0.64044805163854179</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.8660852557331729</v>
+        <v>3.8677842334332651</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>4.5980258861772203</v>
+        <v>4.5082322850718066</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.45192467362474575</v>
+        <v>0.46286393623191535</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20250,15 +20250,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.84160157890763132</v>
+        <v>0.73640138154417734</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.8458657068251183</v>
+        <v>4.8479952557690611</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>5.6874672857327493</v>
+        <v>5.5843966373132385</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.32206547634986193</v>
+        <v>0.33464368324171567</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20296,15 +20296,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>0.96504125037545974</v>
+        <v>0.8444110940785271</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>6.0131932285018506</v>
+        <v>6.0158357675370215</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>6.9782344788773099</v>
+        <v>6.8602468616155488</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.16820865427674037</v>
+        <v>0.18263173618463202</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.0449500908692064</v>
+        <v>0.91433132951055562</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.8004751540328705</v>
+        <v>6.8034636695136399</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>7.8454252449020769</v>
+        <v>7.7177949990241954</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>6.4841280128748791E-2</v>
+        <v>8.0458644406599E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>5.69</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20466,14 +20466,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3300.2229477700002</v>
+        <v>3248.0225847999995</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.20056322920543154</v>
+        <v>0.19957778695608511</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>8.3894050049409827</v>
+        <v>8.3930917865501833</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>4.5980258861772203</v>
+        <v>4.5082322850718066</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>5.6874672857327493</v>
+        <v>5.5843966373132385</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>6.9782344788773099</v>
+        <v>6.8602468616155488</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>7.8454252449020769</v>
+        <v>7.7177949990241954</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20796,7 +20796,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>6888.8446443333341</v>
+        <v>6864.677809625</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20826,7 +20826,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-78483.555355666671</v>
+        <v>-78507.722190375003</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-75111.544966315007</v>
+        <v>-75107.557438588134</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>289869.92812368623</v>
+        <v>289762.92396067944</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20932,7 +20932,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>341067.34067849925</v>
+        <v>341047.16137151787</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.1033467574998115</v>
+        <v>0.10500147473343946</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20955,14 +20955,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>7.0298769771528991E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.68022230665202266</v>
+        <v>0.59522973518862243</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20982,11 +20982,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.1658525572748466</v>
+        <v>0.16584375248097633</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>0.11824413281411626</v>
+        <v>0.11820514758456895</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20996,11 +20996,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>5.3128459724860015E-2</v>
+        <v>5.3125639236926585E-2</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>3.7877791884180549E-2</v>
+        <v>3.7865303531682992E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>364748.53556666663</v>
+        <v>367165.21903749998</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.62887241262797666</v>
+        <v>0.63303907929464343</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-2.9414955196239703</v>
+        <v>-2.9373288529573038</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>5.1694431034646833</v>
+        <v>5.1731298850738812</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>12.86 HKD</v>
+        <v>12.87 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21447,7 +21447,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>10.31 HKD</v>
+        <v>10.32 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21469,7 +21469,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>8.24 HKD</v>
+        <v>8.25 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.55 HKD</v>
+        <v>6.56 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>8.3894050049409827</v>
+        <v>8.3930917865501833</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21638,15 +21638,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>0.73194063044404789</v>
+        <v>0.64044805163854179</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>3.8660852557331729</v>
+        <v>3.8677842334332651</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>4.5980258861772203</v>
+        <v>4.5082322850718066</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21659,15 +21659,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>0.84160157890763132</v>
+        <v>0.73640138154417734</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>4.8458657068251183</v>
+        <v>4.8479952557690611</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>5.6874672857327493</v>
+        <v>5.5843966373132385</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>0.96504125037545974</v>
+        <v>0.8444110940785271</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>6.0131932285018506</v>
+        <v>6.0158357675370215</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>6.9782344788773099</v>
+        <v>6.8602468616155488</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21720,15 +21720,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.0449500908692064</v>
+        <v>0.91433132951055562</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>6.8004751540328705</v>
+        <v>6.8034636695136399</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>7.8454252449020769</v>
+        <v>7.7177949990241954</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD971B09-6B9D-4D4C-94AF-513852F53153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75063E0-C944-4546-BB76-9A67BBA7037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.19957778695608511</v>
+        <v>1.4883278968646201E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>8.3930917865501833</v>
+        <v>4.7880739782573478</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>4.5082322850718066</v>
+        <v>2.8469337559046011</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>5.5843966373132385</v>
+        <v>3.502075881620625</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>6.8602468616155488</v>
+        <v>4.2763128805182129</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>7.7177949990241954</v>
+        <v>4.7955574838842381</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C34" s="289">
         <f>Normalized_FCF!C8</f>
-        <v>533705.04</v>
+        <v>398162</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>6864.677809625</v>
+        <v>6977.6303429583331</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-78507.722190375003</v>
+        <v>-78394.769657041674</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-75107.557438588134</v>
+        <v>-52761.593006588133</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>289762.92396067944</v>
+        <v>290263.04701918905</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>341047.16137151787</v>
+        <v>227963.03833685117</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10500147473343946</v>
+        <v>7.0185176483582926E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.59522973518862243</v>
+        <v>0.89050142966612644</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5917,11 +5917,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.16584375248097633</v>
+        <v>0.11650199885998448</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.11820514758456895</v>
+        <v>0.1183873593012913</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>5.3125639236926585E-2</v>
+        <v>3.7319724555354143E-2</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>3.7865303531682992E-2</v>
+        <v>3.7923672410718354E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C81" s="342">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>3.999044116203212</v>
+        <v>5.3604060658726853</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>367165.21903749998</v>
+        <v>355869.96570416668</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.63303907929464343</v>
+        <v>0.61356463999650612</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-2.9373288529573038</v>
+        <v>-2.956803292255441</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>12.87 HKD</v>
+        <v>8.02 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.10125201658765973</v>
+        <v>-0.10583101104145536</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>10.32 HKD</v>
+        <v>6.18 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.015046515037512E-2</v>
+        <v>-1.9766300946058021E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>8.25 HKD</v>
+        <v>4.68 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>4.8057775524901515E-2</v>
+        <v>8.1652063121764637E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.56 HKD</v>
+        <v>3.46 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.13507645584940894</v>
+        <v>0.20549562324221848</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.17 HKD</v>
+        <v>2.46 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23342996477283839</v>
+        <v>0.36501986827233635</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>8.3930917865501833</v>
+        <v>4.7880739782573478</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>3.8677842334332651</v>
+        <v>2.2064857042660595</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>4.5082322850718066</v>
+        <v>2.8469337559046011</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>4.8479952557690611</v>
+        <v>2.7656745000764476</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>5.5843966373132385</v>
+        <v>3.502075881620625</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>6.0158357675370215</v>
+        <v>3.4319017864396861</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>6.8602468616155488</v>
+        <v>4.2763128805182129</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>6.8034636695136399</v>
+        <v>3.8812261543736826</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>7.7177949990241954</v>
+        <v>4.7955574838842381</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
-        <v>3.999044116203212</v>
+        <v>5.3604060658726853</v>
       </c>
       <c r="D50" s="92">
         <f>G31/Normalized_FCF!G8</f>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.11897894424739897</v>
+        <v>8.8762314104121762E-2</v>
       </c>
       <c r="D54" s="89">
         <f>Normalized_FCF!G8/G35</f>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>367165.21903749998</v>
+        <v>355869.96570416668</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-686467.78096250002</v>
+        <v>-697763.03429583332</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.5348615466303397</v>
+        <v>1.5100155041364474</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10473,7 +10473,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>686467.78096250002</v>
+        <v>697763.03429583332</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10605,11 +10605,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>367165.21903749998</v>
+        <v>355869.96570416668</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.63303907929464343</v>
+        <v>0.61356463999650612</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10639,11 +10639,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2564957.4190375004</v>
+        <v>2553662.165704167</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>4.4223096273496081</v>
+        <v>4.4028351880514709</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="C5" s="270">
         <f>C26</f>
-        <v>-7540118.96</v>
+        <v>-7675662</v>
       </c>
       <c r="E5" s="238"/>
       <c r="G5" s="274">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="C6" s="271">
         <f>C4+C5</f>
-        <v>1028198.04</v>
+        <v>892655</v>
       </c>
       <c r="E6" s="238"/>
       <c r="G6" s="271">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="C8" s="272">
         <f>C6+C7</f>
-        <v>533705.04</v>
+        <v>398162</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="244"/>
@@ -11124,24 +11124,24 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-78507.722190375003</v>
+        <v>-78394.769657041674</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>-73720.076039320571</v>
+        <v>-73219.952980810951</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-79075.331151620063</v>
+        <v>-78589.659046614499</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>-73198.225261499756</v>
+        <v>-72781.774081401934</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>-83053.973364167803</v>
+        <v>-82971.866648375872</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
@@ -11179,24 +11179,24 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>455197.31780962506</v>
+        <v>319767.23034295836</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>324441.92396067944</v>
+        <v>324942.04701918905</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>406997.66884837992</v>
+        <v>407483.34095338552</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>143371.77473850024</v>
+        <v>143788.22591859807</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>5824.0266358321969</v>
+        <v>5906.1333516241284</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-75107.557438588134</v>
+        <v>-52761.593006588133</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11346,26 +11346,26 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>341047.16137151787</v>
+        <v>227963.03833685117</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>289762.92396067944</v>
+        <v>290263.04701918905</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>347923.66884837992</v>
+        <v>348409.34095338552</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>109548.77473850024</v>
+        <v>109965.22591859807</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>-23750.973364167803</v>
+        <v>-23668.866648375872</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
@@ -11564,26 +11564,26 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>341047.16137151787</v>
+        <v>227963.03833685117</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>289762.92396067944</v>
+        <v>290263.04701918905</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>347923.66884837992</v>
+        <v>348409.34095338552</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>109548.77473850024</v>
+        <v>109965.22591859807</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>-23750.973364167803</v>
+        <v>-23668.866648375872</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="C23" s="278">
         <f>-C4*C29</f>
-        <v>-7540118.96</v>
+        <v>-7675662</v>
       </c>
       <c r="D23" s="55"/>
       <c r="E23" s="237"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C26" s="271">
         <f>SUM(C23:C25)</f>
-        <v>-7540118.96</v>
+        <v>-7675662</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="243"/>
@@ -11922,7 +11922,8 @@
         <v>40</v>
       </c>
       <c r="C29" s="60">
-        <v>0.88</v>
+        <f>G29</f>
+        <v>0.89581909726262465</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="236"/>
@@ -12093,7 +12094,7 @@
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="E32" s="238"/>
       <c r="G32" s="29">
@@ -12301,19 +12302,19 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>9.959255451806541E-2</v>
+        <v>9.9439270160355253E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.13836197184947133</v>
+        <v>0.1381970606902479</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>0.23009410366977429</v>
+        <v>0.22942768637173294</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.7971964668063007</v>
+        <v>4.730506125859324</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
@@ -12439,24 +12440,24 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>6864.677809625</v>
+        <v>6977.6303429583331</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>30394.923960679429</v>
+        <v>30895.047019189049</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>29516.668848379937</v>
+        <v>30002.340953385505</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>25309.774738500251</v>
+        <v>25726.225918598066</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>4990.0266358321987</v>
+        <v>5072.1333516241302</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
@@ -12551,24 +12552,24 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-78507.722190375003</v>
+        <v>-78394.769657041674</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-73720.076039320571</v>
+        <v>-73219.952980810951</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>-79075.331151620063</v>
+        <v>-78589.659046614499</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>-73198.225261499756</v>
+        <v>-72781.774081401934</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>-83053.973364167803</v>
+        <v>-82971.866648375872</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
@@ -12668,7 +12669,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>6.2514939254372601</v>
+        <v>4.6638257797602032</v>
       </c>
       <c r="E53" s="238"/>
       <c r="G53" s="40">
@@ -13231,7 +13232,7 @@
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="235"/>
@@ -13288,7 +13289,7 @@
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
-        <v>0.12000000000000001</v>
+        <v>0.10418090273737537</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="235"/>
@@ -13402,7 +13403,7 @@
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
-        <v>6.2288199654611291E-2</v>
+        <v>4.6469102391986664E-2</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="235"/>
@@ -13516,7 +13517,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>9.1625604176847099E-3</v>
+        <v>9.1493778366325239E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235" t="s">
@@ -13525,19 +13526,19 @@
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>8.6037988603036714E-3</v>
+        <v>8.5454299812683116E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>9.0980607665787448E-3</v>
+        <v>9.0421814644042094E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1223609019965186E-3</v>
+        <v>9.0704604911690332E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>1.1060954244222416E-2</v>
+        <v>1.1050019443757955E-2</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
@@ -13575,26 +13576,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>5.3125639236926585E-2</v>
+        <v>3.7319724555354143E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>3.7865303531682992E-2</v>
+        <v>3.7923672410718354E-2</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>4.6827366627633656E-2</v>
+        <v>4.6883245929808193E-2</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>1.7867770258799709E-2</v>
+        <v>1.7919670669627193E-2</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>7.7563167090889749E-4</v>
+        <v>7.8656647137335966E-4</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
@@ -13632,7 +13633,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>8.7657304740928858E-3</v>
+        <v>6.1577545516334339E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13747,26 +13748,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>3.9803284749095752E-2</v>
+        <v>2.6605345989982765E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>3.3817950941903693E-2</v>
+        <v>3.3876319820939055E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>4.0030571294657535E-2</v>
+        <v>4.0086450596832073E-2</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>1.3652564061027113E-2</v>
+        <v>1.37044644718546E-2</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>3.1631048942704337E-3</v>
+        <v>3.1521700938059718E-3</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
@@ -13968,26 +13969,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>3.9803284749095752E-2</v>
+        <v>2.6605345989982765E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>3.3817950941903693E-2</v>
+        <v>3.3876319820939055E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>4.0030571294657535E-2</v>
+        <v>4.0086450596832073E-2</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>1.3652564061027113E-2</v>
+        <v>1.37044644718546E-2</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>3.1631048942704337E-3</v>
+        <v>3.1521700938059718E-3</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
@@ -14148,24 +14149,24 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.59522973518862243</v>
+        <v>0.89050142966612644</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.70057759210611448</v>
+        <v>0.69937049732885803</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.95021502821089077</v>
+        <v>0.94889045714257125</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>2.0119032190557333</v>
+        <v>2.0042839061063957</v>
       </c>
       <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v>-9.2796842117010456</v>
+        <v>-9.3118752078111733</v>
       </c>
       <c r="K90" s="152">
         <f t="shared" si="37"/>
@@ -14361,26 +14362,26 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.40301633109780366</v>
+        <v>-1.5925352608876397E-2</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-0.20284082982906526</v>
+        <v>-0.2025636035600259</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>1.8387572769515774</v>
+        <v>1.8339131271017388</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>23.617293790589578</v>
+        <v>23.345577276723311</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.0666128333866958</v>
+        <v>-1.0675519364026962</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
@@ -14972,19 +14973,19 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>5.2146043370443111</v>
+        <v>5.2056195768526781</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>4.7802266672601066</v>
+        <v>4.7735631755708789</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>15.508023746092499</v>
+        <v>15.449293045217788</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-49.027085422812533</v>
+        <v>-49.197159175338143</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -15080,24 +15081,24 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>5.3125639236926585E-2</v>
+        <v>3.7319724555354143E-2</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>3.7865303531682992E-2</v>
+        <v>3.7923672410718354E-2</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>4.6827366627633656E-2</v>
+        <v>4.6883245929808193E-2</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>1.7867770258799709E-2</v>
+        <v>1.7919670669627193E-2</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>7.7563167090889749E-4</v>
+        <v>7.8656647137335966E-4</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
@@ -15245,26 +15246,26 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.16584375248097633</v>
+        <v>0.11650199885998448</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.11820514758456895</v>
+        <v>0.1183873593012913</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.13983709017907836</v>
+        <v>0.14000395839269075</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>5.1349763504082914E-2</v>
+        <v>5.1498918870597855E-2</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>2.0605986732947766E-3</v>
+        <v>2.0896488477202355E-3</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
@@ -15366,26 +15367,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.58800825850726091</v>
+        <v>0.39303698830806438</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.49958777435031987</v>
+        <v>0.50045004948989569</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.59986422344132206</v>
+        <v>0.60070158331706902</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.18887588448630707</v>
+        <v>0.18959389876966265</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-4.0949669334743748E-2</v>
+        <v>-4.0808107016000475E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
@@ -15423,26 +15424,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10500147473343946</v>
+        <v>7.0185176483582926E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.9212102562557127E-2</v>
+        <v>8.9366080266052805E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10711861132880751</v>
+        <v>0.10726813987804805</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3727836515411981E-2</v>
+        <v>3.3856053351725472E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-7.3124409526328128E-3</v>
+        <v>-7.2871619671429425E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -16271,7 +16272,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>341047.16137151787</v>
+        <v>227963.03833685117</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16310,7 +16311,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>367165.21903749998</v>
+        <v>355869.96570416668</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16331,7 +16332,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>4704098.7775381776</v>
+        <v>3144317.7701634648</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16353,7 +16354,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-78507.722190375003</v>
+        <v>-78394.769657041674</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16364,14 +16365,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>-1703662.5809625001</v>
+        <v>-1714957.8342958333</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>-1703662.5809625001</v>
+        <v>-1714957.8342958333</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16394,7 +16395,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>3000436.1965756775</v>
+        <v>1429359.9358676316</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16405,7 +16406,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-2.9373288529573038</v>
+        <v>-2.956803292255441</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16417,7 +16418,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-78507.722190375003</v>
+        <v>-78394.769657041674</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16455,7 +16456,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>3000436.1965756775</v>
+        <v>1429359.9358676316</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16478,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16567,14 +16568,14 @@
       </c>
       <c r="C17" s="310">
         <f>Normalized_FCF!C32</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="E17" s="312" t="s">
         <v>402</v>
       </c>
       <c r="F17" s="315">
         <f>Scenarios!C40</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>414</v>
@@ -16600,7 +16601,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.2472670645017345</v>
+        <v>4.6828399332631063</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16667,7 +16668,7 @@
       </c>
       <c r="E21" s="303">
         <f>$C$17</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F21" s="281">
         <f>I5*(1+D21)</f>
@@ -16675,7 +16676,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>465871.41860962508</v>
+        <v>327730.47034295811</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16683,11 +16684,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>349179.18355952745</v>
+        <v>233831.49175686057</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>2.3844274660744125E-2</v>
+        <v>2.5743004053744301E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16695,7 +16696,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>325574.99632589973</v>
+        <v>218024.70093879773</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16716,7 +16717,7 @@
       </c>
       <c r="E22" s="303">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F22" s="281">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
@@ -16724,7 +16725,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>476759.00142562494</v>
+        <v>335852.97514295799</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16732,11 +16733,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>357473.84619129717</v>
+        <v>239817.31424527025</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>2.3754745478278716E-2</v>
+        <v>2.559887226239721E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16744,7 +16745,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>310777.57342444104</v>
+        <v>208490.33790972253</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16765,7 +16766,7 @@
       </c>
       <c r="E23" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F23" s="281">
         <f t="shared" si="7"/>
@@ -16773,7 +16774,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>487864.33589794498</v>
+        <v>344137.93003895809</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16781,11 +16782,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>365934.40207570238</v>
+        <v>245922.85318344837</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>2.3667622049971415E-2</v>
+        <v>2.5459124823380197E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16793,7 +16794,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>296627.44948611461</v>
+        <v>199345.75239816771</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -16822,7 +16823,7 @@
       </c>
       <c r="E24" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F24" s="281">
         <f t="shared" si="7"/>
@@ -16830,7 +16831,7 @@
       </c>
       <c r="G24" s="281">
         <f t="shared" si="8"/>
-        <v>499191.77705971163</v>
+        <v>352588.58403287816</v>
       </c>
       <c r="H24" s="303">
         <f t="shared" si="2"/>
@@ -16838,11 +16839,11 @@
       </c>
       <c r="I24" s="281">
         <f t="shared" si="9"/>
-        <v>374564.16907779593</v>
+        <v>252150.50290039001</v>
       </c>
       <c r="J24" s="303">
         <f t="shared" si="10"/>
-        <v>2.3582825099642601E-2</v>
+        <v>2.5323590859187339E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16850,7 +16851,7 @@
       </c>
       <c r="L24" s="281">
         <f t="shared" si="4"/>
-        <v>283098.14708354184</v>
+        <v>190577.06542789345</v>
       </c>
       <c r="N24" s="279"/>
       <c r="O24" s="279"/>
@@ -16879,7 +16880,7 @@
       </c>
       <c r="E25" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F25" s="281">
         <f t="shared" si="7"/>
@@ -16887,7 +16888,7 @@
       </c>
       <c r="G25" s="281">
         <f t="shared" si="8"/>
-        <v>510745.76704471326</v>
+        <v>361208.25110667653</v>
       </c>
       <c r="H25" s="303">
         <f t="shared" si="2"/>
@@ -16895,11 +16896,11 @@
       </c>
       <c r="I25" s="281">
         <f t="shared" si="9"/>
-        <v>383366.53141993098</v>
+        <v>258502.70561167033</v>
       </c>
       <c r="J25" s="303">
         <f t="shared" si="10"/>
-        <v>2.3500278640658845E-2</v>
+        <v>2.5192108039497674E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16907,7 +16908,7 @@
       </c>
       <c r="L25" s="281">
         <f t="shared" si="4"/>
-        <v>270164.13279502036</v>
+        <v>182170.72582750898</v>
       </c>
       <c r="N25" s="279"/>
       <c r="O25" s="279"/>
@@ -16936,7 +16937,7 @@
       </c>
       <c r="E26" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F26" s="281">
         <f t="shared" si="7"/>
@@ -16944,7 +16945,7 @@
       </c>
       <c r="G26" s="281">
         <f t="shared" si="8"/>
-        <v>522530.83682941506</v>
+        <v>370000.31152195088</v>
       </c>
       <c r="H26" s="303">
         <f t="shared" si="2"/>
@@ -16952,11 +16953,11 @@
       </c>
       <c r="I26" s="281">
         <f t="shared" si="9"/>
-        <v>392344.94100890891</v>
+        <v>264981.95237717632</v>
       </c>
       <c r="J26" s="303">
         <f t="shared" si="10"/>
-        <v>2.3419909807262718E-2</v>
+        <v>2.5064522052776095E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16964,7 +16965,7 @@
       </c>
       <c r="L26" s="281">
         <f t="shared" si="4"/>
-        <v>257800.79479555905</v>
+        <v>174113.51795093968</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16985,7 +16986,7 @@
       </c>
       <c r="E27" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F27" s="281">
         <f t="shared" si="7"/>
@@ -16993,7 +16994,7 @@
       </c>
       <c r="G27" s="281">
         <f t="shared" si="8"/>
-        <v>534551.60800981079</v>
+        <v>378968.21314553078</v>
       </c>
       <c r="H27" s="303">
         <f t="shared" si="2"/>
@@ -17001,11 +17002,11 @@
       </c>
       <c r="I27" s="281">
         <f t="shared" si="9"/>
-        <v>401502.91878966626</v>
+        <v>271590.78407799249</v>
       </c>
       <c r="J27" s="303">
         <f t="shared" si="10"/>
-        <v>2.3341648696189932E-2</v>
+        <v>2.494068611664968E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -17013,7 +17014,7 @@
       </c>
       <c r="L27" s="281">
         <f t="shared" si="4"/>
-        <v>245984.41993592129</v>
+        <v>166392.56741335173</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -17034,7 +17035,7 @@
       </c>
       <c r="E28" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F28" s="281">
         <f t="shared" si="7"/>
@@ -17042,7 +17043,7 @@
       </c>
       <c r="G28" s="281">
         <f t="shared" si="8"/>
-        <v>546812.79461381468</v>
+        <v>388115.47280158231</v>
       </c>
       <c r="H28" s="303">
         <f t="shared" si="2"/>
@@ -17050,11 +17051,11 @@
       </c>
       <c r="I28" s="281">
         <f t="shared" si="9"/>
-        <v>410844.05612603901</v>
+        <v>278331.79241282499</v>
       </c>
       <c r="J28" s="303">
         <f t="shared" si="10"/>
-        <v>2.326542821788613E-2</v>
+        <v>2.4820460523788279E-2</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -17062,7 +17063,7 @@
       </c>
       <c r="L28" s="281">
         <f t="shared" si="4"/>
-        <v>234692.17044350473</v>
+        <v>158995.34504828588</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -17083,7 +17084,7 @@
       </c>
       <c r="E29" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F29" s="281">
         <f t="shared" si="7"/>
@@ -17091,7 +17092,7 @@
       </c>
       <c r="G29" s="281">
         <f t="shared" si="8"/>
-        <v>559319.20494989841</v>
+        <v>397445.67765075481</v>
       </c>
       <c r="H29" s="303">
         <f t="shared" si="2"/>
@@ -17099,11 +17100,11 @@
       </c>
       <c r="I29" s="281">
         <f t="shared" si="9"/>
-        <v>420372.01620913902</v>
+        <v>285207.62091435411</v>
       </c>
       <c r="J29" s="303">
         <f t="shared" si="10"/>
-        <v>2.3191183956613015E-2</v>
+        <v>2.4703712220308649E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17111,7 +17112,7 @@
       </c>
       <c r="L29" s="281">
         <f t="shared" si="4"/>
-        <v>223902.06036497603</v>
+        <v>151909.66927433788</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17132,7 +17133,7 @@
       </c>
       <c r="E30" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F30" s="281">
         <f t="shared" si="7"/>
@@ -17140,7 +17141,7 @@
       </c>
       <c r="G30" s="281">
         <f t="shared" si="8"/>
-        <v>572075.74349270388</v>
+        <v>406962.48659691075</v>
       </c>
       <c r="H30" s="303">
         <f t="shared" si="2"/>
@@ -17148,11 +17149,11 @@
       </c>
       <c r="I30" s="281">
         <f t="shared" si="9"/>
-        <v>430090.53549390106</v>
+        <v>292220.96598591382</v>
       </c>
       <c r="J30" s="303">
         <f t="shared" si="10"/>
-        <v>2.3118854038864045E-2</v>
+        <v>2.4590314414023817E-2</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17160,7 +17161,7 @@
       </c>
       <c r="L30" s="281">
         <f t="shared" si="4"/>
-        <v>213592.93185785998</v>
+        <v>145123.70704365897</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -17181,7 +17182,7 @@
       </c>
       <c r="E31" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F31" s="281">
         <f t="shared" si="7"/>
@@ -17189,7 +17190,7 @@
       </c>
       <c r="G31" s="281">
         <f t="shared" si="8"/>
-        <v>585087.41280636541</v>
+        <v>416669.63172198972</v>
       </c>
       <c r="H31" s="303">
         <f t="shared" si="2"/>
@@ -17197,11 +17198,11 @@
       </c>
       <c r="I31" s="281">
         <f t="shared" si="9"/>
-        <v>440003.42516435834</v>
+        <v>299374.57795890461</v>
       </c>
       <c r="J31" s="303">
         <f t="shared" si="10"/>
-        <v>2.3048379009488418E-2</v>
+        <v>2.4480146210096532E-2</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17209,7 +17210,7 @@
       </c>
       <c r="L31" s="281">
         <f t="shared" si="4"/>
-        <v>203744.43142663664</v>
+        <v>138625.97352973331</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -17230,7 +17231,7 @@
       </c>
       <c r="E32" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F32" s="281">
         <f t="shared" si="7"/>
@@ -17238,7 +17239,7 @@
       </c>
       <c r="G32" s="281">
         <f t="shared" si="8"/>
-        <v>598359.31550630019</v>
+        <v>426570.91974957031</v>
       </c>
       <c r="H32" s="303">
         <f t="shared" si="2"/>
@@ -17246,11 +17247,11 @@
       </c>
       <c r="I32" s="281">
         <f t="shared" si="9"/>
-        <v>450114.57262822468</v>
+        <v>306671.26217135525</v>
       </c>
       <c r="J32" s="303">
         <f t="shared" si="10"/>
-        <v>2.2979701715025058E-2</v>
+        <v>2.4373092271890329E-2</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
@@ -17258,7 +17259,7 @@
       </c>
       <c r="L32" s="281">
         <f t="shared" si="4"/>
-        <v>194336.98618826864</v>
+        <v>132405.33069823228</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -17279,7 +17280,7 @@
       </c>
       <c r="E33" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F33" s="281">
         <f t="shared" si="7"/>
@@ -17287,7 +17288,7 @@
       </c>
       <c r="G33" s="281">
         <f t="shared" si="8"/>
-        <v>611896.65626023384</v>
+        <v>436670.23353770259</v>
       </c>
       <c r="H33" s="303">
         <f t="shared" si="2"/>
@@ -17295,11 +17296,11 @@
       </c>
       <c r="I33" s="281">
         <f t="shared" si="9"/>
-        <v>460427.94304136856</v>
+        <v>314113.880068055</v>
       </c>
       <c r="J33" s="303">
         <f t="shared" si="10"/>
-        <v>2.2912767193747907E-2</v>
+        <v>2.4269042505003613E-2</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
@@ -17307,7 +17308,7 @@
       </c>
       <c r="L33" s="281">
         <f t="shared" si="4"/>
-        <v>185351.78024236366</v>
+        <v>126450.98489215545</v>
       </c>
       <c r="N33" s="279"/>
       <c r="O33" s="279"/>
@@ -17336,7 +17337,7 @@
       </c>
       <c r="E34" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F34" s="281">
         <f t="shared" si="7"/>
@@ -17344,7 +17345,7 @@
       </c>
       <c r="G34" s="281">
         <f t="shared" si="8"/>
-        <v>625704.74382924603</v>
+        <v>446971.53360159753</v>
       </c>
       <c r="H34" s="303">
         <f t="shared" si="2"/>
@@ -17352,11 +17353,11 @@
       </c>
       <c r="I34" s="281">
         <f t="shared" si="9"/>
-        <v>470947.58086277527</v>
+        <v>321705.35032268876</v>
       </c>
       <c r="J34" s="303">
         <f t="shared" si="10"/>
-        <v>2.2847522571977308E-2</v>
+        <v>2.4167891762659544E-2</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17364,7 +17365,7 @@
       </c>
       <c r="L34" s="281">
         <f t="shared" si="4"/>
-        <v>176770.73121231445</v>
+        <v>120752.48355087251</v>
       </c>
       <c r="N34" s="279"/>
       <c r="O34" s="279"/>
@@ -17393,7 +17394,7 @@
       </c>
       <c r="E35" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F35" s="281">
         <f t="shared" si="7"/>
@@ -17401,7 +17402,7 @@
       </c>
       <c r="G35" s="281">
         <f t="shared" si="8"/>
-        <v>639788.99314963841</v>
+        <v>457478.85966677032</v>
       </c>
       <c r="H35" s="303">
         <f t="shared" si="2"/>
@@ -17409,11 +17410,11 @@
       </c>
       <c r="I35" s="281">
         <f t="shared" si="9"/>
-        <v>481677.61144060991</v>
+        <v>329448.64998241508</v>
       </c>
       <c r="J35" s="303">
         <f t="shared" si="10"/>
-        <v>2.2783916966251816E-2</v>
+        <v>2.406953957078839E-2</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
@@ -17421,7 +17422,7 @@
       </c>
       <c r="L35" s="281">
         <f t="shared" si="4"/>
-        <v>168576.46701568249</v>
+        <v>115299.71117200115</v>
       </c>
       <c r="N35" s="279"/>
       <c r="O35" s="279"/>
@@ -17450,7 +17451,7 @@
       </c>
       <c r="E36" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F36" s="281">
         <f t="shared" si="7"/>
@@ -17458,7 +17459,7 @@
       </c>
       <c r="G36" s="281">
         <f t="shared" si="8"/>
-        <v>654154.92745643866</v>
+        <v>468196.33225324668</v>
       </c>
       <c r="H36" s="303">
         <f t="shared" si="2"/>
@@ -17466,11 +17467,11 @@
       </c>
       <c r="I36" s="281">
         <f t="shared" si="9"/>
-        <v>492622.24263000139</v>
+        <v>337346.8156353361</v>
       </c>
       <c r="J36" s="303">
         <f t="shared" si="10"/>
-        <v>2.2721901390969856E-2</v>
+        <v>2.3973889871282239E-2</v>
       </c>
       <c r="K36" s="119">
         <f t="shared" si="3"/>
@@ -17478,7 +17479,7 @@
       </c>
       <c r="L36" s="281">
         <f t="shared" si="4"/>
-        <v>160752.30291473281</v>
+        <v>110082.8846152255</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -17499,7 +17500,7 @@
       </c>
       <c r="E37" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F37" s="281">
         <f t="shared" si="7"/>
@@ -17507,7 +17508,7 @@
       </c>
       <c r="G37" s="281">
         <f t="shared" si="8"/>
-        <v>668808.18044937484</v>
+        <v>479128.15429145226</v>
       </c>
       <c r="H37" s="303">
         <f t="shared" si="2"/>
@@ -17515,11 +17516,11 @@
       </c>
       <c r="I37" s="281">
         <f t="shared" si="9"/>
-        <v>503785.76644318056</v>
+        <v>345402.94460131525</v>
       </c>
       <c r="J37" s="303">
         <f t="shared" si="10"/>
-        <v>2.2661428671144845E-2</v>
+        <v>2.3880850782026064E-2</v>
       </c>
       <c r="K37" s="119">
         <f t="shared" si="3"/>
@@ -17527,7 +17528,7 @@
       </c>
       <c r="L37" s="281">
         <f t="shared" si="4"/>
-        <v>153282.21889133545</v>
+        <v>105092.54783811347</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -17548,7 +17549,7 @@
       </c>
       <c r="E38" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F38" s="281">
         <f t="shared" si="7"/>
@@ -17556,7 +17557,7 @@
       </c>
       <c r="G38" s="281">
         <f t="shared" si="8"/>
-        <v>683754.49850216974</v>
+        <v>490278.61277042213</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="2"/>
@@ -17564,11 +17565,11 @@
       </c>
       <c r="I38" s="281">
         <f t="shared" si="9"/>
-        <v>515172.56073262345</v>
+        <v>353620.19614661415</v>
       </c>
       <c r="J38" s="303">
         <f t="shared" si="10"/>
-        <v>2.2602453359958474E-2</v>
+        <v>2.3790334372463917E-2</v>
       </c>
       <c r="K38" s="119">
         <f t="shared" si="3"/>
@@ -17576,7 +17577,7 @@
       </c>
       <c r="L38" s="281">
         <f t="shared" si="4"/>
-        <v>146150.83738437091</v>
+        <v>100319.56614567492</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -17597,7 +17598,7 @@
       </c>
       <c r="E39" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F39" s="281">
         <f t="shared" si="7"/>
@@ -17605,7 +17606,7 @@
       </c>
       <c r="G39" s="281">
         <f t="shared" si="8"/>
-        <v>698999.74291602068</v>
+        <v>501652.08041897148</v>
       </c>
       <c r="H39" s="303">
         <f t="shared" si="2"/>
@@ -17613,11 +17614,11 @@
       </c>
       <c r="I39" s="281">
         <f t="shared" si="9"/>
-        <v>526787.09090785519</v>
+        <v>362001.79272281908</v>
       </c>
       <c r="J39" s="303">
         <f t="shared" si="10"/>
-        <v>2.2544931660791079E-2</v>
+        <v>2.3702256453502546E-2</v>
       </c>
       <c r="K39" s="119">
         <f t="shared" si="3"/>
@@ -17625,7 +17626,7 @@
       </c>
       <c r="L39" s="281">
         <f t="shared" si="4"/>
-        <v>139343.40142225544</v>
+        <v>95755.120027751822</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -17646,7 +17647,7 @@
       </c>
       <c r="E40" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F40" s="281">
         <f t="shared" si="7"/>
@@ -17654,7 +17655,7 @@
       </c>
       <c r="G40" s="281">
         <f t="shared" si="8"/>
-        <v>714549.89221814869</v>
+        <v>513253.01742049179</v>
       </c>
       <c r="H40" s="303">
         <f t="shared" si="2"/>
@@ -17662,11 +17663,11 @@
       </c>
       <c r="I40" s="281">
         <f t="shared" si="9"/>
-        <v>538633.91168659169</v>
+        <v>370551.02123054815</v>
       </c>
       <c r="J40" s="303">
         <f t="shared" si="10"/>
-        <v>2.248882135346153E-2</v>
+        <v>2.3616536380733244E-2</v>
       </c>
       <c r="K40" s="119">
         <f t="shared" si="3"/>
@@ -17674,7 +17675,7 @@
       </c>
       <c r="L40" s="281">
         <f t="shared" si="4"/>
-        <v>132845.75317820438</v>
+        <v>91390.69865130879</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -17695,7 +17696,7 @@
       </c>
       <c r="E41" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F41" s="281">
         <f t="shared" si="7"/>
@@ -17703,7 +17704,7 @@
       </c>
       <c r="G41" s="281">
         <f t="shared" si="8"/>
-        <v>730411.04450631922</v>
+        <v>525085.97316204233</v>
       </c>
       <c r="H41" s="303">
         <f t="shared" si="2"/>
@@ -17711,11 +17712,11 @@
       </c>
       <c r="I41" s="281">
         <f t="shared" si="9"/>
-        <v>550717.66888090281</v>
+        <v>379271.23430843157</v>
       </c>
       <c r="J41" s="303">
         <f t="shared" si="10"/>
-        <v>2.2434081724401533E-2</v>
+        <v>2.3533096869966297E-2</v>
       </c>
       <c r="K41" s="119">
         <f t="shared" si="3"/>
@@ -17723,7 +17724,7 @@
       </c>
       <c r="L41" s="281">
         <f t="shared" si="4"/>
-        <v>126644.31297132297</v>
+        <v>87218.093068236762</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -17744,7 +17745,7 @@
       </c>
       <c r="E42" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F42" s="281">
         <f t="shared" si="7"/>
@@ -17752,7 +17753,7 @@
       </c>
       <c r="G42" s="281">
         <f t="shared" si="8"/>
-        <v>746589.41984025307</v>
+        <v>537155.58801842399</v>
       </c>
       <c r="H42" s="303">
         <f t="shared" si="2"/>
@@ -17760,11 +17761,11 @@
       </c>
       <c r="I42" s="281">
         <f t="shared" si="9"/>
-        <v>563043.10121910006</v>
+        <v>388165.85164787283</v>
       </c>
       <c r="J42" s="303">
         <f t="shared" si="10"/>
-        <v>2.2380673500531412E-2</v>
+        <v>2.3451863824209607E-2</v>
       </c>
       <c r="K42" s="119">
         <f t="shared" si="3"/>
@@ -17772,7 +17773,7 @@
       </c>
       <c r="L42" s="281">
         <f t="shared" si="4"/>
-        <v>120726.0587325252</v>
+        <v>83229.389193361581</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -17793,7 +17794,7 @@
       </c>
       <c r="E43" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F43" s="281">
         <f t="shared" si="7"/>
@@ -17801,7 +17802,7 @@
       </c>
       <c r="G43" s="281">
         <f t="shared" si="8"/>
-        <v>763091.36268086557</v>
+        <v>549466.59517193341</v>
       </c>
       <c r="H43" s="303">
         <f t="shared" si="2"/>
@@ -17809,11 +17810,11 @@
       </c>
       <c r="I43" s="281">
         <f t="shared" si="9"/>
-        <v>575615.04220406129</v>
+        <v>397238.36133410293</v>
       </c>
       <c r="J43" s="303">
         <f t="shared" si="10"/>
-        <v>2.2328558786601782E-2</v>
+        <v>2.3372766171250614E-2</v>
       </c>
       <c r="K43" s="119">
         <f t="shared" si="3"/>
@@ -17821,7 +17822,7 @@
       </c>
       <c r="L43" s="281">
         <f t="shared" si="4"/>
-        <v>115078.50595059126</v>
+        <v>79416.960601915198</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -17842,7 +17843,7 @@
       </c>
       <c r="E44" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F44" s="281">
         <f t="shared" si="7"/>
@@ -17850,7 +17851,7 @@
       </c>
       <c r="G44" s="281">
         <f t="shared" si="8"/>
-        <v>779923.34437829035</v>
+        <v>562023.82246851281</v>
       </c>
       <c r="H44" s="303">
         <f t="shared" si="2"/>
@@ -17858,11 +17859,11 @@
       </c>
       <c r="I44" s="281">
         <f t="shared" si="9"/>
-        <v>588438.42200872174</v>
+        <v>406492.32121405751</v>
       </c>
       <c r="J44" s="303">
         <f t="shared" si="10"/>
-        <v>2.2277701005795514E-2</v>
+        <v>2.329573571111232E-2</v>
       </c>
       <c r="K44" s="119">
         <f t="shared" si="3"/>
@@ -17870,7 +17871,7 @@
       </c>
       <c r="L44" s="281">
         <f t="shared" si="4"/>
-        <v>109689.68811035169</v>
+        <v>75773.461190747985</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -17891,7 +17892,7 @@
       </c>
       <c r="E45" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F45" s="281">
         <f t="shared" si="7"/>
@@ -17899,7 +17900,7 @@
       </c>
       <c r="G45" s="281">
         <f t="shared" si="8"/>
-        <v>797091.96570966358</v>
+        <v>574832.19431102381</v>
       </c>
       <c r="H45" s="303">
         <f t="shared" si="2"/>
@@ -17907,11 +17908,11 @@
       </c>
       <c r="I45" s="281">
         <f t="shared" si="9"/>
-        <v>601518.26940947538</v>
+        <v>415931.36029161117</v>
       </c>
       <c r="J45" s="303">
         <f t="shared" si="10"/>
-        <v>2.2228064843392792E-2</v>
+        <v>2.3220706972673977E-2</v>
       </c>
       <c r="K45" s="119">
         <f t="shared" si="3"/>
@@ -17919,7 +17920,7 @@
       </c>
       <c r="L45" s="281">
         <f t="shared" si="4"/>
-        <v>104548.13763200011</v>
+        <v>72291.817742996383</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -17940,7 +17941,7 @@
       </c>
       <c r="E46" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F46" s="281">
         <f t="shared" si="7"/>
@@ -17948,7 +17949,7 @@
       </c>
       <c r="G46" s="281">
         <f t="shared" si="8"/>
-        <v>814603.95946766436</v>
+        <v>587896.73359038518</v>
       </c>
       <c r="H46" s="303">
         <f t="shared" si="2"/>
@@ -17956,11 +17957,11 @@
       </c>
       <c r="I46" s="281">
         <f t="shared" si="9"/>
-        <v>614859.71375824418</v>
+        <v>425559.1801507161</v>
       </c>
       <c r="J46" s="303">
         <f t="shared" si="10"/>
-        <v>2.2179616193314322E-2</v>
+        <v>2.3147617078824734E-2</v>
       </c>
       <c r="K46" s="119">
         <f t="shared" si="3"/>
@@ -17968,7 +17969,7 @@
       </c>
       <c r="L46" s="281">
         <f t="shared" si="4"/>
-        <v>99642.867317858938</v>
+        <v>68965.222431742164</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -17989,7 +17990,7 @@
       </c>
       <c r="E47" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F47" s="281">
         <f t="shared" si="7"/>
@@ -17997,7 +17998,7 @@
       </c>
       <c r="G47" s="281">
         <f t="shared" si="8"/>
-        <v>832466.19310082507</v>
+        <v>601222.56365533371</v>
       </c>
       <c r="H47" s="303">
         <f t="shared" si="2"/>
@@ -18005,11 +18006,11 @@
       </c>
       <c r="I47" s="281">
         <f t="shared" si="9"/>
-        <v>628467.98699398816</v>
+        <v>435379.55640700296</v>
       </c>
       <c r="J47" s="303">
         <f t="shared" si="10"/>
-        <v>2.2132322107371927E-2</v>
+        <v>2.3076405619563589E-2</v>
       </c>
       <c r="K47" s="119">
         <f t="shared" si="3"/>
@@ -18017,7 +18018,7 @@
       </c>
       <c r="L47" s="281">
         <f t="shared" si="4"/>
-        <v>94963.352310526709</v>
+        <v>65787.125294378056</v>
       </c>
       <c r="N47" s="279"/>
       <c r="O47" s="279"/>
@@ -18046,7 +18047,7 @@
       </c>
       <c r="E48" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F48" s="281">
         <f t="shared" si="7"/>
@@ -18054,7 +18055,7 @@
       </c>
       <c r="G48" s="281">
         <f t="shared" si="8"/>
-        <v>850685.67140664905</v>
+        <v>614814.91032158118</v>
       </c>
       <c r="H48" s="303">
         <f t="shared" si="2"/>
@@ -18062,11 +18063,11 @@
       </c>
       <c r="I48" s="281">
         <f t="shared" si="9"/>
-        <v>642348.42569444724</v>
+        <v>445396.34018841555</v>
       </c>
       <c r="J48" s="303">
         <f t="shared" si="10"/>
-        <v>2.2086150747073541E-2</v>
+        <v>2.3007014532507419E-2</v>
       </c>
       <c r="K48" s="119">
         <f t="shared" si="3"/>
@@ -18074,7 +18075,7 @@
       </c>
       <c r="L48" s="281">
         <f t="shared" si="4"/>
-        <v>90499.512564199962</v>
+        <v>62751.226705899957</v>
       </c>
       <c r="N48" s="279"/>
       <c r="O48" s="279"/>
@@ -18103,7 +18104,7 @@
       </c>
       <c r="E49" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F49" s="281">
         <f t="shared" si="7"/>
@@ -18111,7 +18112,7 @@
       </c>
       <c r="G49" s="281">
         <f t="shared" si="8"/>
-        <v>869269.53927858954</v>
+        <v>628679.10392115347</v>
       </c>
       <c r="H49" s="303">
         <f t="shared" si="2"/>
@@ -18119,11 +18120,11 @@
       </c>
       <c r="I49" s="281">
         <f t="shared" si="9"/>
-        <v>656506.47316891549</v>
+        <v>455613.4596454564</v>
       </c>
       <c r="J49" s="303">
         <f t="shared" si="10"/>
-        <v>2.2041071337820961E-2</v>
+        <v>2.2939387990298155E-2</v>
       </c>
       <c r="K49" s="119">
         <f t="shared" si="3"/>
@@ -18131,7 +18132,7 @@
       </c>
       <c r="L49" s="281">
         <f t="shared" si="4"/>
-        <v>86241.695829058735</v>
+        <v>59851.469876152667</v>
       </c>
       <c r="N49" s="279"/>
       <c r="O49" s="279"/>
@@ -18160,7 +18161,7 @@
       </c>
       <c r="E50" s="303">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F50" s="281">
         <f t="shared" si="7"/>
@@ -18168,7 +18169,7 @@
       </c>
       <c r="G50" s="281">
         <f t="shared" si="8"/>
-        <v>888225.08450796898</v>
+        <v>642820.58139271755</v>
       </c>
       <c r="H50" s="303">
         <f t="shared" si="2"/>
@@ -18176,11 +18177,11 @@
       </c>
       <c r="I50" s="281">
         <f t="shared" si="9"/>
-        <v>670947.68159287318</v>
+        <v>466034.92149163829</v>
       </c>
       <c r="J50" s="303">
         <f t="shared" si="10"/>
-        <v>2.1997054125378002E-2</v>
+        <v>2.2873472294456576E-2</v>
       </c>
       <c r="K50" s="119">
         <f t="shared" si="3"/>
@@ -18188,7 +18189,7 @@
       </c>
       <c r="L50" s="281">
         <f t="shared" si="4"/>
-        <v>82180.661146923012</v>
+        <v>57082.033393144389</v>
       </c>
       <c r="N50" s="279"/>
       <c r="O50" s="279"/>
@@ -18217,7 +18218,7 @@
       </c>
       <c r="E51" s="305">
         <f>F17</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="F51" s="281">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
@@ -18225,7 +18226,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>888225.08450796898</v>
+        <v>642820.58139271755</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18233,7 +18234,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>9254450.7805913556</v>
+        <v>6428067.8826432871</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18245,7 +18246,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>1133526.3606472141</v>
+        <v>787338.39162957785</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18258,7 +18259,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>6487110.7396015767</v>
+        <v>4431023.8814818859</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18282,7 +18283,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>6487110.7396015767</v>
+        <v>4431023.8814818859</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18317,19 +18318,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>4704098.7775381757</v>
+        <v>3144317.7701634611</v>
       </c>
       <c r="C56" s="118">
-        <v>4760181.6891796207</v>
+        <v>3184789.8627152508</v>
       </c>
       <c r="D56" s="118">
-        <v>4816264.6008210685</v>
+        <v>3225261.9552670424</v>
       </c>
       <c r="E56" s="118">
-        <v>4872347.5124625135</v>
+        <v>3265734.0478188307</v>
       </c>
       <c r="F56" s="118">
-        <v>4928430.4241039604</v>
+        <v>3306206.1403706213</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18343,19 +18344,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C57" s="118">
-        <v>4812996.365876927</v>
+        <v>3222903.4417150728</v>
       </c>
       <c r="D57" s="118">
-        <v>4922939.7893978031</v>
+        <v>3302243.8376033138</v>
       </c>
       <c r="E57" s="118">
-        <v>5033929.0481008049</v>
+        <v>3382338.9578281869</v>
       </c>
       <c r="F57" s="118">
-        <v>5145964.1419859277</v>
+        <v>3463188.8023896869</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18369,19 +18370,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C58" s="118">
-        <v>4862733.264211921</v>
+        <v>3258795.9496776089</v>
       </c>
       <c r="D58" s="118">
-        <v>5024393.1155966567</v>
+        <v>3375457.3760490012</v>
       </c>
       <c r="E58" s="118">
-        <v>5189107.585823359</v>
+        <v>3494323.1604478927</v>
       </c>
       <c r="F58" s="118">
-        <v>5356905.929022993</v>
+        <v>3615414.4140445394</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18395,19 +18396,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634611</v>
       </c>
       <c r="C59" s="118">
-        <v>4909571.7418980189</v>
+        <v>3292596.8196469899</v>
       </c>
       <c r="D59" s="118">
-        <v>5120880.195058506</v>
+        <v>3445087.034990353</v>
       </c>
       <c r="E59" s="118">
-        <v>5338136.857482315</v>
+        <v>3601869.7606327855</v>
       </c>
       <c r="F59" s="118">
-        <v>5561455.5406952957</v>
+        <v>3763027.1283765165</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18421,19 +18422,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C60" s="118">
-        <v>4953680.7045674454</v>
+        <v>3324427.9419491561</v>
       </c>
       <c r="D60" s="118">
-        <v>5212644.1307704709</v>
+        <v>3511308.2490884215</v>
       </c>
       <c r="E60" s="118">
-        <v>5481260.5402876548</v>
+        <v>3705154.6074303989</v>
       </c>
       <c r="F60" s="118">
-        <v>5759806.6792866206</v>
+        <v>3906166.7301529795</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18447,19 +18448,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C61" s="118">
-        <v>4995219.2148668598</v>
+        <v>3354404.1037442051</v>
       </c>
       <c r="D61" s="118">
-        <v>5299916.12557346</v>
+        <v>3574287.8652935773</v>
       </c>
       <c r="E61" s="118">
-        <v>5618712.6552428985</v>
+        <v>3804346.5815110896</v>
       </c>
       <c r="F61" s="118">
-        <v>5952147.177314572</v>
+        <v>4044968.7682392481</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18473,19 +18474,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C62" s="118">
-        <v>5034337.0660579177</v>
+        <v>3382633.4029637859</v>
       </c>
       <c r="D62" s="118">
-        <v>5382916.064686792</v>
+        <v>3634184.5632229578</v>
       </c>
       <c r="E62" s="118">
-        <v>5750717.9497919912</v>
+        <v>3899607.8713042024</v>
       </c>
       <c r="F62" s="118">
-        <v>6138659.1754022818</v>
+        <v>4179564.6839592643</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18499,19 +18500,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C63" s="118">
-        <v>5071175.3221912179</v>
+        <v>3409217.6381262802</v>
       </c>
       <c r="D63" s="118">
-        <v>5461853.069717655</v>
+        <v>3691149.2549599903</v>
       </c>
       <c r="E63" s="118">
-        <v>5877492.2653030064</v>
+        <v>3991094.2381917583</v>
       </c>
       <c r="F63" s="118">
-        <v>6319519.2947600596</v>
+        <v>4310081.9355665529</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18525,19 +18526,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634611</v>
       </c>
       <c r="C64" s="118">
-        <v>5105866.8268016009</v>
+        <v>3434252.6754354816</v>
       </c>
       <c r="D64" s="118">
-        <v>5536926.0255511999</v>
+        <v>3745325.4652833212</v>
       </c>
       <c r="E64" s="118">
-        <v>5999242.8899895754</v>
+        <v>4078955.2711933255</v>
       </c>
       <c r="F64" s="118">
-        <v>6494898.8044403326</v>
+        <v>4436644.1189433178</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18551,19 +18552,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>4704098.7775381766</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C65" s="118">
-        <v>5138536.6819591634</v>
+        <v>3457828.794486572</v>
       </c>
       <c r="D65" s="118">
-        <v>5608324.081448839</v>
+        <v>3796849.6932831332</v>
       </c>
       <c r="E65" s="118">
-        <v>6116168.8978470732</v>
+        <v>4163334.6315584686</v>
       </c>
       <c r="F65" s="118">
-        <v>6664963.7835242301</v>
+        <v>4559371.0846419986</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18577,19 +18578,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>4704098.7775381757</v>
+        <v>3144317.7701634606</v>
       </c>
       <c r="C66" s="281">
-        <v>5275452.5748052029</v>
+        <v>3556633.8052267926</v>
       </c>
       <c r="D66" s="118">
-        <v>5916187.7210902767</v>
+        <v>4019018.7168273991</v>
       </c>
       <c r="E66" s="118">
-        <v>6634862.2276278175</v>
+        <v>4537648.3723124173</v>
       </c>
       <c r="F66" s="118">
-        <v>7441039.6109333932</v>
+        <v>5119424.2593937032</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18612,19 +18613,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>4704098.7775381748</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C67" s="281">
-        <v>5376861.0441353805</v>
+        <v>3629814.9728256827</v>
       </c>
       <c r="D67" s="118">
-        <v>6155724.8026400981</v>
+        <v>4191880.0510614403</v>
       </c>
       <c r="E67" s="118">
-        <v>7058612.7849416845</v>
+        <v>4843446.8993954072</v>
       </c>
       <c r="F67" s="118">
-        <v>8106441.9892267343</v>
+        <v>5599610.2171171959</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18647,19 +18648,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>4704098.7775381748</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C68" s="281">
-        <v>5451970.4959172383</v>
+        <v>3684017.5203585965</v>
       </c>
       <c r="D68" s="118">
-        <v>6342099.5674685556</v>
+        <v>4326376.9327440448</v>
       </c>
       <c r="E68" s="118">
-        <v>7404799.1045145933</v>
+        <v>5093271.3888137545</v>
       </c>
       <c r="F68" s="118">
-        <v>8676953.6704325955</v>
+        <v>6011318.5412366893</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18682,19 +18683,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>4704098.7775381748</v>
+        <v>3144317.7701634616</v>
       </c>
       <c r="C69" s="281">
-        <v>5507601.2512598056</v>
+        <v>3724163.3154511335</v>
       </c>
       <c r="D69" s="118">
-        <v>6487110.7396015767</v>
+        <v>4431023.8814818859</v>
       </c>
       <c r="E69" s="118">
-        <v>7687618.7157007772</v>
+        <v>5297367.4520240277</v>
       </c>
       <c r="F69" s="118">
-        <v>9166106.6837223265</v>
+        <v>6364314.5866705887</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18791,23 +18792,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18822,23 +18823,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.1731298850738785</v>
+        <v>2.4643965464764759</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.2698238879610004</v>
+        <v>2.5341755311887937</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.3665178908481295</v>
+        <v>2.6039545159011146</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.4632118937352514</v>
+        <v>2.6737335006134302</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.5599058966223787</v>
+        <v>2.7435124853257498</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18853,23 +18854,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.3608830421950309</v>
+        <v>2.5998881415006294</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.5504393508851742</v>
+        <v>2.7366809763329365</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.7417988111443092</v>
+        <v>2.8747750509734016</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>5.934961422972429</v>
+        <v>3.0141703654220171</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18884,23 +18885,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4466357189095973</v>
+        <v>2.6617713456171357</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.7253576625287996</v>
+        <v>2.8629103373030649</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.0093461537376225</v>
+        <v>3.0678499198505738</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.2986516303421851</v>
+        <v>3.2766264915759753</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18915,23 +18916,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764759</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.5273911533913749</v>
+        <v>2.7200483024075055</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8917135393367266</v>
+        <v>2.9829606386452832</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2662913871838795</v>
+        <v>3.2532738032477653</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.6513209223370957</v>
+        <v>3.5311294017858721</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18946,23 +18947,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.6034405602227002</v>
+        <v>2.7749291661448203</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.0499261214757292</v>
+        <v>3.0971343518099093</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.5130546416823876</v>
+        <v>3.4313498870697776</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9933032660897387</v>
+        <v>3.7779201025954694</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18977,23 +18978,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6750581834391483</v>
+        <v>2.8266118443496615</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2003940317617756</v>
+        <v>3.2057191419524909</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.7500393989163836</v>
+        <v>3.6023693428615458</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.3249225085165444</v>
+        <v>4.0172322973199304</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19009,23 +19010,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.7425022854891381</v>
+        <v>2.8752827114703057</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.3434963800058464</v>
+        <v>3.3089885927174656</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.9776331517844659</v>
+        <v>3.7666118039016623</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.6464926829910205</v>
+        <v>4.249292607355768</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19040,23 +19041,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.80601607856185</v>
+        <v>2.9211172809731942</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.4795937181960159</v>
+        <v>3.4072028955428952</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>7.1962080379887743</v>
+        <v>3.9243458224296948</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.958318306723843</v>
+        <v>4.4743207867844594</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19072,23 +19073,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764759</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8658286016419838</v>
+        <v>2.9642808382672889</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.609028948922326</v>
+        <v>3.5006095052230233</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>7.4061214485159894</v>
+        <v>4.0758293087549822</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>8.2606946691314356</v>
+        <v>4.6925299304728867</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19104,23 +19105,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738794</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>5.9221555464540421</v>
+        <v>3.0049290367447132</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.7321281893333644</v>
+        <v>3.5894437633803489</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.6077166120059951</v>
+        <v>4.2213099529648188</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5539081114660647</v>
+        <v>4.904126675867726</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19136,23 +19137,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738785</v>
+        <v>2.464396546476475</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.158215789238664</v>
+        <v>3.1752813190024134</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>7.2629238771651377</v>
+        <v>3.9724911404737862</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.5020092380380365</v>
+        <v>4.8666739840007009</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.8919605787825517</v>
+        <v>5.8697288835884178</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19168,23 +19169,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738767</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.3330567619913092</v>
+        <v>3.3014548685558012</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.6759159736353038</v>
+        <v>4.2705258512669806</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.232608567015232</v>
+        <v>5.3939091576964495</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>11.039198081342022</v>
+        <v>6.6976299504823658</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19200,23 +19201,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738767</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.462554916328898</v>
+        <v>3.3949068869022216</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.9972495406873421</v>
+        <v>4.5024154141497341</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.8294773814996788</v>
+        <v>5.8246380409529346</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>12.022832071359229</v>
+        <v>7.4074669528045431</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19232,23 +19233,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.1731298850738767</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.5584693448110993</v>
+        <v>3.4641232937000979</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>8.2472670645017345</v>
+        <v>4.6828399332631063</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>10.317094010169198</v>
+        <v>6.1765253582783179</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>12.866193471381994</v>
+        <v>8.0160765923066517</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19295,7 +19296,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>12.866193471381994</v>
+        <v>8.0160765923066517</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19323,7 +19324,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>10.317094010169198</v>
+        <v>6.1765253582783179</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19351,7 +19352,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>8.2472670645017345</v>
+        <v>4.6828399332631063</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19379,7 +19380,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.5584693448110993</v>
+        <v>3.4641232937000979</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19407,7 +19408,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.1731298850738767</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19616,7 +19617,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>289762.92396067944</v>
+        <v>290263.04701918905</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19629,7 +19630,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>341047.16137151787</v>
+        <v>227963.03833685117</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19685,7 +19686,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.62636359906346839</v>
+        <v>0.62468132907960161</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19767,7 +19768,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>10.317094010169198</v>
+        <v>6.1765253582783179</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19791,7 +19792,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>8.2472670645017345</v>
+        <v>4.6828399332631063</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19814,7 +19815,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>6.5584693448110993</v>
+        <v>3.4641232937000979</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19830,7 +19831,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>8.3234729096970987</v>
+        <v>4.737833690353547</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19878,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>12.866193471381994</v>
+        <v>8.0160765923066517</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19900,7 +19901,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>5.1731298850738767</v>
+        <v>2.4643965464764768</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19956,7 +19957,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19957778695608511</v>
+        <v>1.4883278968646201E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19965,7 +19966,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19976,7 +19977,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.23342996477283787</v>
+        <v>0.36501986827233529</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19985,7 +19986,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>8.3930917865501833</v>
+        <v>4.7880739782573478</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20023,7 +20024,7 @@
       </c>
       <c r="C40" s="138">
         <f>DCF!C17</f>
-        <v>0.88</v>
+        <v>0.89581909726262465</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>403</v>
@@ -20088,7 +20089,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>8.2472670645017345</v>
+        <v>4.6828399332631063</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20151,7 +20152,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.52689875671755426</v>
+        <v>0.91954201377103884</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20229,11 +20230,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.8677842334332651</v>
+        <v>2.2064857042660595</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>4.5082322850718066</v>
+        <v>2.8469337559046011</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20241,7 +20242,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46286393623191535</v>
+        <v>0.40541149346636407</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20254,11 +20255,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.8479952557690611</v>
+        <v>2.7656745000764476</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>5.5843966373132385</v>
+        <v>3.502075881620625</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20266,7 +20267,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33464368324171567</v>
+        <v>0.26858358965973428</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20300,11 +20301,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>6.0158357675370215</v>
+        <v>3.4319017864396861</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>6.8602468616155488</v>
+        <v>4.2763128805182129</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20312,7 +20313,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18263173618463202</v>
+        <v>0.10688245421082521</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20325,11 +20326,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>6.8034636695136399</v>
+        <v>3.8812261543736826</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>7.7177949990241954</v>
+        <v>4.7955574838842381</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20337,7 +20338,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.0458644406599E-2</v>
+        <v>-1.5629469512945526E-3</v>
       </c>
     </row>
   </sheetData>
@@ -20473,7 +20474,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.19957778695608511</v>
+        <v>1.4883278968646201E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20481,13 +20482,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20551,7 +20552,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>8.3930917865501833</v>
+        <v>4.7880739782573478</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20603,7 +20604,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>4.5082322850718066</v>
+        <v>2.8469337559046011</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20619,7 +20620,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>5.5843966373132385</v>
+        <v>3.502075881620625</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20635,7 +20636,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>6.8602468616155488</v>
+        <v>4.2763128805182129</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20651,7 +20652,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>7.7177949990241954</v>
+        <v>4.7955574838842381</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20672,22 +20673,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20713,7 +20714,7 @@
       </c>
       <c r="C34" s="377">
         <f>Normalized_FCF!C8</f>
-        <v>533705.04</v>
+        <v>398162</v>
       </c>
       <c r="D34" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20796,7 +20797,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>6864.677809625</v>
+        <v>6977.6303429583331</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20826,7 +20827,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-78507.722190375003</v>
+        <v>-78394.769657041674</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20867,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-75107.557438588134</v>
+        <v>-52761.593006588133</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20877,10 +20878,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20896,22 +20897,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20919,7 +20920,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>289762.92396067944</v>
+        <v>290263.04701918905</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20932,7 +20933,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>341047.16137151787</v>
+        <v>227963.03833685117</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20945,7 +20946,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10500147473343946</v>
+        <v>7.0185176483582926E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20962,7 +20963,7 @@
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.59522973518862243</v>
+        <v>0.89050142966612644</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20982,11 +20983,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.16584375248097633</v>
+        <v>0.11650199885998448</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>0.11820514758456895</v>
+        <v>0.1183873593012913</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20996,11 +20997,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>5.3125639236926585E-2</v>
+        <v>3.7319724555354143E-2</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>3.7865303531682992E-2</v>
+        <v>3.7923672410718354E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21046,22 +21047,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21069,13 +21070,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21118,7 +21119,7 @@
       </c>
       <c r="C81" s="393">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>3.999044116203212</v>
+        <v>5.3604060658726853</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -21132,7 +21133,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>367165.21903749998</v>
+        <v>355869.96570416668</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21158,7 +21159,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.63303907929464343</v>
+        <v>0.61356463999650612</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21202,7 +21203,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>-2.9373288529573038</v>
+        <v>-2.956803292255441</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21224,33 +21225,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21313,23 +21314,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21361,7 +21362,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>5.1731298850738812</v>
+        <v>2.4643965464764821</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21373,13 +21374,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21424,7 +21425,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>12.87 HKD</v>
+        <v>8.02 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21447,7 +21448,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>10.32 HKD</v>
+        <v>6.18 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21469,7 +21470,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>8.25 HKD</v>
+        <v>4.68 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21491,7 +21492,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.56 HKD</v>
+        <v>3.46 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21513,7 +21514,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.17 HKD</v>
+        <v>2.46 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21535,7 +21536,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>8.3930917865501833</v>
+        <v>4.7880739782573478</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21543,13 +21544,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21562,22 +21563,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21642,11 +21643,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>3.8677842334332651</v>
+        <v>2.2064857042660595</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>4.5082322850718066</v>
+        <v>2.8469337559046011</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21663,11 +21664,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>4.8479952557690611</v>
+        <v>2.7656745000764476</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>5.5843966373132385</v>
+        <v>3.502075881620625</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21703,11 +21704,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>6.0158357675370215</v>
+        <v>3.4319017864396861</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>6.8602468616155488</v>
+        <v>4.2763128805182129</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21724,11 +21725,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>6.8034636695136399</v>
+        <v>3.8812261543736826</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>7.7177949990241954</v>
+        <v>4.7955574838842381</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21746,13 +21747,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21760,13 +21761,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21803,22 +21804,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21842,12 +21843,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21862,15 +21866,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75063E0-C944-4546-BB76-9A67BBA7037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC45CF2-0C78-4A6C-9E01-28D6B18225BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>5.6</v>
+        <v>5.41</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>3248.0225847999995</v>
+        <v>3137.8218185300002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>1.4883278968646201E-2</v>
+        <v>2.7406762407438955E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.0185176483582926E-2</v>
+        <v>7.2650090260270667E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.25E-2</v>
+        <v>6.4695009242144177E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14225,24 +14225,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.25E-2</v>
+        <v>6.4695009242144177E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.25E-2</v>
+        <v>6.4695009242144177E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>0.10178571428571428</v>
+        <v>0.1053604436229205</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7857142857142866E-2</v>
+        <v>7.0240295748613679E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7857142857142866E-2</v>
+        <v>7.0240295748613679E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15424,50 +15424,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.0185176483582926E-2</v>
+        <v>7.2650090260270667E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.9366080266052805E-2</v>
+        <v>9.2504630219943748E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10726813987804805</v>
+        <v>0.11103541281276691</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3856053351725472E-2</v>
+        <v>3.5045082951878491E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-7.2871619671429425E-3</v>
+        <v>-7.5430881730130265E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6590570692512016E-2</v>
+        <v>-3.7875636946038314E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>6.4228001669774604E-2</v>
+        <v>6.6483698586088311E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.17173371965156664</v>
+        <v>0.1777650332807344</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.14165541894725805</v>
+        <v>0.14663037820788263</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.15928337518991012</v>
+        <v>0.16487743088049844</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.15529756546660822</v>
+        <v>0.16075163893031533</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15481,43 +15481,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2385888294085612E-2</v>
+        <v>7.4928091394986948E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10259011176811693</v>
+        <v>0.10619309166385484</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4232212706995835E-2</v>
+        <v>3.5434453079330248E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0350496043139468E-3</v>
+        <v>7.2821215867205349E-3</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11100600152452487</v>
+        <v>0.11490454871300171</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2901934348643203E-2</v>
+        <v>2.3706253669575218E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18229860924334051</v>
+        <v>0.18870096335724709</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14140757584303607</v>
+        <v>0.14637383081719074</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15512515287236683</v>
+        <v>0.16057317118026879</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15943854652472736</v>
+        <v>0.16503805185554032</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>5.6</v>
+        <v>5.41</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>1.4883278968646201E-2</v>
+        <v>2.7406762407438955E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20449,7 +20449,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>5.6</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20467,14 +20467,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>3248.0225847999995</v>
+        <v>3137.8218185300002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>1.4883278968646201E-2</v>
+        <v>2.7406762407438955E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20482,13 +20482,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20673,22 +20673,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20878,10 +20878,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20897,22 +20897,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>7.0185176483582926E-2</v>
+        <v>7.2650090260270667E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20956,7 +20956,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.25E-2</v>
+        <v>6.4695009242144177E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21047,22 +21047,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21070,13 +21070,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21225,33 +21225,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21314,23 +21314,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21374,13 +21374,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21544,13 +21544,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21563,22 +21563,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21747,13 +21747,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21761,13 +21761,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21804,22 +21804,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21843,15 +21843,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21866,12 +21863,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0341.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC45CF2-0C78-4A6C-9E01-28D6B18225BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B551109F-CEAA-48FC-A8AD-DE2A74C54DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>2.7406762407438955E-2</v>
+        <v>1.8039466578554902E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>4.7880739782573478</v>
+        <v>4.791760759866543</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>2.8469337559046011</v>
+        <v>2.7571401547991856</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>3.502075881620625</v>
+        <v>3.3990052332011103</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>4.2763128805182129</v>
+        <v>4.1583252632564474</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>4.7955574838842381</v>
+        <v>4.667927238006353</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>6977.6303429583331</v>
+        <v>6953.4635082499999</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-78394.769657041674</v>
+        <v>-78418.936491750006</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-52761.593006588133</v>
+        <v>-52757.605478861253</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>290263.04701918905</v>
+        <v>290156.04285618226</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>227963.03833685117</v>
+        <v>227942.85902986967</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.2650090260270667E-2</v>
+        <v>7.2643659268280522E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,14 +5890,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.4695009242144177E-2</v>
+        <v>5.5452865064695017E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.89050142966612644</v>
+        <v>0.76335451191826487</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5917,11 +5917,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.11650199885998448</v>
+        <v>0.11649319406611419</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.1183873593012913</v>
+        <v>0.11834837407174398</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>3.7319724555354143E-2</v>
+        <v>3.7316904067420706E-2</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>3.7923672410718354E-2</v>
+        <v>3.7911184058220797E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>355869.96570416668</v>
+        <v>358286.64917500003</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.61356463999650612</v>
+        <v>0.61773130666317277</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-2.956803292255441</v>
+        <v>-2.9526366255887742</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>2.4643965464764821</v>
+        <v>2.4680833280856755</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.10583101104145536</v>
+        <v>-0.113155497433193</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-1.9766300946058021E-2</v>
+        <v>-2.8522035478130404E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>4.68 HKD</v>
+        <v>4.69 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>8.1652063121764637E-2</v>
+        <v>7.0991073063453258E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>3.46 HKD</v>
+        <v>3.47 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.20549562324221848</v>
+        <v>0.19216664332816669</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>2.46 HKD</v>
+        <v>2.47 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.36501986827233635</v>
+        <v>0.34766213291301834</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>4.7880739782573478</v>
+        <v>4.791760759866543</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.35</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6562,15 +6562,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>0.64044805163854179</v>
+        <v>0.54895547283303592</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.2064857042660595</v>
+        <v>2.2081846819661495</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>2.8469337559046011</v>
+        <v>2.7571401547991856</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6583,15 +6583,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>0.73640138154417734</v>
+        <v>0.63120118418072357</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>2.7656745000764476</v>
+        <v>2.7678040490203868</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>3.502075881620625</v>
+        <v>3.3990052332011103</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6630,15 +6630,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>0.8444110940785271</v>
+        <v>0.7237809377815948</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>3.4319017864396861</v>
+        <v>3.4345443254748527</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>4.2763128805182129</v>
+        <v>4.1583252632564474</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6651,15 +6651,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>0.91433132951055562</v>
+        <v>0.78371256815190493</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>3.8812261543736826</v>
+        <v>3.884214669854448</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>4.7955574838842381</v>
+        <v>4.667927238006353</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>355869.96570416668</v>
+        <v>358286.64917500003</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-697763.03429583332</v>
+        <v>-695346.35082499997</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.5100155041364474</v>
+        <v>1.5152635787185877</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10473,7 +10473,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>697763.03429583332</v>
+        <v>695346.35082499997</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10605,11 +10605,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>355869.96570416668</v>
+        <v>358286.64917500003</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.61356463999650612</v>
+        <v>0.61773130666317277</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10639,11 +10639,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2553662.165704167</v>
+        <v>2556078.8491750001</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>4.4028351880514709</v>
+        <v>4.4070018547181373</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11124,24 +11124,24 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-78394.769657041674</v>
+        <v>-78418.936491750006</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>-73219.952980810951</v>
+        <v>-73326.957143817723</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-78589.659046614499</v>
+        <v>-78693.571346212775</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>-72781.774081401934</v>
+        <v>-72870.876171780139</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>-82971.866648375872</v>
+        <v>-82989.433845590756</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
@@ -11179,24 +11179,24 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>319767.23034295836</v>
+        <v>319743.06350824999</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>324942.04701918905</v>
+        <v>324835.04285618226</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>407483.34095338552</v>
+        <v>407379.42865378724</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>143788.22591859807</v>
+        <v>143699.12382821986</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>5906.1333516241284</v>
+        <v>5888.5661544092436</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-52761.593006588133</v>
+        <v>-52757.605478861253</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11346,26 +11346,26 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>227963.03833685117</v>
+        <v>227942.85902986967</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>290263.04701918905</v>
+        <v>290156.04285618226</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>348409.34095338552</v>
+        <v>348305.42865378724</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>109965.22591859807</v>
+        <v>109876.12382821986</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>-23668.866648375872</v>
+        <v>-23686.433845590756</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
@@ -11564,26 +11564,26 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>227963.03833685117</v>
+        <v>227942.85902986967</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>290263.04701918905</v>
+        <v>290156.04285618226</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>348409.34095338552</v>
+        <v>348305.42865378724</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>109965.22591859807</v>
+        <v>109876.12382821986</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>-23668.866648375872</v>
+        <v>-23686.433845590756</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
@@ -12302,19 +12302,19 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>9.9439270160355253E-2</v>
+        <v>9.9472026527340648E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>0.1381970606902479</v>
+        <v>0.13823231130273342</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>0.22942768637173294</v>
+        <v>0.22956994532155642</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.730506125859324</v>
+        <v>4.7446185144884243</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
@@ -12440,24 +12440,24 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>6977.6303429583331</v>
+        <v>6953.4635082499999</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>30895.047019189049</v>
+        <v>30788.042856182274</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>30002.340953385505</v>
+        <v>29898.428653787229</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>25726.225918598066</v>
+        <v>25637.123828219857</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>5072.1333516241302</v>
+        <v>5054.5661544092436</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
@@ -12552,24 +12552,24 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-78394.769657041674</v>
+        <v>-78418.936491750006</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-73219.952980810951</v>
+        <v>-73326.957143817723</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>-78589.659046614499</v>
+        <v>-78693.571346212775</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>-72781.774081401934</v>
+        <v>-72870.876171780139</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>-82971.866648375872</v>
+        <v>-82989.433845590756</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>9.1493778366325239E-3</v>
+        <v>9.1521983245659577E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235" t="s">
@@ -13526,19 +13526,19 @@
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>8.5454299812683116E-3</v>
+        <v>8.5579183337658633E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>9.0421814644042094E-3</v>
+        <v>9.0541371578217594E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>9.0704604911690332E-3</v>
+        <v>9.0815648782309934E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>1.1050019443757955E-2</v>
+        <v>1.1052359006294489E-2</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
@@ -13576,26 +13576,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>3.7319724555354143E-2</v>
+        <v>3.7316904067420706E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>3.7923672410718354E-2</v>
+        <v>3.7911184058220797E-2</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>4.6883245929808193E-2</v>
+        <v>4.6871290236390646E-2</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>1.7919670669627193E-2</v>
+        <v>1.7908566282565232E-2</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>7.8656647137335966E-4</v>
+        <v>7.8422690883682596E-4</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>6.1577545516334339E-3</v>
+        <v>6.1572891711244174E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13748,26 +13748,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>2.6605345989982765E-2</v>
+        <v>2.6602990882558346E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>3.3876319820939055E-2</v>
+        <v>3.3863831468441498E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>4.0086450596832073E-2</v>
+        <v>4.0074494903414519E-2</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>1.37044644718546E-2</v>
+        <v>1.3693360084792638E-2</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>3.1521700938059718E-3</v>
+        <v>3.1545096563425053E-3</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
@@ -13969,26 +13969,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>2.6605345989982765E-2</v>
+        <v>2.6602990882558346E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>3.3876319820939055E-2</v>
+        <v>3.3863831468441498E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>4.0086450596832073E-2</v>
+        <v>4.0074494903414519E-2</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>1.37044644718546E-2</v>
+        <v>1.3693360084792638E-2</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>3.1521700938059718E-3</v>
+        <v>3.1545096563425053E-3</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
@@ -14037,8 +14037,8 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C88" s="110">
-        <f>G88</f>
-        <v>0.35</v>
+        <f>0.1+0.2</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>203001.41154999999</v>
+        <v>174001.20990000005</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
@@ -14149,24 +14149,24 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.89050142966612644</v>
+        <v>0.76335451191826487</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.69937049732885803</v>
+        <v>0.69962841218722771</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.94889045714257125</v>
+        <v>0.94917354601043535</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>2.0042839061063957</v>
+        <v>2.0059092445286417</v>
       </c>
       <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v>-9.3118752078111733</v>
+        <v>-9.3049689951967114</v>
       </c>
       <c r="K90" s="152">
         <f t="shared" si="37"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4695009242144177E-2</v>
+        <v>5.5452865064695017E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
@@ -14362,26 +14362,26 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-1.5925352608876397E-2</v>
+        <v>-1.5675585069763187E-2</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-0.2025636035600259</v>
+        <v>-0.20262286210763869</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>1.8339131271017388</v>
+        <v>1.8349471994051605</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>23.345577276723311</v>
+        <v>23.403075393934525</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.0675519364026962</v>
+        <v>-1.0673510099896975</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
@@ -14973,19 +14973,19 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>5.2056195768526781</v>
+        <v>5.2075393127308969</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>4.7735631755708789</v>
+        <v>4.7749873047576346</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>15.449293045217788</v>
+        <v>15.461821374915207</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>-49.197159175338143</v>
+        <v>-49.160671783302718</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -15081,24 +15081,24 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>3.7319724555354143E-2</v>
+        <v>3.7316904067420706E-2</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>3.7923672410718354E-2</v>
+        <v>3.7911184058220797E-2</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>4.6883245929808193E-2</v>
+        <v>4.6871290236390646E-2</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>1.7919670669627193E-2</v>
+        <v>1.7908566282565232E-2</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>7.8656647137335966E-4</v>
+        <v>7.8422690883682596E-4</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
@@ -15246,26 +15246,26 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.11650199885998448</v>
+        <v>0.11649319406611419</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.1183873593012913</v>
+        <v>0.11834837407174398</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.14000395839269075</v>
+        <v>0.13996825599259899</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>5.1498918870597855E-2</v>
+        <v>5.146700623453692E-2</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>2.0896488477202355E-3</v>
+        <v>2.083433398248939E-3</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
@@ -15367,26 +15367,26 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.39303698830806438</v>
+        <v>0.39300219664139763</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.50045004948989569</v>
+        <v>0.5002655608365093</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.60070158331706902</v>
+        <v>0.60052242542559575</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.18959389876966265</v>
+        <v>0.18944027554411827</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-4.0808107016000475E-2</v>
+        <v>-4.0838395076454162E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
@@ -15424,26 +15424,26 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.2650090260270667E-2</v>
+        <v>7.2643659268280522E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.2504630219943748E-2</v>
+        <v>9.2470528805269736E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.11103541281276691</v>
+        <v>0.11100229675149643</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5045082951878491E-2</v>
+        <v>3.5016686791888775E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-7.5430881730130265E-3</v>
+        <v>-7.5486867054443919E-3</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>227963.03833685117</v>
+        <v>227942.85902986967</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>355869.96570416668</v>
+        <v>358286.64917500003</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3144317.7701634648</v>
+        <v>3144039.4348947541</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-78394.769657041674</v>
+        <v>-78418.936491750006</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16365,14 +16365,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>-1714957.8342958333</v>
+        <v>-1712541.1508250001</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>-1714957.8342958333</v>
+        <v>-1712541.1508250001</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>1429359.9358676316</v>
+        <v>1431498.284069754</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-2.956803292255441</v>
+        <v>-2.9526366255887742</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-78394.769657041674</v>
+        <v>-78418.936491750006</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>1429359.9358676316</v>
+        <v>1431498.284069754</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.4643965464764821</v>
+        <v>2.4680833280856755</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>4.6828399332631063</v>
+        <v>4.6865267148723024</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>327730.47034295811</v>
+        <v>327706.30350824975</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16684,11 +16684,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>233831.49175686057</v>
+        <v>233811.31244987907</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>2.5743004053744301E-2</v>
+        <v>2.574528302832424E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>218024.70093879773</v>
+        <v>218005.88573415298</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>335852.97514295799</v>
+        <v>335828.80830824963</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16733,11 +16733,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>239817.31424527025</v>
+        <v>239797.1349382888</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
- 